--- a/Donnees_Mensuelle.xlsx
+++ b/Donnees_Mensuelle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE5175A-C406-4FDA-A8C3-C7DA5375AD8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0C9FF6-5D88-4681-8369-545D1F10B958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43493,7 +43493,7 @@
         <v>29250</v>
       </c>
       <c r="L1006" s="1">
-        <v>3500</v>
+        <v>74000</v>
       </c>
       <c r="M1006" s="1"/>
       <c r="N1006" s="1"/>

--- a/Donnees_Mensuelle.xlsx
+++ b/Donnees_Mensuelle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1E7EC6-BEEC-47EA-83EF-88BA2E8A20FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4284B7ED-1B6A-4128-ADD2-3644FD53C047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10682" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11669" uniqueCount="157">
   <si>
     <t>Date</t>
   </si>
@@ -499,6 +499,12 @@
   <si>
     <t>Seynabou Sow RZ</t>
   </si>
+  <si>
+    <t>Autre</t>
+  </si>
+  <si>
+    <t>Aicha BAUDIAN</t>
+  </si>
 </sst>
 </file>
 
@@ -870,8 +876,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}" name="Tableau1" displayName="Tableau1" ref="A1:P1522" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
-  <autoFilter ref="A1:P1522" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}" name="Tableau1" displayName="Tableau1" ref="A1:P1663" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="A1:P1663" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{713E4B58-7C9F-4B80-8C6C-D9C3181B21C1}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{0868AEE8-A7A6-4928-8DDB-60543BB07F07}" name="Telephone_Team_Leader" dataDxfId="14"/>
@@ -1211,7 +1217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P1522"/>
+  <dimension ref="A1:P1663"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.3984375" customWidth="1"/>
@@ -65280,6 +65286,6492 @@
         <v>142</v>
       </c>
     </row>
+    <row r="1523" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1523" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1523" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1523" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1523" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1523" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1523" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1523" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1523" s="1"/>
+      <c r="I1523" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1523" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1523" s="1">
+        <v>26000</v>
+      </c>
+      <c r="L1523" s="1">
+        <v>5000</v>
+      </c>
+      <c r="M1523" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1523" s="1"/>
+      <c r="O1523" s="1">
+        <v>5025</v>
+      </c>
+      <c r="P1523" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1524" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1524" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1524" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1524" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1524" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1524" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1524" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1524" s="1"/>
+      <c r="I1524" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1524" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1524" s="1">
+        <v>19500</v>
+      </c>
+      <c r="L1524" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1524" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1524" s="1"/>
+      <c r="O1524" s="1">
+        <v>5026</v>
+      </c>
+      <c r="P1524" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1525" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1525" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1525" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1525" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1525" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1525" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1525" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1525" s="1"/>
+      <c r="I1525" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1525" s="1">
+        <v>0.66666669999999995</v>
+      </c>
+      <c r="K1525" s="1">
+        <v>17333.333999999999</v>
+      </c>
+      <c r="L1525" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1525" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1525" s="1"/>
+      <c r="O1525" s="1">
+        <v>5027</v>
+      </c>
+      <c r="P1525" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1526" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1526" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1526" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1526" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1526" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1526" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1526" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1526" s="1"/>
+      <c r="I1526" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1526" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1526" s="1">
+        <v>26000</v>
+      </c>
+      <c r="L1526" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1526" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1526" s="1"/>
+      <c r="O1526" s="1">
+        <v>5028</v>
+      </c>
+      <c r="P1526" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1527" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1527" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1527" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1527" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1527" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1527" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1527" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H1527" s="1"/>
+      <c r="I1527" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1527" s="1">
+        <v>0.77777779999999996</v>
+      </c>
+      <c r="K1527" s="1">
+        <v>20222.223000000002</v>
+      </c>
+      <c r="L1527" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1527" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1527" s="1"/>
+      <c r="O1527" s="1">
+        <v>5029</v>
+      </c>
+      <c r="P1527" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1528" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1528" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1528" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1528" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1528" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1528" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1528" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H1528" s="1"/>
+      <c r="I1528" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1528" s="1">
+        <v>0.22222222</v>
+      </c>
+      <c r="K1528" s="1">
+        <v>6222.2219999999998</v>
+      </c>
+      <c r="L1528" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1528" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1528" s="1"/>
+      <c r="O1528" s="1">
+        <v>5030</v>
+      </c>
+      <c r="P1528" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1529" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1529" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1529" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1529" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1529" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1529" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1529" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1529" s="1"/>
+      <c r="I1529" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1529" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1529" s="1">
+        <v>28000</v>
+      </c>
+      <c r="L1529" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1529" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1529" s="1"/>
+      <c r="O1529" s="1">
+        <v>5031</v>
+      </c>
+      <c r="P1529" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1530" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1530" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1530" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1530" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1530" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1530" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1530" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1530" s="1"/>
+      <c r="I1530" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1530" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K1530" s="1">
+        <v>8750</v>
+      </c>
+      <c r="L1530" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1530" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1530" s="1"/>
+      <c r="O1530" s="1">
+        <v>5032</v>
+      </c>
+      <c r="P1530" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1531" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1531" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1531" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1531" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1531" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1531" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1531" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1531" s="1"/>
+      <c r="I1531" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1531" s="1">
+        <v>4.1666667999999997E-2</v>
+      </c>
+      <c r="K1531" s="1">
+        <v>1395.8334</v>
+      </c>
+      <c r="L1531" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1531" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1531" s="1"/>
+      <c r="O1531" s="1">
+        <v>5033</v>
+      </c>
+      <c r="P1531" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1532" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1532" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1532" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1532" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1532" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1532" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1532" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1532" s="1"/>
+      <c r="I1532" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1532" s="1">
+        <v>0.66666669999999995</v>
+      </c>
+      <c r="K1532" s="1">
+        <v>18666.666000000001</v>
+      </c>
+      <c r="L1532" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1532" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1532" s="1"/>
+      <c r="O1532" s="1">
+        <v>5034</v>
+      </c>
+      <c r="P1532" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1533" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1533" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1533" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1533" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1533" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1533" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1533" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H1533" s="1"/>
+      <c r="I1533" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1533" s="1">
+        <v>0</v>
+      </c>
+      <c r="K1533" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1533" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1533" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1533" s="1"/>
+      <c r="O1533" s="1">
+        <v>5035</v>
+      </c>
+      <c r="P1533" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1534" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1534" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1534" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1534" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1534" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1534" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1534" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1534" s="1"/>
+      <c r="I1534" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1534" s="1">
+        <v>0.55555560000000004</v>
+      </c>
+      <c r="K1534" s="1">
+        <v>15555.556</v>
+      </c>
+      <c r="L1534" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1534" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1534" s="1"/>
+      <c r="O1534" s="1">
+        <v>5036</v>
+      </c>
+      <c r="P1534" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1535" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1535" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1535" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1535" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1535" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1535" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1535" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1535" s="1"/>
+      <c r="I1535" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1535" s="1">
+        <v>0.16666666999999999</v>
+      </c>
+      <c r="K1535" s="1">
+        <v>2083.3332999999998</v>
+      </c>
+      <c r="L1535" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1535" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1535" s="1"/>
+      <c r="O1535" s="1">
+        <v>5037</v>
+      </c>
+      <c r="P1535" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1536" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1536" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1536" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1536" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1536" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1536" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1536" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1536" s="1"/>
+      <c r="I1536" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1536" s="1">
+        <v>8.3333335999999994E-2</v>
+      </c>
+      <c r="K1536" s="1">
+        <v>1291.6666</v>
+      </c>
+      <c r="L1536" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1536" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1536" s="1"/>
+      <c r="O1536" s="1">
+        <v>5038</v>
+      </c>
+      <c r="P1536" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1537" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1537" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1537" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1537" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1537" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1537" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1537" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1537" s="1"/>
+      <c r="I1537" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1537" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1537" s="1">
+        <v>12500</v>
+      </c>
+      <c r="L1537" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1537" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1537" s="1"/>
+      <c r="O1537" s="1">
+        <v>5039</v>
+      </c>
+      <c r="P1537" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1538" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1538" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1538" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1538" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1538" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1538" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1538" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1538" s="1"/>
+      <c r="I1538" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1538" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1538" s="1">
+        <v>15500</v>
+      </c>
+      <c r="L1538" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1538" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1538" s="1"/>
+      <c r="O1538" s="1">
+        <v>5040</v>
+      </c>
+      <c r="P1538" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1539" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1539" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1539" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1539" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1539" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1539" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1539" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1539" s="1"/>
+      <c r="I1539" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1539" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="K1539" s="1">
+        <v>1100</v>
+      </c>
+      <c r="L1539" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1539" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1539" s="1"/>
+      <c r="O1539" s="1">
+        <v>5041</v>
+      </c>
+      <c r="P1539" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1540" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1540" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1540" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1540" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1540" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1540" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1540" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1540" s="1"/>
+      <c r="I1540" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1540" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K1540" s="1">
+        <v>6250</v>
+      </c>
+      <c r="L1540" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1540" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1540" s="1"/>
+      <c r="O1540" s="1">
+        <v>5042</v>
+      </c>
+      <c r="P1540" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1541" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1541" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1541" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1541" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1541" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1541" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1541" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1541" s="1"/>
+      <c r="I1541" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1541" s="1">
+        <v>0.66666669999999995</v>
+      </c>
+      <c r="K1541" s="1">
+        <v>8000</v>
+      </c>
+      <c r="L1541" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1541" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1541" s="1"/>
+      <c r="O1541" s="1">
+        <v>5043</v>
+      </c>
+      <c r="P1541" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1542" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1542" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1542" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1542" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1542" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1542" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1542" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1542" s="1"/>
+      <c r="I1542" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1542" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1542" s="1">
+        <v>31000</v>
+      </c>
+      <c r="L1542" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1542" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1542" s="1"/>
+      <c r="O1542" s="1">
+        <v>5044</v>
+      </c>
+      <c r="P1542" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1543" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1543" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1543" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1543" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1543" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1543" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1543" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1543" s="1"/>
+      <c r="I1543" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1543" s="1">
+        <v>0.66666669999999995</v>
+      </c>
+      <c r="K1543" s="1">
+        <v>6666.6665000000003</v>
+      </c>
+      <c r="L1543" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1543" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1543" s="1"/>
+      <c r="O1543" s="1">
+        <v>5045</v>
+      </c>
+      <c r="P1543" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1544" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1544" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1544" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1544" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1544" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1544" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1544" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1544" s="1"/>
+      <c r="I1544" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1544" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1544" s="1">
+        <v>4500</v>
+      </c>
+      <c r="L1544" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1544" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1544" s="1"/>
+      <c r="O1544" s="1">
+        <v>5046</v>
+      </c>
+      <c r="P1544" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1545" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1545" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1545" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1545" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1545" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1545" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1545" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1545" s="1"/>
+      <c r="I1545" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1545" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1545" s="1">
+        <v>9000</v>
+      </c>
+      <c r="L1545" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1545" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1545" s="1"/>
+      <c r="O1545" s="1">
+        <v>5047</v>
+      </c>
+      <c r="P1545" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1546" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1546" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1546" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1546" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1546" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1546" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1546" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1546" s="1"/>
+      <c r="I1546" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1546" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1546" s="1">
+        <v>9000</v>
+      </c>
+      <c r="L1546" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1546" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1546" s="1"/>
+      <c r="O1546" s="1">
+        <v>5048</v>
+      </c>
+      <c r="P1546" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1547" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1547" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1547" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1547" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1547" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1547" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1547" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1547" s="1"/>
+      <c r="I1547" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1547" s="1">
+        <v>8.3333335999999994E-2</v>
+      </c>
+      <c r="K1547" s="1">
+        <v>2208.3332999999998</v>
+      </c>
+      <c r="L1547" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1547" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1547" s="1"/>
+      <c r="O1547" s="1">
+        <v>5049</v>
+      </c>
+      <c r="P1547" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1548" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1548" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1548" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1548" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1548" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1548" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1548" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1548" s="1"/>
+      <c r="I1548" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1548" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1548" s="1">
+        <v>11500</v>
+      </c>
+      <c r="L1548" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1548" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1548" s="1"/>
+      <c r="O1548" s="1">
+        <v>5050</v>
+      </c>
+      <c r="P1548" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1549" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1549" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1549" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1549" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1549" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1549" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1549" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1549" s="1"/>
+      <c r="I1549" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1549" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1549" s="1">
+        <v>11500</v>
+      </c>
+      <c r="L1549" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1549" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1549" s="1"/>
+      <c r="O1549" s="1">
+        <v>5051</v>
+      </c>
+      <c r="P1549" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1550" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1550" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1550" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1550" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1550" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1550" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1550" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H1550" s="1"/>
+      <c r="I1550" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1550" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1550" s="1">
+        <v>11500</v>
+      </c>
+      <c r="L1550" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1550" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1550" s="1"/>
+      <c r="O1550" s="1">
+        <v>5052</v>
+      </c>
+      <c r="P1550" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1551" s="2">
+        <v>46219</v>
+      </c>
+      <c r="B1551" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1551" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1551" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1551" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1551" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1551" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H1551" s="1"/>
+      <c r="I1551" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1551" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1551" s="1">
+        <v>11500</v>
+      </c>
+      <c r="L1551" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1551" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1551" s="1"/>
+      <c r="O1551" s="1">
+        <v>5053</v>
+      </c>
+      <c r="P1551" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1552" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1552" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1552" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1552" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1552" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1552" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1552" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1552" s="1"/>
+      <c r="I1552" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1552" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1552" s="1">
+        <v>26000</v>
+      </c>
+      <c r="L1552" s="1">
+        <v>4500</v>
+      </c>
+      <c r="M1552" s="1">
+        <v>5000</v>
+      </c>
+      <c r="N1552" s="1"/>
+      <c r="O1552" s="1">
+        <v>4875</v>
+      </c>
+      <c r="P1552" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1553" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1553" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1553" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1553" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1553" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1553" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1553" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1553" s="1"/>
+      <c r="I1553" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1553" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1553" s="1">
+        <v>52000</v>
+      </c>
+      <c r="L1553" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1553" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1553" s="1"/>
+      <c r="O1553" s="1">
+        <v>4876</v>
+      </c>
+      <c r="P1553" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1554" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1554" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1554" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1554" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1554" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1554" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1554" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1554" s="1"/>
+      <c r="I1554" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1554" s="1">
+        <v>0.44444444999999999</v>
+      </c>
+      <c r="K1554" s="1">
+        <v>11555.556</v>
+      </c>
+      <c r="L1554" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1554" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1554" s="1"/>
+      <c r="O1554" s="1">
+        <v>4877</v>
+      </c>
+      <c r="P1554" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1555" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1555" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1555" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1555" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1555" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1555" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1555" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H1555" s="1"/>
+      <c r="I1555" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1555" s="1">
+        <v>0.88888889999999998</v>
+      </c>
+      <c r="K1555" s="1">
+        <v>23111.111000000001</v>
+      </c>
+      <c r="L1555" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1555" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1555" s="1"/>
+      <c r="O1555" s="1">
+        <v>4878</v>
+      </c>
+      <c r="P1555" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1556" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1556" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1556" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1556" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1556" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1556" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1556" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H1556" s="1"/>
+      <c r="I1556" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1556" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="K1556" s="1">
+        <v>29250</v>
+      </c>
+      <c r="L1556" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1556" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1556" s="1"/>
+      <c r="O1556" s="1">
+        <v>4879</v>
+      </c>
+      <c r="P1556" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1557" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1557" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1557" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1557" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1557" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1557" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1557" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1557" s="1"/>
+      <c r="I1557" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1557" s="1">
+        <v>0.66666669999999995</v>
+      </c>
+      <c r="K1557" s="1">
+        <v>18666.666000000001</v>
+      </c>
+      <c r="L1557" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1557" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1557" s="1"/>
+      <c r="O1557" s="1">
+        <v>4880</v>
+      </c>
+      <c r="P1557" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1558" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1558" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1558" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1558" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1558" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1558" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1558" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1558" s="1"/>
+      <c r="I1558" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1558" s="1">
+        <v>4.1666667999999997E-2</v>
+      </c>
+      <c r="K1558" s="1">
+        <v>1395.8334</v>
+      </c>
+      <c r="L1558" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1558" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1558" s="1"/>
+      <c r="O1558" s="1">
+        <v>4881</v>
+      </c>
+      <c r="P1558" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1559" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1559" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1559" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1559" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1559" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1559" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1559" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1559" s="1"/>
+      <c r="I1559" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1559" s="1">
+        <v>4.1666667999999997E-2</v>
+      </c>
+      <c r="K1559" s="1">
+        <v>729.16669999999999</v>
+      </c>
+      <c r="L1559" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1559" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1559" s="1"/>
+      <c r="O1559" s="1">
+        <v>4882</v>
+      </c>
+      <c r="P1559" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1560" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1560" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1560" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1560" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1560" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1560" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1560" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1560" s="1"/>
+      <c r="I1560" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1560" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1560" s="1">
+        <v>33500</v>
+      </c>
+      <c r="L1560" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1560" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1560" s="1"/>
+      <c r="O1560" s="1">
+        <v>4883</v>
+      </c>
+      <c r="P1560" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1561" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1561" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1561" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1561" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1561" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1561" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1561" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1561" s="1"/>
+      <c r="I1561" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1561" s="1">
+        <v>0.77777779999999996</v>
+      </c>
+      <c r="K1561" s="1">
+        <v>21777.776999999998</v>
+      </c>
+      <c r="L1561" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1561" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1561" s="1"/>
+      <c r="O1561" s="1">
+        <v>4884</v>
+      </c>
+      <c r="P1561" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1562" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1562" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1562" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1562" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1562" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1562" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1562" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H1562" s="1"/>
+      <c r="I1562" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1562" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1562" s="1">
+        <v>28000</v>
+      </c>
+      <c r="L1562" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1562" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1562" s="1"/>
+      <c r="O1562" s="1">
+        <v>4885</v>
+      </c>
+      <c r="P1562" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1563" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1563" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1563" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1563" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1563" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1563" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1563" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H1563" s="1"/>
+      <c r="I1563" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1563" s="1">
+        <v>4.1666667999999997E-2</v>
+      </c>
+      <c r="K1563" s="1">
+        <v>1395.8334</v>
+      </c>
+      <c r="L1563" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1563" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1563" s="1"/>
+      <c r="O1563" s="1">
+        <v>4886</v>
+      </c>
+      <c r="P1563" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1564" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1564" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1564" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1564" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1564" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1564" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1564" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H1564" s="1"/>
+      <c r="I1564" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1564" s="1">
+        <v>0.45833333999999998</v>
+      </c>
+      <c r="K1564" s="1">
+        <v>8020.8334999999997</v>
+      </c>
+      <c r="L1564" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1564" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1564" s="1"/>
+      <c r="O1564" s="1">
+        <v>4887</v>
+      </c>
+      <c r="P1564" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1565" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1565" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1565" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1565" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1565" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1565" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1565" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1565" s="1"/>
+      <c r="I1565" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1565" s="1">
+        <v>0.55555560000000004</v>
+      </c>
+      <c r="K1565" s="1">
+        <v>15555.556</v>
+      </c>
+      <c r="L1565" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1565" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1565" s="1"/>
+      <c r="O1565" s="1">
+        <v>4888</v>
+      </c>
+      <c r="P1565" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1566" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1566" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1566" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1566" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1566" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1566" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1566" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1566" s="1"/>
+      <c r="I1566" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1566" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1566" s="1">
+        <v>17500</v>
+      </c>
+      <c r="L1566" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1566" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1566" s="1"/>
+      <c r="O1566" s="1">
+        <v>4889</v>
+      </c>
+      <c r="P1566" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1567" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1567" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1567" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1567" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1567" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1567" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1567" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1567" s="1"/>
+      <c r="I1567" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1567" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1567" s="1">
+        <v>12500</v>
+      </c>
+      <c r="L1567" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1567" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1567" s="1"/>
+      <c r="O1567" s="1">
+        <v>4890</v>
+      </c>
+      <c r="P1567" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1568" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1568" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1568" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1568" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1568" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1568" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1568" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1568" s="1"/>
+      <c r="I1568" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1568" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K1568" s="1">
+        <v>7750</v>
+      </c>
+      <c r="L1568" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1568" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1568" s="1"/>
+      <c r="O1568" s="1">
+        <v>4891</v>
+      </c>
+      <c r="P1568" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1569" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1569" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1569" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1569" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1569" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1569" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1569" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1569" s="1"/>
+      <c r="I1569" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1569" s="1">
+        <v>0.33333333999999998</v>
+      </c>
+      <c r="K1569" s="1">
+        <v>4166.6665000000003</v>
+      </c>
+      <c r="L1569" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1569" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1569" s="1"/>
+      <c r="O1569" s="1">
+        <v>4892</v>
+      </c>
+      <c r="P1569" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1570" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1570" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1570" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1570" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1570" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1570" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1570" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1570" s="1"/>
+      <c r="I1570" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1570" s="1">
+        <v>0.16666666999999999</v>
+      </c>
+      <c r="K1570" s="1">
+        <v>2583.3332999999998</v>
+      </c>
+      <c r="L1570" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1570" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1570" s="1"/>
+      <c r="O1570" s="1">
+        <v>4893</v>
+      </c>
+      <c r="P1570" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1571" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1571" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1571" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1571" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1571" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1571" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1571" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1571" s="1"/>
+      <c r="I1571" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1571" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K1571" s="1">
+        <v>5000</v>
+      </c>
+      <c r="L1571" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1571" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1571" s="1"/>
+      <c r="O1571" s="1">
+        <v>4894</v>
+      </c>
+      <c r="P1571" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1572" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1572" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1572" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1572" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1572" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1572" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1572" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1572" s="1"/>
+      <c r="I1572" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1572" s="1">
+        <v>0.33333333999999998</v>
+      </c>
+      <c r="K1572" s="1">
+        <v>4000</v>
+      </c>
+      <c r="L1572" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1572" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1572" s="1"/>
+      <c r="O1572" s="1">
+        <v>4895</v>
+      </c>
+      <c r="P1572" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1573" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1573" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1573" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1573" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1573" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1573" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1573" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1573" s="1"/>
+      <c r="I1573" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1573" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K1573" s="1">
+        <v>6000</v>
+      </c>
+      <c r="L1573" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1573" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1573" s="1"/>
+      <c r="O1573" s="1">
+        <v>4896</v>
+      </c>
+      <c r="P1573" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1574" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1574" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1574" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1574" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1574" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1574" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1574" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1574" s="1"/>
+      <c r="I1574" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1574" s="1">
+        <v>0.33333333999999998</v>
+      </c>
+      <c r="K1574" s="1">
+        <v>3333.3332999999998</v>
+      </c>
+      <c r="L1574" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1574" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1574" s="1"/>
+      <c r="O1574" s="1">
+        <v>4897</v>
+      </c>
+      <c r="P1574" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1575" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1575" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1575" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1575" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1575" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1575" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1575" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H1575" s="1"/>
+      <c r="I1575" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1575" s="1">
+        <v>0.16666666999999999</v>
+      </c>
+      <c r="K1575" s="1">
+        <v>1666.6666</v>
+      </c>
+      <c r="L1575" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1575" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1575" s="1"/>
+      <c r="O1575" s="1">
+        <v>4898</v>
+      </c>
+      <c r="P1575" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1576" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1576" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1576" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1576" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1576" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1576" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1576" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H1576" s="1"/>
+      <c r="I1576" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1576" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1576" s="1">
+        <v>15500</v>
+      </c>
+      <c r="L1576" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1576" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1576" s="1"/>
+      <c r="O1576" s="1">
+        <v>4899</v>
+      </c>
+      <c r="P1576" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1577" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1577" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1577" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1577" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1577" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1577" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1577" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1577" s="1"/>
+      <c r="I1577" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1577" s="1">
+        <v>0.33333333999999998</v>
+      </c>
+      <c r="K1577" s="1">
+        <v>3333.3332999999998</v>
+      </c>
+      <c r="L1577" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1577" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1577" s="1"/>
+      <c r="O1577" s="1">
+        <v>4900</v>
+      </c>
+      <c r="P1577" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1578" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1578" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1578" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1578" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1578" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1578" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1578" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1578" s="1"/>
+      <c r="I1578" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1578" s="1">
+        <v>0.16666666999999999</v>
+      </c>
+      <c r="K1578" s="1">
+        <v>2000</v>
+      </c>
+      <c r="L1578" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1578" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1578" s="1"/>
+      <c r="O1578" s="1">
+        <v>4901</v>
+      </c>
+      <c r="P1578" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1579" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1579" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1579" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1579" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1579" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1579" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1579" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1579" s="1"/>
+      <c r="I1579" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1579" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1579" s="1">
+        <v>15500</v>
+      </c>
+      <c r="L1579" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1579" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1579" s="1"/>
+      <c r="O1579" s="1">
+        <v>4902</v>
+      </c>
+      <c r="P1579" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1580" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1580" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1580" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1580" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1580" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1580" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1580" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1580" s="1"/>
+      <c r="I1580" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1580" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1580" s="1">
+        <v>4500</v>
+      </c>
+      <c r="L1580" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1580" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1580" s="1"/>
+      <c r="O1580" s="1">
+        <v>4903</v>
+      </c>
+      <c r="P1580" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1581" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1581" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1581" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1581" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1581" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1581" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1581" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1581" s="1"/>
+      <c r="I1581" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1581" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1581" s="1">
+        <v>10500</v>
+      </c>
+      <c r="L1581" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1581" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1581" s="1"/>
+      <c r="O1581" s="1">
+        <v>4904</v>
+      </c>
+      <c r="P1581" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1582" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1582" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1582" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1582" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1582" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1582" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1582" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1582" s="1"/>
+      <c r="I1582" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1582" s="1">
+        <v>4</v>
+      </c>
+      <c r="K1582" s="1">
+        <v>18000</v>
+      </c>
+      <c r="L1582" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1582" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1582" s="1"/>
+      <c r="O1582" s="1">
+        <v>4905</v>
+      </c>
+      <c r="P1582" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1583" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1583" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1583" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1583" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1583" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1583" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1583" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1583" s="1"/>
+      <c r="I1583" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1583" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1583" s="1">
+        <v>12000</v>
+      </c>
+      <c r="L1583" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1583" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1583" s="1"/>
+      <c r="O1583" s="1">
+        <v>4906</v>
+      </c>
+      <c r="P1583" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1584" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1584" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1584" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1584" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1584" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1584" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1584" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1584" s="1"/>
+      <c r="I1584" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1584" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1584" s="1">
+        <v>10500</v>
+      </c>
+      <c r="L1584" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1584" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1584" s="1"/>
+      <c r="O1584" s="1">
+        <v>4907</v>
+      </c>
+      <c r="P1584" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1585" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1585" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1585" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1585" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1585" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1585" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1585" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1585" s="1"/>
+      <c r="I1585" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1585" s="1">
+        <v>0.16666666999999999</v>
+      </c>
+      <c r="K1585" s="1">
+        <v>4416.6665000000003</v>
+      </c>
+      <c r="L1585" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1585" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1585" s="1"/>
+      <c r="O1585" s="1">
+        <v>4908</v>
+      </c>
+      <c r="P1585" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1586" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1586" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1586" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1586" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1586" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1586" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1586" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1586" s="1"/>
+      <c r="I1586" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1586" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1586" s="1">
+        <v>10500</v>
+      </c>
+      <c r="L1586" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1586" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1586" s="1"/>
+      <c r="O1586" s="1">
+        <v>4909</v>
+      </c>
+      <c r="P1586" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1587" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1587" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1587" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1587" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1587" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1587" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1587" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1587" s="1"/>
+      <c r="I1587" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1587" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1587" s="1">
+        <v>4500</v>
+      </c>
+      <c r="L1587" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1587" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1587" s="1"/>
+      <c r="O1587" s="1">
+        <v>4910</v>
+      </c>
+      <c r="P1587" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1588" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1588" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1588" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1588" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1588" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1588" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1588" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1588" s="1"/>
+      <c r="I1588" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1588" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1588" s="1">
+        <v>9000</v>
+      </c>
+      <c r="L1588" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1588" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1588" s="1"/>
+      <c r="O1588" s="1">
+        <v>4911</v>
+      </c>
+      <c r="P1588" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1589" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1589" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1589" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1589" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1589" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1589" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1589" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1589" s="1"/>
+      <c r="I1589" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1589" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="K1589" s="1">
+        <v>17250</v>
+      </c>
+      <c r="L1589" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1589" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1589" s="1"/>
+      <c r="O1589" s="1">
+        <v>4912</v>
+      </c>
+      <c r="P1589" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1590" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1590" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1590" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1590" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1590" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1590" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1590" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1590" s="1"/>
+      <c r="I1590" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1590" s="1">
+        <v>2.1666666999999999</v>
+      </c>
+      <c r="K1590" s="1">
+        <v>24916.666000000001</v>
+      </c>
+      <c r="L1590" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1590" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1590" s="1"/>
+      <c r="O1590" s="1">
+        <v>4913</v>
+      </c>
+      <c r="P1590" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1591" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1591" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1591" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1591" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1591" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1591" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1591" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H1591" s="1"/>
+      <c r="I1591" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1591" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1591" s="1">
+        <v>11500</v>
+      </c>
+      <c r="L1591" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1591" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1591" s="1"/>
+      <c r="O1591" s="1">
+        <v>4914</v>
+      </c>
+      <c r="P1591" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1592" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B1592" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1592" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1592" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1592" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1592" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1592" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H1592" s="1"/>
+      <c r="I1592" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1592" s="1">
+        <v>1.0833333999999999</v>
+      </c>
+      <c r="K1592" s="1">
+        <v>12458.333000000001</v>
+      </c>
+      <c r="L1592" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1592" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1592" s="1"/>
+      <c r="O1592" s="1">
+        <v>4915</v>
+      </c>
+      <c r="P1592" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1593" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1593" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1593" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1593" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1593" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1593" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1593" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1593" s="1"/>
+      <c r="I1593" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1593" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1593" s="1">
+        <v>26000</v>
+      </c>
+      <c r="L1593" s="1">
+        <v>2500</v>
+      </c>
+      <c r="M1593" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1593" s="1"/>
+      <c r="O1593" s="1">
+        <v>4738</v>
+      </c>
+      <c r="P1593" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1594" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1594" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1594" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1594" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1594" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1594" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1594" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1594" s="1"/>
+      <c r="I1594" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1594" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K1594" s="1">
+        <v>9750</v>
+      </c>
+      <c r="L1594" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1594" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1594" s="1"/>
+      <c r="O1594" s="1">
+        <v>4739</v>
+      </c>
+      <c r="P1594" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1595" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1595" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1595" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1595" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1595" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1595" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1595" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1595" s="1"/>
+      <c r="I1595" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1595" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1595" s="1">
+        <v>52000</v>
+      </c>
+      <c r="L1595" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1595" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1595" s="1"/>
+      <c r="O1595" s="1">
+        <v>4740</v>
+      </c>
+      <c r="P1595" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1596" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1596" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1596" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1596" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1596" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1596" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1596" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1596" s="1"/>
+      <c r="I1596" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1596" s="1">
+        <v>0.44444444999999999</v>
+      </c>
+      <c r="K1596" s="1">
+        <v>11555.556</v>
+      </c>
+      <c r="L1596" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1596" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1596" s="1"/>
+      <c r="O1596" s="1">
+        <v>4741</v>
+      </c>
+      <c r="P1596" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1597" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1597" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1597" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1597" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1597" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1597" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1597" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H1597" s="1"/>
+      <c r="I1597" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1597" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1597" s="1">
+        <v>26000</v>
+      </c>
+      <c r="L1597" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1597" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1597" s="1"/>
+      <c r="O1597" s="1">
+        <v>4742</v>
+      </c>
+      <c r="P1597" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1598" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1598" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1598" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1598" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1598" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1598" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1598" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H1598" s="1"/>
+      <c r="I1598" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1598" s="1">
+        <v>0.33333333999999998</v>
+      </c>
+      <c r="K1598" s="1">
+        <v>9333.3330000000005</v>
+      </c>
+      <c r="L1598" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1598" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1598" s="1"/>
+      <c r="O1598" s="1">
+        <v>4743</v>
+      </c>
+      <c r="P1598" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1599" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1599" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1599" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1599" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1599" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1599" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1599" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1599" s="1"/>
+      <c r="I1599" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1599" s="1">
+        <v>0.44444444999999999</v>
+      </c>
+      <c r="K1599" s="1">
+        <v>12444.444</v>
+      </c>
+      <c r="L1599" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1599" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1599" s="1"/>
+      <c r="O1599" s="1">
+        <v>4744</v>
+      </c>
+      <c r="P1599" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1600" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1600" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1600" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1600" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1600" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1600" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1600" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1600" s="1"/>
+      <c r="I1600" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1600" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1600" s="1">
+        <v>28000</v>
+      </c>
+      <c r="L1600" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1600" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1600" s="1"/>
+      <c r="O1600" s="1">
+        <v>4745</v>
+      </c>
+      <c r="P1600" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1601" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1601" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1601" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1601" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1601" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1601" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1601" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H1601" s="1"/>
+      <c r="I1601" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1601" s="1">
+        <v>0.55555560000000004</v>
+      </c>
+      <c r="K1601" s="1">
+        <v>15555.556</v>
+      </c>
+      <c r="L1601" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1601" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1601" s="1"/>
+      <c r="O1601" s="1">
+        <v>4746</v>
+      </c>
+      <c r="P1601" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1602" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1602" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1602" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1602" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1602" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1602" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1602" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1602" s="1"/>
+      <c r="I1602" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1602" s="1">
+        <v>0.77777779999999996</v>
+      </c>
+      <c r="K1602" s="1">
+        <v>21777.776999999998</v>
+      </c>
+      <c r="L1602" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1602" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1602" s="1"/>
+      <c r="O1602" s="1">
+        <v>4747</v>
+      </c>
+      <c r="P1602" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1603" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1603" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1603" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1603" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1603" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1603" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1603" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H1603" s="1"/>
+      <c r="I1603" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1603" s="1">
+        <v>0.44444444999999999</v>
+      </c>
+      <c r="K1603" s="1">
+        <v>12444.444</v>
+      </c>
+      <c r="L1603" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1603" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1603" s="1"/>
+      <c r="O1603" s="1">
+        <v>4748</v>
+      </c>
+      <c r="P1603" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1604" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1604" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1604" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1604" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1604" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1604" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1604" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1604" s="1"/>
+      <c r="I1604" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1604" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="K1604" s="1">
+        <v>3125</v>
+      </c>
+      <c r="L1604" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1604" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1604" s="1"/>
+      <c r="O1604" s="1">
+        <v>4749</v>
+      </c>
+      <c r="P1604" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1605" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1605" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1605" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1605" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1605" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1605" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1605" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1605" s="1"/>
+      <c r="I1605" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1605" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="K1605" s="1">
+        <v>3875</v>
+      </c>
+      <c r="L1605" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1605" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1605" s="1"/>
+      <c r="O1605" s="1">
+        <v>4750</v>
+      </c>
+      <c r="P1605" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1606" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1606" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1606" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1606" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1606" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1606" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1606" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1606" s="1"/>
+      <c r="I1606" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1606" s="1">
+        <v>0.41666666000000002</v>
+      </c>
+      <c r="K1606" s="1">
+        <v>5208.3334999999997</v>
+      </c>
+      <c r="L1606" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1606" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1606" s="1"/>
+      <c r="O1606" s="1">
+        <v>4751</v>
+      </c>
+      <c r="P1606" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1607" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1607" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1607" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1607" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1607" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1607" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1607" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1607" s="1"/>
+      <c r="I1607" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1607" s="1">
+        <v>0.33333333999999998</v>
+      </c>
+      <c r="K1607" s="1">
+        <v>4166.6665000000003</v>
+      </c>
+      <c r="L1607" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1607" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1607" s="1"/>
+      <c r="O1607" s="1">
+        <v>4752</v>
+      </c>
+      <c r="P1607" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1608" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1608" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1608" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1608" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1608" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1608" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1608" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1608" s="1"/>
+      <c r="I1608" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1608" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="K1608" s="1">
+        <v>3875</v>
+      </c>
+      <c r="L1608" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1608" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1608" s="1"/>
+      <c r="O1608" s="1">
+        <v>4753</v>
+      </c>
+      <c r="P1608" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1609" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1609" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1609" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1609" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1609" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1609" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1609" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1609" s="1"/>
+      <c r="I1609" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1609" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="K1609" s="1">
+        <v>3125</v>
+      </c>
+      <c r="L1609" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1609" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1609" s="1"/>
+      <c r="O1609" s="1">
+        <v>4754</v>
+      </c>
+      <c r="P1609" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1610" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1610" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1610" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1610" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1610" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1610" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1610" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1610" s="1"/>
+      <c r="I1610" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1610" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="K1610" s="1">
+        <v>3125</v>
+      </c>
+      <c r="L1610" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1610" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1610" s="1"/>
+      <c r="O1610" s="1">
+        <v>4755</v>
+      </c>
+      <c r="P1610" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1611" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1611" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1611" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1611" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1611" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1611" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1611" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1611" s="1"/>
+      <c r="I1611" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1611" s="1">
+        <v>8.3333335999999994E-2</v>
+      </c>
+      <c r="K1611" s="1">
+        <v>1291.6666</v>
+      </c>
+      <c r="L1611" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1611" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1611" s="1"/>
+      <c r="O1611" s="1">
+        <v>4756</v>
+      </c>
+      <c r="P1611" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1612" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1612" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1612" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1612" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1612" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1612" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1612" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1612" s="1"/>
+      <c r="I1612" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1612" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K1612" s="1">
+        <v>5000</v>
+      </c>
+      <c r="L1612" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1612" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1612" s="1"/>
+      <c r="O1612" s="1">
+        <v>4757</v>
+      </c>
+      <c r="P1612" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1613" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1613" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1613" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1613" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1613" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1613" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1613" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1613" s="1"/>
+      <c r="I1613" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1613" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K1613" s="1">
+        <v>6000</v>
+      </c>
+      <c r="L1613" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1613" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1613" s="1"/>
+      <c r="O1613" s="1">
+        <v>4758</v>
+      </c>
+      <c r="P1613" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1614" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1614" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1614" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1614" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1614" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1614" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1614" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1614" s="1"/>
+      <c r="I1614" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1614" s="1">
+        <v>0.16666666999999999</v>
+      </c>
+      <c r="K1614" s="1">
+        <v>1666.6666</v>
+      </c>
+      <c r="L1614" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1614" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1614" s="1"/>
+      <c r="O1614" s="1">
+        <v>4759</v>
+      </c>
+      <c r="P1614" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1615" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1615" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1615" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1615" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1615" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1615" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1615" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1615" s="1"/>
+      <c r="I1615" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1615" s="1">
+        <v>0.33333333999999998</v>
+      </c>
+      <c r="K1615" s="1">
+        <v>4000</v>
+      </c>
+      <c r="L1615" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1615" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1615" s="1"/>
+      <c r="O1615" s="1">
+        <v>4760</v>
+      </c>
+      <c r="P1615" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1616" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1616" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1616" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1616" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1616" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1616" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1616" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H1616" s="1"/>
+      <c r="I1616" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1616" s="1">
+        <v>0.33333333999999998</v>
+      </c>
+      <c r="K1616" s="1">
+        <v>3333.3332999999998</v>
+      </c>
+      <c r="L1616" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1616" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1616" s="1"/>
+      <c r="O1616" s="1">
+        <v>4761</v>
+      </c>
+      <c r="P1616" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1617" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1617" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1617" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1617" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1617" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1617" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1617" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1617" s="1"/>
+      <c r="I1617" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1617" s="1">
+        <v>1.3333333999999999</v>
+      </c>
+      <c r="K1617" s="1">
+        <v>13333.333000000001</v>
+      </c>
+      <c r="L1617" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1617" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1617" s="1"/>
+      <c r="O1617" s="1">
+        <v>4762</v>
+      </c>
+      <c r="P1617" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1618" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1618" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1618" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1618" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1618" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1618" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1618" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1618" s="1"/>
+      <c r="I1618" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1618" s="1">
+        <v>0.16666666999999999</v>
+      </c>
+      <c r="K1618" s="1">
+        <v>2000</v>
+      </c>
+      <c r="L1618" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1618" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1618" s="1"/>
+      <c r="O1618" s="1">
+        <v>4763</v>
+      </c>
+      <c r="P1618" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1619" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1619" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1619" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1619" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1619" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1619" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1619" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1619" s="1"/>
+      <c r="I1619" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1619" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1619" s="1">
+        <v>10500</v>
+      </c>
+      <c r="L1619" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1619" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1619" s="1"/>
+      <c r="O1619" s="1">
+        <v>4764</v>
+      </c>
+      <c r="P1619" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1620" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1620" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1620" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1620" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1620" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1620" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1620" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1620" s="1"/>
+      <c r="I1620" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1620" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="K1620" s="1">
+        <v>1200</v>
+      </c>
+      <c r="L1620" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1620" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1620" s="1"/>
+      <c r="O1620" s="1">
+        <v>4765</v>
+      </c>
+      <c r="P1620" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1621" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1621" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1621" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1621" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1621" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1621" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1621" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1621" s="1"/>
+      <c r="I1621" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1621" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1621" s="1">
+        <v>10500</v>
+      </c>
+      <c r="L1621" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1621" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1621" s="1"/>
+      <c r="O1621" s="1">
+        <v>4766</v>
+      </c>
+      <c r="P1621" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1622" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1622" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1622" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1622" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1622" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1622" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1622" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1622" s="1"/>
+      <c r="I1622" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1622" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1622" s="1">
+        <v>10500</v>
+      </c>
+      <c r="L1622" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1622" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1622" s="1"/>
+      <c r="O1622" s="1">
+        <v>4767</v>
+      </c>
+      <c r="P1622" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1623" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1623" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1623" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1623" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1623" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1623" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1623" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1623" s="1"/>
+      <c r="I1623" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1623" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1623" s="1">
+        <v>9000</v>
+      </c>
+      <c r="L1623" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1623" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1623" s="1"/>
+      <c r="O1623" s="1">
+        <v>4768</v>
+      </c>
+      <c r="P1623" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1624" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1624" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1624" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1624" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1624" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1624" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1624" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1624" s="1"/>
+      <c r="I1624" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1624" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1624" s="1">
+        <v>10500</v>
+      </c>
+      <c r="L1624" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1624" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1624" s="1"/>
+      <c r="O1624" s="1">
+        <v>4769</v>
+      </c>
+      <c r="P1624" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1625" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1625" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1625" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1625" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1625" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1625" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1625" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1625" s="1"/>
+      <c r="I1625" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1625" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1625" s="1">
+        <v>4500</v>
+      </c>
+      <c r="L1625" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1625" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1625" s="1"/>
+      <c r="O1625" s="1">
+        <v>4770</v>
+      </c>
+      <c r="P1625" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1626" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1626" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1626" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1626" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1626" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1626" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1626" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1626" s="1"/>
+      <c r="I1626" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1626" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1626" s="1">
+        <v>11500</v>
+      </c>
+      <c r="L1626" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1626" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1626" s="1"/>
+      <c r="O1626" s="1">
+        <v>4771</v>
+      </c>
+      <c r="P1626" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1627" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1627" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1627" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1627" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1627" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1627" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1627" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1627" s="1"/>
+      <c r="I1627" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1627" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1627" s="1">
+        <v>11500</v>
+      </c>
+      <c r="L1627" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1627" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1627" s="1"/>
+      <c r="O1627" s="1">
+        <v>4772</v>
+      </c>
+      <c r="P1627" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1628" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1628" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1628" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1628" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1628" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1628" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1628" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H1628" s="1"/>
+      <c r="I1628" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1628" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="K1628" s="1">
+        <v>8625</v>
+      </c>
+      <c r="L1628" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1628" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1628" s="1"/>
+      <c r="O1628" s="1">
+        <v>4773</v>
+      </c>
+      <c r="P1628" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1629" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1629" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1629" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1629" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1629" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1629" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1629" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H1629" s="1"/>
+      <c r="I1629" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1629" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1629" s="1">
+        <v>11500</v>
+      </c>
+      <c r="L1629" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1629" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1629" s="1"/>
+      <c r="O1629" s="1">
+        <v>4774</v>
+      </c>
+      <c r="P1629" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1630" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1630" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1630" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1630" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1630" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1630" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1630" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1630" s="1"/>
+      <c r="I1630" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1630" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="K1630" s="1">
+        <v>1800</v>
+      </c>
+      <c r="L1630" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1630" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1630" s="1"/>
+      <c r="O1630" s="1">
+        <v>4775</v>
+      </c>
+      <c r="P1630" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1631" s="2">
+        <v>46217</v>
+      </c>
+      <c r="B1631" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1631" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1631" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1631" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1631" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1631" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H1631" s="1"/>
+      <c r="I1631" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1631" s="1">
+        <v>0</v>
+      </c>
+      <c r="K1631" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1631" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1631" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1631" s="1"/>
+      <c r="O1631" s="1">
+        <v>4776</v>
+      </c>
+      <c r="P1631" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1632" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1632" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1632" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1632" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1632" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1632" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1632" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1632" s="1"/>
+      <c r="I1632" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1632" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1632" s="1">
+        <v>39000</v>
+      </c>
+      <c r="L1632" s="1">
+        <v>4500</v>
+      </c>
+      <c r="M1632" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1632" s="1"/>
+      <c r="O1632" s="1">
+        <v>4665</v>
+      </c>
+      <c r="P1632" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1633" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1633" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1633" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1633" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1633" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1633" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1633" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1633" s="1"/>
+      <c r="I1633" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1633" s="1">
+        <v>0.44444444999999999</v>
+      </c>
+      <c r="K1633" s="1">
+        <v>11555.556</v>
+      </c>
+      <c r="L1633" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1633" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1633" s="1"/>
+      <c r="O1633" s="1">
+        <v>4666</v>
+      </c>
+      <c r="P1633" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1634" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1634" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1634" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1634" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1634" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1634" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1634" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1634" s="1"/>
+      <c r="I1634" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1634" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1634" s="1">
+        <v>52000</v>
+      </c>
+      <c r="L1634" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1634" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1634" s="1"/>
+      <c r="O1634" s="1">
+        <v>4667</v>
+      </c>
+      <c r="P1634" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1635" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1635" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1635" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1635" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1635" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1635" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1635" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1635" s="1"/>
+      <c r="I1635" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1635" s="1">
+        <v>3</v>
+      </c>
+      <c r="K1635" s="1">
+        <v>78000</v>
+      </c>
+      <c r="L1635" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1635" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1635" s="1"/>
+      <c r="O1635" s="1">
+        <v>4668</v>
+      </c>
+      <c r="P1635" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1636" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1636" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1636" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1636" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1636" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1636" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1636" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H1636" s="1"/>
+      <c r="I1636" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1636" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1636" s="1">
+        <v>26000</v>
+      </c>
+      <c r="L1636" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1636" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1636" s="1"/>
+      <c r="O1636" s="1">
+        <v>4669</v>
+      </c>
+      <c r="P1636" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1637" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1637" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1637" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1637" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1637" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1637" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1637" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H1637" s="1"/>
+      <c r="I1637" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1637" s="1">
+        <v>0.11111111</v>
+      </c>
+      <c r="K1637" s="1">
+        <v>3111.1109999999999</v>
+      </c>
+      <c r="L1637" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1637" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1637" s="1"/>
+      <c r="O1637" s="1">
+        <v>4670</v>
+      </c>
+      <c r="P1637" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1638" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1638" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1638" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1638" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1638" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1638" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1638" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1638" s="1"/>
+      <c r="I1638" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1638" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1638" s="1">
+        <v>28000</v>
+      </c>
+      <c r="L1638" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1638" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1638" s="1"/>
+      <c r="O1638" s="1">
+        <v>4671</v>
+      </c>
+      <c r="P1638" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1639" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1639" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1639" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1639" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1639" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1639" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1639" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1639" s="1"/>
+      <c r="I1639" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1639" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K1639" s="1">
+        <v>8750</v>
+      </c>
+      <c r="L1639" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1639" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1639" s="1"/>
+      <c r="O1639" s="1">
+        <v>4672</v>
+      </c>
+      <c r="P1639" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1640" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1640" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1640" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1640" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1640" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1640" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1640" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1640" s="1"/>
+      <c r="I1640" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1640" s="1">
+        <v>1.5555555999999999</v>
+      </c>
+      <c r="K1640" s="1">
+        <v>43555.555</v>
+      </c>
+      <c r="L1640" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1640" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1640" s="1"/>
+      <c r="O1640" s="1">
+        <v>4673</v>
+      </c>
+      <c r="P1640" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1641" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1641" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1641" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1641" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1641" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1641" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1641" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H1641" s="1"/>
+      <c r="I1641" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1641" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1641" s="1">
+        <v>28000</v>
+      </c>
+      <c r="L1641" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1641" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1641" s="1"/>
+      <c r="O1641" s="1">
+        <v>4674</v>
+      </c>
+      <c r="P1641" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1642" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1642" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1642" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1642" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1642" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1642" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1642" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1642" s="1"/>
+      <c r="I1642" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1642" s="1">
+        <v>0.66666669999999995</v>
+      </c>
+      <c r="K1642" s="1">
+        <v>18666.666000000001</v>
+      </c>
+      <c r="L1642" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1642" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1642" s="1"/>
+      <c r="O1642" s="1">
+        <v>4675</v>
+      </c>
+      <c r="P1642" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1643" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1643" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1643" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1643" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1643" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1643" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1643" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1643" s="1"/>
+      <c r="I1643" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1643" s="1">
+        <v>4.1666667999999997E-2</v>
+      </c>
+      <c r="K1643" s="1">
+        <v>1395.8334</v>
+      </c>
+      <c r="L1643" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1643" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1643" s="1"/>
+      <c r="O1643" s="1">
+        <v>4676</v>
+      </c>
+      <c r="P1643" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1644" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1644" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1644" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1644" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1644" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1644" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1644" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1644" s="1"/>
+      <c r="I1644" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1644" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="K1644" s="1">
+        <v>2200</v>
+      </c>
+      <c r="L1644" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1644" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1644" s="1"/>
+      <c r="O1644" s="1">
+        <v>4677</v>
+      </c>
+      <c r="P1644" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1645" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1645" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1645" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1645" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1645" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1645" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1645" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1645" s="1"/>
+      <c r="I1645" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1645" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="K1645" s="1">
+        <v>4400</v>
+      </c>
+      <c r="L1645" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1645" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1645" s="1"/>
+      <c r="O1645" s="1">
+        <v>4678</v>
+      </c>
+      <c r="P1645" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1646" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1646" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1646" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1646" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1646" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1646" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1646" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1646" s="1"/>
+      <c r="I1646" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1646" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="K1646" s="1">
+        <v>3300</v>
+      </c>
+      <c r="L1646" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1646" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1646" s="1"/>
+      <c r="O1646" s="1">
+        <v>4679</v>
+      </c>
+      <c r="P1646" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1647" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1647" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1647" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1647" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1647" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1647" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1647" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1647" s="1"/>
+      <c r="I1647" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1647" s="1">
+        <v>0.16666666999999999</v>
+      </c>
+      <c r="K1647" s="1">
+        <v>1666.6666</v>
+      </c>
+      <c r="L1647" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1647" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1647" s="1"/>
+      <c r="O1647" s="1">
+        <v>4680</v>
+      </c>
+      <c r="P1647" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1648" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1648" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1648" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1648" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1648" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1648" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1648" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1648" s="1"/>
+      <c r="I1648" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1648" s="1">
+        <v>0.16666666999999999</v>
+      </c>
+      <c r="K1648" s="1">
+        <v>1666.6666</v>
+      </c>
+      <c r="L1648" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1648" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1648" s="1"/>
+      <c r="O1648" s="1">
+        <v>4681</v>
+      </c>
+      <c r="P1648" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1649" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1649" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1649" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1649" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1649" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1649" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1649" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1649" s="1"/>
+      <c r="I1649" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1649" s="1">
+        <v>0.33333333999999998</v>
+      </c>
+      <c r="K1649" s="1">
+        <v>4000</v>
+      </c>
+      <c r="L1649" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1649" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1649" s="1"/>
+      <c r="O1649" s="1">
+        <v>4682</v>
+      </c>
+      <c r="P1649" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1650" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1650" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1650" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1650" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1650" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1650" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1650" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1650" s="1"/>
+      <c r="I1650" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1650" s="1">
+        <v>0.16666666999999999</v>
+      </c>
+      <c r="K1650" s="1">
+        <v>1666.6666</v>
+      </c>
+      <c r="L1650" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1650" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1650" s="1"/>
+      <c r="O1650" s="1">
+        <v>4683</v>
+      </c>
+      <c r="P1650" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1651" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1651" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1651" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1651" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1651" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1651" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1651" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1651" s="1"/>
+      <c r="I1651" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1651" s="1">
+        <v>0.16666666999999999</v>
+      </c>
+      <c r="K1651" s="1">
+        <v>2000</v>
+      </c>
+      <c r="L1651" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1651" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1651" s="1"/>
+      <c r="O1651" s="1">
+        <v>4684</v>
+      </c>
+      <c r="P1651" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1652" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1652" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1652" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1652" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1652" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1652" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1652" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1652" s="1"/>
+      <c r="I1652" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1652" s="1">
+        <v>2</v>
+      </c>
+      <c r="K1652" s="1">
+        <v>21000</v>
+      </c>
+      <c r="L1652" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1652" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1652" s="1"/>
+      <c r="O1652" s="1">
+        <v>4685</v>
+      </c>
+      <c r="P1652" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1653" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1653" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1653" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1653" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1653" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1653" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1653" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1653" s="1"/>
+      <c r="I1653" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1653" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="K1653" s="1">
+        <v>600</v>
+      </c>
+      <c r="L1653" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1653" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1653" s="1"/>
+      <c r="O1653" s="1">
+        <v>4686</v>
+      </c>
+      <c r="P1653" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1654" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1654" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1654" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1654" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1654" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1654" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1654" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1654" s="1"/>
+      <c r="I1654" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1654" s="1">
+        <v>0.20833333000000001</v>
+      </c>
+      <c r="K1654" s="1">
+        <v>5520.8334999999997</v>
+      </c>
+      <c r="L1654" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1654" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1654" s="1"/>
+      <c r="O1654" s="1">
+        <v>4687</v>
+      </c>
+      <c r="P1654" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1655" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1655" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1655" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1655" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1655" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1655" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1655" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1655" s="1"/>
+      <c r="I1655" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1655" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1655" s="1">
+        <v>10500</v>
+      </c>
+      <c r="L1655" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1655" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1655" s="1"/>
+      <c r="O1655" s="1">
+        <v>4688</v>
+      </c>
+      <c r="P1655" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1656" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1656" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1656" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1656" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1656" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1656" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1656" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1656" s="1"/>
+      <c r="I1656" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1656" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="K1656" s="1">
+        <v>600</v>
+      </c>
+      <c r="L1656" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1656" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1656" s="1"/>
+      <c r="O1656" s="1">
+        <v>4689</v>
+      </c>
+      <c r="P1656" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1657" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1657" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1657" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1657" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1657" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1657" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1657" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1657" s="1"/>
+      <c r="I1657" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1657" s="1">
+        <v>4.1666667999999997E-2</v>
+      </c>
+      <c r="K1657" s="1">
+        <v>1104.1666</v>
+      </c>
+      <c r="L1657" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1657" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1657" s="1"/>
+      <c r="O1657" s="1">
+        <v>4690</v>
+      </c>
+      <c r="P1657" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1658" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1658" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1658" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1658" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1658" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1658" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1658" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1658" s="1"/>
+      <c r="I1658" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1658" s="1">
+        <v>5</v>
+      </c>
+      <c r="K1658" s="1">
+        <v>52500</v>
+      </c>
+      <c r="L1658" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1658" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1658" s="1"/>
+      <c r="O1658" s="1">
+        <v>4691</v>
+      </c>
+      <c r="P1658" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1659" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1659" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1659" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1659" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1659" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1659" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1659" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1659" s="1"/>
+      <c r="I1659" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1659" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1659" s="1">
+        <v>11500</v>
+      </c>
+      <c r="L1659" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1659" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1659" s="1"/>
+      <c r="O1659" s="1">
+        <v>4692</v>
+      </c>
+      <c r="P1659" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1660" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1660" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1660" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1660" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1660" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1660" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1660" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1660" s="1"/>
+      <c r="I1660" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1660" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1660" s="1">
+        <v>11500</v>
+      </c>
+      <c r="L1660" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1660" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1660" s="1"/>
+      <c r="O1660" s="1">
+        <v>4693</v>
+      </c>
+      <c r="P1660" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1661" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1661" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1661" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1661" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1661" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1661" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1661" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H1661" s="1"/>
+      <c r="I1661" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1661" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1661" s="1">
+        <v>11500</v>
+      </c>
+      <c r="L1661" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1661" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1661" s="1"/>
+      <c r="O1661" s="1">
+        <v>4694</v>
+      </c>
+      <c r="P1661" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1662" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1662" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1662" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1662" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1662" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1662" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1662" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H1662" s="1"/>
+      <c r="I1662" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1662" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="K1662" s="1">
+        <v>14375</v>
+      </c>
+      <c r="L1662" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1662" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1662" s="1"/>
+      <c r="O1662" s="1">
+        <v>4695</v>
+      </c>
+      <c r="P1662" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1663" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B1663" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1663" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1663" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1663" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1663" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1663" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1663" s="1"/>
+      <c r="I1663" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1663" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="K1663" s="1">
+        <v>7200</v>
+      </c>
+      <c r="L1663" s="1">
+        <v>0</v>
+      </c>
+      <c r="M1663" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1663" s="1"/>
+      <c r="O1663" s="1">
+        <v>4696</v>
+      </c>
+      <c r="P1663" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Donnees_Mensuelle.xlsx
+++ b/Donnees_Mensuelle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FB1CF4-02AF-4DB2-A6AD-6677A3579136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB14F28-51EE-476A-8030-D5E2A53F54CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6874,7 +6874,7 @@
         <v>31111.111000000001</v>
       </c>
       <c r="L116" s="1">
-        <v>2000</v>
+        <v>55000</v>
       </c>
       <c r="M116" s="1">
         <v>0</v>

--- a/Donnees_Mensuelle.xlsx
+++ b/Donnees_Mensuelle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB14F28-51EE-476A-8030-D5E2A53F54CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626F2C8A-6796-44E9-A15F-9F42BDF5E7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -762,6 +762,7 @@
         <name val="TIMES"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -779,7 +780,6 @@
         <name val="TIMES"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -812,25 +812,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}" name="Tableau1" displayName="Tableau1" ref="A1:Q390" totalsRowShown="0" headerRowDxfId="18" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}" name="Tableau1" displayName="Tableau1" ref="A1:Q390" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="A1:Q390" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{713E4B58-7C9F-4B80-8C6C-D9C3181B21C1}" name="Date" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{0868AEE8-A7A6-4928-8DDB-60543BB07F07}" name="Telephone_Team_Leader" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{7DDBD232-39E0-4049-85D8-CBC33FD0C3E4}" name="tata" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{C0EDCB67-A631-48D7-8CFE-26AD231B8363}" name="team_leader" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{9550684E-288A-4106-BD9A-B84CD9E390E4}" name="Operation" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{6FA5D6E7-C628-4BE0-85EB-4901587B0CBC}" name="zone" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{D1C4565F-7390-4813-9672-F2524F9FE1BB}" name="Prenom_Nom_Promoteur" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{8976EFAB-6B69-4492-9360-C49C99918CCE}" name="Precisez" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{452BC7EF-2861-4BF0-BF60-AD2D7F0945E6}" name="Produit" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{241794E5-DDEE-48AD-97C9-8279B969CD67}" name="Quantites_Cartons" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{382E59E3-C036-4213-96E0-71DAA9420A6F}" name="Montant" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{29710B84-EB9A-46FA-8DD5-BA58C0E7079D}" name="Transport" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{F254323B-32D4-4084-9BC4-7EDCB52A5D46}" name="Stationnement" dataDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{CDF347EC-10E0-4E54-A1F1-3CBB977329B7}" name="Commentaire" dataDxfId="4"/>
-    <tableColumn id="15" xr3:uid="{C2E2A4CA-D1AF-400A-A9B9-17392C634295}" name="ID_Produit" dataDxfId="3"/>
-    <tableColumn id="16" xr3:uid="{A1DAFBDD-815C-431A-BECB-4EDEA9572E1B}" name="Numero_semaine" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{713E4B58-7C9F-4B80-8C6C-D9C3181B21C1}" name="Date" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{0868AEE8-A7A6-4928-8DDB-60543BB07F07}" name="Telephone_Team_Leader" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{7DDBD232-39E0-4049-85D8-CBC33FD0C3E4}" name="tata" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{C0EDCB67-A631-48D7-8CFE-26AD231B8363}" name="team_leader" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{9550684E-288A-4106-BD9A-B84CD9E390E4}" name="Operation" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{6FA5D6E7-C628-4BE0-85EB-4901587B0CBC}" name="zone" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{D1C4565F-7390-4813-9672-F2524F9FE1BB}" name="Prenom_Nom_Promoteur" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{8976EFAB-6B69-4492-9360-C49C99918CCE}" name="Precisez" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{452BC7EF-2861-4BF0-BF60-AD2D7F0945E6}" name="Produit" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{241794E5-DDEE-48AD-97C9-8279B969CD67}" name="Quantites_Cartons" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{382E59E3-C036-4213-96E0-71DAA9420A6F}" name="Montant" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{29710B84-EB9A-46FA-8DD5-BA58C0E7079D}" name="Transport" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{F254323B-32D4-4084-9BC4-7EDCB52A5D46}" name="Stationnement" dataDxfId="4"/>
+    <tableColumn id="14" xr3:uid="{CDF347EC-10E0-4E54-A1F1-3CBB977329B7}" name="Commentaire" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{C2E2A4CA-D1AF-400A-A9B9-17392C634295}" name="ID_Produit" dataDxfId="2"/>
+    <tableColumn id="16" xr3:uid="{A1DAFBDD-815C-431A-BECB-4EDEA9572E1B}" name="Numero_semaine" dataDxfId="1"/>
     <tableColumn id="17" xr3:uid="{407DA9A2-3FAC-46B9-9644-FAE8D70A10A5}" name="Equipe" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6402,7 +6402,7 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A107" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B107" s="1">
         <v>0</v>

--- a/Donnees_Mensuelle.xlsx
+++ b/Donnees_Mensuelle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A028F6DB-7DAA-4288-96D7-E945FF09C173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE840FAA-E70A-44F9-BA74-2576880936FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6676" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6668" uniqueCount="151">
   <si>
     <t>Date</t>
   </si>
@@ -875,8 +875,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}" name="Tableau1" displayName="Tableau1" ref="A1:Q832" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:Q832" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}" name="Tableau1" displayName="Tableau1" ref="A1:Q831" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+  <autoFilter ref="A1:Q831" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{713E4B58-7C9F-4B80-8C6C-D9C3181B21C1}" name="Date" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{0868AEE8-A7A6-4928-8DDB-60543BB07F07}" name="Telephone_Team_Leader" dataDxfId="15"/>
@@ -1217,7 +1217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q832"/>
+  <dimension ref="A1:Q831"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.3984375" customWidth="1"/>
@@ -25859,45 +25859,45 @@
         <v>0</v>
       </c>
       <c r="C503" s="1" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="D503" s="1" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="E503" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F503" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G503" s="1" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="H503" s="1"/>
       <c r="I503" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J503" s="1">
-        <v>0.16666666999999999</v>
+        <v>1</v>
       </c>
       <c r="K503" s="1">
-        <v>5583.3334999999997</v>
+        <v>26000</v>
       </c>
       <c r="L503" s="1">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="M503" s="1">
         <v>0</v>
       </c>
       <c r="N503" s="1"/>
       <c r="O503" s="1">
-        <v>1295</v>
+        <v>1175</v>
       </c>
       <c r="P503" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q503" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="504" spans="1:17" x14ac:dyDescent="0.45">
@@ -25920,27 +25920,27 @@
         <v>143</v>
       </c>
       <c r="G504" s="1" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="H504" s="1"/>
       <c r="I504" s="1" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="J504" s="1">
         <v>1</v>
       </c>
       <c r="K504" s="1">
-        <v>26000</v>
+        <v>11250</v>
       </c>
       <c r="L504" s="1">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="M504" s="1">
         <v>0</v>
       </c>
       <c r="N504" s="1"/>
       <c r="O504" s="1">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="P504" s="1" t="s">
         <v>131</v>
@@ -25969,17 +25969,17 @@
         <v>143</v>
       </c>
       <c r="G505" s="1" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="H505" s="1"/>
       <c r="I505" s="1" t="s">
         <v>116</v>
       </c>
       <c r="J505" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K505" s="1">
-        <v>11250</v>
+        <v>5625</v>
       </c>
       <c r="L505" s="1">
         <v>0</v>
@@ -25989,7 +25989,7 @@
       </c>
       <c r="N505" s="1"/>
       <c r="O505" s="1">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="P505" s="1" t="s">
         <v>131</v>
@@ -26018,17 +26018,17 @@
         <v>143</v>
       </c>
       <c r="G506" s="1" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="H506" s="1"/>
       <c r="I506" s="1" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="J506" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K506" s="1">
-        <v>5625</v>
+        <v>0</v>
       </c>
       <c r="L506" s="1">
         <v>0</v>
@@ -26038,13 +26038,13 @@
       </c>
       <c r="N506" s="1"/>
       <c r="O506" s="1">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="P506" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q506" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="507" spans="1:17" x14ac:dyDescent="0.45">
@@ -26067,7 +26067,7 @@
         <v>143</v>
       </c>
       <c r="G507" s="1" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="H507" s="1"/>
       <c r="I507" s="1" t="s">
@@ -26087,7 +26087,7 @@
       </c>
       <c r="N507" s="1"/>
       <c r="O507" s="1">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="P507" s="1" t="s">
         <v>131</v>
@@ -26116,17 +26116,17 @@
         <v>143</v>
       </c>
       <c r="G508" s="1" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="H508" s="1"/>
       <c r="I508" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J508" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K508" s="1">
-        <v>0</v>
+        <v>6250</v>
       </c>
       <c r="L508" s="1">
         <v>0</v>
@@ -26136,13 +26136,13 @@
       </c>
       <c r="N508" s="1"/>
       <c r="O508" s="1">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="P508" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q508" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="509" spans="1:17" x14ac:dyDescent="0.45">
@@ -26165,7 +26165,7 @@
         <v>143</v>
       </c>
       <c r="G509" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H509" s="1"/>
       <c r="I509" s="1" t="s">
@@ -26185,7 +26185,7 @@
       </c>
       <c r="N509" s="1"/>
       <c r="O509" s="1">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="P509" s="1" t="s">
         <v>131</v>
@@ -26214,17 +26214,17 @@
         <v>143</v>
       </c>
       <c r="G510" s="1" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="H510" s="1"/>
       <c r="I510" s="1" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="J510" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K510" s="1">
-        <v>6250</v>
+        <v>0</v>
       </c>
       <c r="L510" s="1">
         <v>0</v>
@@ -26234,13 +26234,13 @@
       </c>
       <c r="N510" s="1"/>
       <c r="O510" s="1">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="P510" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q510" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="511" spans="1:17" x14ac:dyDescent="0.45">
@@ -26263,17 +26263,17 @@
         <v>143</v>
       </c>
       <c r="G511" s="1" t="s">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="H511" s="1"/>
       <c r="I511" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J511" s="1">
-        <v>0</v>
+        <v>0.16666666999999999</v>
       </c>
       <c r="K511" s="1">
-        <v>0</v>
+        <v>1666.6666</v>
       </c>
       <c r="L511" s="1">
         <v>0</v>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="N511" s="1"/>
       <c r="O511" s="1">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="P511" s="1" t="s">
         <v>131</v>
@@ -26312,17 +26312,17 @@
         <v>143</v>
       </c>
       <c r="G512" s="1" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="H512" s="1"/>
       <c r="I512" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="J512" s="1">
-        <v>0.16666666999999999</v>
+        <v>2</v>
       </c>
       <c r="K512" s="1">
-        <v>1666.6666</v>
+        <v>31000</v>
       </c>
       <c r="L512" s="1">
         <v>0</v>
@@ -26332,7 +26332,7 @@
       </c>
       <c r="N512" s="1"/>
       <c r="O512" s="1">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="P512" s="1" t="s">
         <v>131</v>
@@ -26361,17 +26361,17 @@
         <v>143</v>
       </c>
       <c r="G513" s="1" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="H513" s="1"/>
       <c r="I513" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J513" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K513" s="1">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="L513" s="1">
         <v>0</v>
@@ -26381,13 +26381,13 @@
       </c>
       <c r="N513" s="1"/>
       <c r="O513" s="1">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="P513" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q513" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="514" spans="1:17" x14ac:dyDescent="0.45">
@@ -26410,7 +26410,7 @@
         <v>143</v>
       </c>
       <c r="G514" s="1" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="H514" s="1"/>
       <c r="I514" s="1" t="s">
@@ -26430,7 +26430,7 @@
       </c>
       <c r="N514" s="1"/>
       <c r="O514" s="1">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="P514" s="1" t="s">
         <v>131</v>
@@ -26459,17 +26459,17 @@
         <v>143</v>
       </c>
       <c r="G515" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H515" s="1"/>
       <c r="I515" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J515" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K515" s="1">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="L515" s="1">
         <v>0</v>
@@ -26479,7 +26479,7 @@
       </c>
       <c r="N515" s="1"/>
       <c r="O515" s="1">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="P515" s="1" t="s">
         <v>131</v>
@@ -26508,17 +26508,17 @@
         <v>143</v>
       </c>
       <c r="G516" s="1" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="H516" s="1"/>
       <c r="I516" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J516" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K516" s="1">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="L516" s="1">
         <v>0</v>
@@ -26528,7 +26528,7 @@
       </c>
       <c r="N516" s="1"/>
       <c r="O516" s="1">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="P516" s="1" t="s">
         <v>131</v>
@@ -26557,17 +26557,17 @@
         <v>143</v>
       </c>
       <c r="G517" s="1" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="H517" s="1"/>
       <c r="I517" s="1" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="J517" s="1">
-        <v>0</v>
+        <v>0.29166666000000002</v>
       </c>
       <c r="K517" s="1">
-        <v>0</v>
+        <v>3354.1667000000002</v>
       </c>
       <c r="L517" s="1">
         <v>0</v>
@@ -26577,13 +26577,13 @@
       </c>
       <c r="N517" s="1"/>
       <c r="O517" s="1">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="P517" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q517" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="518" spans="1:17" x14ac:dyDescent="0.45">
@@ -26606,17 +26606,17 @@
         <v>143</v>
       </c>
       <c r="G518" s="1" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="H518" s="1"/>
       <c r="I518" s="1" t="s">
         <v>80</v>
       </c>
       <c r="J518" s="1">
-        <v>0.29166666000000002</v>
+        <v>0</v>
       </c>
       <c r="K518" s="1">
-        <v>3354.1667000000002</v>
+        <v>0</v>
       </c>
       <c r="L518" s="1">
         <v>0</v>
@@ -26626,7 +26626,7 @@
       </c>
       <c r="N518" s="1"/>
       <c r="O518" s="1">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="P518" s="1" t="s">
         <v>131</v>
@@ -26655,17 +26655,17 @@
         <v>143</v>
       </c>
       <c r="G519" s="1" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="H519" s="1"/>
       <c r="I519" s="1" t="s">
         <v>80</v>
       </c>
       <c r="J519" s="1">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="K519" s="1">
-        <v>0</v>
+        <v>2875</v>
       </c>
       <c r="L519" s="1">
         <v>0</v>
@@ -26675,7 +26675,7 @@
       </c>
       <c r="N519" s="1"/>
       <c r="O519" s="1">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="P519" s="1" t="s">
         <v>131</v>
@@ -26701,20 +26701,20 @@
         <v>18</v>
       </c>
       <c r="F520" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G520" s="1" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H520" s="1"/>
       <c r="I520" s="1" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="J520" s="1">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="K520" s="1">
-        <v>2875</v>
+        <v>26000</v>
       </c>
       <c r="L520" s="1">
         <v>0</v>
@@ -26724,13 +26724,13 @@
       </c>
       <c r="N520" s="1"/>
       <c r="O520" s="1">
-        <v>1191</v>
+        <v>1298</v>
       </c>
       <c r="P520" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q520" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="521" spans="1:17" x14ac:dyDescent="0.45">
@@ -26757,13 +26757,13 @@
       </c>
       <c r="H521" s="1"/>
       <c r="I521" s="1" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="J521" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K521" s="1">
-        <v>26000</v>
+        <v>22500</v>
       </c>
       <c r="L521" s="1">
         <v>0</v>
@@ -26773,7 +26773,7 @@
       </c>
       <c r="N521" s="1"/>
       <c r="O521" s="1">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="P521" s="1" t="s">
         <v>131</v>
@@ -26802,17 +26802,17 @@
         <v>141</v>
       </c>
       <c r="G522" s="1" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="H522" s="1"/>
       <c r="I522" s="1" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="J522" s="1">
-        <v>2</v>
+        <v>0.77777779999999996</v>
       </c>
       <c r="K522" s="1">
-        <v>22500</v>
+        <v>20222.223000000002</v>
       </c>
       <c r="L522" s="1">
         <v>0</v>
@@ -26822,7 +26822,7 @@
       </c>
       <c r="N522" s="1"/>
       <c r="O522" s="1">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="P522" s="1" t="s">
         <v>131</v>
@@ -26851,17 +26851,17 @@
         <v>141</v>
       </c>
       <c r="G523" s="1" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="H523" s="1"/>
       <c r="I523" s="1" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="J523" s="1">
-        <v>0.77777779999999996</v>
+        <v>1.5</v>
       </c>
       <c r="K523" s="1">
-        <v>20222.223000000002</v>
+        <v>16875</v>
       </c>
       <c r="L523" s="1">
         <v>0</v>
@@ -26871,7 +26871,7 @@
       </c>
       <c r="N523" s="1"/>
       <c r="O523" s="1">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="P523" s="1" t="s">
         <v>131</v>
@@ -26904,13 +26904,13 @@
       </c>
       <c r="H524" s="1"/>
       <c r="I524" s="1" t="s">
-        <v>116</v>
+        <v>41</v>
       </c>
       <c r="J524" s="1">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K524" s="1">
-        <v>16875</v>
+        <v>19500</v>
       </c>
       <c r="L524" s="1">
         <v>0</v>
@@ -26920,7 +26920,7 @@
       </c>
       <c r="N524" s="1"/>
       <c r="O524" s="1">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="P524" s="1" t="s">
         <v>131</v>
@@ -26949,17 +26949,17 @@
         <v>141</v>
       </c>
       <c r="G525" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H525" s="1"/>
       <c r="I525" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J525" s="1">
-        <v>1</v>
+        <v>0.11111111</v>
       </c>
       <c r="K525" s="1">
-        <v>19500</v>
+        <v>2888.8890000000001</v>
       </c>
       <c r="L525" s="1">
         <v>0</v>
@@ -26969,7 +26969,7 @@
       </c>
       <c r="N525" s="1"/>
       <c r="O525" s="1">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="P525" s="1" t="s">
         <v>131</v>
@@ -26998,17 +26998,17 @@
         <v>141</v>
       </c>
       <c r="G526" s="1" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="H526" s="1"/>
       <c r="I526" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J526" s="1">
-        <v>0.11111111</v>
+        <v>2</v>
       </c>
       <c r="K526" s="1">
-        <v>2888.8890000000001</v>
+        <v>56000</v>
       </c>
       <c r="L526" s="1">
         <v>0</v>
@@ -27018,13 +27018,13 @@
       </c>
       <c r="N526" s="1"/>
       <c r="O526" s="1">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="P526" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q526" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="527" spans="1:17" x14ac:dyDescent="0.45">
@@ -27047,17 +27047,17 @@
         <v>141</v>
       </c>
       <c r="G527" s="1" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="H527" s="1"/>
       <c r="I527" s="1" t="s">
         <v>42</v>
       </c>
       <c r="J527" s="1">
-        <v>2</v>
+        <v>4.5555553</v>
       </c>
       <c r="K527" s="1">
-        <v>56000</v>
+        <v>127555.55499999999</v>
       </c>
       <c r="L527" s="1">
         <v>0</v>
@@ -27067,7 +27067,7 @@
       </c>
       <c r="N527" s="1"/>
       <c r="O527" s="1">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="P527" s="1" t="s">
         <v>131</v>
@@ -27100,13 +27100,13 @@
       </c>
       <c r="H528" s="1"/>
       <c r="I528" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J528" s="1">
-        <v>4.5555553</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K528" s="1">
-        <v>127555.55499999999</v>
+        <v>1395.8334</v>
       </c>
       <c r="L528" s="1">
         <v>0</v>
@@ -27116,7 +27116,7 @@
       </c>
       <c r="N528" s="1"/>
       <c r="O528" s="1">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="P528" s="1" t="s">
         <v>131</v>
@@ -27145,17 +27145,17 @@
         <v>141</v>
       </c>
       <c r="G529" s="1" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="H529" s="1"/>
       <c r="I529" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J529" s="1">
-        <v>4.1666667999999997E-2</v>
+        <v>0.5</v>
       </c>
       <c r="K529" s="1">
-        <v>1395.8334</v>
+        <v>6250</v>
       </c>
       <c r="L529" s="1">
         <v>0</v>
@@ -27165,13 +27165,13 @@
       </c>
       <c r="N529" s="1"/>
       <c r="O529" s="1">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="P529" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q529" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="530" spans="1:17" x14ac:dyDescent="0.45">
@@ -27194,17 +27194,17 @@
         <v>141</v>
       </c>
       <c r="G530" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H530" s="1"/>
       <c r="I530" s="1" t="s">
         <v>39</v>
       </c>
       <c r="J530" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K530" s="1">
-        <v>6250</v>
+        <v>12500</v>
       </c>
       <c r="L530" s="1">
         <v>0</v>
@@ -27214,7 +27214,7 @@
       </c>
       <c r="N530" s="1"/>
       <c r="O530" s="1">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="P530" s="1" t="s">
         <v>131</v>
@@ -27243,17 +27243,17 @@
         <v>141</v>
       </c>
       <c r="G531" s="1" t="s">
-        <v>67</v>
+        <v>138</v>
       </c>
       <c r="H531" s="1"/>
       <c r="I531" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="J531" s="1">
         <v>1</v>
       </c>
       <c r="K531" s="1">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="L531" s="1">
         <v>0</v>
@@ -27263,13 +27263,13 @@
       </c>
       <c r="N531" s="1"/>
       <c r="O531" s="1">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="P531" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q531" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="532" spans="1:17" x14ac:dyDescent="0.45">
@@ -27292,17 +27292,17 @@
         <v>141</v>
       </c>
       <c r="G532" s="1" t="s">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="H532" s="1"/>
       <c r="I532" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J532" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K532" s="1">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="L532" s="1">
         <v>0</v>
@@ -27312,7 +27312,7 @@
       </c>
       <c r="N532" s="1"/>
       <c r="O532" s="1">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="P532" s="1" t="s">
         <v>131</v>
@@ -27345,13 +27345,13 @@
       </c>
       <c r="H533" s="1"/>
       <c r="I533" s="1" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="J533" s="1">
         <v>0.5</v>
       </c>
       <c r="K533" s="1">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="L533" s="1">
         <v>0</v>
@@ -27361,7 +27361,7 @@
       </c>
       <c r="N533" s="1"/>
       <c r="O533" s="1">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="P533" s="1" t="s">
         <v>131</v>
@@ -27390,17 +27390,17 @@
         <v>141</v>
       </c>
       <c r="G534" s="1" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="H534" s="1"/>
       <c r="I534" s="1" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="J534" s="1">
-        <v>0.5</v>
+        <v>0.66666669999999995</v>
       </c>
       <c r="K534" s="1">
-        <v>6000</v>
+        <v>6666.6665000000003</v>
       </c>
       <c r="L534" s="1">
         <v>0</v>
@@ -27410,7 +27410,7 @@
       </c>
       <c r="N534" s="1"/>
       <c r="O534" s="1">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="P534" s="1" t="s">
         <v>131</v>
@@ -27439,17 +27439,17 @@
         <v>141</v>
       </c>
       <c r="G535" s="1" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="H535" s="1"/>
       <c r="I535" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J535" s="1">
-        <v>0.66666669999999995</v>
+        <v>0.5</v>
       </c>
       <c r="K535" s="1">
-        <v>6666.6665000000003</v>
+        <v>5250</v>
       </c>
       <c r="L535" s="1">
         <v>0</v>
@@ -27459,13 +27459,13 @@
       </c>
       <c r="N535" s="1"/>
       <c r="O535" s="1">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="P535" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q535" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="536" spans="1:17" x14ac:dyDescent="0.45">
@@ -27488,7 +27488,7 @@
         <v>141</v>
       </c>
       <c r="G536" s="1" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="H536" s="1"/>
       <c r="I536" s="1" t="s">
@@ -27508,7 +27508,7 @@
       </c>
       <c r="N536" s="1"/>
       <c r="O536" s="1">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="P536" s="1" t="s">
         <v>131</v>
@@ -27537,17 +27537,17 @@
         <v>141</v>
       </c>
       <c r="G537" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H537" s="1"/>
       <c r="I537" s="1" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="J537" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K537" s="1">
-        <v>5250</v>
+        <v>26500</v>
       </c>
       <c r="L537" s="1">
         <v>0</v>
@@ -27557,7 +27557,7 @@
       </c>
       <c r="N537" s="1"/>
       <c r="O537" s="1">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="P537" s="1" t="s">
         <v>131</v>
@@ -27586,17 +27586,17 @@
         <v>141</v>
       </c>
       <c r="G538" s="1" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="H538" s="1"/>
       <c r="I538" s="1" t="s">
         <v>82</v>
       </c>
       <c r="J538" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K538" s="1">
-        <v>26500</v>
+        <v>13250</v>
       </c>
       <c r="L538" s="1">
         <v>0</v>
@@ -27606,7 +27606,7 @@
       </c>
       <c r="N538" s="1"/>
       <c r="O538" s="1">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="P538" s="1" t="s">
         <v>131</v>
@@ -27635,17 +27635,17 @@
         <v>141</v>
       </c>
       <c r="G539" s="1" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="H539" s="1"/>
       <c r="I539" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J539" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K539" s="1">
-        <v>13250</v>
+        <v>0</v>
       </c>
       <c r="L539" s="1">
         <v>0</v>
@@ -27655,13 +27655,13 @@
       </c>
       <c r="N539" s="1"/>
       <c r="O539" s="1">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="P539" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q539" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="540" spans="1:17" x14ac:dyDescent="0.45">
@@ -27684,7 +27684,7 @@
         <v>141</v>
       </c>
       <c r="G540" s="1" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="H540" s="1"/>
       <c r="I540" s="1" t="s">
@@ -27704,7 +27704,7 @@
       </c>
       <c r="N540" s="1"/>
       <c r="O540" s="1">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="P540" s="1" t="s">
         <v>131</v>
@@ -27733,7 +27733,7 @@
         <v>141</v>
       </c>
       <c r="G541" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H541" s="1"/>
       <c r="I541" s="1" t="s">
@@ -27753,7 +27753,7 @@
       </c>
       <c r="N541" s="1"/>
       <c r="O541" s="1">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="P541" s="1" t="s">
         <v>131</v>
@@ -27782,17 +27782,17 @@
         <v>141</v>
       </c>
       <c r="G542" s="1" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="H542" s="1"/>
       <c r="I542" s="1" t="s">
         <v>80</v>
       </c>
       <c r="J542" s="1">
-        <v>0</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K542" s="1">
-        <v>0</v>
+        <v>479.16665999999998</v>
       </c>
       <c r="L542" s="1">
         <v>0</v>
@@ -27802,7 +27802,7 @@
       </c>
       <c r="N542" s="1"/>
       <c r="O542" s="1">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="P542" s="1" t="s">
         <v>131</v>
@@ -27831,17 +27831,17 @@
         <v>141</v>
       </c>
       <c r="G543" s="1" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="H543" s="1"/>
       <c r="I543" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J543" s="1">
-        <v>4.1666667999999997E-2</v>
+        <v>1</v>
       </c>
       <c r="K543" s="1">
-        <v>479.16665999999998</v>
+        <v>11000</v>
       </c>
       <c r="L543" s="1">
         <v>0</v>
@@ -27851,46 +27851,46 @@
       </c>
       <c r="N543" s="1"/>
       <c r="O543" s="1">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="P543" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q543" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="544" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A544" s="2">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B544" s="1">
         <v>0</v>
       </c>
       <c r="C544" s="1" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="D544" s="1" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="E544" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F544" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G544" s="1" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="H544" s="1"/>
       <c r="I544" s="1" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="J544" s="1">
         <v>1</v>
       </c>
       <c r="K544" s="1">
-        <v>11000</v>
+        <v>9000</v>
       </c>
       <c r="L544" s="1">
         <v>0</v>
@@ -27900,13 +27900,13 @@
       </c>
       <c r="N544" s="1"/>
       <c r="O544" s="1">
-        <v>1321</v>
+        <v>1106</v>
       </c>
       <c r="P544" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q544" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="545" spans="1:17" x14ac:dyDescent="0.45">
@@ -27929,17 +27929,17 @@
         <v>143</v>
       </c>
       <c r="G545" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H545" s="1"/>
       <c r="I545" s="1" t="s">
         <v>26</v>
       </c>
       <c r="J545" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K545" s="1">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="L545" s="1">
         <v>0</v>
@@ -27949,7 +27949,7 @@
       </c>
       <c r="N545" s="1"/>
       <c r="O545" s="1">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="P545" s="1" t="s">
         <v>131</v>
@@ -27978,7 +27978,7 @@
         <v>143</v>
       </c>
       <c r="G546" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H546" s="1"/>
       <c r="I546" s="1" t="s">
@@ -27998,7 +27998,7 @@
       </c>
       <c r="N546" s="1"/>
       <c r="O546" s="1">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="P546" s="1" t="s">
         <v>131</v>
@@ -28027,7 +28027,7 @@
         <v>143</v>
       </c>
       <c r="G547" s="1" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="H547" s="1"/>
       <c r="I547" s="1" t="s">
@@ -28047,7 +28047,7 @@
       </c>
       <c r="N547" s="1"/>
       <c r="O547" s="1">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="P547" s="1" t="s">
         <v>131</v>
@@ -28076,17 +28076,17 @@
         <v>143</v>
       </c>
       <c r="G548" s="1" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H548" s="1"/>
       <c r="I548" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J548" s="1">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="K548" s="1">
-        <v>0</v>
+        <v>1875</v>
       </c>
       <c r="L548" s="1">
         <v>0</v>
@@ -28096,7 +28096,7 @@
       </c>
       <c r="N548" s="1"/>
       <c r="O548" s="1">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="P548" s="1" t="s">
         <v>131</v>
@@ -28125,17 +28125,17 @@
         <v>143</v>
       </c>
       <c r="G549" s="1" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="H549" s="1"/>
       <c r="I549" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J549" s="1">
-        <v>0.125</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K549" s="1">
-        <v>1875</v>
+        <v>750</v>
       </c>
       <c r="L549" s="1">
         <v>0</v>
@@ -28145,7 +28145,7 @@
       </c>
       <c r="N549" s="1"/>
       <c r="O549" s="1">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="P549" s="1" t="s">
         <v>131</v>
@@ -28174,17 +28174,17 @@
         <v>143</v>
       </c>
       <c r="G550" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H550" s="1"/>
       <c r="I550" s="1" t="s">
         <v>26</v>
       </c>
       <c r="J550" s="1">
-        <v>8.3333335999999994E-2</v>
+        <v>0</v>
       </c>
       <c r="K550" s="1">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="L550" s="1">
         <v>0</v>
@@ -28194,7 +28194,7 @@
       </c>
       <c r="N550" s="1"/>
       <c r="O550" s="1">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="P550" s="1" t="s">
         <v>131</v>
@@ -28223,17 +28223,17 @@
         <v>143</v>
       </c>
       <c r="G551" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H551" s="1"/>
       <c r="I551" s="1" t="s">
         <v>26</v>
       </c>
       <c r="J551" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K551" s="1">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="L551" s="1">
         <v>0</v>
@@ -28243,7 +28243,7 @@
       </c>
       <c r="N551" s="1"/>
       <c r="O551" s="1">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="P551" s="1" t="s">
         <v>131</v>
@@ -28272,17 +28272,17 @@
         <v>143</v>
       </c>
       <c r="G552" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H552" s="1"/>
       <c r="I552" s="1" t="s">
         <v>26</v>
       </c>
       <c r="J552" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K552" s="1">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="L552" s="1">
         <v>0</v>
@@ -28292,7 +28292,7 @@
       </c>
       <c r="N552" s="1"/>
       <c r="O552" s="1">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="P552" s="1" t="s">
         <v>131</v>
@@ -28321,17 +28321,17 @@
         <v>143</v>
       </c>
       <c r="G553" s="1" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="H553" s="1"/>
       <c r="I553" s="1" t="s">
         <v>26</v>
       </c>
       <c r="J553" s="1">
-        <v>0</v>
+        <v>0.33333333999999998</v>
       </c>
       <c r="K553" s="1">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="L553" s="1">
         <v>0</v>
@@ -28341,7 +28341,7 @@
       </c>
       <c r="N553" s="1"/>
       <c r="O553" s="1">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="P553" s="1" t="s">
         <v>131</v>
@@ -28374,13 +28374,13 @@
       </c>
       <c r="H554" s="1"/>
       <c r="I554" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J554" s="1">
-        <v>0.33333333999999998</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K554" s="1">
-        <v>3000</v>
+        <v>750</v>
       </c>
       <c r="L554" s="1">
         <v>0</v>
@@ -28390,7 +28390,7 @@
       </c>
       <c r="N554" s="1"/>
       <c r="O554" s="1">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="P554" s="1" t="s">
         <v>131</v>
@@ -28419,17 +28419,17 @@
         <v>143</v>
       </c>
       <c r="G555" s="1" t="s">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="H555" s="1"/>
       <c r="I555" s="1" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="J555" s="1">
-        <v>8.3333335999999994E-2</v>
+        <v>0</v>
       </c>
       <c r="K555" s="1">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="L555" s="1">
         <v>0</v>
@@ -28439,13 +28439,13 @@
       </c>
       <c r="N555" s="1"/>
       <c r="O555" s="1">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="P555" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q555" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="556" spans="1:17" x14ac:dyDescent="0.45">
@@ -28468,7 +28468,7 @@
         <v>143</v>
       </c>
       <c r="G556" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H556" s="1"/>
       <c r="I556" s="1" t="s">
@@ -28488,7 +28488,7 @@
       </c>
       <c r="N556" s="1"/>
       <c r="O556" s="1">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="P556" s="1" t="s">
         <v>131</v>
@@ -28517,7 +28517,7 @@
         <v>143</v>
       </c>
       <c r="G557" s="1" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="H557" s="1"/>
       <c r="I557" s="1" t="s">
@@ -28537,7 +28537,7 @@
       </c>
       <c r="N557" s="1"/>
       <c r="O557" s="1">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="P557" s="1" t="s">
         <v>131</v>
@@ -28566,7 +28566,7 @@
         <v>143</v>
       </c>
       <c r="G558" s="1" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="H558" s="1"/>
       <c r="I558" s="1" t="s">
@@ -28586,7 +28586,7 @@
       </c>
       <c r="N558" s="1"/>
       <c r="O558" s="1">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="P558" s="1" t="s">
         <v>131</v>
@@ -28615,7 +28615,7 @@
         <v>143</v>
       </c>
       <c r="G559" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H559" s="1"/>
       <c r="I559" s="1" t="s">
@@ -28635,7 +28635,7 @@
       </c>
       <c r="N559" s="1"/>
       <c r="O559" s="1">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="P559" s="1" t="s">
         <v>131</v>
@@ -28664,7 +28664,7 @@
         <v>143</v>
       </c>
       <c r="G560" s="1" t="s">
-        <v>28</v>
+        <v>132</v>
       </c>
       <c r="H560" s="1"/>
       <c r="I560" s="1" t="s">
@@ -28684,7 +28684,7 @@
       </c>
       <c r="N560" s="1"/>
       <c r="O560" s="1">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="P560" s="1" t="s">
         <v>131</v>
@@ -28713,7 +28713,7 @@
         <v>143</v>
       </c>
       <c r="G561" s="1" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="H561" s="1"/>
       <c r="I561" s="1" t="s">
@@ -28733,7 +28733,7 @@
       </c>
       <c r="N561" s="1"/>
       <c r="O561" s="1">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="P561" s="1" t="s">
         <v>131</v>
@@ -28762,7 +28762,7 @@
         <v>143</v>
       </c>
       <c r="G562" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H562" s="1"/>
       <c r="I562" s="1" t="s">
@@ -28782,7 +28782,7 @@
       </c>
       <c r="N562" s="1"/>
       <c r="O562" s="1">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="P562" s="1" t="s">
         <v>131</v>
@@ -28811,7 +28811,7 @@
         <v>143</v>
       </c>
       <c r="G563" s="1" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="H563" s="1"/>
       <c r="I563" s="1" t="s">
@@ -28831,7 +28831,7 @@
       </c>
       <c r="N563" s="1"/>
       <c r="O563" s="1">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="P563" s="1" t="s">
         <v>131</v>
@@ -28860,7 +28860,7 @@
         <v>143</v>
       </c>
       <c r="G564" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H564" s="1"/>
       <c r="I564" s="1" t="s">
@@ -28880,7 +28880,7 @@
       </c>
       <c r="N564" s="1"/>
       <c r="O564" s="1">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="P564" s="1" t="s">
         <v>131</v>
@@ -28897,29 +28897,29 @@
         <v>0</v>
       </c>
       <c r="C565" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D565" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E565" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F565" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G565" s="1" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="H565" s="1"/>
       <c r="I565" s="1" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="J565" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K565" s="1">
-        <v>0</v>
+        <v>19500</v>
       </c>
       <c r="L565" s="1">
         <v>0</v>
@@ -28929,13 +28929,13 @@
       </c>
       <c r="N565" s="1"/>
       <c r="O565" s="1">
-        <v>1126</v>
+        <v>1155</v>
       </c>
       <c r="P565" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q565" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="566" spans="1:17" x14ac:dyDescent="0.45">
@@ -28958,17 +28958,17 @@
         <v>144</v>
       </c>
       <c r="G566" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H566" s="1"/>
       <c r="I566" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J566" s="1">
-        <v>1</v>
+        <v>0.11111111</v>
       </c>
       <c r="K566" s="1">
-        <v>19500</v>
+        <v>2888.8890000000001</v>
       </c>
       <c r="L566" s="1">
         <v>0</v>
@@ -28978,7 +28978,7 @@
       </c>
       <c r="N566" s="1"/>
       <c r="O566" s="1">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="P566" s="1" t="s">
         <v>131</v>
@@ -29007,17 +29007,17 @@
         <v>144</v>
       </c>
       <c r="G567" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="H567" s="1"/>
       <c r="I567" s="1" t="s">
         <v>43</v>
       </c>
       <c r="J567" s="1">
-        <v>0.11111111</v>
+        <v>0.22222222</v>
       </c>
       <c r="K567" s="1">
-        <v>2888.8890000000001</v>
+        <v>5777.7780000000002</v>
       </c>
       <c r="L567" s="1">
         <v>0</v>
@@ -29027,7 +29027,7 @@
       </c>
       <c r="N567" s="1"/>
       <c r="O567" s="1">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="P567" s="1" t="s">
         <v>131</v>
@@ -29056,17 +29056,17 @@
         <v>144</v>
       </c>
       <c r="G568" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="H568" s="1"/>
       <c r="I568" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J568" s="1">
-        <v>0.22222222</v>
+        <v>1</v>
       </c>
       <c r="K568" s="1">
-        <v>5777.7780000000002</v>
+        <v>19500</v>
       </c>
       <c r="L568" s="1">
         <v>0</v>
@@ -29076,7 +29076,7 @@
       </c>
       <c r="N568" s="1"/>
       <c r="O568" s="1">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="P568" s="1" t="s">
         <v>131</v>
@@ -29105,17 +29105,17 @@
         <v>144</v>
       </c>
       <c r="G569" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H569" s="1"/>
       <c r="I569" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J569" s="1">
-        <v>1</v>
+        <v>0.33333333999999998</v>
       </c>
       <c r="K569" s="1">
-        <v>19500</v>
+        <v>8666.6669999999995</v>
       </c>
       <c r="L569" s="1">
         <v>0</v>
@@ -29125,7 +29125,7 @@
       </c>
       <c r="N569" s="1"/>
       <c r="O569" s="1">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="P569" s="1" t="s">
         <v>131</v>
@@ -29154,17 +29154,17 @@
         <v>144</v>
       </c>
       <c r="G570" s="1" t="s">
-        <v>133</v>
+        <v>53</v>
       </c>
       <c r="H570" s="1"/>
       <c r="I570" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J570" s="1">
-        <v>0.33333333999999998</v>
+        <v>0.11111111</v>
       </c>
       <c r="K570" s="1">
-        <v>8666.6669999999995</v>
+        <v>3111.1109999999999</v>
       </c>
       <c r="L570" s="1">
         <v>0</v>
@@ -29174,13 +29174,13 @@
       </c>
       <c r="N570" s="1"/>
       <c r="O570" s="1">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="P570" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q570" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="571" spans="1:17" x14ac:dyDescent="0.45">
@@ -29207,13 +29207,13 @@
       </c>
       <c r="H571" s="1"/>
       <c r="I571" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J571" s="1">
-        <v>0.11111111</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K571" s="1">
-        <v>3111.1109999999999</v>
+        <v>2791.6667000000002</v>
       </c>
       <c r="L571" s="1">
         <v>0</v>
@@ -29223,7 +29223,7 @@
       </c>
       <c r="N571" s="1"/>
       <c r="O571" s="1">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="P571" s="1" t="s">
         <v>131</v>
@@ -29252,17 +29252,17 @@
         <v>144</v>
       </c>
       <c r="G572" s="1" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="H572" s="1"/>
       <c r="I572" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J572" s="1">
-        <v>8.3333335999999994E-2</v>
+        <v>1</v>
       </c>
       <c r="K572" s="1">
-        <v>2791.6667000000002</v>
+        <v>28000</v>
       </c>
       <c r="L572" s="1">
         <v>0</v>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="N572" s="1"/>
       <c r="O572" s="1">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="P572" s="1" t="s">
         <v>131</v>
@@ -29301,17 +29301,17 @@
         <v>144</v>
       </c>
       <c r="G573" s="1" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="H573" s="1"/>
       <c r="I573" s="1" t="s">
         <v>42</v>
       </c>
       <c r="J573" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K573" s="1">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="L573" s="1">
         <v>0</v>
@@ -29321,7 +29321,7 @@
       </c>
       <c r="N573" s="1"/>
       <c r="O573" s="1">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="P573" s="1" t="s">
         <v>131</v>
@@ -29350,17 +29350,17 @@
         <v>144</v>
       </c>
       <c r="G574" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="H574" s="1"/>
       <c r="I574" s="1" t="s">
         <v>42</v>
       </c>
       <c r="J574" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K574" s="1">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="L574" s="1">
         <v>0</v>
@@ -29370,7 +29370,7 @@
       </c>
       <c r="N574" s="1"/>
       <c r="O574" s="1">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="P574" s="1" t="s">
         <v>131</v>
@@ -29399,17 +29399,17 @@
         <v>144</v>
       </c>
       <c r="G575" s="1" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="H575" s="1"/>
       <c r="I575" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="J575" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K575" s="1">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="L575" s="1">
         <v>0</v>
@@ -29419,13 +29419,13 @@
       </c>
       <c r="N575" s="1"/>
       <c r="O575" s="1">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="P575" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q575" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="576" spans="1:17" x14ac:dyDescent="0.45">
@@ -29448,7 +29448,7 @@
         <v>144</v>
       </c>
       <c r="G576" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H576" s="1"/>
       <c r="I576" s="1" t="s">
@@ -29468,7 +29468,7 @@
       </c>
       <c r="N576" s="1"/>
       <c r="O576" s="1">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="P576" s="1" t="s">
         <v>131</v>
@@ -29497,7 +29497,7 @@
         <v>144</v>
       </c>
       <c r="G577" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H577" s="1"/>
       <c r="I577" s="1" t="s">
@@ -29517,7 +29517,7 @@
       </c>
       <c r="N577" s="1"/>
       <c r="O577" s="1">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="P577" s="1" t="s">
         <v>131</v>
@@ -29546,17 +29546,17 @@
         <v>144</v>
       </c>
       <c r="G578" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H578" s="1"/>
       <c r="I578" s="1" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="J578" s="1">
-        <v>0</v>
+        <v>1.5416666000000001</v>
       </c>
       <c r="K578" s="1">
-        <v>0</v>
+        <v>17729.166000000001</v>
       </c>
       <c r="L578" s="1">
         <v>0</v>
@@ -29566,13 +29566,13 @@
       </c>
       <c r="N578" s="1"/>
       <c r="O578" s="1">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="P578" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q578" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="579" spans="1:17" x14ac:dyDescent="0.45">
@@ -29595,17 +29595,17 @@
         <v>144</v>
       </c>
       <c r="G579" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H579" s="1"/>
       <c r="I579" s="1" t="s">
         <v>80</v>
       </c>
       <c r="J579" s="1">
-        <v>1.5416666000000001</v>
+        <v>1.25</v>
       </c>
       <c r="K579" s="1">
-        <v>17729.166000000001</v>
+        <v>14375</v>
       </c>
       <c r="L579" s="1">
         <v>0</v>
@@ -29615,7 +29615,7 @@
       </c>
       <c r="N579" s="1"/>
       <c r="O579" s="1">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="P579" s="1" t="s">
         <v>131</v>
@@ -29644,17 +29644,17 @@
         <v>144</v>
       </c>
       <c r="G580" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H580" s="1"/>
       <c r="I580" s="1" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="J580" s="1">
-        <v>1.25</v>
+        <v>0.16666666999999999</v>
       </c>
       <c r="K580" s="1">
-        <v>14375</v>
+        <v>1666.6666</v>
       </c>
       <c r="L580" s="1">
         <v>0</v>
@@ -29664,13 +29664,13 @@
       </c>
       <c r="N580" s="1"/>
       <c r="O580" s="1">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="P580" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q580" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="581" spans="1:17" x14ac:dyDescent="0.45">
@@ -29693,7 +29693,7 @@
         <v>144</v>
       </c>
       <c r="G581" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H581" s="1"/>
       <c r="I581" s="1" t="s">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="N581" s="1"/>
       <c r="O581" s="1">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="P581" s="1" t="s">
         <v>131</v>
@@ -29742,17 +29742,17 @@
         <v>144</v>
       </c>
       <c r="G582" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H582" s="1"/>
       <c r="I582" s="1" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="J582" s="1">
-        <v>0.16666666999999999</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K582" s="1">
-        <v>1666.6666</v>
+        <v>1291.6666</v>
       </c>
       <c r="L582" s="1">
         <v>0</v>
@@ -29762,13 +29762,13 @@
       </c>
       <c r="N582" s="1"/>
       <c r="O582" s="1">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="P582" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q582" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="583" spans="1:17" x14ac:dyDescent="0.45">
@@ -29795,13 +29795,13 @@
       </c>
       <c r="H583" s="1"/>
       <c r="I583" s="1" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="J583" s="1">
         <v>8.3333335999999994E-2</v>
       </c>
       <c r="K583" s="1">
-        <v>1291.6666</v>
+        <v>1041.6666</v>
       </c>
       <c r="L583" s="1">
         <v>0</v>
@@ -29811,7 +29811,7 @@
       </c>
       <c r="N583" s="1"/>
       <c r="O583" s="1">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="P583" s="1" t="s">
         <v>131</v>
@@ -29840,17 +29840,17 @@
         <v>144</v>
       </c>
       <c r="G584" s="1" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="H584" s="1"/>
       <c r="I584" s="1" t="s">
         <v>38</v>
       </c>
       <c r="J584" s="1">
-        <v>8.3333335999999994E-2</v>
+        <v>0.16666666999999999</v>
       </c>
       <c r="K584" s="1">
-        <v>1041.6666</v>
+        <v>2083.3332999999998</v>
       </c>
       <c r="L584" s="1">
         <v>0</v>
@@ -29860,7 +29860,7 @@
       </c>
       <c r="N584" s="1"/>
       <c r="O584" s="1">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="P584" s="1" t="s">
         <v>131</v>
@@ -29871,35 +29871,35 @@
     </row>
     <row r="585" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A585" s="2">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="B585" s="1">
         <v>0</v>
       </c>
       <c r="C585" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D585" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E585" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F585" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G585" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="H585" s="1"/>
       <c r="I585" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="J585" s="1">
-        <v>0.16666666999999999</v>
+        <v>1.25</v>
       </c>
       <c r="K585" s="1">
-        <v>2083.3332999999998</v>
+        <v>18750</v>
       </c>
       <c r="L585" s="1">
         <v>0</v>
@@ -29909,13 +29909,13 @@
       </c>
       <c r="N585" s="1"/>
       <c r="O585" s="1">
-        <v>1174</v>
+        <v>981</v>
       </c>
       <c r="P585" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q585" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="586" spans="1:17" x14ac:dyDescent="0.45">
@@ -29942,13 +29942,13 @@
       </c>
       <c r="H586" s="1"/>
       <c r="I586" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J586" s="1">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="K586" s="1">
-        <v>18750</v>
+        <v>4500</v>
       </c>
       <c r="L586" s="1">
         <v>0</v>
@@ -29958,7 +29958,7 @@
       </c>
       <c r="N586" s="1"/>
       <c r="O586" s="1">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="P586" s="1" t="s">
         <v>131</v>
@@ -29987,17 +29987,17 @@
         <v>145</v>
       </c>
       <c r="G587" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H587" s="1"/>
       <c r="I587" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J587" s="1">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="K587" s="1">
-        <v>4500</v>
+        <v>9375</v>
       </c>
       <c r="L587" s="1">
         <v>0</v>
@@ -30007,7 +30007,7 @@
       </c>
       <c r="N587" s="1"/>
       <c r="O587" s="1">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="P587" s="1" t="s">
         <v>131</v>
@@ -30040,13 +30040,13 @@
       </c>
       <c r="H588" s="1"/>
       <c r="I588" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J588" s="1">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="K588" s="1">
-        <v>9375</v>
+        <v>15000</v>
       </c>
       <c r="L588" s="1">
         <v>0</v>
@@ -30056,7 +30056,7 @@
       </c>
       <c r="N588" s="1"/>
       <c r="O588" s="1">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="P588" s="1" t="s">
         <v>131</v>
@@ -30089,13 +30089,13 @@
       </c>
       <c r="H589" s="1"/>
       <c r="I589" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J589" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K589" s="1">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="L589" s="1">
         <v>0</v>
@@ -30105,7 +30105,7 @@
       </c>
       <c r="N589" s="1"/>
       <c r="O589" s="1">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="P589" s="1" t="s">
         <v>131</v>
@@ -30134,17 +30134,17 @@
         <v>145</v>
       </c>
       <c r="G590" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H590" s="1"/>
       <c r="I590" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J590" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K590" s="1">
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="L590" s="1">
         <v>0</v>
@@ -30154,7 +30154,7 @@
       </c>
       <c r="N590" s="1"/>
       <c r="O590" s="1">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="P590" s="1" t="s">
         <v>131</v>
@@ -30187,13 +30187,13 @@
       </c>
       <c r="H591" s="1"/>
       <c r="I591" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J591" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K591" s="1">
-        <v>15000</v>
+        <v>4500</v>
       </c>
       <c r="L591" s="1">
         <v>0</v>
@@ -30203,7 +30203,7 @@
       </c>
       <c r="N591" s="1"/>
       <c r="O591" s="1">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="P591" s="1" t="s">
         <v>131</v>
@@ -30232,17 +30232,17 @@
         <v>145</v>
       </c>
       <c r="G592" s="1" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="H592" s="1"/>
       <c r="I592" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J592" s="1">
-        <v>0.5</v>
+        <v>2.25</v>
       </c>
       <c r="K592" s="1">
-        <v>4500</v>
+        <v>33750</v>
       </c>
       <c r="L592" s="1">
         <v>0</v>
@@ -30252,7 +30252,7 @@
       </c>
       <c r="N592" s="1"/>
       <c r="O592" s="1">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="P592" s="1" t="s">
         <v>131</v>
@@ -30285,13 +30285,13 @@
       </c>
       <c r="H593" s="1"/>
       <c r="I593" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J593" s="1">
-        <v>2.25</v>
+        <v>0.25</v>
       </c>
       <c r="K593" s="1">
-        <v>33750</v>
+        <v>2250</v>
       </c>
       <c r="L593" s="1">
         <v>0</v>
@@ -30301,7 +30301,7 @@
       </c>
       <c r="N593" s="1"/>
       <c r="O593" s="1">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="P593" s="1" t="s">
         <v>131</v>
@@ -30330,17 +30330,17 @@
         <v>145</v>
       </c>
       <c r="G594" s="1" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H594" s="1"/>
       <c r="I594" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J594" s="1">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="K594" s="1">
-        <v>2250</v>
+        <v>11250</v>
       </c>
       <c r="L594" s="1">
         <v>0</v>
@@ -30350,7 +30350,7 @@
       </c>
       <c r="N594" s="1"/>
       <c r="O594" s="1">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="P594" s="1" t="s">
         <v>131</v>
@@ -30383,13 +30383,13 @@
       </c>
       <c r="H595" s="1"/>
       <c r="I595" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J595" s="1">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="K595" s="1">
-        <v>11250</v>
+        <v>4500</v>
       </c>
       <c r="L595" s="1">
         <v>0</v>
@@ -30399,7 +30399,7 @@
       </c>
       <c r="N595" s="1"/>
       <c r="O595" s="1">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="P595" s="1" t="s">
         <v>131</v>
@@ -30428,17 +30428,17 @@
         <v>145</v>
       </c>
       <c r="G596" s="1" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="H596" s="1"/>
       <c r="I596" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J596" s="1">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K596" s="1">
-        <v>4500</v>
+        <v>3750</v>
       </c>
       <c r="L596" s="1">
         <v>0</v>
@@ -30448,7 +30448,7 @@
       </c>
       <c r="N596" s="1"/>
       <c r="O596" s="1">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="P596" s="1" t="s">
         <v>131</v>
@@ -30477,17 +30477,17 @@
         <v>145</v>
       </c>
       <c r="G597" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H597" s="1"/>
       <c r="I597" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J597" s="1">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="K597" s="1">
-        <v>3750</v>
+        <v>4500</v>
       </c>
       <c r="L597" s="1">
         <v>0</v>
@@ -30497,7 +30497,7 @@
       </c>
       <c r="N597" s="1"/>
       <c r="O597" s="1">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="P597" s="1" t="s">
         <v>131</v>
@@ -30526,17 +30526,17 @@
         <v>145</v>
       </c>
       <c r="G598" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H598" s="1"/>
       <c r="I598" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J598" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K598" s="1">
-        <v>4500</v>
+        <v>15000</v>
       </c>
       <c r="L598" s="1">
         <v>0</v>
@@ -30546,7 +30546,7 @@
       </c>
       <c r="N598" s="1"/>
       <c r="O598" s="1">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="P598" s="1" t="s">
         <v>131</v>
@@ -30579,13 +30579,13 @@
       </c>
       <c r="H599" s="1"/>
       <c r="I599" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J599" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K599" s="1">
-        <v>15000</v>
+        <v>4500</v>
       </c>
       <c r="L599" s="1">
         <v>0</v>
@@ -30595,7 +30595,7 @@
       </c>
       <c r="N599" s="1"/>
       <c r="O599" s="1">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="P599" s="1" t="s">
         <v>131</v>
@@ -30624,17 +30624,17 @@
         <v>145</v>
       </c>
       <c r="G600" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H600" s="1"/>
       <c r="I600" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J600" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K600" s="1">
-        <v>4500</v>
+        <v>15000</v>
       </c>
       <c r="L600" s="1">
         <v>0</v>
@@ -30644,7 +30644,7 @@
       </c>
       <c r="N600" s="1"/>
       <c r="O600" s="1">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="P600" s="1" t="s">
         <v>131</v>
@@ -30673,17 +30673,17 @@
         <v>145</v>
       </c>
       <c r="G601" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H601" s="1"/>
       <c r="I601" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J601" s="1">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K601" s="1">
-        <v>15000</v>
+        <v>3750</v>
       </c>
       <c r="L601" s="1">
         <v>0</v>
@@ -30693,7 +30693,7 @@
       </c>
       <c r="N601" s="1"/>
       <c r="O601" s="1">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="P601" s="1" t="s">
         <v>131</v>
@@ -30726,13 +30726,13 @@
       </c>
       <c r="H602" s="1"/>
       <c r="I602" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J602" s="1">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="K602" s="1">
-        <v>3750</v>
+        <v>4500</v>
       </c>
       <c r="L602" s="1">
         <v>0</v>
@@ -30742,7 +30742,7 @@
       </c>
       <c r="N602" s="1"/>
       <c r="O602" s="1">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="P602" s="1" t="s">
         <v>131</v>
@@ -30771,17 +30771,17 @@
         <v>145</v>
       </c>
       <c r="G603" s="1" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="H603" s="1"/>
       <c r="I603" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J603" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K603" s="1">
-        <v>4500</v>
+        <v>15000</v>
       </c>
       <c r="L603" s="1">
         <v>0</v>
@@ -30791,7 +30791,7 @@
       </c>
       <c r="N603" s="1"/>
       <c r="O603" s="1">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="P603" s="1" t="s">
         <v>131</v>
@@ -30824,13 +30824,13 @@
       </c>
       <c r="H604" s="1"/>
       <c r="I604" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J604" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K604" s="1">
-        <v>15000</v>
+        <v>4500</v>
       </c>
       <c r="L604" s="1">
         <v>0</v>
@@ -30840,7 +30840,7 @@
       </c>
       <c r="N604" s="1"/>
       <c r="O604" s="1">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="P604" s="1" t="s">
         <v>131</v>
@@ -30869,17 +30869,17 @@
         <v>145</v>
       </c>
       <c r="G605" s="1" t="s">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="H605" s="1"/>
       <c r="I605" s="1" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="J605" s="1">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K605" s="1">
-        <v>4500</v>
+        <v>2750</v>
       </c>
       <c r="L605" s="1">
         <v>0</v>
@@ -30889,13 +30889,13 @@
       </c>
       <c r="N605" s="1"/>
       <c r="O605" s="1">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="P605" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q605" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="606" spans="1:17" x14ac:dyDescent="0.45">
@@ -30918,17 +30918,17 @@
         <v>145</v>
       </c>
       <c r="G606" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H606" s="1"/>
       <c r="I606" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J606" s="1">
-        <v>0.25</v>
+        <v>0.58333330000000005</v>
       </c>
       <c r="K606" s="1">
-        <v>2750</v>
+        <v>6416.6665000000003</v>
       </c>
       <c r="L606" s="1">
         <v>0</v>
@@ -30938,7 +30938,7 @@
       </c>
       <c r="N606" s="1"/>
       <c r="O606" s="1">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="P606" s="1" t="s">
         <v>131</v>
@@ -30967,17 +30967,17 @@
         <v>145</v>
       </c>
       <c r="G607" s="1" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="H607" s="1"/>
       <c r="I607" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J607" s="1">
-        <v>0.58333330000000005</v>
+        <v>0.25</v>
       </c>
       <c r="K607" s="1">
-        <v>6416.6665000000003</v>
+        <v>2750</v>
       </c>
       <c r="L607" s="1">
         <v>0</v>
@@ -30987,7 +30987,7 @@
       </c>
       <c r="N607" s="1"/>
       <c r="O607" s="1">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="P607" s="1" t="s">
         <v>131</v>
@@ -31016,17 +31016,17 @@
         <v>145</v>
       </c>
       <c r="G608" s="1" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="H608" s="1"/>
       <c r="I608" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J608" s="1">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="K608" s="1">
-        <v>2750</v>
+        <v>5500</v>
       </c>
       <c r="L608" s="1">
         <v>0</v>
@@ -31036,7 +31036,7 @@
       </c>
       <c r="N608" s="1"/>
       <c r="O608" s="1">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="P608" s="1" t="s">
         <v>131</v>
@@ -31065,7 +31065,7 @@
         <v>145</v>
       </c>
       <c r="G609" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H609" s="1"/>
       <c r="I609" s="1" t="s">
@@ -31085,7 +31085,7 @@
       </c>
       <c r="N609" s="1"/>
       <c r="O609" s="1">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="P609" s="1" t="s">
         <v>131</v>
@@ -31114,7 +31114,7 @@
         <v>145</v>
       </c>
       <c r="G610" s="1" t="s">
-        <v>28</v>
+        <v>132</v>
       </c>
       <c r="H610" s="1"/>
       <c r="I610" s="1" t="s">
@@ -31134,7 +31134,7 @@
       </c>
       <c r="N610" s="1"/>
       <c r="O610" s="1">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="P610" s="1" t="s">
         <v>131</v>
@@ -31163,17 +31163,17 @@
         <v>145</v>
       </c>
       <c r="G611" s="1" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="H611" s="1"/>
       <c r="I611" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J611" s="1">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K611" s="1">
-        <v>5500</v>
+        <v>2750</v>
       </c>
       <c r="L611" s="1">
         <v>0</v>
@@ -31183,7 +31183,7 @@
       </c>
       <c r="N611" s="1"/>
       <c r="O611" s="1">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="P611" s="1" t="s">
         <v>131</v>
@@ -31212,17 +31212,17 @@
         <v>145</v>
       </c>
       <c r="G612" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H612" s="1"/>
       <c r="I612" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J612" s="1">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="K612" s="1">
-        <v>2750</v>
+        <v>5500</v>
       </c>
       <c r="L612" s="1">
         <v>0</v>
@@ -31232,7 +31232,7 @@
       </c>
       <c r="N612" s="1"/>
       <c r="O612" s="1">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="P612" s="1" t="s">
         <v>131</v>
@@ -31261,7 +31261,7 @@
         <v>145</v>
       </c>
       <c r="G613" s="1" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="H613" s="1"/>
       <c r="I613" s="1" t="s">
@@ -31281,7 +31281,7 @@
       </c>
       <c r="N613" s="1"/>
       <c r="O613" s="1">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="P613" s="1" t="s">
         <v>131</v>
@@ -31310,17 +31310,17 @@
         <v>145</v>
       </c>
       <c r="G614" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H614" s="1"/>
       <c r="I614" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J614" s="1">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K614" s="1">
-        <v>5500</v>
+        <v>2750</v>
       </c>
       <c r="L614" s="1">
         <v>0</v>
@@ -31330,7 +31330,7 @@
       </c>
       <c r="N614" s="1"/>
       <c r="O614" s="1">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="P614" s="1" t="s">
         <v>131</v>
@@ -31347,45 +31347,45 @@
         <v>0</v>
       </c>
       <c r="C615" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D615" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E615" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F615" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G615" s="1" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="H615" s="1"/>
       <c r="I615" s="1" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="J615" s="1">
-        <v>0.25</v>
+        <v>0.22222222</v>
       </c>
       <c r="K615" s="1">
-        <v>2750</v>
+        <v>5777.7780000000002</v>
       </c>
       <c r="L615" s="1">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="M615" s="1">
         <v>0</v>
       </c>
       <c r="N615" s="1"/>
       <c r="O615" s="1">
-        <v>1010</v>
+        <v>1085</v>
       </c>
       <c r="P615" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q615" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="616" spans="1:17" x14ac:dyDescent="0.45">
@@ -31408,27 +31408,27 @@
         <v>146</v>
       </c>
       <c r="G616" s="1" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="H616" s="1"/>
       <c r="I616" s="1" t="s">
         <v>43</v>
       </c>
       <c r="J616" s="1">
-        <v>0.22222222</v>
+        <v>0.11111111</v>
       </c>
       <c r="K616" s="1">
-        <v>5777.7780000000002</v>
+        <v>2888.8890000000001</v>
       </c>
       <c r="L616" s="1">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="M616" s="1">
         <v>0</v>
       </c>
       <c r="N616" s="1"/>
       <c r="O616" s="1">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="P616" s="1" t="s">
         <v>131</v>
@@ -31457,7 +31457,7 @@
         <v>146</v>
       </c>
       <c r="G617" s="1" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="H617" s="1"/>
       <c r="I617" s="1" t="s">
@@ -31477,7 +31477,7 @@
       </c>
       <c r="N617" s="1"/>
       <c r="O617" s="1">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="P617" s="1" t="s">
         <v>131</v>
@@ -31506,7 +31506,7 @@
         <v>146</v>
       </c>
       <c r="G618" s="1" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="H618" s="1"/>
       <c r="I618" s="1" t="s">
@@ -31526,7 +31526,7 @@
       </c>
       <c r="N618" s="1"/>
       <c r="O618" s="1">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="P618" s="1" t="s">
         <v>131</v>
@@ -31555,17 +31555,17 @@
         <v>146</v>
       </c>
       <c r="G619" s="1" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="H619" s="1"/>
       <c r="I619" s="1" t="s">
         <v>43</v>
       </c>
       <c r="J619" s="1">
-        <v>0.11111111</v>
+        <v>0.77777779999999996</v>
       </c>
       <c r="K619" s="1">
-        <v>2888.8890000000001</v>
+        <v>20222.223000000002</v>
       </c>
       <c r="L619" s="1">
         <v>0</v>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="N619" s="1"/>
       <c r="O619" s="1">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="P619" s="1" t="s">
         <v>131</v>
@@ -31604,17 +31604,17 @@
         <v>146</v>
       </c>
       <c r="G620" s="1" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="H620" s="1"/>
       <c r="I620" s="1" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="J620" s="1">
-        <v>0.77777779999999996</v>
+        <v>1.0833333999999999</v>
       </c>
       <c r="K620" s="1">
-        <v>20222.223000000002</v>
+        <v>16791.666000000001</v>
       </c>
       <c r="L620" s="1">
         <v>0</v>
@@ -31624,13 +31624,13 @@
       </c>
       <c r="N620" s="1"/>
       <c r="O620" s="1">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="P620" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q620" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="621" spans="1:17" x14ac:dyDescent="0.45">
@@ -31657,13 +31657,13 @@
       </c>
       <c r="H621" s="1"/>
       <c r="I621" s="1" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="J621" s="1">
-        <v>1.0833333999999999</v>
+        <v>1.2083333999999999</v>
       </c>
       <c r="K621" s="1">
-        <v>16791.666000000001</v>
+        <v>15104.166999999999</v>
       </c>
       <c r="L621" s="1">
         <v>0</v>
@@ -31673,7 +31673,7 @@
       </c>
       <c r="N621" s="1"/>
       <c r="O621" s="1">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="P621" s="1" t="s">
         <v>131</v>
@@ -31702,17 +31702,17 @@
         <v>146</v>
       </c>
       <c r="G622" s="1" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="H622" s="1"/>
       <c r="I622" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J622" s="1">
-        <v>1.2083333999999999</v>
+        <v>1</v>
       </c>
       <c r="K622" s="1">
-        <v>15104.166999999999</v>
+        <v>28000</v>
       </c>
       <c r="L622" s="1">
         <v>0</v>
@@ -31722,13 +31722,13 @@
       </c>
       <c r="N622" s="1"/>
       <c r="O622" s="1">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="P622" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q622" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="623" spans="1:17" x14ac:dyDescent="0.45">
@@ -31755,13 +31755,13 @@
       </c>
       <c r="H623" s="1"/>
       <c r="I623" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J623" s="1">
-        <v>1</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K623" s="1">
-        <v>28000</v>
+        <v>729.16669999999999</v>
       </c>
       <c r="L623" s="1">
         <v>0</v>
@@ -31771,7 +31771,7 @@
       </c>
       <c r="N623" s="1"/>
       <c r="O623" s="1">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="P623" s="1" t="s">
         <v>131</v>
@@ -31800,17 +31800,17 @@
         <v>146</v>
       </c>
       <c r="G624" s="1" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="H624" s="1"/>
       <c r="I624" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J624" s="1">
-        <v>4.1666667999999997E-2</v>
+        <v>0.66666669999999995</v>
       </c>
       <c r="K624" s="1">
-        <v>729.16669999999999</v>
+        <v>18666.666000000001</v>
       </c>
       <c r="L624" s="1">
         <v>0</v>
@@ -31820,7 +31820,7 @@
       </c>
       <c r="N624" s="1"/>
       <c r="O624" s="1">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="P624" s="1" t="s">
         <v>131</v>
@@ -31853,13 +31853,13 @@
       </c>
       <c r="H625" s="1"/>
       <c r="I625" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J625" s="1">
-        <v>0.66666669999999995</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K625" s="1">
-        <v>18666.666000000001</v>
+        <v>729.16669999999999</v>
       </c>
       <c r="L625" s="1">
         <v>0</v>
@@ -31869,7 +31869,7 @@
       </c>
       <c r="N625" s="1"/>
       <c r="O625" s="1">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="P625" s="1" t="s">
         <v>131</v>
@@ -31898,17 +31898,17 @@
         <v>146</v>
       </c>
       <c r="G626" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="H626" s="1"/>
       <c r="I626" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J626" s="1">
-        <v>4.1666667999999997E-2</v>
+        <v>0.11111111</v>
       </c>
       <c r="K626" s="1">
-        <v>729.16669999999999</v>
+        <v>3111.1109999999999</v>
       </c>
       <c r="L626" s="1">
         <v>0</v>
@@ -31918,7 +31918,7 @@
       </c>
       <c r="N626" s="1"/>
       <c r="O626" s="1">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="P626" s="1" t="s">
         <v>131</v>
@@ -31947,17 +31947,17 @@
         <v>146</v>
       </c>
       <c r="G627" s="1" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="H627" s="1"/>
       <c r="I627" s="1" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="J627" s="1">
-        <v>0.11111111</v>
+        <v>2</v>
       </c>
       <c r="K627" s="1">
-        <v>3111.1109999999999</v>
+        <v>23000</v>
       </c>
       <c r="L627" s="1">
         <v>0</v>
@@ -31967,13 +31967,13 @@
       </c>
       <c r="N627" s="1"/>
       <c r="O627" s="1">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="P627" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q627" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="628" spans="1:17" x14ac:dyDescent="0.45">
@@ -31996,17 +31996,17 @@
         <v>146</v>
       </c>
       <c r="G628" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H628" s="1"/>
       <c r="I628" s="1" t="s">
         <v>80</v>
       </c>
       <c r="J628" s="1">
-        <v>2</v>
+        <v>1.5416666000000001</v>
       </c>
       <c r="K628" s="1">
-        <v>23000</v>
+        <v>17729.166000000001</v>
       </c>
       <c r="L628" s="1">
         <v>0</v>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="N628" s="1"/>
       <c r="O628" s="1">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="P628" s="1" t="s">
         <v>131</v>
@@ -32045,17 +32045,17 @@
         <v>146</v>
       </c>
       <c r="G629" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H629" s="1"/>
       <c r="I629" s="1" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="J629" s="1">
-        <v>1.5416666000000001</v>
+        <v>0.16666666999999999</v>
       </c>
       <c r="K629" s="1">
-        <v>17729.166000000001</v>
+        <v>1666.6666</v>
       </c>
       <c r="L629" s="1">
         <v>0</v>
@@ -32065,13 +32065,13 @@
       </c>
       <c r="N629" s="1"/>
       <c r="O629" s="1">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="P629" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q629" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="630" spans="1:17" x14ac:dyDescent="0.45">
@@ -32094,7 +32094,7 @@
         <v>146</v>
       </c>
       <c r="G630" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H630" s="1"/>
       <c r="I630" s="1" t="s">
@@ -32114,7 +32114,7 @@
       </c>
       <c r="N630" s="1"/>
       <c r="O630" s="1">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="P630" s="1" t="s">
         <v>131</v>
@@ -32143,17 +32143,17 @@
         <v>146</v>
       </c>
       <c r="G631" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H631" s="1"/>
       <c r="I631" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J631" s="1">
-        <v>0.16666666999999999</v>
+        <v>0.5</v>
       </c>
       <c r="K631" s="1">
-        <v>1666.6666</v>
+        <v>5250</v>
       </c>
       <c r="L631" s="1">
         <v>0</v>
@@ -32163,13 +32163,13 @@
       </c>
       <c r="N631" s="1"/>
       <c r="O631" s="1">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="P631" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q631" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="632" spans="1:17" x14ac:dyDescent="0.45">
@@ -32196,13 +32196,13 @@
       </c>
       <c r="H632" s="1"/>
       <c r="I632" s="1" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="J632" s="1">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="K632" s="1">
-        <v>5250</v>
+        <v>10800</v>
       </c>
       <c r="L632" s="1">
         <v>0</v>
@@ -32212,7 +32212,7 @@
       </c>
       <c r="N632" s="1"/>
       <c r="O632" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="P632" s="1" t="s">
         <v>131</v>
@@ -32241,17 +32241,17 @@
         <v>146</v>
       </c>
       <c r="G633" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H633" s="1"/>
       <c r="I633" s="1" t="s">
         <v>76</v>
       </c>
       <c r="J633" s="1">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="K633" s="1">
-        <v>10800</v>
+        <v>4500</v>
       </c>
       <c r="L633" s="1">
         <v>0</v>
@@ -32261,7 +32261,7 @@
       </c>
       <c r="N633" s="1"/>
       <c r="O633" s="1">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="P633" s="1" t="s">
         <v>131</v>
@@ -32290,17 +32290,17 @@
         <v>146</v>
       </c>
       <c r="G634" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H634" s="1"/>
       <c r="I634" s="1" t="s">
         <v>76</v>
       </c>
       <c r="J634" s="1">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="K634" s="1">
-        <v>4500</v>
+        <v>11700</v>
       </c>
       <c r="L634" s="1">
         <v>0</v>
@@ -32310,7 +32310,7 @@
       </c>
       <c r="N634" s="1"/>
       <c r="O634" s="1">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="P634" s="1" t="s">
         <v>131</v>
@@ -32343,13 +32343,13 @@
       </c>
       <c r="H635" s="1"/>
       <c r="I635" s="1" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="J635" s="1">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="K635" s="1">
-        <v>11700</v>
+        <v>600</v>
       </c>
       <c r="L635" s="1">
         <v>0</v>
@@ -32359,7 +32359,7 @@
       </c>
       <c r="N635" s="1"/>
       <c r="O635" s="1">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="P635" s="1" t="s">
         <v>131</v>
@@ -32376,29 +32376,29 @@
         <v>0</v>
       </c>
       <c r="C636" s="1" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="D636" s="1" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="E636" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F636" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G636" s="1" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="H636" s="1"/>
       <c r="I636" s="1" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="J636" s="1">
-        <v>0.1</v>
+        <v>0.66666669999999995</v>
       </c>
       <c r="K636" s="1">
-        <v>600</v>
+        <v>17333.333999999999</v>
       </c>
       <c r="L636" s="1">
         <v>0</v>
@@ -32408,13 +32408,13 @@
       </c>
       <c r="N636" s="1"/>
       <c r="O636" s="1">
-        <v>1105</v>
+        <v>1011</v>
       </c>
       <c r="P636" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q636" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="637" spans="1:17" x14ac:dyDescent="0.45">
@@ -32441,13 +32441,13 @@
       </c>
       <c r="H637" s="1"/>
       <c r="I637" s="1" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="J637" s="1">
-        <v>0.66666669999999995</v>
+        <v>0.5</v>
       </c>
       <c r="K637" s="1">
-        <v>17333.333999999999</v>
+        <v>5625</v>
       </c>
       <c r="L637" s="1">
         <v>0</v>
@@ -32457,7 +32457,7 @@
       </c>
       <c r="N637" s="1"/>
       <c r="O637" s="1">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="P637" s="1" t="s">
         <v>131</v>
@@ -32486,17 +32486,17 @@
         <v>145</v>
       </c>
       <c r="G638" s="1" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="H638" s="1"/>
       <c r="I638" s="1" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="J638" s="1">
-        <v>0.5</v>
+        <v>0.55555560000000004</v>
       </c>
       <c r="K638" s="1">
-        <v>5625</v>
+        <v>14444.444</v>
       </c>
       <c r="L638" s="1">
         <v>0</v>
@@ -32506,7 +32506,7 @@
       </c>
       <c r="N638" s="1"/>
       <c r="O638" s="1">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="P638" s="1" t="s">
         <v>131</v>
@@ -32535,17 +32535,17 @@
         <v>145</v>
       </c>
       <c r="G639" s="1" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="H639" s="1"/>
       <c r="I639" s="1" t="s">
         <v>43</v>
       </c>
       <c r="J639" s="1">
-        <v>0.55555560000000004</v>
+        <v>0.66666669999999995</v>
       </c>
       <c r="K639" s="1">
-        <v>14444.444</v>
+        <v>17333.333999999999</v>
       </c>
       <c r="L639" s="1">
         <v>0</v>
@@ -32555,7 +32555,7 @@
       </c>
       <c r="N639" s="1"/>
       <c r="O639" s="1">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="P639" s="1" t="s">
         <v>131</v>
@@ -32588,13 +32588,13 @@
       </c>
       <c r="H640" s="1"/>
       <c r="I640" s="1" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="J640" s="1">
-        <v>0.66666669999999995</v>
+        <v>1</v>
       </c>
       <c r="K640" s="1">
-        <v>17333.333999999999</v>
+        <v>11250</v>
       </c>
       <c r="L640" s="1">
         <v>0</v>
@@ -32604,7 +32604,7 @@
       </c>
       <c r="N640" s="1"/>
       <c r="O640" s="1">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="P640" s="1" t="s">
         <v>131</v>
@@ -32633,17 +32633,17 @@
         <v>145</v>
       </c>
       <c r="G641" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H641" s="1"/>
       <c r="I641" s="1" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="J641" s="1">
-        <v>1</v>
+        <v>0.66666669999999995</v>
       </c>
       <c r="K641" s="1">
-        <v>11250</v>
+        <v>17333.333999999999</v>
       </c>
       <c r="L641" s="1">
         <v>0</v>
@@ -32653,7 +32653,7 @@
       </c>
       <c r="N641" s="1"/>
       <c r="O641" s="1">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="P641" s="1" t="s">
         <v>131</v>
@@ -32682,17 +32682,17 @@
         <v>145</v>
       </c>
       <c r="G642" s="1" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="H642" s="1"/>
       <c r="I642" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J642" s="1">
-        <v>0.66666669999999995</v>
+        <v>0.22222222</v>
       </c>
       <c r="K642" s="1">
-        <v>17333.333999999999</v>
+        <v>6222.2219999999998</v>
       </c>
       <c r="L642" s="1">
         <v>0</v>
@@ -32702,13 +32702,13 @@
       </c>
       <c r="N642" s="1"/>
       <c r="O642" s="1">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="P642" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q642" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="643" spans="1:17" x14ac:dyDescent="0.45">
@@ -32731,17 +32731,17 @@
         <v>145</v>
       </c>
       <c r="G643" s="1" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="H643" s="1"/>
       <c r="I643" s="1" t="s">
         <v>42</v>
       </c>
       <c r="J643" s="1">
-        <v>0.22222222</v>
+        <v>1.1111112000000001</v>
       </c>
       <c r="K643" s="1">
-        <v>6222.2219999999998</v>
+        <v>31111.111000000001</v>
       </c>
       <c r="L643" s="1">
         <v>0</v>
@@ -32751,7 +32751,7 @@
       </c>
       <c r="N643" s="1"/>
       <c r="O643" s="1">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="P643" s="1" t="s">
         <v>131</v>
@@ -32780,17 +32780,17 @@
         <v>145</v>
       </c>
       <c r="G644" s="1" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="H644" s="1"/>
       <c r="I644" s="1" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="J644" s="1">
-        <v>1.1111112000000001</v>
+        <v>3</v>
       </c>
       <c r="K644" s="1">
-        <v>31111.111000000001</v>
+        <v>33000</v>
       </c>
       <c r="L644" s="1">
         <v>0</v>
@@ -32800,13 +32800,13 @@
       </c>
       <c r="N644" s="1"/>
       <c r="O644" s="1">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="P644" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q644" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="645" spans="1:17" x14ac:dyDescent="0.45">
@@ -32833,13 +32833,13 @@
       </c>
       <c r="H645" s="1"/>
       <c r="I645" s="1" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="J645" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K645" s="1">
-        <v>33000</v>
+        <v>12500</v>
       </c>
       <c r="L645" s="1">
         <v>0</v>
@@ -32849,7 +32849,7 @@
       </c>
       <c r="N645" s="1"/>
       <c r="O645" s="1">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="P645" s="1" t="s">
         <v>131</v>
@@ -32882,13 +32882,13 @@
       </c>
       <c r="H646" s="1"/>
       <c r="I646" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J646" s="1">
-        <v>1</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K646" s="1">
-        <v>12500</v>
+        <v>1041.6666</v>
       </c>
       <c r="L646" s="1">
         <v>0</v>
@@ -32898,7 +32898,7 @@
       </c>
       <c r="N646" s="1"/>
       <c r="O646" s="1">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="P646" s="1" t="s">
         <v>131</v>
@@ -32927,17 +32927,17 @@
         <v>145</v>
       </c>
       <c r="G647" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H647" s="1"/>
       <c r="I647" s="1" t="s">
         <v>39</v>
       </c>
       <c r="J647" s="1">
-        <v>8.3333335999999994E-2</v>
+        <v>1</v>
       </c>
       <c r="K647" s="1">
-        <v>1041.6666</v>
+        <v>12500</v>
       </c>
       <c r="L647" s="1">
         <v>0</v>
@@ -32947,7 +32947,7 @@
       </c>
       <c r="N647" s="1"/>
       <c r="O647" s="1">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="P647" s="1" t="s">
         <v>131</v>
@@ -32980,13 +32980,13 @@
       </c>
       <c r="H648" s="1"/>
       <c r="I648" s="1" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="J648" s="1">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K648" s="1">
-        <v>12500</v>
+        <v>6600</v>
       </c>
       <c r="L648" s="1">
         <v>0</v>
@@ -32996,7 +32996,7 @@
       </c>
       <c r="N648" s="1"/>
       <c r="O648" s="1">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="P648" s="1" t="s">
         <v>131</v>
@@ -33025,17 +33025,17 @@
         <v>145</v>
       </c>
       <c r="G649" s="1" t="s">
-        <v>67</v>
+        <v>138</v>
       </c>
       <c r="H649" s="1"/>
       <c r="I649" s="1" t="s">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="J649" s="1">
-        <v>0.6</v>
+        <v>0.33333333999999998</v>
       </c>
       <c r="K649" s="1">
-        <v>6600</v>
+        <v>3333.3332999999998</v>
       </c>
       <c r="L649" s="1">
         <v>0</v>
@@ -33045,13 +33045,13 @@
       </c>
       <c r="N649" s="1"/>
       <c r="O649" s="1">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="P649" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q649" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="650" spans="1:17" x14ac:dyDescent="0.45">
@@ -33074,17 +33074,17 @@
         <v>145</v>
       </c>
       <c r="G650" s="1" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="H650" s="1"/>
       <c r="I650" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J650" s="1">
-        <v>0.33333333999999998</v>
+        <v>0.66666669999999995</v>
       </c>
       <c r="K650" s="1">
-        <v>3333.3332999999998</v>
+        <v>6666.6665000000003</v>
       </c>
       <c r="L650" s="1">
         <v>0</v>
@@ -33094,7 +33094,7 @@
       </c>
       <c r="N650" s="1"/>
       <c r="O650" s="1">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="P650" s="1" t="s">
         <v>131</v>
@@ -33123,17 +33123,17 @@
         <v>145</v>
       </c>
       <c r="G651" s="1" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="H651" s="1"/>
       <c r="I651" s="1" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="J651" s="1">
-        <v>0.66666669999999995</v>
+        <v>0.5</v>
       </c>
       <c r="K651" s="1">
-        <v>6666.6665000000003</v>
+        <v>13250</v>
       </c>
       <c r="L651" s="1">
         <v>0</v>
@@ -33143,13 +33143,13 @@
       </c>
       <c r="N651" s="1"/>
       <c r="O651" s="1">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="P651" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q651" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="652" spans="1:17" x14ac:dyDescent="0.45">
@@ -33172,7 +33172,7 @@
         <v>145</v>
       </c>
       <c r="G652" s="1" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="H652" s="1"/>
       <c r="I652" s="1" t="s">
@@ -33192,7 +33192,7 @@
       </c>
       <c r="N652" s="1"/>
       <c r="O652" s="1">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="P652" s="1" t="s">
         <v>131</v>
@@ -33221,17 +33221,17 @@
         <v>145</v>
       </c>
       <c r="G653" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H653" s="1"/>
       <c r="I653" s="1" t="s">
         <v>82</v>
       </c>
       <c r="J653" s="1">
-        <v>0.5</v>
+        <v>0.125</v>
       </c>
       <c r="K653" s="1">
-        <v>13250</v>
+        <v>3312.5</v>
       </c>
       <c r="L653" s="1">
         <v>0</v>
@@ -33241,7 +33241,7 @@
       </c>
       <c r="N653" s="1"/>
       <c r="O653" s="1">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="P653" s="1" t="s">
         <v>131</v>
@@ -33274,13 +33274,13 @@
       </c>
       <c r="H654" s="1"/>
       <c r="I654" s="1" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="J654" s="1">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="K654" s="1">
-        <v>3312.5</v>
+        <v>10500</v>
       </c>
       <c r="L654" s="1">
         <v>0</v>
@@ -33290,7 +33290,7 @@
       </c>
       <c r="N654" s="1"/>
       <c r="O654" s="1">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="P654" s="1" t="s">
         <v>131</v>
@@ -33323,13 +33323,13 @@
       </c>
       <c r="H655" s="1"/>
       <c r="I655" s="1" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="J655" s="1">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="K655" s="1">
-        <v>10500</v>
+        <v>600</v>
       </c>
       <c r="L655" s="1">
         <v>0</v>
@@ -33339,7 +33339,7 @@
       </c>
       <c r="N655" s="1"/>
       <c r="O655" s="1">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="P655" s="1" t="s">
         <v>131</v>
@@ -33368,17 +33368,17 @@
         <v>145</v>
       </c>
       <c r="G656" s="1" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="H656" s="1"/>
       <c r="I656" s="1" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="J656" s="1">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="K656" s="1">
-        <v>600</v>
+        <v>4500</v>
       </c>
       <c r="L656" s="1">
         <v>0</v>
@@ -33388,7 +33388,7 @@
       </c>
       <c r="N656" s="1"/>
       <c r="O656" s="1">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="P656" s="1" t="s">
         <v>131</v>
@@ -33417,17 +33417,17 @@
         <v>145</v>
       </c>
       <c r="G657" s="1" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="H657" s="1"/>
       <c r="I657" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J657" s="1">
-        <v>1</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K657" s="1">
-        <v>4500</v>
+        <v>479.16665999999998</v>
       </c>
       <c r="L657" s="1">
         <v>0</v>
@@ -33437,13 +33437,13 @@
       </c>
       <c r="N657" s="1"/>
       <c r="O657" s="1">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="P657" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q657" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="658" spans="1:17" x14ac:dyDescent="0.45">
@@ -33466,7 +33466,7 @@
         <v>145</v>
       </c>
       <c r="G658" s="1" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="H658" s="1"/>
       <c r="I658" s="1" t="s">
@@ -33486,7 +33486,7 @@
       </c>
       <c r="N658" s="1"/>
       <c r="O658" s="1">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="P658" s="1" t="s">
         <v>131</v>
@@ -33515,7 +33515,7 @@
         <v>145</v>
       </c>
       <c r="G659" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H659" s="1"/>
       <c r="I659" s="1" t="s">
@@ -33535,7 +33535,7 @@
       </c>
       <c r="N659" s="1"/>
       <c r="O659" s="1">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="P659" s="1" t="s">
         <v>131</v>
@@ -33564,7 +33564,7 @@
         <v>145</v>
       </c>
       <c r="G660" s="1" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="H660" s="1"/>
       <c r="I660" s="1" t="s">
@@ -33584,7 +33584,7 @@
       </c>
       <c r="N660" s="1"/>
       <c r="O660" s="1">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P660" s="1" t="s">
         <v>131</v>
@@ -33626,14 +33626,14 @@
         <v>479.16665999999998</v>
       </c>
       <c r="L661" s="1">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="M661" s="1">
         <v>0</v>
       </c>
       <c r="N661" s="1"/>
       <c r="O661" s="1">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="P661" s="1" t="s">
         <v>131</v>
@@ -33644,51 +33644,51 @@
     </row>
     <row r="662" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A662" s="2">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B662" s="1">
         <v>0</v>
       </c>
       <c r="C662" s="1" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="D662" s="1" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="E662" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F662" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G662" s="1" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="H662" s="1"/>
       <c r="I662" s="1" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="J662" s="1">
-        <v>4.1666667999999997E-2</v>
+        <v>2</v>
       </c>
       <c r="K662" s="1">
-        <v>479.16665999999998</v>
+        <v>30000</v>
       </c>
       <c r="L662" s="1">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="M662" s="1">
         <v>0</v>
       </c>
       <c r="N662" s="1"/>
       <c r="O662" s="1">
-        <v>1036</v>
+        <v>835</v>
       </c>
       <c r="P662" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q662" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="663" spans="1:17" x14ac:dyDescent="0.45">
@@ -33715,13 +33715,13 @@
       </c>
       <c r="H663" s="1"/>
       <c r="I663" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J663" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K663" s="1">
-        <v>30000</v>
+        <v>9000</v>
       </c>
       <c r="L663" s="1">
         <v>0</v>
@@ -33731,7 +33731,7 @@
       </c>
       <c r="N663" s="1"/>
       <c r="O663" s="1">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="P663" s="1" t="s">
         <v>131</v>
@@ -33760,17 +33760,17 @@
         <v>147</v>
       </c>
       <c r="G664" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H664" s="1"/>
       <c r="I664" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J664" s="1">
-        <v>1</v>
+        <v>0.125</v>
       </c>
       <c r="K664" s="1">
-        <v>9000</v>
+        <v>1875</v>
       </c>
       <c r="L664" s="1">
         <v>0</v>
@@ -33780,7 +33780,7 @@
       </c>
       <c r="N664" s="1"/>
       <c r="O664" s="1">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="P664" s="1" t="s">
         <v>131</v>
@@ -33813,13 +33813,13 @@
       </c>
       <c r="H665" s="1"/>
       <c r="I665" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J665" s="1">
-        <v>0.125</v>
+        <v>2.0833333000000001</v>
       </c>
       <c r="K665" s="1">
-        <v>1875</v>
+        <v>18750</v>
       </c>
       <c r="L665" s="1">
         <v>0</v>
@@ -33829,7 +33829,7 @@
       </c>
       <c r="N665" s="1"/>
       <c r="O665" s="1">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="P665" s="1" t="s">
         <v>131</v>
@@ -33858,17 +33858,17 @@
         <v>147</v>
       </c>
       <c r="G666" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H666" s="1"/>
       <c r="I666" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J666" s="1">
-        <v>2.0833333000000001</v>
+        <v>1</v>
       </c>
       <c r="K666" s="1">
-        <v>18750</v>
+        <v>15000</v>
       </c>
       <c r="L666" s="1">
         <v>0</v>
@@ -33878,7 +33878,7 @@
       </c>
       <c r="N666" s="1"/>
       <c r="O666" s="1">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="P666" s="1" t="s">
         <v>131</v>
@@ -33911,13 +33911,13 @@
       </c>
       <c r="H667" s="1"/>
       <c r="I667" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J667" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K667" s="1">
-        <v>15000</v>
+        <v>4500</v>
       </c>
       <c r="L667" s="1">
         <v>0</v>
@@ -33927,7 +33927,7 @@
       </c>
       <c r="N667" s="1"/>
       <c r="O667" s="1">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="P667" s="1" t="s">
         <v>131</v>
@@ -33956,17 +33956,17 @@
         <v>147</v>
       </c>
       <c r="G668" s="1" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="H668" s="1"/>
       <c r="I668" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J668" s="1">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K668" s="1">
-        <v>4500</v>
+        <v>11250</v>
       </c>
       <c r="L668" s="1">
         <v>0</v>
@@ -33976,7 +33976,7 @@
       </c>
       <c r="N668" s="1"/>
       <c r="O668" s="1">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="P668" s="1" t="s">
         <v>131</v>
@@ -34009,13 +34009,13 @@
       </c>
       <c r="H669" s="1"/>
       <c r="I669" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J669" s="1">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="K669" s="1">
-        <v>11250</v>
+        <v>4500</v>
       </c>
       <c r="L669" s="1">
         <v>0</v>
@@ -34025,7 +34025,7 @@
       </c>
       <c r="N669" s="1"/>
       <c r="O669" s="1">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="P669" s="1" t="s">
         <v>131</v>
@@ -34054,17 +34054,17 @@
         <v>147</v>
       </c>
       <c r="G670" s="1" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H670" s="1"/>
       <c r="I670" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J670" s="1">
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
       <c r="K670" s="1">
-        <v>4500</v>
+        <v>13125</v>
       </c>
       <c r="L670" s="1">
         <v>0</v>
@@ -34074,7 +34074,7 @@
       </c>
       <c r="N670" s="1"/>
       <c r="O670" s="1">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="P670" s="1" t="s">
         <v>131</v>
@@ -34107,13 +34107,13 @@
       </c>
       <c r="H671" s="1"/>
       <c r="I671" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J671" s="1">
-        <v>0.875</v>
+        <v>0.5</v>
       </c>
       <c r="K671" s="1">
-        <v>13125</v>
+        <v>4500</v>
       </c>
       <c r="L671" s="1">
         <v>0</v>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="N671" s="1"/>
       <c r="O671" s="1">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="P671" s="1" t="s">
         <v>131</v>
@@ -34152,17 +34152,17 @@
         <v>147</v>
       </c>
       <c r="G672" s="1" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="H672" s="1"/>
       <c r="I672" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J672" s="1">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K672" s="1">
-        <v>4500</v>
+        <v>3750</v>
       </c>
       <c r="L672" s="1">
         <v>0</v>
@@ -34172,7 +34172,7 @@
       </c>
       <c r="N672" s="1"/>
       <c r="O672" s="1">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="P672" s="1" t="s">
         <v>131</v>
@@ -34205,13 +34205,13 @@
       </c>
       <c r="H673" s="1"/>
       <c r="I673" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J673" s="1">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="K673" s="1">
-        <v>3750</v>
+        <v>4500</v>
       </c>
       <c r="L673" s="1">
         <v>0</v>
@@ -34221,7 +34221,7 @@
       </c>
       <c r="N673" s="1"/>
       <c r="O673" s="1">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="P673" s="1" t="s">
         <v>131</v>
@@ -34250,17 +34250,17 @@
         <v>147</v>
       </c>
       <c r="G674" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H674" s="1"/>
       <c r="I674" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J674" s="1">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="K674" s="1">
-        <v>4500</v>
+        <v>9375</v>
       </c>
       <c r="L674" s="1">
         <v>0</v>
@@ -34270,7 +34270,7 @@
       </c>
       <c r="N674" s="1"/>
       <c r="O674" s="1">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="P674" s="1" t="s">
         <v>131</v>
@@ -34303,13 +34303,13 @@
       </c>
       <c r="H675" s="1"/>
       <c r="I675" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J675" s="1">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="K675" s="1">
-        <v>9375</v>
+        <v>4500</v>
       </c>
       <c r="L675" s="1">
         <v>0</v>
@@ -34319,7 +34319,7 @@
       </c>
       <c r="N675" s="1"/>
       <c r="O675" s="1">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="P675" s="1" t="s">
         <v>131</v>
@@ -34348,17 +34348,17 @@
         <v>147</v>
       </c>
       <c r="G676" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H676" s="1"/>
       <c r="I676" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J676" s="1">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="K676" s="1">
-        <v>4500</v>
+        <v>22500</v>
       </c>
       <c r="L676" s="1">
         <v>0</v>
@@ -34368,7 +34368,7 @@
       </c>
       <c r="N676" s="1"/>
       <c r="O676" s="1">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="P676" s="1" t="s">
         <v>131</v>
@@ -34401,13 +34401,13 @@
       </c>
       <c r="H677" s="1"/>
       <c r="I677" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J677" s="1">
-        <v>1.5</v>
+        <v>0.125</v>
       </c>
       <c r="K677" s="1">
-        <v>22500</v>
+        <v>1875</v>
       </c>
       <c r="L677" s="1">
         <v>0</v>
@@ -34417,7 +34417,7 @@
       </c>
       <c r="N677" s="1"/>
       <c r="O677" s="1">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="P677" s="1" t="s">
         <v>131</v>
@@ -34450,13 +34450,13 @@
       </c>
       <c r="H678" s="1"/>
       <c r="I678" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J678" s="1">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="K678" s="1">
-        <v>1875</v>
+        <v>9000</v>
       </c>
       <c r="L678" s="1">
         <v>0</v>
@@ -34466,7 +34466,7 @@
       </c>
       <c r="N678" s="1"/>
       <c r="O678" s="1">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="P678" s="1" t="s">
         <v>131</v>
@@ -34495,17 +34495,17 @@
         <v>147</v>
       </c>
       <c r="G679" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H679" s="1"/>
       <c r="I679" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J679" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K679" s="1">
-        <v>9000</v>
+        <v>7500</v>
       </c>
       <c r="L679" s="1">
         <v>0</v>
@@ -34515,7 +34515,7 @@
       </c>
       <c r="N679" s="1"/>
       <c r="O679" s="1">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="P679" s="1" t="s">
         <v>131</v>
@@ -34548,13 +34548,13 @@
       </c>
       <c r="H680" s="1"/>
       <c r="I680" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J680" s="1">
         <v>0.5</v>
       </c>
       <c r="K680" s="1">
-        <v>7500</v>
+        <v>4500</v>
       </c>
       <c r="L680" s="1">
         <v>0</v>
@@ -34564,7 +34564,7 @@
       </c>
       <c r="N680" s="1"/>
       <c r="O680" s="1">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="P680" s="1" t="s">
         <v>131</v>
@@ -34593,17 +34593,17 @@
         <v>147</v>
       </c>
       <c r="G681" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H681" s="1"/>
       <c r="I681" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J681" s="1">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="K681" s="1">
-        <v>4500</v>
+        <v>5625</v>
       </c>
       <c r="L681" s="1">
         <v>0</v>
@@ -34613,7 +34613,7 @@
       </c>
       <c r="N681" s="1"/>
       <c r="O681" s="1">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="P681" s="1" t="s">
         <v>131</v>
@@ -34646,13 +34646,13 @@
       </c>
       <c r="H682" s="1"/>
       <c r="I682" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J682" s="1">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="K682" s="1">
-        <v>5625</v>
+        <v>4500</v>
       </c>
       <c r="L682" s="1">
         <v>0</v>
@@ -34662,7 +34662,7 @@
       </c>
       <c r="N682" s="1"/>
       <c r="O682" s="1">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="P682" s="1" t="s">
         <v>131</v>
@@ -34691,17 +34691,17 @@
         <v>147</v>
       </c>
       <c r="G683" s="1" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="H683" s="1"/>
       <c r="I683" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J683" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K683" s="1">
-        <v>4500</v>
+        <v>15000</v>
       </c>
       <c r="L683" s="1">
         <v>0</v>
@@ -34711,7 +34711,7 @@
       </c>
       <c r="N683" s="1"/>
       <c r="O683" s="1">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="P683" s="1" t="s">
         <v>131</v>
@@ -34744,13 +34744,13 @@
       </c>
       <c r="H684" s="1"/>
       <c r="I684" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J684" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K684" s="1">
-        <v>15000</v>
+        <v>4500</v>
       </c>
       <c r="L684" s="1">
         <v>0</v>
@@ -34760,7 +34760,7 @@
       </c>
       <c r="N684" s="1"/>
       <c r="O684" s="1">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="P684" s="1" t="s">
         <v>131</v>
@@ -34789,17 +34789,17 @@
         <v>147</v>
       </c>
       <c r="G685" s="1" t="s">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="H685" s="1"/>
       <c r="I685" s="1" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="J685" s="1">
-        <v>0.5</v>
+        <v>0.33333333999999998</v>
       </c>
       <c r="K685" s="1">
-        <v>4500</v>
+        <v>3666.6667000000002</v>
       </c>
       <c r="L685" s="1">
         <v>0</v>
@@ -34809,13 +34809,13 @@
       </c>
       <c r="N685" s="1"/>
       <c r="O685" s="1">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="P685" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q685" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="686" spans="1:17" x14ac:dyDescent="0.45">
@@ -34838,17 +34838,17 @@
         <v>147</v>
       </c>
       <c r="G686" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H686" s="1"/>
       <c r="I686" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J686" s="1">
-        <v>0.33333333999999998</v>
+        <v>0.5</v>
       </c>
       <c r="K686" s="1">
-        <v>3666.6667000000002</v>
+        <v>5500</v>
       </c>
       <c r="L686" s="1">
         <v>0</v>
@@ -34858,7 +34858,7 @@
       </c>
       <c r="N686" s="1"/>
       <c r="O686" s="1">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="P686" s="1" t="s">
         <v>131</v>
@@ -34887,17 +34887,17 @@
         <v>147</v>
       </c>
       <c r="G687" s="1" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="H687" s="1"/>
       <c r="I687" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J687" s="1">
-        <v>0.5</v>
+        <v>0.66666669999999995</v>
       </c>
       <c r="K687" s="1">
-        <v>5500</v>
+        <v>7333.3334999999997</v>
       </c>
       <c r="L687" s="1">
         <v>0</v>
@@ -34907,7 +34907,7 @@
       </c>
       <c r="N687" s="1"/>
       <c r="O687" s="1">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="P687" s="1" t="s">
         <v>131</v>
@@ -34936,17 +34936,17 @@
         <v>147</v>
       </c>
       <c r="G688" s="1" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="H688" s="1"/>
       <c r="I688" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J688" s="1">
-        <v>0.66666669999999995</v>
+        <v>0.5</v>
       </c>
       <c r="K688" s="1">
-        <v>7333.3334999999997</v>
+        <v>5500</v>
       </c>
       <c r="L688" s="1">
         <v>0</v>
@@ -34956,7 +34956,7 @@
       </c>
       <c r="N688" s="1"/>
       <c r="O688" s="1">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="P688" s="1" t="s">
         <v>131</v>
@@ -34985,17 +34985,17 @@
         <v>147</v>
       </c>
       <c r="G689" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H689" s="1"/>
       <c r="I689" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J689" s="1">
-        <v>0.5</v>
+        <v>0.33333333999999998</v>
       </c>
       <c r="K689" s="1">
-        <v>5500</v>
+        <v>3666.6667000000002</v>
       </c>
       <c r="L689" s="1">
         <v>0</v>
@@ -35005,7 +35005,7 @@
       </c>
       <c r="N689" s="1"/>
       <c r="O689" s="1">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="P689" s="1" t="s">
         <v>131</v>
@@ -35034,17 +35034,17 @@
         <v>147</v>
       </c>
       <c r="G690" s="1" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="H690" s="1"/>
       <c r="I690" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J690" s="1">
-        <v>0.33333333999999998</v>
+        <v>0.58333330000000005</v>
       </c>
       <c r="K690" s="1">
-        <v>3666.6667000000002</v>
+        <v>6416.6665000000003</v>
       </c>
       <c r="L690" s="1">
         <v>0</v>
@@ -35054,7 +35054,7 @@
       </c>
       <c r="N690" s="1"/>
       <c r="O690" s="1">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="P690" s="1" t="s">
         <v>131</v>
@@ -35083,17 +35083,17 @@
         <v>147</v>
       </c>
       <c r="G691" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H691" s="1"/>
       <c r="I691" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J691" s="1">
-        <v>0.58333330000000005</v>
+        <v>0.25</v>
       </c>
       <c r="K691" s="1">
-        <v>6416.6665000000003</v>
+        <v>2750</v>
       </c>
       <c r="L691" s="1">
         <v>0</v>
@@ -35103,7 +35103,7 @@
       </c>
       <c r="N691" s="1"/>
       <c r="O691" s="1">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="P691" s="1" t="s">
         <v>131</v>
@@ -35132,17 +35132,17 @@
         <v>147</v>
       </c>
       <c r="G692" s="1" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="H692" s="1"/>
       <c r="I692" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J692" s="1">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="K692" s="1">
-        <v>2750</v>
+        <v>11000</v>
       </c>
       <c r="L692" s="1">
         <v>0</v>
@@ -35152,7 +35152,7 @@
       </c>
       <c r="N692" s="1"/>
       <c r="O692" s="1">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="P692" s="1" t="s">
         <v>131</v>
@@ -35181,17 +35181,17 @@
         <v>147</v>
       </c>
       <c r="G693" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H693" s="1"/>
       <c r="I693" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J693" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K693" s="1">
-        <v>11000</v>
+        <v>5500</v>
       </c>
       <c r="L693" s="1">
         <v>0</v>
@@ -35201,7 +35201,7 @@
       </c>
       <c r="N693" s="1"/>
       <c r="O693" s="1">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="P693" s="1" t="s">
         <v>131</v>
@@ -35230,17 +35230,17 @@
         <v>147</v>
       </c>
       <c r="G694" s="1" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="H694" s="1"/>
       <c r="I694" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J694" s="1">
-        <v>0.5</v>
+        <v>0.16666666999999999</v>
       </c>
       <c r="K694" s="1">
-        <v>5500</v>
+        <v>1833.3334</v>
       </c>
       <c r="L694" s="1">
         <v>0</v>
@@ -35250,7 +35250,7 @@
       </c>
       <c r="N694" s="1"/>
       <c r="O694" s="1">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="P694" s="1" t="s">
         <v>131</v>
@@ -35267,45 +35267,45 @@
         <v>0</v>
       </c>
       <c r="C695" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D695" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E695" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F695" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G695" s="1" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="H695" s="1"/>
       <c r="I695" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="J695" s="1">
-        <v>0.16666666999999999</v>
+        <v>1</v>
       </c>
       <c r="K695" s="1">
-        <v>1833.3334</v>
+        <v>26500</v>
       </c>
       <c r="L695" s="1">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="M695" s="1">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="N695" s="1"/>
       <c r="O695" s="1">
-        <v>867</v>
+        <v>946</v>
       </c>
       <c r="P695" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q695" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="696" spans="1:17" x14ac:dyDescent="0.45">
@@ -35332,23 +35332,23 @@
       </c>
       <c r="H696" s="1"/>
       <c r="I696" s="1" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="J696" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K696" s="1">
-        <v>26500</v>
+        <v>4500</v>
       </c>
       <c r="L696" s="1">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="M696" s="1">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="N696" s="1"/>
       <c r="O696" s="1">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="P696" s="1" t="s">
         <v>131</v>
@@ -35381,13 +35381,13 @@
       </c>
       <c r="H697" s="1"/>
       <c r="I697" s="1" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="J697" s="1">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="K697" s="1">
-        <v>4500</v>
+        <v>900</v>
       </c>
       <c r="L697" s="1">
         <v>0</v>
@@ -35397,7 +35397,7 @@
       </c>
       <c r="N697" s="1"/>
       <c r="O697" s="1">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="P697" s="1" t="s">
         <v>131</v>
@@ -35426,17 +35426,17 @@
         <v>148</v>
       </c>
       <c r="G698" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H698" s="1"/>
       <c r="I698" s="1" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="J698" s="1">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="K698" s="1">
-        <v>900</v>
+        <v>36000</v>
       </c>
       <c r="L698" s="1">
         <v>0</v>
@@ -35446,7 +35446,7 @@
       </c>
       <c r="N698" s="1"/>
       <c r="O698" s="1">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="P698" s="1" t="s">
         <v>131</v>
@@ -35475,17 +35475,17 @@
         <v>148</v>
       </c>
       <c r="G699" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H699" s="1"/>
       <c r="I699" s="1" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="J699" s="1">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="K699" s="1">
-        <v>36000</v>
+        <v>28125</v>
       </c>
       <c r="L699" s="1">
         <v>0</v>
@@ -35495,13 +35495,13 @@
       </c>
       <c r="N699" s="1"/>
       <c r="O699" s="1">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="P699" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q699" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="700" spans="1:17" x14ac:dyDescent="0.45">
@@ -35528,13 +35528,13 @@
       </c>
       <c r="H700" s="1"/>
       <c r="I700" s="1" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="J700" s="1">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="K700" s="1">
-        <v>28125</v>
+        <v>26000</v>
       </c>
       <c r="L700" s="1">
         <v>0</v>
@@ -35544,7 +35544,7 @@
       </c>
       <c r="N700" s="1"/>
       <c r="O700" s="1">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="P700" s="1" t="s">
         <v>131</v>
@@ -35573,17 +35573,17 @@
         <v>148</v>
       </c>
       <c r="G701" s="1" t="s">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="H701" s="1"/>
       <c r="I701" s="1" t="s">
         <v>43</v>
       </c>
       <c r="J701" s="1">
-        <v>1</v>
+        <v>0.77777779999999996</v>
       </c>
       <c r="K701" s="1">
-        <v>26000</v>
+        <v>20222.223000000002</v>
       </c>
       <c r="L701" s="1">
         <v>0</v>
@@ -35593,7 +35593,7 @@
       </c>
       <c r="N701" s="1"/>
       <c r="O701" s="1">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="P701" s="1" t="s">
         <v>131</v>
@@ -35622,17 +35622,17 @@
         <v>148</v>
       </c>
       <c r="G702" s="1" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="H702" s="1"/>
       <c r="I702" s="1" t="s">
         <v>43</v>
       </c>
       <c r="J702" s="1">
-        <v>0.77777779999999996</v>
+        <v>1.5555555999999999</v>
       </c>
       <c r="K702" s="1">
-        <v>20222.223000000002</v>
+        <v>40444.445</v>
       </c>
       <c r="L702" s="1">
         <v>0</v>
@@ -35642,7 +35642,7 @@
       </c>
       <c r="N702" s="1"/>
       <c r="O702" s="1">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="P702" s="1" t="s">
         <v>131</v>
@@ -35675,13 +35675,13 @@
       </c>
       <c r="H703" s="1"/>
       <c r="I703" s="1" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="J703" s="1">
-        <v>1.5555555999999999</v>
+        <v>0.5</v>
       </c>
       <c r="K703" s="1">
-        <v>40444.445</v>
+        <v>5625</v>
       </c>
       <c r="L703" s="1">
         <v>0</v>
@@ -35691,7 +35691,7 @@
       </c>
       <c r="N703" s="1"/>
       <c r="O703" s="1">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="P703" s="1" t="s">
         <v>131</v>
@@ -35720,17 +35720,17 @@
         <v>148</v>
       </c>
       <c r="G704" s="1" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="H704" s="1"/>
       <c r="I704" s="1" t="s">
         <v>116</v>
       </c>
       <c r="J704" s="1">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="K704" s="1">
-        <v>5625</v>
+        <v>16875</v>
       </c>
       <c r="L704" s="1">
         <v>0</v>
@@ -35740,7 +35740,7 @@
       </c>
       <c r="N704" s="1"/>
       <c r="O704" s="1">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="P704" s="1" t="s">
         <v>131</v>
@@ -35773,13 +35773,13 @@
       </c>
       <c r="H705" s="1"/>
       <c r="I705" s="1" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="J705" s="1">
-        <v>1.5</v>
+        <v>0.77777779999999996</v>
       </c>
       <c r="K705" s="1">
-        <v>16875</v>
+        <v>20222.223000000002</v>
       </c>
       <c r="L705" s="1">
         <v>0</v>
@@ -35789,7 +35789,7 @@
       </c>
       <c r="N705" s="1"/>
       <c r="O705" s="1">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="P705" s="1" t="s">
         <v>131</v>
@@ -35822,13 +35822,13 @@
       </c>
       <c r="H706" s="1"/>
       <c r="I706" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J706" s="1">
-        <v>0.77777779999999996</v>
+        <v>1</v>
       </c>
       <c r="K706" s="1">
-        <v>20222.223000000002</v>
+        <v>19500</v>
       </c>
       <c r="L706" s="1">
         <v>0</v>
@@ -35838,7 +35838,7 @@
       </c>
       <c r="N706" s="1"/>
       <c r="O706" s="1">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="P706" s="1" t="s">
         <v>131</v>
@@ -35867,17 +35867,17 @@
         <v>148</v>
       </c>
       <c r="G707" s="1" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="H707" s="1"/>
       <c r="I707" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J707" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K707" s="1">
-        <v>19500</v>
+        <v>78000</v>
       </c>
       <c r="L707" s="1">
         <v>0</v>
@@ -35887,7 +35887,7 @@
       </c>
       <c r="N707" s="1"/>
       <c r="O707" s="1">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="P707" s="1" t="s">
         <v>131</v>
@@ -35920,13 +35920,13 @@
       </c>
       <c r="H708" s="1"/>
       <c r="I708" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J708" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K708" s="1">
-        <v>78000</v>
+        <v>39000</v>
       </c>
       <c r="L708" s="1">
         <v>0</v>
@@ -35936,7 +35936,7 @@
       </c>
       <c r="N708" s="1"/>
       <c r="O708" s="1">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="P708" s="1" t="s">
         <v>131</v>
@@ -35969,13 +35969,13 @@
       </c>
       <c r="H709" s="1"/>
       <c r="I709" s="1" t="s">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="J709" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K709" s="1">
-        <v>39000</v>
+        <v>11250</v>
       </c>
       <c r="L709" s="1">
         <v>0</v>
@@ -35985,7 +35985,7 @@
       </c>
       <c r="N709" s="1"/>
       <c r="O709" s="1">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="P709" s="1" t="s">
         <v>131</v>
@@ -36014,17 +36014,17 @@
         <v>148</v>
       </c>
       <c r="G710" s="1" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="H710" s="1"/>
       <c r="I710" s="1" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="J710" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K710" s="1">
-        <v>11250</v>
+        <v>140000</v>
       </c>
       <c r="L710" s="1">
         <v>0</v>
@@ -36034,13 +36034,13 @@
       </c>
       <c r="N710" s="1"/>
       <c r="O710" s="1">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="P710" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q710" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="711" spans="1:17" x14ac:dyDescent="0.45">
@@ -36067,13 +36067,13 @@
       </c>
       <c r="H711" s="1"/>
       <c r="I711" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J711" s="1">
-        <v>5</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K711" s="1">
-        <v>140000</v>
+        <v>1395.8334</v>
       </c>
       <c r="L711" s="1">
         <v>0</v>
@@ -36083,7 +36083,7 @@
       </c>
       <c r="N711" s="1"/>
       <c r="O711" s="1">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="P711" s="1" t="s">
         <v>131</v>
@@ -36112,17 +36112,17 @@
         <v>148</v>
       </c>
       <c r="G712" s="1" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="H712" s="1"/>
       <c r="I712" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J712" s="1">
-        <v>4.1666667999999997E-2</v>
+        <v>0.54166669999999995</v>
       </c>
       <c r="K712" s="1">
-        <v>1395.8334</v>
+        <v>9479.1669999999995</v>
       </c>
       <c r="L712" s="1">
         <v>0</v>
@@ -36132,7 +36132,7 @@
       </c>
       <c r="N712" s="1"/>
       <c r="O712" s="1">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="P712" s="1" t="s">
         <v>131</v>
@@ -36165,13 +36165,13 @@
       </c>
       <c r="H713" s="1"/>
       <c r="I713" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J713" s="1">
-        <v>0.54166669999999995</v>
+        <v>0.66666669999999995</v>
       </c>
       <c r="K713" s="1">
-        <v>9479.1669999999995</v>
+        <v>18666.666000000001</v>
       </c>
       <c r="L713" s="1">
         <v>0</v>
@@ -36181,7 +36181,7 @@
       </c>
       <c r="N713" s="1"/>
       <c r="O713" s="1">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="P713" s="1" t="s">
         <v>131</v>
@@ -36210,17 +36210,17 @@
         <v>148</v>
       </c>
       <c r="G714" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="H714" s="1"/>
       <c r="I714" s="1" t="s">
         <v>42</v>
       </c>
       <c r="J714" s="1">
-        <v>0.66666669999999995</v>
+        <v>3</v>
       </c>
       <c r="K714" s="1">
-        <v>18666.666000000001</v>
+        <v>84000</v>
       </c>
       <c r="L714" s="1">
         <v>0</v>
@@ -36230,7 +36230,7 @@
       </c>
       <c r="N714" s="1"/>
       <c r="O714" s="1">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="P714" s="1" t="s">
         <v>131</v>
@@ -36259,17 +36259,17 @@
         <v>148</v>
       </c>
       <c r="G715" s="1" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="H715" s="1"/>
       <c r="I715" s="1" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="J715" s="1">
-        <v>3</v>
+        <v>2.0416666999999999</v>
       </c>
       <c r="K715" s="1">
-        <v>84000</v>
+        <v>23479.166000000001</v>
       </c>
       <c r="L715" s="1">
         <v>0</v>
@@ -36279,13 +36279,13 @@
       </c>
       <c r="N715" s="1"/>
       <c r="O715" s="1">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="P715" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q715" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="716" spans="1:17" x14ac:dyDescent="0.45">
@@ -36308,17 +36308,17 @@
         <v>148</v>
       </c>
       <c r="G716" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H716" s="1"/>
       <c r="I716" s="1" t="s">
         <v>80</v>
       </c>
       <c r="J716" s="1">
-        <v>2.0416666999999999</v>
+        <v>1</v>
       </c>
       <c r="K716" s="1">
-        <v>23479.166000000001</v>
+        <v>11500</v>
       </c>
       <c r="L716" s="1">
         <v>0</v>
@@ -36328,7 +36328,7 @@
       </c>
       <c r="N716" s="1"/>
       <c r="O716" s="1">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="P716" s="1" t="s">
         <v>131</v>
@@ -36357,17 +36357,17 @@
         <v>148</v>
       </c>
       <c r="G717" s="1" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H717" s="1"/>
       <c r="I717" s="1" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="J717" s="1">
-        <v>1</v>
+        <v>0.20833333000000001</v>
       </c>
       <c r="K717" s="1">
-        <v>11500</v>
+        <v>2604.1667000000002</v>
       </c>
       <c r="L717" s="1">
         <v>0</v>
@@ -36377,13 +36377,13 @@
       </c>
       <c r="N717" s="1"/>
       <c r="O717" s="1">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="P717" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q717" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="718" spans="1:17" x14ac:dyDescent="0.45">
@@ -36410,13 +36410,13 @@
       </c>
       <c r="H718" s="1"/>
       <c r="I718" s="1" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J718" s="1">
-        <v>0.20833333000000001</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K718" s="1">
-        <v>2604.1667000000002</v>
+        <v>1291.6666</v>
       </c>
       <c r="L718" s="1">
         <v>0</v>
@@ -36426,7 +36426,7 @@
       </c>
       <c r="N718" s="1"/>
       <c r="O718" s="1">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="P718" s="1" t="s">
         <v>131</v>
@@ -36459,13 +36459,13 @@
       </c>
       <c r="H719" s="1"/>
       <c r="I719" s="1" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="J719" s="1">
         <v>8.3333335999999994E-2</v>
       </c>
       <c r="K719" s="1">
-        <v>1291.6666</v>
+        <v>1041.6666</v>
       </c>
       <c r="L719" s="1">
         <v>0</v>
@@ -36475,7 +36475,7 @@
       </c>
       <c r="N719" s="1"/>
       <c r="O719" s="1">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="P719" s="1" t="s">
         <v>131</v>
@@ -36504,17 +36504,17 @@
         <v>148</v>
       </c>
       <c r="G720" s="1" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="H720" s="1"/>
       <c r="I720" s="1" t="s">
         <v>39</v>
       </c>
       <c r="J720" s="1">
-        <v>8.3333335999999994E-2</v>
+        <v>1.25</v>
       </c>
       <c r="K720" s="1">
-        <v>1041.6666</v>
+        <v>15625</v>
       </c>
       <c r="L720" s="1">
         <v>0</v>
@@ -36524,7 +36524,7 @@
       </c>
       <c r="N720" s="1"/>
       <c r="O720" s="1">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="P720" s="1" t="s">
         <v>131</v>
@@ -36557,13 +36557,13 @@
       </c>
       <c r="H721" s="1"/>
       <c r="I721" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J721" s="1">
-        <v>1.25</v>
+        <v>0.66666669999999995</v>
       </c>
       <c r="K721" s="1">
-        <v>15625</v>
+        <v>8333.3330000000005</v>
       </c>
       <c r="L721" s="1">
         <v>0</v>
@@ -36573,7 +36573,7 @@
       </c>
       <c r="N721" s="1"/>
       <c r="O721" s="1">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="P721" s="1" t="s">
         <v>131</v>
@@ -36606,13 +36606,13 @@
       </c>
       <c r="H722" s="1"/>
       <c r="I722" s="1" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J722" s="1">
-        <v>0.66666669999999995</v>
+        <v>0.16666666999999999</v>
       </c>
       <c r="K722" s="1">
-        <v>8333.3330000000005</v>
+        <v>2583.3332999999998</v>
       </c>
       <c r="L722" s="1">
         <v>0</v>
@@ -36622,7 +36622,7 @@
       </c>
       <c r="N722" s="1"/>
       <c r="O722" s="1">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="P722" s="1" t="s">
         <v>131</v>
@@ -36651,17 +36651,17 @@
         <v>148</v>
       </c>
       <c r="G723" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="H723" s="1"/>
       <c r="I723" s="1" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="J723" s="1">
-        <v>0.16666666999999999</v>
+        <v>1</v>
       </c>
       <c r="K723" s="1">
-        <v>2583.3332999999998</v>
+        <v>15500</v>
       </c>
       <c r="L723" s="1">
         <v>0</v>
@@ -36671,13 +36671,13 @@
       </c>
       <c r="N723" s="1"/>
       <c r="O723" s="1">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="P723" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q723" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="724" spans="1:17" x14ac:dyDescent="0.45">
@@ -36704,13 +36704,13 @@
       </c>
       <c r="H724" s="1"/>
       <c r="I724" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="J724" s="1">
-        <v>1</v>
+        <v>0.33333333999999998</v>
       </c>
       <c r="K724" s="1">
-        <v>15500</v>
+        <v>3333.3332999999998</v>
       </c>
       <c r="L724" s="1">
         <v>0</v>
@@ -36720,7 +36720,7 @@
       </c>
       <c r="N724" s="1"/>
       <c r="O724" s="1">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="P724" s="1" t="s">
         <v>131</v>
@@ -36753,13 +36753,13 @@
       </c>
       <c r="H725" s="1"/>
       <c r="I725" s="1" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="J725" s="1">
         <v>0.33333333999999998</v>
       </c>
       <c r="K725" s="1">
-        <v>3333.3332999999998</v>
+        <v>4000</v>
       </c>
       <c r="L725" s="1">
         <v>0</v>
@@ -36769,7 +36769,7 @@
       </c>
       <c r="N725" s="1"/>
       <c r="O725" s="1">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="P725" s="1" t="s">
         <v>131</v>
@@ -36798,17 +36798,17 @@
         <v>148</v>
       </c>
       <c r="G726" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H726" s="1"/>
       <c r="I726" s="1" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="J726" s="1">
-        <v>0.33333333999999998</v>
+        <v>0.5</v>
       </c>
       <c r="K726" s="1">
-        <v>4000</v>
+        <v>7750</v>
       </c>
       <c r="L726" s="1">
         <v>0</v>
@@ -36818,7 +36818,7 @@
       </c>
       <c r="N726" s="1"/>
       <c r="O726" s="1">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="P726" s="1" t="s">
         <v>131</v>
@@ -36851,13 +36851,13 @@
       </c>
       <c r="H727" s="1"/>
       <c r="I727" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="J727" s="1">
-        <v>0.5</v>
+        <v>1.3333333999999999</v>
       </c>
       <c r="K727" s="1">
-        <v>7750</v>
+        <v>13333.333000000001</v>
       </c>
       <c r="L727" s="1">
         <v>0</v>
@@ -36867,7 +36867,7 @@
       </c>
       <c r="N727" s="1"/>
       <c r="O727" s="1">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="P727" s="1" t="s">
         <v>131</v>
@@ -36900,13 +36900,13 @@
       </c>
       <c r="H728" s="1"/>
       <c r="I728" s="1" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="J728" s="1">
-        <v>1.3333333999999999</v>
+        <v>0.5</v>
       </c>
       <c r="K728" s="1">
-        <v>13333.333000000001</v>
+        <v>6000</v>
       </c>
       <c r="L728" s="1">
         <v>0</v>
@@ -36916,7 +36916,7 @@
       </c>
       <c r="N728" s="1"/>
       <c r="O728" s="1">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="P728" s="1" t="s">
         <v>131</v>
@@ -36933,45 +36933,45 @@
         <v>0</v>
       </c>
       <c r="C729" s="1" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="D729" s="1" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="E729" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F729" s="1" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="G729" s="1" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="H729" s="1"/>
       <c r="I729" s="1" t="s">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="J729" s="1">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="K729" s="1">
-        <v>6000</v>
+        <v>28125</v>
       </c>
       <c r="L729" s="1">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="M729" s="1">
         <v>0</v>
       </c>
       <c r="N729" s="1"/>
       <c r="O729" s="1">
-        <v>979</v>
+        <v>873</v>
       </c>
       <c r="P729" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q729" s="1" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="730" spans="1:17" x14ac:dyDescent="0.45">
@@ -36998,23 +36998,23 @@
       </c>
       <c r="H730" s="1"/>
       <c r="I730" s="1" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="J730" s="1">
-        <v>2.5</v>
+        <v>0.77777779999999996</v>
       </c>
       <c r="K730" s="1">
-        <v>28125</v>
+        <v>20222.223000000002</v>
       </c>
       <c r="L730" s="1">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="M730" s="1">
         <v>0</v>
       </c>
       <c r="N730" s="1"/>
       <c r="O730" s="1">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="P730" s="1" t="s">
         <v>131</v>
@@ -37047,13 +37047,13 @@
       </c>
       <c r="H731" s="1"/>
       <c r="I731" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J731" s="1">
-        <v>0.77777779999999996</v>
+        <v>0.5</v>
       </c>
       <c r="K731" s="1">
-        <v>20222.223000000002</v>
+        <v>9750</v>
       </c>
       <c r="L731" s="1">
         <v>0</v>
@@ -37063,7 +37063,7 @@
       </c>
       <c r="N731" s="1"/>
       <c r="O731" s="1">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="P731" s="1" t="s">
         <v>131</v>
@@ -37092,17 +37092,17 @@
         <v>136</v>
       </c>
       <c r="G732" s="1" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="H732" s="1"/>
       <c r="I732" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J732" s="1">
-        <v>0.5</v>
+        <v>3.5555555999999999</v>
       </c>
       <c r="K732" s="1">
-        <v>9750</v>
+        <v>92444.445000000007</v>
       </c>
       <c r="L732" s="1">
         <v>0</v>
@@ -37112,7 +37112,7 @@
       </c>
       <c r="N732" s="1"/>
       <c r="O732" s="1">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="P732" s="1" t="s">
         <v>131</v>
@@ -37145,13 +37145,13 @@
       </c>
       <c r="H733" s="1"/>
       <c r="I733" s="1" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="J733" s="1">
-        <v>3.5555555999999999</v>
+        <v>1</v>
       </c>
       <c r="K733" s="1">
-        <v>92444.445000000007</v>
+        <v>11250</v>
       </c>
       <c r="L733" s="1">
         <v>0</v>
@@ -37161,7 +37161,7 @@
       </c>
       <c r="N733" s="1"/>
       <c r="O733" s="1">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="P733" s="1" t="s">
         <v>131</v>
@@ -37190,7 +37190,7 @@
         <v>136</v>
       </c>
       <c r="G734" s="1" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="H734" s="1"/>
       <c r="I734" s="1" t="s">
@@ -37210,7 +37210,7 @@
       </c>
       <c r="N734" s="1"/>
       <c r="O734" s="1">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="P734" s="1" t="s">
         <v>131</v>
@@ -37243,13 +37243,13 @@
       </c>
       <c r="H735" s="1"/>
       <c r="I735" s="1" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="J735" s="1">
-        <v>1</v>
+        <v>0.11111111</v>
       </c>
       <c r="K735" s="1">
-        <v>11250</v>
+        <v>2888.8890000000001</v>
       </c>
       <c r="L735" s="1">
         <v>0</v>
@@ -37259,7 +37259,7 @@
       </c>
       <c r="N735" s="1"/>
       <c r="O735" s="1">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="P735" s="1" t="s">
         <v>131</v>
@@ -37288,17 +37288,17 @@
         <v>136</v>
       </c>
       <c r="G736" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H736" s="1"/>
       <c r="I736" s="1" t="s">
         <v>43</v>
       </c>
       <c r="J736" s="1">
-        <v>0.11111111</v>
+        <v>1.3333333999999999</v>
       </c>
       <c r="K736" s="1">
-        <v>2888.8890000000001</v>
+        <v>34666.667999999998</v>
       </c>
       <c r="L736" s="1">
         <v>0</v>
@@ -37308,7 +37308,7 @@
       </c>
       <c r="N736" s="1"/>
       <c r="O736" s="1">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="P736" s="1" t="s">
         <v>131</v>
@@ -37341,13 +37341,13 @@
       </c>
       <c r="H737" s="1"/>
       <c r="I737" s="1" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="J737" s="1">
-        <v>1.3333333999999999</v>
+        <v>1.5</v>
       </c>
       <c r="K737" s="1">
-        <v>34666.667999999998</v>
+        <v>16875</v>
       </c>
       <c r="L737" s="1">
         <v>0</v>
@@ -37357,7 +37357,7 @@
       </c>
       <c r="N737" s="1"/>
       <c r="O737" s="1">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="P737" s="1" t="s">
         <v>131</v>
@@ -37390,13 +37390,13 @@
       </c>
       <c r="H738" s="1"/>
       <c r="I738" s="1" t="s">
-        <v>116</v>
+        <v>41</v>
       </c>
       <c r="J738" s="1">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="K738" s="1">
-        <v>16875</v>
+        <v>9750</v>
       </c>
       <c r="L738" s="1">
         <v>0</v>
@@ -37406,7 +37406,7 @@
       </c>
       <c r="N738" s="1"/>
       <c r="O738" s="1">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="P738" s="1" t="s">
         <v>131</v>
@@ -37435,17 +37435,17 @@
         <v>136</v>
       </c>
       <c r="G739" s="1" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="H739" s="1"/>
       <c r="I739" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J739" s="1">
-        <v>0.5</v>
+        <v>1.5555555999999999</v>
       </c>
       <c r="K739" s="1">
-        <v>9750</v>
+        <v>43555.555</v>
       </c>
       <c r="L739" s="1">
         <v>0</v>
@@ -37455,13 +37455,13 @@
       </c>
       <c r="N739" s="1"/>
       <c r="O739" s="1">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="P739" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q739" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="740" spans="1:17" x14ac:dyDescent="0.45">
@@ -37488,13 +37488,13 @@
       </c>
       <c r="H740" s="1"/>
       <c r="I740" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J740" s="1">
-        <v>1.5555555999999999</v>
+        <v>0.5</v>
       </c>
       <c r="K740" s="1">
-        <v>43555.555</v>
+        <v>8750</v>
       </c>
       <c r="L740" s="1">
         <v>0</v>
@@ -37504,7 +37504,7 @@
       </c>
       <c r="N740" s="1"/>
       <c r="O740" s="1">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="P740" s="1" t="s">
         <v>131</v>
@@ -37533,17 +37533,17 @@
         <v>136</v>
       </c>
       <c r="G741" s="1" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="H741" s="1"/>
       <c r="I741" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J741" s="1">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="K741" s="1">
-        <v>8750</v>
+        <v>84000</v>
       </c>
       <c r="L741" s="1">
         <v>0</v>
@@ -37553,7 +37553,7 @@
       </c>
       <c r="N741" s="1"/>
       <c r="O741" s="1">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="P741" s="1" t="s">
         <v>131</v>
@@ -37582,17 +37582,17 @@
         <v>136</v>
       </c>
       <c r="G742" s="1" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="H742" s="1"/>
       <c r="I742" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J742" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K742" s="1">
-        <v>84000</v>
+        <v>62500</v>
       </c>
       <c r="L742" s="1">
         <v>0</v>
@@ -37602,13 +37602,13 @@
       </c>
       <c r="N742" s="1"/>
       <c r="O742" s="1">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="P742" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q742" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="743" spans="1:17" x14ac:dyDescent="0.45">
@@ -37635,13 +37635,13 @@
       </c>
       <c r="H743" s="1"/>
       <c r="I743" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J743" s="1">
-        <v>5</v>
+        <v>0.58333330000000005</v>
       </c>
       <c r="K743" s="1">
-        <v>62500</v>
+        <v>7291.6665000000003</v>
       </c>
       <c r="L743" s="1">
         <v>0</v>
@@ -37651,7 +37651,7 @@
       </c>
       <c r="N743" s="1"/>
       <c r="O743" s="1">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="P743" s="1" t="s">
         <v>131</v>
@@ -37684,13 +37684,13 @@
       </c>
       <c r="H744" s="1"/>
       <c r="I744" s="1" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="J744" s="1">
-        <v>0.58333330000000005</v>
+        <v>0.2</v>
       </c>
       <c r="K744" s="1">
-        <v>7291.6665000000003</v>
+        <v>2200</v>
       </c>
       <c r="L744" s="1">
         <v>0</v>
@@ -37700,7 +37700,7 @@
       </c>
       <c r="N744" s="1"/>
       <c r="O744" s="1">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="P744" s="1" t="s">
         <v>131</v>
@@ -37729,17 +37729,17 @@
         <v>136</v>
       </c>
       <c r="G745" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H745" s="1"/>
       <c r="I745" s="1" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="J745" s="1">
-        <v>0.2</v>
+        <v>0.91666669999999995</v>
       </c>
       <c r="K745" s="1">
-        <v>2200</v>
+        <v>14208.333000000001</v>
       </c>
       <c r="L745" s="1">
         <v>0</v>
@@ -37749,7 +37749,7 @@
       </c>
       <c r="N745" s="1"/>
       <c r="O745" s="1">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="P745" s="1" t="s">
         <v>131</v>
@@ -37778,17 +37778,17 @@
         <v>136</v>
       </c>
       <c r="G746" s="1" t="s">
-        <v>67</v>
+        <v>138</v>
       </c>
       <c r="H746" s="1"/>
       <c r="I746" s="1" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="J746" s="1">
-        <v>0.91666669999999995</v>
+        <v>1</v>
       </c>
       <c r="K746" s="1">
-        <v>14208.333000000001</v>
+        <v>10000</v>
       </c>
       <c r="L746" s="1">
         <v>0</v>
@@ -37798,13 +37798,13 @@
       </c>
       <c r="N746" s="1"/>
       <c r="O746" s="1">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="P746" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q746" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="747" spans="1:17" x14ac:dyDescent="0.45">
@@ -37827,17 +37827,17 @@
         <v>136</v>
       </c>
       <c r="G747" s="1" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="H747" s="1"/>
       <c r="I747" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="J747" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K747" s="1">
-        <v>10000</v>
+        <v>31000</v>
       </c>
       <c r="L747" s="1">
         <v>0</v>
@@ -37847,7 +37847,7 @@
       </c>
       <c r="N747" s="1"/>
       <c r="O747" s="1">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="P747" s="1" t="s">
         <v>131</v>
@@ -37880,13 +37880,13 @@
       </c>
       <c r="H748" s="1"/>
       <c r="I748" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="J748" s="1">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="K748" s="1">
-        <v>31000</v>
+        <v>5000</v>
       </c>
       <c r="L748" s="1">
         <v>0</v>
@@ -37896,7 +37896,7 @@
       </c>
       <c r="N748" s="1"/>
       <c r="O748" s="1">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="P748" s="1" t="s">
         <v>131</v>
@@ -37925,17 +37925,17 @@
         <v>136</v>
       </c>
       <c r="G749" s="1" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="H749" s="1"/>
       <c r="I749" s="1" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="J749" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K749" s="1">
-        <v>5000</v>
+        <v>26500</v>
       </c>
       <c r="L749" s="1">
         <v>0</v>
@@ -37945,13 +37945,13 @@
       </c>
       <c r="N749" s="1"/>
       <c r="O749" s="1">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="P749" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q749" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="750" spans="1:17" x14ac:dyDescent="0.45">
@@ -37974,7 +37974,7 @@
         <v>136</v>
       </c>
       <c r="G750" s="1" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="H750" s="1"/>
       <c r="I750" s="1" t="s">
@@ -37994,7 +37994,7 @@
       </c>
       <c r="N750" s="1"/>
       <c r="O750" s="1">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="P750" s="1" t="s">
         <v>131</v>
@@ -38023,17 +38023,17 @@
         <v>136</v>
       </c>
       <c r="G751" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H751" s="1"/>
       <c r="I751" s="1" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="J751" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K751" s="1">
-        <v>26500</v>
+        <v>27000</v>
       </c>
       <c r="L751" s="1">
         <v>0</v>
@@ -38043,7 +38043,7 @@
       </c>
       <c r="N751" s="1"/>
       <c r="O751" s="1">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="P751" s="1" t="s">
         <v>131</v>
@@ -38072,17 +38072,17 @@
         <v>136</v>
       </c>
       <c r="G752" s="1" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="H752" s="1"/>
       <c r="I752" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J752" s="1">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="K752" s="1">
-        <v>27000</v>
+        <v>4500</v>
       </c>
       <c r="L752" s="1">
         <v>0</v>
@@ -38092,7 +38092,7 @@
       </c>
       <c r="N752" s="1"/>
       <c r="O752" s="1">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="P752" s="1" t="s">
         <v>131</v>
@@ -38125,13 +38125,13 @@
       </c>
       <c r="H753" s="1"/>
       <c r="I753" s="1" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="J753" s="1">
         <v>0.5</v>
       </c>
       <c r="K753" s="1">
-        <v>4500</v>
+        <v>13250</v>
       </c>
       <c r="L753" s="1">
         <v>0</v>
@@ -38141,7 +38141,7 @@
       </c>
       <c r="N753" s="1"/>
       <c r="O753" s="1">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="P753" s="1" t="s">
         <v>131</v>
@@ -38170,17 +38170,17 @@
         <v>136</v>
       </c>
       <c r="G754" s="1" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="H754" s="1"/>
       <c r="I754" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J754" s="1">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K754" s="1">
-        <v>13250</v>
+        <v>23000</v>
       </c>
       <c r="L754" s="1">
         <v>0</v>
@@ -38190,13 +38190,13 @@
       </c>
       <c r="N754" s="1"/>
       <c r="O754" s="1">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="P754" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q754" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="755" spans="1:17" x14ac:dyDescent="0.45">
@@ -38219,7 +38219,7 @@
         <v>136</v>
       </c>
       <c r="G755" s="1" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="H755" s="1"/>
       <c r="I755" s="1" t="s">
@@ -38239,7 +38239,7 @@
       </c>
       <c r="N755" s="1"/>
       <c r="O755" s="1">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="P755" s="1" t="s">
         <v>131</v>
@@ -38268,17 +38268,17 @@
         <v>136</v>
       </c>
       <c r="G756" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H756" s="1"/>
       <c r="I756" s="1" t="s">
         <v>80</v>
       </c>
       <c r="J756" s="1">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="K756" s="1">
-        <v>23000</v>
+        <v>14375</v>
       </c>
       <c r="L756" s="1">
         <v>0</v>
@@ -38288,7 +38288,7 @@
       </c>
       <c r="N756" s="1"/>
       <c r="O756" s="1">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="P756" s="1" t="s">
         <v>131</v>
@@ -38317,17 +38317,17 @@
         <v>136</v>
       </c>
       <c r="G757" s="1" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="H757" s="1"/>
       <c r="I757" s="1" t="s">
         <v>80</v>
       </c>
       <c r="J757" s="1">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="K757" s="1">
-        <v>14375</v>
+        <v>11500</v>
       </c>
       <c r="L757" s="1">
         <v>0</v>
@@ -38337,7 +38337,7 @@
       </c>
       <c r="N757" s="1"/>
       <c r="O757" s="1">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="P757" s="1" t="s">
         <v>131</v>
@@ -38348,35 +38348,35 @@
     </row>
     <row r="758" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A758" s="2">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B758" s="1">
         <v>0</v>
       </c>
       <c r="C758" s="1" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="D758" s="1" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="E758" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F758" s="1" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="G758" s="1" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="H758" s="1"/>
       <c r="I758" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="J758" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K758" s="1">
-        <v>11500</v>
+        <v>5500</v>
       </c>
       <c r="L758" s="1">
         <v>0</v>
@@ -38386,13 +38386,13 @@
       </c>
       <c r="N758" s="1"/>
       <c r="O758" s="1">
-        <v>901</v>
+        <v>689</v>
       </c>
       <c r="P758" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q758" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="759" spans="1:17" x14ac:dyDescent="0.45">
@@ -38415,17 +38415,17 @@
         <v>149</v>
       </c>
       <c r="G759" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H759" s="1"/>
       <c r="I759" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J759" s="1">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K759" s="1">
-        <v>5500</v>
+        <v>2750</v>
       </c>
       <c r="L759" s="1">
         <v>0</v>
@@ -38435,7 +38435,7 @@
       </c>
       <c r="N759" s="1"/>
       <c r="O759" s="1">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="P759" s="1" t="s">
         <v>131</v>
@@ -38464,7 +38464,7 @@
         <v>149</v>
       </c>
       <c r="G760" s="1" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="H760" s="1"/>
       <c r="I760" s="1" t="s">
@@ -38484,7 +38484,7 @@
       </c>
       <c r="N760" s="1"/>
       <c r="O760" s="1">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="P760" s="1" t="s">
         <v>131</v>
@@ -38513,17 +38513,17 @@
         <v>149</v>
       </c>
       <c r="G761" s="1" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="H761" s="1"/>
       <c r="I761" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J761" s="1">
-        <v>0.25</v>
+        <v>0.58333330000000005</v>
       </c>
       <c r="K761" s="1">
-        <v>2750</v>
+        <v>6416.6665000000003</v>
       </c>
       <c r="L761" s="1">
         <v>0</v>
@@ -38533,7 +38533,7 @@
       </c>
       <c r="N761" s="1"/>
       <c r="O761" s="1">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="P761" s="1" t="s">
         <v>131</v>
@@ -38562,17 +38562,17 @@
         <v>149</v>
       </c>
       <c r="G762" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H762" s="1"/>
       <c r="I762" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J762" s="1">
-        <v>0.58333330000000005</v>
+        <v>0.25</v>
       </c>
       <c r="K762" s="1">
-        <v>6416.6665000000003</v>
+        <v>2750</v>
       </c>
       <c r="L762" s="1">
         <v>0</v>
@@ -38582,7 +38582,7 @@
       </c>
       <c r="N762" s="1"/>
       <c r="O762" s="1">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="P762" s="1" t="s">
         <v>131</v>
@@ -38611,17 +38611,17 @@
         <v>149</v>
       </c>
       <c r="G763" s="1" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="H763" s="1"/>
       <c r="I763" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J763" s="1">
-        <v>0.25</v>
+        <v>0.16666666999999999</v>
       </c>
       <c r="K763" s="1">
-        <v>2750</v>
+        <v>1833.3334</v>
       </c>
       <c r="L763" s="1">
         <v>0</v>
@@ -38631,7 +38631,7 @@
       </c>
       <c r="N763" s="1"/>
       <c r="O763" s="1">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="P763" s="1" t="s">
         <v>131</v>
@@ -38660,17 +38660,17 @@
         <v>149</v>
       </c>
       <c r="G764" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H764" s="1"/>
       <c r="I764" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J764" s="1">
-        <v>0.16666666999999999</v>
+        <v>0.25</v>
       </c>
       <c r="K764" s="1">
-        <v>1833.3334</v>
+        <v>2750</v>
       </c>
       <c r="L764" s="1">
         <v>0</v>
@@ -38680,7 +38680,7 @@
       </c>
       <c r="N764" s="1"/>
       <c r="O764" s="1">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="P764" s="1" t="s">
         <v>131</v>
@@ -38709,17 +38709,17 @@
         <v>149</v>
       </c>
       <c r="G765" s="1" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="H765" s="1"/>
       <c r="I765" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J765" s="1">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="K765" s="1">
-        <v>2750</v>
+        <v>5500</v>
       </c>
       <c r="L765" s="1">
         <v>0</v>
@@ -38729,7 +38729,7 @@
       </c>
       <c r="N765" s="1"/>
       <c r="O765" s="1">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="P765" s="1" t="s">
         <v>131</v>
@@ -38758,17 +38758,17 @@
         <v>149</v>
       </c>
       <c r="G766" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H766" s="1"/>
       <c r="I766" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J766" s="1">
-        <v>0.5</v>
+        <v>0.16666666999999999</v>
       </c>
       <c r="K766" s="1">
-        <v>5500</v>
+        <v>1833.3334</v>
       </c>
       <c r="L766" s="1">
         <v>0</v>
@@ -38778,7 +38778,7 @@
       </c>
       <c r="N766" s="1"/>
       <c r="O766" s="1">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="P766" s="1" t="s">
         <v>131</v>
@@ -38807,17 +38807,17 @@
         <v>149</v>
       </c>
       <c r="G767" s="1" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="H767" s="1"/>
       <c r="I767" s="1" t="s">
         <v>72</v>
       </c>
       <c r="J767" s="1">
-        <v>0.16666666999999999</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K767" s="1">
-        <v>1833.3334</v>
+        <v>916.66669999999999</v>
       </c>
       <c r="L767" s="1">
         <v>0</v>
@@ -38827,7 +38827,7 @@
       </c>
       <c r="N767" s="1"/>
       <c r="O767" s="1">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="P767" s="1" t="s">
         <v>131</v>
@@ -38856,17 +38856,17 @@
         <v>149</v>
       </c>
       <c r="G768" s="1" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="H768" s="1"/>
       <c r="I768" s="1" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="J768" s="1">
-        <v>8.3333335999999994E-2</v>
+        <v>1.625</v>
       </c>
       <c r="K768" s="1">
-        <v>916.66669999999999</v>
+        <v>24375</v>
       </c>
       <c r="L768" s="1">
         <v>0</v>
@@ -38876,13 +38876,13 @@
       </c>
       <c r="N768" s="1"/>
       <c r="O768" s="1">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="P768" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q768" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="769" spans="1:17" x14ac:dyDescent="0.45">
@@ -38905,17 +38905,17 @@
         <v>149</v>
       </c>
       <c r="G769" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H769" s="1"/>
       <c r="I769" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J769" s="1">
-        <v>1.625</v>
+        <v>2</v>
       </c>
       <c r="K769" s="1">
-        <v>24375</v>
+        <v>30000</v>
       </c>
       <c r="L769" s="1">
         <v>0</v>
@@ -38925,7 +38925,7 @@
       </c>
       <c r="N769" s="1"/>
       <c r="O769" s="1">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="P769" s="1" t="s">
         <v>131</v>
@@ -38958,13 +38958,13 @@
       </c>
       <c r="H770" s="1"/>
       <c r="I770" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J770" s="1">
-        <v>2</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K770" s="1">
-        <v>30000</v>
+        <v>750</v>
       </c>
       <c r="L770" s="1">
         <v>0</v>
@@ -38974,7 +38974,7 @@
       </c>
       <c r="N770" s="1"/>
       <c r="O770" s="1">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="P770" s="1" t="s">
         <v>131</v>
@@ -39003,17 +39003,17 @@
         <v>149</v>
       </c>
       <c r="G771" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H771" s="1"/>
       <c r="I771" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J771" s="1">
-        <v>8.3333335999999994E-2</v>
+        <v>1</v>
       </c>
       <c r="K771" s="1">
-        <v>750</v>
+        <v>15000</v>
       </c>
       <c r="L771" s="1">
         <v>0</v>
@@ -39023,7 +39023,7 @@
       </c>
       <c r="N771" s="1"/>
       <c r="O771" s="1">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="P771" s="1" t="s">
         <v>131</v>
@@ -39056,7 +39056,7 @@
       </c>
       <c r="H772" s="1"/>
       <c r="I772" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J772" s="1">
         <v>1</v>
@@ -39072,7 +39072,7 @@
       </c>
       <c r="N772" s="1"/>
       <c r="O772" s="1">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="P772" s="1" t="s">
         <v>131</v>
@@ -39101,17 +39101,17 @@
         <v>149</v>
       </c>
       <c r="G773" s="1" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="H773" s="1"/>
       <c r="I773" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J773" s="1">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="K773" s="1">
-        <v>15000</v>
+        <v>13125</v>
       </c>
       <c r="L773" s="1">
         <v>0</v>
@@ -39121,7 +39121,7 @@
       </c>
       <c r="N773" s="1"/>
       <c r="O773" s="1">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="P773" s="1" t="s">
         <v>131</v>
@@ -39150,17 +39150,17 @@
         <v>149</v>
       </c>
       <c r="G774" s="1" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H774" s="1"/>
       <c r="I774" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J774" s="1">
-        <v>0.875</v>
+        <v>0.5</v>
       </c>
       <c r="K774" s="1">
-        <v>13125</v>
+        <v>7500</v>
       </c>
       <c r="L774" s="1">
         <v>0</v>
@@ -39170,7 +39170,7 @@
       </c>
       <c r="N774" s="1"/>
       <c r="O774" s="1">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="P774" s="1" t="s">
         <v>131</v>
@@ -39199,7 +39199,7 @@
         <v>149</v>
       </c>
       <c r="G775" s="1" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="H775" s="1"/>
       <c r="I775" s="1" t="s">
@@ -39219,7 +39219,7 @@
       </c>
       <c r="N775" s="1"/>
       <c r="O775" s="1">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="P775" s="1" t="s">
         <v>131</v>
@@ -39248,17 +39248,17 @@
         <v>149</v>
       </c>
       <c r="G776" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H776" s="1"/>
       <c r="I776" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J776" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K776" s="1">
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="L776" s="1">
         <v>0</v>
@@ -39268,7 +39268,7 @@
       </c>
       <c r="N776" s="1"/>
       <c r="O776" s="1">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="P776" s="1" t="s">
         <v>131</v>
@@ -39297,17 +39297,17 @@
         <v>149</v>
       </c>
       <c r="G777" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H777" s="1"/>
       <c r="I777" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J777" s="1">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="K777" s="1">
-        <v>15000</v>
+        <v>13125</v>
       </c>
       <c r="L777" s="1">
         <v>0</v>
@@ -39317,7 +39317,7 @@
       </c>
       <c r="N777" s="1"/>
       <c r="O777" s="1">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="P777" s="1" t="s">
         <v>131</v>
@@ -39346,17 +39346,17 @@
         <v>149</v>
       </c>
       <c r="G778" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="H778" s="1"/>
       <c r="I778" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J778" s="1">
-        <v>0.875</v>
+        <v>1.125</v>
       </c>
       <c r="K778" s="1">
-        <v>13125</v>
+        <v>16875</v>
       </c>
       <c r="L778" s="1">
         <v>0</v>
@@ -39366,7 +39366,7 @@
       </c>
       <c r="N778" s="1"/>
       <c r="O778" s="1">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="P778" s="1" t="s">
         <v>131</v>
@@ -39399,13 +39399,13 @@
       </c>
       <c r="H779" s="1"/>
       <c r="I779" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J779" s="1">
-        <v>1.125</v>
+        <v>1.0833333999999999</v>
       </c>
       <c r="K779" s="1">
-        <v>16875</v>
+        <v>9750</v>
       </c>
       <c r="L779" s="1">
         <v>0</v>
@@ -39415,7 +39415,7 @@
       </c>
       <c r="N779" s="1"/>
       <c r="O779" s="1">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="P779" s="1" t="s">
         <v>131</v>
@@ -39432,45 +39432,45 @@
         <v>0</v>
       </c>
       <c r="C780" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D780" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E780" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F780" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G780" s="1" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="H780" s="1"/>
       <c r="I780" s="1" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="J780" s="1">
-        <v>1.0833333999999999</v>
+        <v>2</v>
       </c>
       <c r="K780" s="1">
-        <v>9750</v>
+        <v>56000</v>
       </c>
       <c r="L780" s="1">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="M780" s="1">
         <v>0</v>
       </c>
       <c r="N780" s="1"/>
       <c r="O780" s="1">
-        <v>710</v>
+        <v>762</v>
       </c>
       <c r="P780" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q780" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="781" spans="1:17" x14ac:dyDescent="0.45">
@@ -39493,27 +39493,27 @@
         <v>150</v>
       </c>
       <c r="G781" s="1" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="H781" s="1"/>
       <c r="I781" s="1" t="s">
         <v>42</v>
       </c>
       <c r="J781" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K781" s="1">
-        <v>56000</v>
+        <v>28000</v>
       </c>
       <c r="L781" s="1">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="M781" s="1">
         <v>0</v>
       </c>
       <c r="N781" s="1"/>
       <c r="O781" s="1">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="P781" s="1" t="s">
         <v>131</v>
@@ -39542,7 +39542,7 @@
         <v>150</v>
       </c>
       <c r="G782" s="1" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="H782" s="1"/>
       <c r="I782" s="1" t="s">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="N782" s="1"/>
       <c r="O782" s="1">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="P782" s="1" t="s">
         <v>131</v>
@@ -39591,17 +39591,17 @@
         <v>150</v>
       </c>
       <c r="G783" s="1" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="H783" s="1"/>
       <c r="I783" s="1" t="s">
         <v>42</v>
       </c>
       <c r="J783" s="1">
-        <v>1</v>
+        <v>0.44444444999999999</v>
       </c>
       <c r="K783" s="1">
-        <v>28000</v>
+        <v>12444.444</v>
       </c>
       <c r="L783" s="1">
         <v>0</v>
@@ -39611,7 +39611,7 @@
       </c>
       <c r="N783" s="1"/>
       <c r="O783" s="1">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="P783" s="1" t="s">
         <v>131</v>
@@ -39640,17 +39640,17 @@
         <v>150</v>
       </c>
       <c r="G784" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H784" s="1"/>
       <c r="I784" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J784" s="1">
-        <v>0.44444444999999999</v>
+        <v>0.25</v>
       </c>
       <c r="K784" s="1">
-        <v>12444.444</v>
+        <v>3125</v>
       </c>
       <c r="L784" s="1">
         <v>0</v>
@@ -39660,13 +39660,13 @@
       </c>
       <c r="N784" s="1"/>
       <c r="O784" s="1">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="P784" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q784" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="785" spans="1:17" x14ac:dyDescent="0.45">
@@ -39693,13 +39693,13 @@
       </c>
       <c r="H785" s="1"/>
       <c r="I785" s="1" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J785" s="1">
-        <v>0.25</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K785" s="1">
-        <v>3125</v>
+        <v>1291.6666</v>
       </c>
       <c r="L785" s="1">
         <v>0</v>
@@ -39709,7 +39709,7 @@
       </c>
       <c r="N785" s="1"/>
       <c r="O785" s="1">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="P785" s="1" t="s">
         <v>131</v>
@@ -39742,13 +39742,13 @@
       </c>
       <c r="H786" s="1"/>
       <c r="I786" s="1" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="J786" s="1">
-        <v>8.3333335999999994E-2</v>
+        <v>0.25</v>
       </c>
       <c r="K786" s="1">
-        <v>1291.6666</v>
+        <v>3125</v>
       </c>
       <c r="L786" s="1">
         <v>0</v>
@@ -39758,7 +39758,7 @@
       </c>
       <c r="N786" s="1"/>
       <c r="O786" s="1">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="P786" s="1" t="s">
         <v>131</v>
@@ -39787,17 +39787,17 @@
         <v>150</v>
       </c>
       <c r="G787" s="1" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="H787" s="1"/>
       <c r="I787" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J787" s="1">
-        <v>0.25</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K787" s="1">
-        <v>3125</v>
+        <v>520.83330000000001</v>
       </c>
       <c r="L787" s="1">
         <v>0</v>
@@ -39807,7 +39807,7 @@
       </c>
       <c r="N787" s="1"/>
       <c r="O787" s="1">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="P787" s="1" t="s">
         <v>131</v>
@@ -39836,17 +39836,17 @@
         <v>150</v>
       </c>
       <c r="G788" s="1" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="H788" s="1"/>
       <c r="I788" s="1" t="s">
-        <v>38</v>
+        <v>116</v>
       </c>
       <c r="J788" s="1">
-        <v>4.1666667999999997E-2</v>
+        <v>3</v>
       </c>
       <c r="K788" s="1">
-        <v>520.83330000000001</v>
+        <v>33750</v>
       </c>
       <c r="L788" s="1">
         <v>0</v>
@@ -39856,13 +39856,13 @@
       </c>
       <c r="N788" s="1"/>
       <c r="O788" s="1">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="P788" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q788" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="789" spans="1:17" x14ac:dyDescent="0.45">
@@ -39889,13 +39889,13 @@
       </c>
       <c r="H789" s="1"/>
       <c r="I789" s="1" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="J789" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K789" s="1">
-        <v>33750</v>
+        <v>26000</v>
       </c>
       <c r="L789" s="1">
         <v>0</v>
@@ -39905,7 +39905,7 @@
       </c>
       <c r="N789" s="1"/>
       <c r="O789" s="1">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="P789" s="1" t="s">
         <v>131</v>
@@ -39934,17 +39934,17 @@
         <v>150</v>
       </c>
       <c r="G790" s="1" t="s">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="H790" s="1"/>
       <c r="I790" s="1" t="s">
         <v>43</v>
       </c>
       <c r="J790" s="1">
-        <v>1</v>
+        <v>0.55555560000000004</v>
       </c>
       <c r="K790" s="1">
-        <v>26000</v>
+        <v>14444.444</v>
       </c>
       <c r="L790" s="1">
         <v>0</v>
@@ -39954,7 +39954,7 @@
       </c>
       <c r="N790" s="1"/>
       <c r="O790" s="1">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="P790" s="1" t="s">
         <v>131</v>
@@ -39983,17 +39983,17 @@
         <v>150</v>
       </c>
       <c r="G791" s="1" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="H791" s="1"/>
       <c r="I791" s="1" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="J791" s="1">
-        <v>0.55555560000000004</v>
+        <v>1</v>
       </c>
       <c r="K791" s="1">
-        <v>14444.444</v>
+        <v>11250</v>
       </c>
       <c r="L791" s="1">
         <v>0</v>
@@ -40003,7 +40003,7 @@
       </c>
       <c r="N791" s="1"/>
       <c r="O791" s="1">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="P791" s="1" t="s">
         <v>131</v>
@@ -40036,13 +40036,13 @@
       </c>
       <c r="H792" s="1"/>
       <c r="I792" s="1" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="J792" s="1">
-        <v>1</v>
+        <v>0.66666669999999995</v>
       </c>
       <c r="K792" s="1">
-        <v>11250</v>
+        <v>17333.333999999999</v>
       </c>
       <c r="L792" s="1">
         <v>0</v>
@@ -40052,7 +40052,7 @@
       </c>
       <c r="N792" s="1"/>
       <c r="O792" s="1">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="P792" s="1" t="s">
         <v>131</v>
@@ -40081,17 +40081,17 @@
         <v>150</v>
       </c>
       <c r="G793" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="H793" s="1"/>
       <c r="I793" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J793" s="1">
-        <v>0.66666669999999995</v>
+        <v>1</v>
       </c>
       <c r="K793" s="1">
-        <v>17333.333999999999</v>
+        <v>19500</v>
       </c>
       <c r="L793" s="1">
         <v>0</v>
@@ -40101,7 +40101,7 @@
       </c>
       <c r="N793" s="1"/>
       <c r="O793" s="1">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="P793" s="1" t="s">
         <v>131</v>
@@ -40134,13 +40134,13 @@
       </c>
       <c r="H794" s="1"/>
       <c r="I794" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J794" s="1">
-        <v>1</v>
+        <v>0.22222222</v>
       </c>
       <c r="K794" s="1">
-        <v>19500</v>
+        <v>5777.7780000000002</v>
       </c>
       <c r="L794" s="1">
         <v>0</v>
@@ -40150,7 +40150,7 @@
       </c>
       <c r="N794" s="1"/>
       <c r="O794" s="1">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="P794" s="1" t="s">
         <v>131</v>
@@ -40179,7 +40179,7 @@
         <v>150</v>
       </c>
       <c r="G795" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="H795" s="1"/>
       <c r="I795" s="1" t="s">
@@ -40199,7 +40199,7 @@
       </c>
       <c r="N795" s="1"/>
       <c r="O795" s="1">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="P795" s="1" t="s">
         <v>131</v>
@@ -40228,17 +40228,17 @@
         <v>150</v>
       </c>
       <c r="G796" s="1" t="s">
-        <v>134</v>
+        <v>46</v>
       </c>
       <c r="H796" s="1"/>
       <c r="I796" s="1" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="J796" s="1">
-        <v>0.22222222</v>
+        <v>1</v>
       </c>
       <c r="K796" s="1">
-        <v>5777.7780000000002</v>
+        <v>26500</v>
       </c>
       <c r="L796" s="1">
         <v>0</v>
@@ -40248,13 +40248,13 @@
       </c>
       <c r="N796" s="1"/>
       <c r="O796" s="1">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="P796" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q796" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="797" spans="1:17" x14ac:dyDescent="0.45">
@@ -40281,13 +40281,13 @@
       </c>
       <c r="H797" s="1"/>
       <c r="I797" s="1" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="J797" s="1">
         <v>1</v>
       </c>
       <c r="K797" s="1">
-        <v>26500</v>
+        <v>9000</v>
       </c>
       <c r="L797" s="1">
         <v>0</v>
@@ -40297,7 +40297,7 @@
       </c>
       <c r="N797" s="1"/>
       <c r="O797" s="1">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="P797" s="1" t="s">
         <v>131</v>
@@ -40326,17 +40326,17 @@
         <v>150</v>
       </c>
       <c r="G798" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H798" s="1"/>
       <c r="I798" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J798" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K798" s="1">
-        <v>9000</v>
+        <v>18000</v>
       </c>
       <c r="L798" s="1">
         <v>0</v>
@@ -40346,7 +40346,7 @@
       </c>
       <c r="N798" s="1"/>
       <c r="O798" s="1">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="P798" s="1" t="s">
         <v>131</v>
@@ -40375,17 +40375,17 @@
         <v>150</v>
       </c>
       <c r="G799" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H799" s="1"/>
       <c r="I799" s="1" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="J799" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K799" s="1">
-        <v>18000</v>
+        <v>11500</v>
       </c>
       <c r="L799" s="1">
         <v>0</v>
@@ -40395,13 +40395,13 @@
       </c>
       <c r="N799" s="1"/>
       <c r="O799" s="1">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="P799" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q799" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="800" spans="1:17" x14ac:dyDescent="0.45">
@@ -40424,7 +40424,7 @@
         <v>150</v>
       </c>
       <c r="G800" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H800" s="1"/>
       <c r="I800" s="1" t="s">
@@ -40444,7 +40444,7 @@
       </c>
       <c r="N800" s="1"/>
       <c r="O800" s="1">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="P800" s="1" t="s">
         <v>131</v>
@@ -40473,17 +40473,17 @@
         <v>150</v>
       </c>
       <c r="G801" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H801" s="1"/>
       <c r="I801" s="1" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="J801" s="1">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K801" s="1">
-        <v>11500</v>
+        <v>15000</v>
       </c>
       <c r="L801" s="1">
         <v>0</v>
@@ -40493,13 +40493,13 @@
       </c>
       <c r="N801" s="1"/>
       <c r="O801" s="1">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="P801" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q801" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="802" spans="1:17" x14ac:dyDescent="0.45">
@@ -40526,13 +40526,13 @@
       </c>
       <c r="H802" s="1"/>
       <c r="I802" s="1" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="J802" s="1">
-        <v>1.5</v>
+        <v>0.33333333999999998</v>
       </c>
       <c r="K802" s="1">
-        <v>15000</v>
+        <v>4000</v>
       </c>
       <c r="L802" s="1">
         <v>0</v>
@@ -40542,7 +40542,7 @@
       </c>
       <c r="N802" s="1"/>
       <c r="O802" s="1">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="P802" s="1" t="s">
         <v>131</v>
@@ -40559,45 +40559,45 @@
         <v>0</v>
       </c>
       <c r="C803" s="1" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="D803" s="1" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="E803" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F803" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G803" s="1" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="H803" s="1"/>
       <c r="I803" s="1" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="J803" s="1">
-        <v>0.33333333999999998</v>
+        <v>0.44444444999999999</v>
       </c>
       <c r="K803" s="1">
-        <v>4000</v>
+        <v>11555.556</v>
       </c>
       <c r="L803" s="1">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="M803" s="1">
         <v>0</v>
       </c>
       <c r="N803" s="1"/>
       <c r="O803" s="1">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="P803" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q803" s="1" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="804" spans="1:17" x14ac:dyDescent="0.45">
@@ -40624,23 +40624,23 @@
       </c>
       <c r="H804" s="1"/>
       <c r="I804" s="1" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="J804" s="1">
-        <v>0.44444444999999999</v>
+        <v>1</v>
       </c>
       <c r="K804" s="1">
-        <v>11555.556</v>
+        <v>11250</v>
       </c>
       <c r="L804" s="1">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="M804" s="1">
         <v>0</v>
       </c>
       <c r="N804" s="1"/>
       <c r="O804" s="1">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="P804" s="1" t="s">
         <v>131</v>
@@ -40669,17 +40669,17 @@
         <v>149</v>
       </c>
       <c r="G805" s="1" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="H805" s="1"/>
       <c r="I805" s="1" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="J805" s="1">
-        <v>1</v>
+        <v>0.33333333999999998</v>
       </c>
       <c r="K805" s="1">
-        <v>11250</v>
+        <v>8666.6669999999995</v>
       </c>
       <c r="L805" s="1">
         <v>0</v>
@@ -40689,7 +40689,7 @@
       </c>
       <c r="N805" s="1"/>
       <c r="O805" s="1">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="P805" s="1" t="s">
         <v>131</v>
@@ -40722,13 +40722,13 @@
       </c>
       <c r="H806" s="1"/>
       <c r="I806" s="1" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="J806" s="1">
-        <v>0.33333333999999998</v>
+        <v>0.5</v>
       </c>
       <c r="K806" s="1">
-        <v>8666.6669999999995</v>
+        <v>5625</v>
       </c>
       <c r="L806" s="1">
         <v>0</v>
@@ -40738,7 +40738,7 @@
       </c>
       <c r="N806" s="1"/>
       <c r="O806" s="1">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="P806" s="1" t="s">
         <v>131</v>
@@ -40767,17 +40767,17 @@
         <v>149</v>
       </c>
       <c r="G807" s="1" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="H807" s="1"/>
       <c r="I807" s="1" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="J807" s="1">
-        <v>0.5</v>
+        <v>0.55555560000000004</v>
       </c>
       <c r="K807" s="1">
-        <v>5625</v>
+        <v>14444.444</v>
       </c>
       <c r="L807" s="1">
         <v>0</v>
@@ -40787,7 +40787,7 @@
       </c>
       <c r="N807" s="1"/>
       <c r="O807" s="1">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="P807" s="1" t="s">
         <v>131</v>
@@ -40820,13 +40820,13 @@
       </c>
       <c r="H808" s="1"/>
       <c r="I808" s="1" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="J808" s="1">
-        <v>0.55555560000000004</v>
+        <v>0.5</v>
       </c>
       <c r="K808" s="1">
-        <v>14444.444</v>
+        <v>5625</v>
       </c>
       <c r="L808" s="1">
         <v>0</v>
@@ -40836,7 +40836,7 @@
       </c>
       <c r="N808" s="1"/>
       <c r="O808" s="1">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="P808" s="1" t="s">
         <v>131</v>
@@ -40865,17 +40865,17 @@
         <v>149</v>
       </c>
       <c r="G809" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H809" s="1"/>
       <c r="I809" s="1" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="J809" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K809" s="1">
-        <v>5625</v>
+        <v>26000</v>
       </c>
       <c r="L809" s="1">
         <v>0</v>
@@ -40885,7 +40885,7 @@
       </c>
       <c r="N809" s="1"/>
       <c r="O809" s="1">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="P809" s="1" t="s">
         <v>131</v>
@@ -40918,13 +40918,13 @@
       </c>
       <c r="H810" s="1"/>
       <c r="I810" s="1" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="J810" s="1">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K810" s="1">
-        <v>26000</v>
+        <v>16875</v>
       </c>
       <c r="L810" s="1">
         <v>0</v>
@@ -40934,7 +40934,7 @@
       </c>
       <c r="N810" s="1"/>
       <c r="O810" s="1">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="P810" s="1" t="s">
         <v>131</v>
@@ -40967,13 +40967,13 @@
       </c>
       <c r="H811" s="1"/>
       <c r="I811" s="1" t="s">
-        <v>116</v>
+        <v>41</v>
       </c>
       <c r="J811" s="1">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="K811" s="1">
-        <v>16875</v>
+        <v>48750</v>
       </c>
       <c r="L811" s="1">
         <v>0</v>
@@ -40983,7 +40983,7 @@
       </c>
       <c r="N811" s="1"/>
       <c r="O811" s="1">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="P811" s="1" t="s">
         <v>131</v>
@@ -41012,17 +41012,17 @@
         <v>149</v>
       </c>
       <c r="G812" s="1" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="H812" s="1"/>
       <c r="I812" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J812" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="K812" s="1">
-        <v>48750</v>
+        <v>56000</v>
       </c>
       <c r="L812" s="1">
         <v>0</v>
@@ -41032,13 +41032,13 @@
       </c>
       <c r="N812" s="1"/>
       <c r="O812" s="1">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="P812" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q812" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="813" spans="1:17" x14ac:dyDescent="0.45">
@@ -41065,13 +41065,13 @@
       </c>
       <c r="H813" s="1"/>
       <c r="I813" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J813" s="1">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="K813" s="1">
-        <v>56000</v>
+        <v>8750</v>
       </c>
       <c r="L813" s="1">
         <v>0</v>
@@ -41081,7 +41081,7 @@
       </c>
       <c r="N813" s="1"/>
       <c r="O813" s="1">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="P813" s="1" t="s">
         <v>131</v>
@@ -41110,17 +41110,17 @@
         <v>149</v>
       </c>
       <c r="G814" s="1" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="H814" s="1"/>
       <c r="I814" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J814" s="1">
         <v>0.5</v>
       </c>
       <c r="K814" s="1">
-        <v>8750</v>
+        <v>16750</v>
       </c>
       <c r="L814" s="1">
         <v>0</v>
@@ -41130,7 +41130,7 @@
       </c>
       <c r="N814" s="1"/>
       <c r="O814" s="1">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="P814" s="1" t="s">
         <v>131</v>
@@ -41163,13 +41163,13 @@
       </c>
       <c r="H815" s="1"/>
       <c r="I815" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J815" s="1">
-        <v>0.5</v>
+        <v>0.77777779999999996</v>
       </c>
       <c r="K815" s="1">
-        <v>16750</v>
+        <v>21777.776999999998</v>
       </c>
       <c r="L815" s="1">
         <v>0</v>
@@ -41179,7 +41179,7 @@
       </c>
       <c r="N815" s="1"/>
       <c r="O815" s="1">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="P815" s="1" t="s">
         <v>131</v>
@@ -41208,17 +41208,17 @@
         <v>149</v>
       </c>
       <c r="G816" s="1" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="H816" s="1"/>
       <c r="I816" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J816" s="1">
-        <v>0.77777779999999996</v>
+        <v>0.75</v>
       </c>
       <c r="K816" s="1">
-        <v>21777.776999999998</v>
+        <v>9375</v>
       </c>
       <c r="L816" s="1">
         <v>0</v>
@@ -41228,13 +41228,13 @@
       </c>
       <c r="N816" s="1"/>
       <c r="O816" s="1">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="P816" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q816" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="817" spans="1:17" x14ac:dyDescent="0.45">
@@ -41257,17 +41257,17 @@
         <v>149</v>
       </c>
       <c r="G817" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H817" s="1"/>
       <c r="I817" s="1" t="s">
         <v>39</v>
       </c>
       <c r="J817" s="1">
-        <v>0.75</v>
+        <v>0.83333330000000005</v>
       </c>
       <c r="K817" s="1">
-        <v>9375</v>
+        <v>10416.666999999999</v>
       </c>
       <c r="L817" s="1">
         <v>0</v>
@@ -41277,7 +41277,7 @@
       </c>
       <c r="N817" s="1"/>
       <c r="O817" s="1">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="P817" s="1" t="s">
         <v>131</v>
@@ -41306,17 +41306,17 @@
         <v>149</v>
       </c>
       <c r="G818" s="1" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="H818" s="1"/>
       <c r="I818" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="J818" s="1">
-        <v>0.83333330000000005</v>
+        <v>0.5</v>
       </c>
       <c r="K818" s="1">
-        <v>10416.666999999999</v>
+        <v>5000</v>
       </c>
       <c r="L818" s="1">
         <v>0</v>
@@ -41326,13 +41326,13 @@
       </c>
       <c r="N818" s="1"/>
       <c r="O818" s="1">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="P818" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q818" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="819" spans="1:17" x14ac:dyDescent="0.45">
@@ -41355,17 +41355,17 @@
         <v>149</v>
       </c>
       <c r="G819" s="1" t="s">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="H819" s="1"/>
       <c r="I819" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J819" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K819" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="L819" s="1">
         <v>0</v>
@@ -41375,7 +41375,7 @@
       </c>
       <c r="N819" s="1"/>
       <c r="O819" s="1">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="P819" s="1" t="s">
         <v>131</v>
@@ -41404,7 +41404,7 @@
         <v>149</v>
       </c>
       <c r="G820" s="1" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="H820" s="1"/>
       <c r="I820" s="1" t="s">
@@ -41424,7 +41424,7 @@
       </c>
       <c r="N820" s="1"/>
       <c r="O820" s="1">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="P820" s="1" t="s">
         <v>131</v>
@@ -41457,13 +41457,13 @@
       </c>
       <c r="H821" s="1"/>
       <c r="I821" s="1" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="J821" s="1">
-        <v>1</v>
+        <v>0.33333333999999998</v>
       </c>
       <c r="K821" s="1">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="L821" s="1">
         <v>0</v>
@@ -41473,7 +41473,7 @@
       </c>
       <c r="N821" s="1"/>
       <c r="O821" s="1">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="P821" s="1" t="s">
         <v>131</v>
@@ -41502,17 +41502,17 @@
         <v>149</v>
       </c>
       <c r="G822" s="1" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="H822" s="1"/>
       <c r="I822" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J822" s="1">
-        <v>0.33333333999999998</v>
+        <v>0.5</v>
       </c>
       <c r="K822" s="1">
-        <v>4000</v>
+        <v>13250</v>
       </c>
       <c r="L822" s="1">
         <v>0</v>
@@ -41522,13 +41522,13 @@
       </c>
       <c r="N822" s="1"/>
       <c r="O822" s="1">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="P822" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q822" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="823" spans="1:17" x14ac:dyDescent="0.45">
@@ -41551,17 +41551,17 @@
         <v>149</v>
       </c>
       <c r="G823" s="1" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="H823" s="1"/>
       <c r="I823" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="J823" s="1">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K823" s="1">
-        <v>13250</v>
+        <v>9000</v>
       </c>
       <c r="L823" s="1">
         <v>0</v>
@@ -41571,7 +41571,7 @@
       </c>
       <c r="N823" s="1"/>
       <c r="O823" s="1">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="P823" s="1" t="s">
         <v>131</v>
@@ -41600,17 +41600,17 @@
         <v>149</v>
       </c>
       <c r="G824" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H824" s="1"/>
       <c r="I824" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J824" s="1">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K824" s="1">
-        <v>9000</v>
+        <v>6625</v>
       </c>
       <c r="L824" s="1">
         <v>0</v>
@@ -41620,7 +41620,7 @@
       </c>
       <c r="N824" s="1"/>
       <c r="O824" s="1">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="P824" s="1" t="s">
         <v>131</v>
@@ -41653,13 +41653,13 @@
       </c>
       <c r="H825" s="1"/>
       <c r="I825" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="J825" s="1">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="K825" s="1">
-        <v>6625</v>
+        <v>4500</v>
       </c>
       <c r="L825" s="1">
         <v>0</v>
@@ -41669,7 +41669,7 @@
       </c>
       <c r="N825" s="1"/>
       <c r="O825" s="1">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="P825" s="1" t="s">
         <v>131</v>
@@ -41698,17 +41698,17 @@
         <v>149</v>
       </c>
       <c r="G826" s="1" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="H826" s="1"/>
       <c r="I826" s="1" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="J826" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K826" s="1">
-        <v>4500</v>
+        <v>18000</v>
       </c>
       <c r="L826" s="1">
         <v>0</v>
@@ -41718,7 +41718,7 @@
       </c>
       <c r="N826" s="1"/>
       <c r="O826" s="1">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="P826" s="1" t="s">
         <v>131</v>
@@ -41751,13 +41751,13 @@
       </c>
       <c r="H827" s="1"/>
       <c r="I827" s="1" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="J827" s="1">
-        <v>2</v>
+        <v>0.29166666000000002</v>
       </c>
       <c r="K827" s="1">
-        <v>18000</v>
+        <v>7729.1665000000003</v>
       </c>
       <c r="L827" s="1">
         <v>0</v>
@@ -41767,7 +41767,7 @@
       </c>
       <c r="N827" s="1"/>
       <c r="O827" s="1">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="P827" s="1" t="s">
         <v>131</v>
@@ -41796,17 +41796,17 @@
         <v>149</v>
       </c>
       <c r="G828" s="1" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="H828" s="1"/>
       <c r="I828" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J828" s="1">
-        <v>0.29166666000000002</v>
+        <v>2</v>
       </c>
       <c r="K828" s="1">
-        <v>7729.1665000000003</v>
+        <v>23000</v>
       </c>
       <c r="L828" s="1">
         <v>0</v>
@@ -41816,13 +41816,13 @@
       </c>
       <c r="N828" s="1"/>
       <c r="O828" s="1">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="P828" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q828" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="829" spans="1:17" x14ac:dyDescent="0.45">
@@ -41845,17 +41845,17 @@
         <v>149</v>
       </c>
       <c r="G829" s="1" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="H829" s="1"/>
       <c r="I829" s="1" t="s">
         <v>80</v>
       </c>
       <c r="J829" s="1">
-        <v>2</v>
+        <v>1.5416666000000001</v>
       </c>
       <c r="K829" s="1">
-        <v>23000</v>
+        <v>17729.166000000001</v>
       </c>
       <c r="L829" s="1">
         <v>0</v>
@@ -41865,7 +41865,7 @@
       </c>
       <c r="N829" s="1"/>
       <c r="O829" s="1">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="P829" s="1" t="s">
         <v>131</v>
@@ -41894,17 +41894,17 @@
         <v>149</v>
       </c>
       <c r="G830" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H830" s="1"/>
       <c r="I830" s="1" t="s">
         <v>80</v>
       </c>
       <c r="J830" s="1">
-        <v>1.5416666000000001</v>
+        <v>1.5</v>
       </c>
       <c r="K830" s="1">
-        <v>17729.166000000001</v>
+        <v>17250</v>
       </c>
       <c r="L830" s="1">
         <v>0</v>
@@ -41914,7 +41914,7 @@
       </c>
       <c r="N830" s="1"/>
       <c r="O830" s="1">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="P830" s="1" t="s">
         <v>131</v>
@@ -41943,17 +41943,17 @@
         <v>149</v>
       </c>
       <c r="G831" s="1" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="H831" s="1"/>
       <c r="I831" s="1" t="s">
         <v>80</v>
       </c>
       <c r="J831" s="1">
-        <v>1.5</v>
+        <v>1.4166666000000001</v>
       </c>
       <c r="K831" s="1">
-        <v>17250</v>
+        <v>16291.666999999999</v>
       </c>
       <c r="L831" s="1">
         <v>0</v>
@@ -41963,61 +41963,12 @@
       </c>
       <c r="N831" s="1"/>
       <c r="O831" s="1">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="P831" s="1" t="s">
         <v>131</v>
       </c>
       <c r="Q831" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="832" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A832" s="2">
-        <v>46251</v>
-      </c>
-      <c r="B832" s="1">
-        <v>0</v>
-      </c>
-      <c r="C832" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D832" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E832" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F832" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="G832" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="H832" s="1"/>
-      <c r="I832" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J832" s="1">
-        <v>1.4166666000000001</v>
-      </c>
-      <c r="K832" s="1">
-        <v>16291.666999999999</v>
-      </c>
-      <c r="L832" s="1">
-        <v>0</v>
-      </c>
-      <c r="M832" s="1">
-        <v>0</v>
-      </c>
-      <c r="N832" s="1"/>
-      <c r="O832" s="1">
-        <v>813</v>
-      </c>
-      <c r="P832" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q832" s="1" t="s">
         <v>113</v>
       </c>
     </row>

--- a/Donnees_Mensuelle.xlsx
+++ b/Donnees_Mensuelle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE840FAA-E70A-44F9-BA74-2576880936FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2443984A-3C99-4455-B89D-CA8AC626635B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6668" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6822" uniqueCount="155">
   <si>
     <t>Date</t>
   </si>
@@ -487,6 +487,18 @@
   <si>
     <t>TIVAOUANE PEULH</t>
   </si>
+  <si>
+    <t>TATA 4</t>
+  </si>
+  <si>
+    <t>TATA 5</t>
+  </si>
+  <si>
+    <t>TATA 6</t>
+  </si>
+  <si>
+    <t>TATA 7</t>
+  </si>
 </sst>
 </file>
 
@@ -495,7 +507,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -506,6 +518,12 @@
     <font>
       <sz val="11"/>
       <name val="TIMES"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -875,8 +893,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}" name="Tableau1" displayName="Tableau1" ref="A1:Q831" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:Q831" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}" name="Tableau1" displayName="Tableau1" ref="A1:Q853" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+  <autoFilter ref="A1:Q853" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{713E4B58-7C9F-4B80-8C6C-D9C3181B21C1}" name="Date" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{0868AEE8-A7A6-4928-8DDB-60543BB07F07}" name="Telephone_Team_Leader" dataDxfId="15"/>
@@ -1217,7 +1235,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q831"/>
+  <dimension ref="A1:Q853"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.3984375" customWidth="1"/>
@@ -41972,7 +41990,1042 @@
         <v>113</v>
       </c>
     </row>
+    <row r="832" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A832" s="2">
+        <v>46252</v>
+      </c>
+      <c r="B832" s="1">
+        <v>0</v>
+      </c>
+      <c r="C832" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D832" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E832" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F832" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G832" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H832" s="1"/>
+      <c r="I832" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J832" s="1">
+        <v>0</v>
+      </c>
+      <c r="K832" s="1">
+        <v>0</v>
+      </c>
+      <c r="L832" s="1">
+        <v>0</v>
+      </c>
+      <c r="M832" s="1">
+        <v>0</v>
+      </c>
+      <c r="N832" s="1"/>
+      <c r="O832" s="1">
+        <v>140</v>
+      </c>
+      <c r="P832" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q832" s="1"/>
+    </row>
+    <row r="833" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A833" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B833" s="1">
+        <v>0</v>
+      </c>
+      <c r="C833" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D833" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E833" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F833" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G833" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H833" s="1"/>
+      <c r="I833" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J833" s="1">
+        <v>0</v>
+      </c>
+      <c r="K833" s="1">
+        <v>0</v>
+      </c>
+      <c r="L833" s="1">
+        <v>0</v>
+      </c>
+      <c r="M833" s="1">
+        <v>0</v>
+      </c>
+      <c r="N833" s="1"/>
+      <c r="O833" s="1">
+        <v>140</v>
+      </c>
+      <c r="P833" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q833" s="1"/>
+    </row>
+    <row r="834" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A834" s="2">
+        <v>46254</v>
+      </c>
+      <c r="B834" s="1">
+        <v>0</v>
+      </c>
+      <c r="C834" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D834" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E834" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F834" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G834" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H834" s="1"/>
+      <c r="I834" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J834" s="1">
+        <v>0</v>
+      </c>
+      <c r="K834" s="1">
+        <v>0</v>
+      </c>
+      <c r="L834" s="1">
+        <v>0</v>
+      </c>
+      <c r="M834" s="1">
+        <v>0</v>
+      </c>
+      <c r="N834" s="1"/>
+      <c r="O834" s="1">
+        <v>140</v>
+      </c>
+      <c r="P834" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q834" s="1"/>
+    </row>
+    <row r="835" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A835" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B835" s="1">
+        <v>0</v>
+      </c>
+      <c r="C835" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D835" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E835" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F835" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G835" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H835" s="1"/>
+      <c r="I835" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J835" s="1">
+        <v>0</v>
+      </c>
+      <c r="K835" s="1">
+        <v>0</v>
+      </c>
+      <c r="L835" s="1">
+        <v>0</v>
+      </c>
+      <c r="M835" s="1">
+        <v>0</v>
+      </c>
+      <c r="N835" s="1"/>
+      <c r="O835" s="1">
+        <v>140</v>
+      </c>
+      <c r="P835" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q835" s="1"/>
+    </row>
+    <row r="836" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A836" s="2">
+        <v>46256</v>
+      </c>
+      <c r="B836" s="1">
+        <v>0</v>
+      </c>
+      <c r="C836" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D836" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E836" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F836" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G836" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H836" s="1"/>
+      <c r="I836" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J836" s="1">
+        <v>0</v>
+      </c>
+      <c r="K836" s="1">
+        <v>0</v>
+      </c>
+      <c r="L836" s="1">
+        <v>0</v>
+      </c>
+      <c r="M836" s="1">
+        <v>0</v>
+      </c>
+      <c r="N836" s="1"/>
+      <c r="O836" s="1">
+        <v>140</v>
+      </c>
+      <c r="P836" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q836" s="1"/>
+    </row>
+    <row r="837" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A837" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B837" s="1">
+        <v>0</v>
+      </c>
+      <c r="C837" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D837" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E837" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F837" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G837" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H837" s="1"/>
+      <c r="I837" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J837" s="1">
+        <v>0</v>
+      </c>
+      <c r="K837" s="1">
+        <v>0</v>
+      </c>
+      <c r="L837" s="1">
+        <v>0</v>
+      </c>
+      <c r="M837" s="1">
+        <v>0</v>
+      </c>
+      <c r="N837" s="1"/>
+      <c r="O837" s="1">
+        <v>140</v>
+      </c>
+      <c r="P837" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q837" s="1"/>
+    </row>
+    <row r="838" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A838" s="2">
+        <v>46252</v>
+      </c>
+      <c r="B838" s="1">
+        <v>0</v>
+      </c>
+      <c r="C838" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D838" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E838" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F838" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G838" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H838" s="1"/>
+      <c r="I838" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J838" s="1">
+        <v>0</v>
+      </c>
+      <c r="K838" s="1">
+        <v>0</v>
+      </c>
+      <c r="L838" s="1">
+        <v>0</v>
+      </c>
+      <c r="M838" s="1">
+        <v>0</v>
+      </c>
+      <c r="N838" s="1"/>
+      <c r="O838" s="1">
+        <v>140</v>
+      </c>
+      <c r="P838" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q838" s="1"/>
+    </row>
+    <row r="839" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A839" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B839" s="1">
+        <v>0</v>
+      </c>
+      <c r="C839" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D839" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E839" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F839" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G839" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H839" s="1"/>
+      <c r="I839" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J839" s="1">
+        <v>0</v>
+      </c>
+      <c r="K839" s="1">
+        <v>0</v>
+      </c>
+      <c r="L839" s="1">
+        <v>0</v>
+      </c>
+      <c r="M839" s="1">
+        <v>0</v>
+      </c>
+      <c r="N839" s="1"/>
+      <c r="O839" s="1">
+        <v>140</v>
+      </c>
+      <c r="P839" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q839" s="1"/>
+    </row>
+    <row r="840" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A840" s="2">
+        <v>46254</v>
+      </c>
+      <c r="B840" s="1">
+        <v>0</v>
+      </c>
+      <c r="C840" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D840" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E840" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F840" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G840" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H840" s="1"/>
+      <c r="I840" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J840" s="1">
+        <v>0</v>
+      </c>
+      <c r="K840" s="1">
+        <v>0</v>
+      </c>
+      <c r="L840" s="1">
+        <v>0</v>
+      </c>
+      <c r="M840" s="1">
+        <v>0</v>
+      </c>
+      <c r="N840" s="1"/>
+      <c r="O840" s="1">
+        <v>140</v>
+      </c>
+      <c r="P840" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q840" s="1"/>
+    </row>
+    <row r="841" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A841" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B841" s="1">
+        <v>0</v>
+      </c>
+      <c r="C841" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D841" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E841" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F841" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G841" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H841" s="1"/>
+      <c r="I841" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J841" s="1">
+        <v>0</v>
+      </c>
+      <c r="K841" s="1">
+        <v>0</v>
+      </c>
+      <c r="L841" s="1">
+        <v>0</v>
+      </c>
+      <c r="M841" s="1">
+        <v>0</v>
+      </c>
+      <c r="N841" s="1"/>
+      <c r="O841" s="1">
+        <v>140</v>
+      </c>
+      <c r="P841" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q841" s="1"/>
+    </row>
+    <row r="842" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A842" s="2">
+        <v>46256</v>
+      </c>
+      <c r="B842" s="1">
+        <v>0</v>
+      </c>
+      <c r="C842" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D842" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E842" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F842" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G842" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H842" s="1"/>
+      <c r="I842" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J842" s="1">
+        <v>0</v>
+      </c>
+      <c r="K842" s="1">
+        <v>0</v>
+      </c>
+      <c r="L842" s="1">
+        <v>0</v>
+      </c>
+      <c r="M842" s="1">
+        <v>0</v>
+      </c>
+      <c r="N842" s="1"/>
+      <c r="O842" s="1">
+        <v>140</v>
+      </c>
+      <c r="P842" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q842" s="1"/>
+    </row>
+    <row r="843" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A843" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B843" s="1">
+        <v>0</v>
+      </c>
+      <c r="C843" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D843" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E843" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F843" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G843" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H843" s="1"/>
+      <c r="I843" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J843" s="1">
+        <v>0</v>
+      </c>
+      <c r="K843" s="1">
+        <v>0</v>
+      </c>
+      <c r="L843" s="1">
+        <v>0</v>
+      </c>
+      <c r="M843" s="1">
+        <v>0</v>
+      </c>
+      <c r="N843" s="1"/>
+      <c r="O843" s="1">
+        <v>140</v>
+      </c>
+      <c r="P843" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q843" s="1"/>
+    </row>
+    <row r="844" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A844" s="2">
+        <v>46256</v>
+      </c>
+      <c r="B844" s="1">
+        <v>0</v>
+      </c>
+      <c r="C844" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D844" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E844" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F844" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G844" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H844" s="1"/>
+      <c r="I844" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J844" s="1">
+        <v>0</v>
+      </c>
+      <c r="K844" s="1">
+        <v>0</v>
+      </c>
+      <c r="L844" s="1">
+        <v>0</v>
+      </c>
+      <c r="M844" s="1">
+        <v>0</v>
+      </c>
+      <c r="N844" s="1"/>
+      <c r="O844" s="1">
+        <v>140</v>
+      </c>
+      <c r="P844" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q844" s="1"/>
+    </row>
+    <row r="845" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A845" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B845" s="1">
+        <v>0</v>
+      </c>
+      <c r="C845" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D845" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E845" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F845" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G845" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H845" s="1"/>
+      <c r="I845" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J845" s="1">
+        <v>0</v>
+      </c>
+      <c r="K845" s="1">
+        <v>0</v>
+      </c>
+      <c r="L845" s="1">
+        <v>0</v>
+      </c>
+      <c r="M845" s="1">
+        <v>0</v>
+      </c>
+      <c r="N845" s="1"/>
+      <c r="O845" s="1">
+        <v>140</v>
+      </c>
+      <c r="P845" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q845" s="1"/>
+    </row>
+    <row r="846" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A846" s="2">
+        <v>46254</v>
+      </c>
+      <c r="B846" s="1">
+        <v>0</v>
+      </c>
+      <c r="C846" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D846" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E846" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F846" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G846" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H846" s="1"/>
+      <c r="I846" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J846" s="1">
+        <v>0</v>
+      </c>
+      <c r="K846" s="1">
+        <v>0</v>
+      </c>
+      <c r="L846" s="1">
+        <v>0</v>
+      </c>
+      <c r="M846" s="1">
+        <v>0</v>
+      </c>
+      <c r="N846" s="1"/>
+      <c r="O846" s="1">
+        <v>140</v>
+      </c>
+      <c r="P846" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q846" s="1"/>
+    </row>
+    <row r="847" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A847" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B847" s="1">
+        <v>0</v>
+      </c>
+      <c r="C847" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D847" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E847" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F847" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G847" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H847" s="1"/>
+      <c r="I847" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J847" s="1">
+        <v>0</v>
+      </c>
+      <c r="K847" s="1">
+        <v>0</v>
+      </c>
+      <c r="L847" s="1">
+        <v>0</v>
+      </c>
+      <c r="M847" s="1">
+        <v>0</v>
+      </c>
+      <c r="N847" s="1"/>
+      <c r="O847" s="1">
+        <v>140</v>
+      </c>
+      <c r="P847" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q847" s="1"/>
+    </row>
+    <row r="848" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A848" s="2">
+        <v>46256</v>
+      </c>
+      <c r="B848" s="1">
+        <v>1</v>
+      </c>
+      <c r="C848" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D848" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E848" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F848" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G848" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H848" s="1"/>
+      <c r="I848" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J848" s="1">
+        <v>0</v>
+      </c>
+      <c r="K848" s="1">
+        <v>0</v>
+      </c>
+      <c r="L848" s="1">
+        <v>0</v>
+      </c>
+      <c r="M848" s="1">
+        <v>0</v>
+      </c>
+      <c r="N848" s="1"/>
+      <c r="O848" s="1">
+        <v>140</v>
+      </c>
+      <c r="P848" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q848" s="1"/>
+    </row>
+    <row r="849" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A849" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B849" s="1">
+        <v>2</v>
+      </c>
+      <c r="C849" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D849" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E849" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F849" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G849" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H849" s="1"/>
+      <c r="I849" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J849" s="1">
+        <v>0</v>
+      </c>
+      <c r="K849" s="1">
+        <v>0</v>
+      </c>
+      <c r="L849" s="1">
+        <v>0</v>
+      </c>
+      <c r="M849" s="1">
+        <v>0</v>
+      </c>
+      <c r="N849" s="1"/>
+      <c r="O849" s="1">
+        <v>140</v>
+      </c>
+      <c r="P849" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q849" s="1"/>
+    </row>
+    <row r="850" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A850" s="2">
+        <v>46252</v>
+      </c>
+      <c r="B850" s="1">
+        <v>3</v>
+      </c>
+      <c r="C850" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D850" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E850" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F850" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G850" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H850" s="1"/>
+      <c r="I850" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J850" s="1">
+        <v>0</v>
+      </c>
+      <c r="K850" s="1">
+        <v>0</v>
+      </c>
+      <c r="L850" s="1">
+        <v>0</v>
+      </c>
+      <c r="M850" s="1">
+        <v>0</v>
+      </c>
+      <c r="N850" s="1"/>
+      <c r="O850" s="1">
+        <v>140</v>
+      </c>
+      <c r="P850" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q850" s="1"/>
+    </row>
+    <row r="851" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A851" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B851" s="1">
+        <v>4</v>
+      </c>
+      <c r="C851" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D851" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E851" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F851" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G851" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H851" s="1"/>
+      <c r="I851" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J851" s="1">
+        <v>0</v>
+      </c>
+      <c r="K851" s="1">
+        <v>0</v>
+      </c>
+      <c r="L851" s="1">
+        <v>0</v>
+      </c>
+      <c r="M851" s="1">
+        <v>0</v>
+      </c>
+      <c r="N851" s="1"/>
+      <c r="O851" s="1">
+        <v>140</v>
+      </c>
+      <c r="P851" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q851" s="1"/>
+    </row>
+    <row r="852" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A852" s="2">
+        <v>46254</v>
+      </c>
+      <c r="B852" s="1">
+        <v>5</v>
+      </c>
+      <c r="C852" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D852" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E852" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F852" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G852" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H852" s="1"/>
+      <c r="I852" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J852" s="1">
+        <v>0</v>
+      </c>
+      <c r="K852" s="1">
+        <v>0</v>
+      </c>
+      <c r="L852" s="1">
+        <v>0</v>
+      </c>
+      <c r="M852" s="1">
+        <v>0</v>
+      </c>
+      <c r="N852" s="1"/>
+      <c r="O852" s="1">
+        <v>140</v>
+      </c>
+      <c r="P852" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q852" s="1"/>
+    </row>
+    <row r="853" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A853" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B853" s="1">
+        <v>6</v>
+      </c>
+      <c r="C853" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D853" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E853" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F853" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G853" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H853" s="1"/>
+      <c r="I853" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J853" s="1">
+        <v>0</v>
+      </c>
+      <c r="K853" s="1">
+        <v>0</v>
+      </c>
+      <c r="L853" s="1">
+        <v>0</v>
+      </c>
+      <c r="M853" s="1">
+        <v>0</v>
+      </c>
+      <c r="N853" s="1"/>
+      <c r="O853" s="1">
+        <v>140</v>
+      </c>
+      <c r="P853" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q853" s="1"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/Donnees_Mensuelle.xlsx
+++ b/Donnees_Mensuelle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2443984A-3C99-4455-B89D-CA8AC626635B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84BD8E1-B206-44BD-BCE9-99482BFFF2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6822" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6822" uniqueCount="151">
   <si>
     <t>Date</t>
   </si>
@@ -486,18 +486,6 @@
   </si>
   <si>
     <t>TIVAOUANE PEULH</t>
-  </si>
-  <si>
-    <t>TATA 4</t>
-  </si>
-  <si>
-    <t>TATA 5</t>
-  </si>
-  <si>
-    <t>TATA 6</t>
-  </si>
-  <si>
-    <t>TATA 7</t>
   </si>
 </sst>
 </file>
@@ -42750,7 +42738,7 @@
         <v>1</v>
       </c>
       <c r="C848" s="1" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="D848" s="1" t="s">
         <v>33</v>
@@ -42797,7 +42785,7 @@
         <v>2</v>
       </c>
       <c r="C849" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D849" s="1" t="s">
         <v>33</v>
@@ -42844,7 +42832,7 @@
         <v>3</v>
       </c>
       <c r="C850" s="1" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="D850" s="1" t="s">
         <v>33</v>
@@ -42891,7 +42879,7 @@
         <v>4</v>
       </c>
       <c r="C851" s="1" t="s">
-        <v>152</v>
+        <v>32</v>
       </c>
       <c r="D851" s="1" t="s">
         <v>33</v>
@@ -42938,7 +42926,7 @@
         <v>5</v>
       </c>
       <c r="C852" s="1" t="s">
-        <v>153</v>
+        <v>32</v>
       </c>
       <c r="D852" s="1" t="s">
         <v>33</v>
@@ -42985,7 +42973,7 @@
         <v>6</v>
       </c>
       <c r="C853" s="1" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="D853" s="1" t="s">
         <v>33</v>

--- a/Donnees_Mensuelle.xlsx
+++ b/Donnees_Mensuelle.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84BD8E1-B206-44BD-BCE9-99482BFFF2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713383B5-E5C8-4642-BEBB-4B7497999D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25859,7 +25859,7 @@
     </row>
     <row r="503" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A503" s="2">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B503" s="1">
         <v>0</v>
@@ -25908,7 +25908,7 @@
     </row>
     <row r="504" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A504" s="2">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B504" s="1">
         <v>0</v>
@@ -25957,7 +25957,7 @@
     </row>
     <row r="505" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A505" s="2">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B505" s="1">
         <v>0</v>
@@ -26006,7 +26006,7 @@
     </row>
     <row r="506" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A506" s="2">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B506" s="1">
         <v>0</v>
@@ -26055,7 +26055,7 @@
     </row>
     <row r="507" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A507" s="2">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B507" s="1">
         <v>0</v>
@@ -26104,7 +26104,7 @@
     </row>
     <row r="508" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A508" s="2">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B508" s="1">
         <v>0</v>
@@ -26153,7 +26153,7 @@
     </row>
     <row r="509" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A509" s="2">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B509" s="1">
         <v>0</v>
@@ -26202,7 +26202,7 @@
     </row>
     <row r="510" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A510" s="2">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B510" s="1">
         <v>0</v>
@@ -26251,7 +26251,7 @@
     </row>
     <row r="511" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A511" s="2">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B511" s="1">
         <v>0</v>
@@ -26300,7 +26300,7 @@
     </row>
     <row r="512" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A512" s="2">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B512" s="1">
         <v>0</v>
@@ -26349,7 +26349,7 @@
     </row>
     <row r="513" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A513" s="2">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B513" s="1">
         <v>0</v>
@@ -26398,7 +26398,7 @@
     </row>
     <row r="514" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A514" s="2">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B514" s="1">
         <v>0</v>
@@ -26447,7 +26447,7 @@
     </row>
     <row r="515" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A515" s="2">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B515" s="1">
         <v>0</v>
@@ -26496,7 +26496,7 @@
     </row>
     <row r="516" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A516" s="2">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B516" s="1">
         <v>0</v>
@@ -26545,7 +26545,7 @@
     </row>
     <row r="517" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A517" s="2">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B517" s="1">
         <v>0</v>
@@ -26594,7 +26594,7 @@
     </row>
     <row r="518" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A518" s="2">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B518" s="1">
         <v>0</v>
@@ -26643,7 +26643,7 @@
     </row>
     <row r="519" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A519" s="2">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B519" s="1">
         <v>0</v>

--- a/Donnees_Mensuelle.xlsx
+++ b/Donnees_Mensuelle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B689C92C-48B1-4443-9219-BA0A228CEC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF609C36-2FE4-4213-8488-747AD06F07C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -897,16 +897,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}" name="Tableau1" displayName="Tableau1" ref="A1:Q1093" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:Q1093" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="Chamsdine Aidara"/>
-        <filter val="Djibril THIOMBANE"/>
-        <filter val="Issa KANE"/>
-        <filter val="Mohamed Dione"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:Q1093" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{713E4B58-7C9F-4B80-8C6C-D9C3181B21C1}" name="Date" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{0868AEE8-A7A6-4928-8DDB-60543BB07F07}" name="Telephone_Team_Leader" dataDxfId="15"/>
@@ -1322,7 +1313,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>46248</v>
       </c>
@@ -1373,7 +1364,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>46248</v>
       </c>
@@ -1424,7 +1415,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>46248</v>
       </c>
@@ -1475,7 +1466,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>46248</v>
       </c>
@@ -1526,7 +1517,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>46248</v>
       </c>
@@ -1577,7 +1568,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>46248</v>
       </c>
@@ -1628,7 +1619,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>46248</v>
       </c>
@@ -1679,7 +1670,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>46248</v>
       </c>
@@ -1730,7 +1721,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>46248</v>
       </c>
@@ -1781,7 +1772,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <v>46248</v>
       </c>
@@ -1832,7 +1823,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
         <v>46248</v>
       </c>
@@ -1883,7 +1874,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
         <v>46248</v>
       </c>
@@ -1934,7 +1925,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
         <v>46247</v>
       </c>
@@ -1985,7 +1976,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A15" s="2">
         <v>46248</v>
       </c>
@@ -2034,7 +2025,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
         <v>46248</v>
       </c>
@@ -2083,7 +2074,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
         <v>46248</v>
       </c>
@@ -2132,7 +2123,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
         <v>46248</v>
       </c>
@@ -2181,7 +2172,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
         <v>46248</v>
       </c>
@@ -2230,7 +2221,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
         <v>46248</v>
       </c>
@@ -2279,7 +2270,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
         <v>46248</v>
       </c>
@@ -2328,7 +2319,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>46248</v>
       </c>
@@ -2377,7 +2368,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
         <v>46248</v>
       </c>
@@ -2426,7 +2417,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <v>46248</v>
       </c>
@@ -2475,7 +2466,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <v>46248</v>
       </c>
@@ -2524,7 +2515,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
         <v>46248</v>
       </c>
@@ -2573,7 +2564,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
         <v>46248</v>
       </c>
@@ -2622,7 +2613,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A28" s="2">
         <v>46248</v>
       </c>
@@ -2671,7 +2662,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
         <v>46248</v>
       </c>
@@ -2720,7 +2711,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
         <v>46248</v>
       </c>
@@ -2769,7 +2760,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
         <v>46248</v>
       </c>
@@ -2818,7 +2809,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
         <v>46248</v>
       </c>
@@ -2867,7 +2858,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
         <v>46248</v>
       </c>
@@ -2916,7 +2907,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
         <v>46248</v>
       </c>
@@ -2965,7 +2956,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
         <v>46248</v>
       </c>
@@ -3014,7 +3005,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
         <v>46248</v>
       </c>
@@ -3063,7 +3054,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
         <v>46248</v>
       </c>
@@ -3112,7 +3103,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
         <v>46248</v>
       </c>
@@ -3161,7 +3152,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
         <v>46248</v>
       </c>
@@ -3210,7 +3201,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
         <v>46248</v>
       </c>
@@ -3259,7 +3250,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A41" s="2">
         <v>46248</v>
       </c>
@@ -3308,7 +3299,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
         <v>46248</v>
       </c>
@@ -3357,7 +3348,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
         <v>46248</v>
       </c>
@@ -3406,7 +3397,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A44" s="2">
         <v>46248</v>
       </c>
@@ -3455,7 +3446,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A45" s="2">
         <v>46248</v>
       </c>
@@ -3504,7 +3495,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
         <v>46248</v>
       </c>
@@ -3553,7 +3544,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A47" s="2">
         <v>46248</v>
       </c>
@@ -3602,7 +3593,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A48" s="2">
         <v>46248</v>
       </c>
@@ -3651,7 +3642,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A49" s="2">
         <v>46248</v>
       </c>
@@ -3700,7 +3691,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
         <v>46248</v>
       </c>
@@ -3749,7 +3740,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
         <v>46248</v>
       </c>
@@ -3798,7 +3789,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
         <v>46248</v>
       </c>
@@ -3847,7 +3838,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
         <v>46248</v>
       </c>
@@ -3896,7 +3887,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
         <v>46248</v>
       </c>
@@ -3945,7 +3936,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A55" s="2">
         <v>46248</v>
       </c>
@@ -3994,7 +3985,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A56" s="2">
         <v>46248</v>
       </c>
@@ -4043,7 +4034,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
         <v>46248</v>
       </c>
@@ -4092,7 +4083,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
         <v>46248</v>
       </c>
@@ -4141,7 +4132,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A59" s="2">
         <v>46248</v>
       </c>
@@ -4190,7 +4181,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
         <v>46248</v>
       </c>
@@ -4239,7 +4230,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
         <v>46248</v>
       </c>
@@ -4288,7 +4279,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A62" s="2">
         <v>46248</v>
       </c>
@@ -4337,7 +4328,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A63" s="2">
         <v>46248</v>
       </c>
@@ -4386,7 +4377,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A64" s="2">
         <v>46248</v>
       </c>
@@ -4435,7 +4426,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A65" s="2">
         <v>46248</v>
       </c>
@@ -4484,7 +4475,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A66" s="2">
         <v>46248</v>
       </c>
@@ -4533,7 +4524,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A67" s="2">
         <v>46248</v>
       </c>
@@ -4582,7 +4573,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A68" s="2">
         <v>46248</v>
       </c>
@@ -4631,7 +4622,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A69" s="2">
         <v>46248</v>
       </c>
@@ -4680,7 +4671,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A70" s="2">
         <v>46248</v>
       </c>
@@ -4729,7 +4720,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A71" s="2">
         <v>46248</v>
       </c>
@@ -4778,7 +4769,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A72" s="2">
         <v>46248</v>
       </c>
@@ -4827,7 +4818,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A73" s="2">
         <v>46248</v>
       </c>
@@ -4876,7 +4867,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A74" s="2">
         <v>46248</v>
       </c>
@@ -4925,7 +4916,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A75" s="2">
         <v>46248</v>
       </c>
@@ -4974,7 +4965,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A76" s="2">
         <v>46248</v>
       </c>
@@ -5023,7 +5014,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A77" s="2">
         <v>46248</v>
       </c>
@@ -5072,7 +5063,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A78" s="2">
         <v>46248</v>
       </c>
@@ -5121,7 +5112,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A79" s="2">
         <v>46248</v>
       </c>
@@ -5170,7 +5161,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A80" s="2">
         <v>46248</v>
       </c>
@@ -5219,7 +5210,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A81" s="2">
         <v>46248</v>
       </c>
@@ -5268,7 +5259,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A82" s="2">
         <v>46248</v>
       </c>
@@ -5317,7 +5308,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A83" s="2">
         <v>46248</v>
       </c>
@@ -5366,7 +5357,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A84" s="2">
         <v>46248</v>
       </c>
@@ -5415,7 +5406,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A85" s="2">
         <v>46248</v>
       </c>
@@ -5464,7 +5455,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A86" s="2">
         <v>46248</v>
       </c>
@@ -5513,7 +5504,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A87" s="2">
         <v>46248</v>
       </c>
@@ -5562,7 +5553,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A88" s="2">
         <v>46248</v>
       </c>
@@ -5611,7 +5602,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A89" s="2">
         <v>46248</v>
       </c>
@@ -5660,7 +5651,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A90" s="2">
         <v>46248</v>
       </c>
@@ -5709,7 +5700,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A91" s="2">
         <v>46248</v>
       </c>
@@ -5758,7 +5749,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A92" s="2">
         <v>46248</v>
       </c>
@@ -5807,7 +5798,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A93" s="2">
         <v>46248</v>
       </c>
@@ -5856,7 +5847,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A94" s="2">
         <v>46247</v>
       </c>
@@ -5905,7 +5896,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A95" s="2">
         <v>46247</v>
       </c>
@@ -5954,7 +5945,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A96" s="2">
         <v>46247</v>
       </c>
@@ -6003,7 +5994,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A97" s="2">
         <v>46247</v>
       </c>
@@ -6052,7 +6043,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A98" s="2">
         <v>46247</v>
       </c>
@@ -6101,7 +6092,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A99" s="2">
         <v>46247</v>
       </c>
@@ -6150,7 +6141,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A100" s="2">
         <v>46247</v>
       </c>
@@ -6199,7 +6190,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A101" s="2">
         <v>46247</v>
       </c>
@@ -6248,7 +6239,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A102" s="2">
         <v>46247</v>
       </c>
@@ -6297,7 +6288,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A103" s="2">
         <v>46247</v>
       </c>
@@ -6346,7 +6337,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A104" s="2">
         <v>46247</v>
       </c>
@@ -6395,7 +6386,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A105" s="2">
         <v>46247</v>
       </c>
@@ -6444,7 +6435,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A106" s="2">
         <v>46247</v>
       </c>
@@ -6493,7 +6484,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A107" s="2">
         <v>46248</v>
       </c>
@@ -6542,7 +6533,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A108" s="2">
         <v>46247</v>
       </c>
@@ -6591,7 +6582,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A109" s="2">
         <v>46247</v>
       </c>
@@ -6640,7 +6631,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A110" s="2">
         <v>46247</v>
       </c>
@@ -6689,7 +6680,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A111" s="2">
         <v>46247</v>
       </c>
@@ -6738,7 +6729,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A112" s="2">
         <v>46247</v>
       </c>
@@ -6787,7 +6778,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A113" s="2">
         <v>46247</v>
       </c>
@@ -6836,7 +6827,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A114" s="2">
         <v>46247</v>
       </c>
@@ -6885,7 +6876,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A115" s="2">
         <v>46247</v>
       </c>
@@ -6934,7 +6925,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A116" s="2">
         <v>46247</v>
       </c>
@@ -6983,7 +6974,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A117" s="2">
         <v>46247</v>
       </c>
@@ -7032,7 +7023,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A118" s="2">
         <v>46247</v>
       </c>
@@ -7081,7 +7072,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A119" s="2">
         <v>46247</v>
       </c>
@@ -7130,7 +7121,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A120" s="2">
         <v>46247</v>
       </c>
@@ -7179,7 +7170,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A121" s="2">
         <v>46247</v>
       </c>
@@ -7228,7 +7219,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A122" s="2">
         <v>46247</v>
       </c>
@@ -7277,7 +7268,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A123" s="2">
         <v>46247</v>
       </c>
@@ -7326,7 +7317,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A124" s="2">
         <v>46247</v>
       </c>
@@ -7375,7 +7366,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A125" s="2">
         <v>46247</v>
       </c>
@@ -7424,7 +7415,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A126" s="2">
         <v>46247</v>
       </c>
@@ -7473,7 +7464,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A127" s="2">
         <v>46247</v>
       </c>
@@ -7522,7 +7513,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A128" s="2">
         <v>46247</v>
       </c>
@@ -7571,7 +7562,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A129" s="2">
         <v>46247</v>
       </c>
@@ -7620,7 +7611,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A130" s="2">
         <v>46247</v>
       </c>
@@ -7669,7 +7660,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A131" s="2">
         <v>46247</v>
       </c>
@@ -7718,7 +7709,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A132" s="2">
         <v>46247</v>
       </c>
@@ -7767,7 +7758,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A133" s="2">
         <v>46247</v>
       </c>
@@ -7816,7 +7807,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A134" s="2">
         <v>46247</v>
       </c>
@@ -7865,7 +7856,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A135" s="2">
         <v>46247</v>
       </c>
@@ -7914,7 +7905,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A136" s="2">
         <v>46247</v>
       </c>
@@ -8110,7 +8101,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A140" s="2">
         <v>46247</v>
       </c>
@@ -8159,7 +8150,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A141" s="2">
         <v>46247</v>
       </c>
@@ -8208,7 +8199,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A142" s="2">
         <v>46247</v>
       </c>
@@ -8257,7 +8248,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A143" s="2">
         <v>46247</v>
       </c>
@@ -8306,7 +8297,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A144" s="2">
         <v>46247</v>
       </c>
@@ -8355,7 +8346,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A145" s="2">
         <v>46247</v>
       </c>
@@ -8404,7 +8395,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A146" s="2">
         <v>46247</v>
       </c>
@@ -8453,7 +8444,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A147" s="2">
         <v>46247</v>
       </c>
@@ -8502,7 +8493,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A148" s="2">
         <v>46247</v>
       </c>
@@ -8551,7 +8542,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A149" s="2">
         <v>46247</v>
       </c>
@@ -8600,7 +8591,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A150" s="2">
         <v>46247</v>
       </c>
@@ -8649,7 +8640,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A151" s="2">
         <v>46247</v>
       </c>
@@ -8698,7 +8689,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A152" s="2">
         <v>46247</v>
       </c>
@@ -8747,7 +8738,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A153" s="2">
         <v>46247</v>
       </c>
@@ -8796,7 +8787,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A154" s="2">
         <v>46247</v>
       </c>
@@ -8845,7 +8836,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A155" s="2">
         <v>46247</v>
       </c>
@@ -8894,7 +8885,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A156" s="2">
         <v>46247</v>
       </c>
@@ -8943,7 +8934,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A157" s="2">
         <v>46247</v>
       </c>
@@ -8992,7 +8983,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A158" s="2">
         <v>46247</v>
       </c>
@@ -9041,7 +9032,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A159" s="2">
         <v>46247</v>
       </c>
@@ -9090,7 +9081,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A160" s="2">
         <v>46246</v>
       </c>
@@ -9139,7 +9130,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A161" s="2">
         <v>46246</v>
       </c>
@@ -9188,7 +9179,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A162" s="2">
         <v>46246</v>
       </c>
@@ -9237,7 +9228,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A163" s="2">
         <v>46246</v>
       </c>
@@ -9286,7 +9277,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A164" s="2">
         <v>46246</v>
       </c>
@@ -9335,7 +9326,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A165" s="2">
         <v>46246</v>
       </c>
@@ -9384,7 +9375,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A166" s="2">
         <v>46246</v>
       </c>
@@ -9433,7 +9424,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A167" s="2">
         <v>46246</v>
       </c>
@@ -9482,7 +9473,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A168" s="2">
         <v>46246</v>
       </c>
@@ -9531,7 +9522,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A169" s="2">
         <v>46246</v>
       </c>
@@ -9580,7 +9571,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A170" s="2">
         <v>46246</v>
       </c>
@@ -9629,7 +9620,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A171" s="2">
         <v>46246</v>
       </c>
@@ -9678,7 +9669,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A172" s="2">
         <v>46246</v>
       </c>
@@ -9727,7 +9718,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A173" s="2">
         <v>46246</v>
       </c>
@@ -9776,7 +9767,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A174" s="2">
         <v>46246</v>
       </c>
@@ -9825,7 +9816,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A175" s="2">
         <v>46246</v>
       </c>
@@ -9874,7 +9865,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A176" s="2">
         <v>46246</v>
       </c>
@@ -9923,7 +9914,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A177" s="2">
         <v>46246</v>
       </c>
@@ -9972,7 +9963,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A178" s="2">
         <v>46246</v>
       </c>
@@ -10021,7 +10012,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A179" s="2">
         <v>46246</v>
       </c>
@@ -10070,7 +10061,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A180" s="2">
         <v>46246</v>
       </c>
@@ -10119,7 +10110,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A181" s="2">
         <v>46246</v>
       </c>
@@ -10168,7 +10159,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A182" s="2">
         <v>46246</v>
       </c>
@@ -10217,7 +10208,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A183" s="2">
         <v>46246</v>
       </c>
@@ -10266,7 +10257,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A184" s="2">
         <v>46246</v>
       </c>
@@ -10315,7 +10306,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A185" s="2">
         <v>46246</v>
       </c>
@@ -10364,7 +10355,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A186" s="2">
         <v>46246</v>
       </c>
@@ -10413,7 +10404,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A187" s="2">
         <v>46246</v>
       </c>
@@ -10462,7 +10453,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A188" s="2">
         <v>46246</v>
       </c>
@@ -10511,7 +10502,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A189" s="2">
         <v>46246</v>
       </c>
@@ -10560,7 +10551,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A190" s="2">
         <v>46246</v>
       </c>
@@ -10609,7 +10600,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A191" s="2">
         <v>46246</v>
       </c>
@@ -10658,7 +10649,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A192" s="2">
         <v>46246</v>
       </c>
@@ -10707,7 +10698,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A193" s="2">
         <v>46246</v>
       </c>
@@ -10756,7 +10747,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A194" s="2">
         <v>46246</v>
       </c>
@@ -10805,7 +10796,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A195" s="2">
         <v>46246</v>
       </c>
@@ -10854,7 +10845,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A196" s="2">
         <v>46246</v>
       </c>
@@ -10903,7 +10894,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A197" s="2">
         <v>46246</v>
       </c>
@@ -10952,7 +10943,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A198" s="2">
         <v>46246</v>
       </c>
@@ -11001,7 +10992,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A199" s="2">
         <v>46246</v>
       </c>
@@ -11050,7 +11041,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A200" s="2">
         <v>46246</v>
       </c>
@@ -11099,7 +11090,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A201" s="2">
         <v>46246</v>
       </c>
@@ -11148,7 +11139,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A202" s="2">
         <v>46246</v>
       </c>
@@ -11197,7 +11188,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A203" s="2">
         <v>46246</v>
       </c>
@@ -11246,7 +11237,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A204" s="2">
         <v>46246</v>
       </c>
@@ -11295,7 +11286,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A205" s="2">
         <v>46246</v>
       </c>
@@ -11344,7 +11335,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A206" s="2">
         <v>46246</v>
       </c>
@@ -11393,7 +11384,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A207" s="2">
         <v>46246</v>
       </c>
@@ -11442,7 +11433,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A208" s="2">
         <v>46246</v>
       </c>
@@ -11491,7 +11482,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A209" s="2">
         <v>46246</v>
       </c>
@@ -11540,7 +11531,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A210" s="2">
         <v>46246</v>
       </c>
@@ -11589,7 +11580,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A211" s="2">
         <v>46246</v>
       </c>
@@ -11638,7 +11629,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A212" s="2">
         <v>46246</v>
       </c>
@@ -11687,7 +11678,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A213" s="2">
         <v>46246</v>
       </c>
@@ -11736,7 +11727,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A214" s="2">
         <v>46246</v>
       </c>
@@ -11785,7 +11776,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A215" s="2">
         <v>46246</v>
       </c>
@@ -11834,7 +11825,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A216" s="2">
         <v>46246</v>
       </c>
@@ -11932,7 +11923,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="218" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A218" s="2">
         <v>46246</v>
       </c>
@@ -11981,7 +11972,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="219" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A219" s="2">
         <v>46246</v>
       </c>
@@ -12030,7 +12021,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="220" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A220" s="2">
         <v>46246</v>
       </c>
@@ -12079,7 +12070,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="221" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A221" s="2">
         <v>46246</v>
       </c>
@@ -12128,7 +12119,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A222" s="2">
         <v>46246</v>
       </c>
@@ -12177,7 +12168,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A223" s="2">
         <v>46246</v>
       </c>
@@ -12226,7 +12217,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A224" s="2">
         <v>46246</v>
       </c>
@@ -12275,7 +12266,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A225" s="2">
         <v>46246</v>
       </c>
@@ -12324,7 +12315,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A226" s="2">
         <v>46246</v>
       </c>
@@ -12373,7 +12364,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A227" s="2">
         <v>46246</v>
       </c>
@@ -12422,7 +12413,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A228" s="2">
         <v>46246</v>
       </c>
@@ -12471,7 +12462,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A229" s="2">
         <v>46246</v>
       </c>
@@ -12520,7 +12511,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A230" s="2">
         <v>46246</v>
       </c>
@@ -12569,7 +12560,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A231" s="2">
         <v>46246</v>
       </c>
@@ -12618,7 +12609,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A232" s="2">
         <v>46246</v>
       </c>
@@ -12667,7 +12658,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A233" s="2">
         <v>46246</v>
       </c>
@@ -12716,7 +12707,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A234" s="2">
         <v>46246</v>
       </c>
@@ -12765,7 +12756,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A235" s="2">
         <v>46246</v>
       </c>
@@ -12814,7 +12805,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A236" s="2">
         <v>46246</v>
       </c>
@@ -12863,7 +12854,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="237" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A237" s="2">
         <v>46246</v>
       </c>
@@ -12912,7 +12903,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="238" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A238" s="2">
         <v>46246</v>
       </c>
@@ -12961,7 +12952,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A239" s="2">
         <v>46246</v>
       </c>
@@ -13010,7 +13001,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="240" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A240" s="2">
         <v>46246</v>
       </c>
@@ -13059,7 +13050,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="241" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A241" s="2">
         <v>46246</v>
       </c>
@@ -13108,7 +13099,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="242" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A242" s="2">
         <v>46246</v>
       </c>
@@ -13157,7 +13148,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="243" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A243" s="2">
         <v>46246</v>
       </c>
@@ -13206,7 +13197,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="244" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A244" s="2">
         <v>46245</v>
       </c>
@@ -13255,7 +13246,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="245" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A245" s="2">
         <v>46245</v>
       </c>
@@ -13304,7 +13295,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="246" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A246" s="2">
         <v>46245</v>
       </c>
@@ -13353,7 +13344,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="247" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A247" s="2">
         <v>46245</v>
       </c>
@@ -13402,7 +13393,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="248" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A248" s="2">
         <v>46245</v>
       </c>
@@ -13451,7 +13442,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="249" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A249" s="2">
         <v>46245</v>
       </c>
@@ -13500,7 +13491,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="250" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A250" s="2">
         <v>46245</v>
       </c>
@@ -13549,7 +13540,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="251" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A251" s="2">
         <v>46245</v>
       </c>
@@ -13598,7 +13589,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="252" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A252" s="2">
         <v>46245</v>
       </c>
@@ -13647,7 +13638,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="253" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A253" s="2">
         <v>46245</v>
       </c>
@@ -13696,7 +13687,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="254" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A254" s="2">
         <v>46245</v>
       </c>
@@ -13745,7 +13736,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="255" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A255" s="2">
         <v>46245</v>
       </c>
@@ -13794,7 +13785,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="256" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A256" s="2">
         <v>46245</v>
       </c>
@@ -13843,7 +13834,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="257" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A257" s="2">
         <v>46245</v>
       </c>
@@ -13892,7 +13883,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="258" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A258" s="2">
         <v>46245</v>
       </c>
@@ -13941,7 +13932,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="259" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A259" s="2">
         <v>46245</v>
       </c>
@@ -13990,7 +13981,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="260" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A260" s="2">
         <v>46245</v>
       </c>
@@ -14039,7 +14030,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="261" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A261" s="2">
         <v>46245</v>
       </c>
@@ -14088,7 +14079,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="262" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A262" s="2">
         <v>46245</v>
       </c>
@@ -14137,7 +14128,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="263" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A263" s="2">
         <v>46245</v>
       </c>
@@ -14186,7 +14177,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="264" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A264" s="2">
         <v>46245</v>
       </c>
@@ -14235,7 +14226,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="265" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A265" s="2">
         <v>46245</v>
       </c>
@@ -14284,7 +14275,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="266" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A266" s="2">
         <v>46245</v>
       </c>
@@ -14333,7 +14324,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="267" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A267" s="2">
         <v>46245</v>
       </c>
@@ -14382,7 +14373,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="268" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A268" s="2">
         <v>46245</v>
       </c>
@@ -14431,7 +14422,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="269" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A269" s="2">
         <v>46245</v>
       </c>
@@ -14480,7 +14471,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="270" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A270" s="2">
         <v>46245</v>
       </c>
@@ -14529,7 +14520,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="271" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A271" s="2">
         <v>46245</v>
       </c>
@@ -14578,7 +14569,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="272" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A272" s="2">
         <v>46245</v>
       </c>
@@ -14627,7 +14618,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="273" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A273" s="2">
         <v>46245</v>
       </c>
@@ -14676,7 +14667,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="274" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A274" s="2">
         <v>46245</v>
       </c>
@@ -14725,7 +14716,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="275" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A275" s="2">
         <v>46245</v>
       </c>
@@ -14774,7 +14765,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="276" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A276" s="2">
         <v>46245</v>
       </c>
@@ -14823,7 +14814,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="277" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A277" s="2">
         <v>46245</v>
       </c>
@@ -14872,7 +14863,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="278" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A278" s="2">
         <v>46245</v>
       </c>
@@ -14921,7 +14912,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="279" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A279" s="2">
         <v>46245</v>
       </c>
@@ -14970,7 +14961,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="280" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A280" s="2">
         <v>46245</v>
       </c>
@@ -15019,7 +15010,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="281" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A281" s="2">
         <v>46245</v>
       </c>
@@ -15068,7 +15059,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="282" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A282" s="2">
         <v>46245</v>
       </c>
@@ -15117,7 +15108,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="283" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A283" s="2">
         <v>46245</v>
       </c>
@@ -15166,7 +15157,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="284" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A284" s="2">
         <v>46245</v>
       </c>
@@ -15215,7 +15206,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="285" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A285" s="2">
         <v>46245</v>
       </c>
@@ -15264,7 +15255,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="286" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A286" s="2">
         <v>46245</v>
       </c>
@@ -15362,7 +15353,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="288" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A288" s="2">
         <v>46245</v>
       </c>
@@ -15411,7 +15402,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="289" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A289" s="2">
         <v>46245</v>
       </c>
@@ -15460,7 +15451,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="290" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A290" s="2">
         <v>46245</v>
       </c>
@@ -15509,7 +15500,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="291" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A291" s="2">
         <v>46245</v>
       </c>
@@ -15558,7 +15549,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="292" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A292" s="2">
         <v>46245</v>
       </c>
@@ -15607,7 +15598,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="293" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A293" s="2">
         <v>46245</v>
       </c>
@@ -15656,7 +15647,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="294" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A294" s="2">
         <v>46245</v>
       </c>
@@ -15705,7 +15696,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="295" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A295" s="2">
         <v>46245</v>
       </c>
@@ -15754,7 +15745,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="296" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A296" s="2">
         <v>46245</v>
       </c>
@@ -15803,7 +15794,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="297" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A297" s="2">
         <v>46245</v>
       </c>
@@ -15852,7 +15843,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="298" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A298" s="2">
         <v>46245</v>
       </c>
@@ -15901,7 +15892,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="299" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A299" s="2">
         <v>46245</v>
       </c>
@@ -15950,7 +15941,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="300" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A300" s="2">
         <v>46245</v>
       </c>
@@ -15999,7 +15990,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="301" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A301" s="2">
         <v>46245</v>
       </c>
@@ -16048,7 +16039,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="302" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A302" s="2">
         <v>46245</v>
       </c>
@@ -16097,7 +16088,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="303" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A303" s="2">
         <v>46245</v>
       </c>
@@ -16146,7 +16137,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="304" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A304" s="2">
         <v>46245</v>
       </c>
@@ -16195,7 +16186,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="305" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A305" s="2">
         <v>46245</v>
       </c>
@@ -16244,7 +16235,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="306" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A306" s="2">
         <v>46245</v>
       </c>
@@ -16293,7 +16284,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="307" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A307" s="2">
         <v>46245</v>
       </c>
@@ -16342,7 +16333,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="308" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A308" s="2">
         <v>46245</v>
       </c>
@@ -16391,7 +16382,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="309" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A309" s="2">
         <v>46245</v>
       </c>
@@ -16440,7 +16431,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="310" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A310" s="2">
         <v>46245</v>
       </c>
@@ -16489,7 +16480,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="311" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A311" s="2">
         <v>46245</v>
       </c>
@@ -16538,7 +16529,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="312" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A312" s="2">
         <v>46245</v>
       </c>
@@ -16587,7 +16578,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="313" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A313" s="2">
         <v>46245</v>
       </c>
@@ -16636,7 +16627,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="314" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A314" s="2">
         <v>46245</v>
       </c>
@@ -16685,7 +16676,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="315" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A315" s="2">
         <v>46245</v>
       </c>
@@ -16734,7 +16725,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="316" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A316" s="2">
         <v>46245</v>
       </c>
@@ -16783,7 +16774,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="317" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A317" s="2">
         <v>46245</v>
       </c>
@@ -16832,7 +16823,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="318" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A318" s="2">
         <v>46244</v>
       </c>
@@ -16881,7 +16872,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="319" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A319" s="2">
         <v>46244</v>
       </c>
@@ -16930,7 +16921,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="320" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A320" s="2">
         <v>46244</v>
       </c>
@@ -16979,7 +16970,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="321" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A321" s="2">
         <v>46244</v>
       </c>
@@ -17028,7 +17019,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="322" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A322" s="2">
         <v>46244</v>
       </c>
@@ -17077,7 +17068,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="323" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A323" s="2">
         <v>46244</v>
       </c>
@@ -17126,7 +17117,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="324" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A324" s="2">
         <v>46244</v>
       </c>
@@ -17175,7 +17166,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="325" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A325" s="2">
         <v>46244</v>
       </c>
@@ -17224,7 +17215,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="326" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A326" s="2">
         <v>46244</v>
       </c>
@@ -17273,7 +17264,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="327" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A327" s="2">
         <v>46244</v>
       </c>
@@ -17322,7 +17313,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="328" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A328" s="2">
         <v>46244</v>
       </c>
@@ -17371,7 +17362,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="329" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A329" s="2">
         <v>46244</v>
       </c>
@@ -17420,7 +17411,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="330" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A330" s="2">
         <v>46244</v>
       </c>
@@ -17469,7 +17460,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="331" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A331" s="2">
         <v>46244</v>
       </c>
@@ -17518,7 +17509,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="332" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A332" s="2">
         <v>46244</v>
       </c>
@@ -17567,7 +17558,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="333" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A333" s="2">
         <v>46244</v>
       </c>
@@ -17616,7 +17607,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="334" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A334" s="2">
         <v>46244</v>
       </c>
@@ -17665,7 +17656,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="335" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A335" s="2">
         <v>46244</v>
       </c>
@@ -17714,7 +17705,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="336" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A336" s="2">
         <v>46244</v>
       </c>
@@ -17763,7 +17754,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="337" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A337" s="2">
         <v>46244</v>
       </c>
@@ -17812,7 +17803,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="338" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A338" s="2">
         <v>46244</v>
       </c>
@@ -17861,7 +17852,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="339" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A339" s="2">
         <v>46244</v>
       </c>
@@ -17910,7 +17901,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="340" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A340" s="2">
         <v>46244</v>
       </c>
@@ -17959,7 +17950,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="341" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A341" s="2">
         <v>46244</v>
       </c>
@@ -18008,7 +17999,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="342" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A342" s="2">
         <v>46244</v>
       </c>
@@ -18057,7 +18048,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="343" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A343" s="2">
         <v>46244</v>
       </c>
@@ -18106,7 +18097,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="344" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A344" s="2">
         <v>46244</v>
       </c>
@@ -18155,7 +18146,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="345" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A345" s="2">
         <v>46244</v>
       </c>
@@ -18204,7 +18195,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="346" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A346" s="2">
         <v>46244</v>
       </c>
@@ -18253,7 +18244,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="347" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A347" s="2">
         <v>46244</v>
       </c>
@@ -18302,7 +18293,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="348" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A348" s="2">
         <v>46244</v>
       </c>
@@ -18351,7 +18342,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="349" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A349" s="2">
         <v>46244</v>
       </c>
@@ -18400,7 +18391,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="350" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A350" s="2">
         <v>46244</v>
       </c>
@@ -18449,7 +18440,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="351" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A351" s="2">
         <v>46244</v>
       </c>
@@ -18498,7 +18489,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="352" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A352" s="2">
         <v>46244</v>
       </c>
@@ -18547,7 +18538,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="353" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A353" s="2">
         <v>46244</v>
       </c>
@@ -18596,7 +18587,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="354" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A354" s="2">
         <v>46244</v>
       </c>
@@ -18645,7 +18636,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="355" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A355" s="2">
         <v>46244</v>
       </c>
@@ -18694,7 +18685,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="356" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A356" s="2">
         <v>46244</v>
       </c>
@@ -18743,7 +18734,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="357" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A357" s="2">
         <v>46244</v>
       </c>
@@ -18792,7 +18783,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="358" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A358" s="2">
         <v>46244</v>
       </c>
@@ -18841,7 +18832,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="359" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A359" s="2">
         <v>46244</v>
       </c>
@@ -18890,7 +18881,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="360" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A360" s="2">
         <v>46244</v>
       </c>
@@ -18939,7 +18930,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="361" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A361" s="2">
         <v>46244</v>
       </c>
@@ -18988,7 +18979,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="362" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A362" s="2">
         <v>46244</v>
       </c>
@@ -19037,7 +19028,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="363" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A363" s="2">
         <v>46244</v>
       </c>
@@ -19086,7 +19077,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="364" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A364" s="2">
         <v>46244</v>
       </c>
@@ -19135,7 +19126,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="365" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A365" s="2">
         <v>46244</v>
       </c>
@@ -19184,7 +19175,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="366" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A366" s="2">
         <v>46244</v>
       </c>
@@ -19233,7 +19224,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="367" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A367" s="2">
         <v>46244</v>
       </c>
@@ -19282,7 +19273,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="368" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A368" s="2">
         <v>46244</v>
       </c>
@@ -19331,7 +19322,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="369" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A369" s="2">
         <v>46244</v>
       </c>
@@ -19380,7 +19371,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="370" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A370" s="2">
         <v>46244</v>
       </c>
@@ -19429,7 +19420,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="371" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A371" s="2">
         <v>46244</v>
       </c>
@@ -19478,7 +19469,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="372" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A372" s="2">
         <v>46244</v>
       </c>
@@ -19527,7 +19518,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="373" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A373" s="2">
         <v>46244</v>
       </c>
@@ -19576,7 +19567,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="374" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A374" s="2">
         <v>46244</v>
       </c>
@@ -19625,7 +19616,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="375" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A375" s="2">
         <v>46244</v>
       </c>
@@ -19674,7 +19665,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="376" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A376" s="2">
         <v>46244</v>
       </c>
@@ -19723,7 +19714,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="377" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A377" s="2">
         <v>46244</v>
       </c>
@@ -19772,7 +19763,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="378" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A378" s="2">
         <v>46244</v>
       </c>
@@ -19821,7 +19812,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="379" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A379" s="2">
         <v>46244</v>
       </c>
@@ -19870,7 +19861,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="380" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A380" s="2">
         <v>46244</v>
       </c>
@@ -19919,7 +19910,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="381" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A381" s="2">
         <v>46244</v>
       </c>
@@ -19968,7 +19959,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="382" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A382" s="2">
         <v>46244</v>
       </c>
@@ -20017,7 +20008,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="383" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A383" s="2">
         <v>46244</v>
       </c>
@@ -20409,7 +20400,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="391" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A391" s="2">
         <v>46256</v>
       </c>
@@ -20458,7 +20449,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="392" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A392" s="2">
         <v>46256</v>
       </c>
@@ -20507,7 +20498,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="393" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A393" s="2">
         <v>46256</v>
       </c>
@@ -20556,7 +20547,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="394" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A394" s="2">
         <v>46256</v>
       </c>
@@ -20605,7 +20596,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="395" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A395" s="2">
         <v>46256</v>
       </c>
@@ -20654,7 +20645,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="396" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A396" s="2">
         <v>46256</v>
       </c>
@@ -20703,7 +20694,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="397" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A397" s="2">
         <v>46256</v>
       </c>
@@ -20752,7 +20743,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="398" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A398" s="2">
         <v>46256</v>
       </c>
@@ -20801,7 +20792,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="399" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A399" s="2">
         <v>46256</v>
       </c>
@@ -20842,7 +20833,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="400" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A400" s="2">
         <v>46256</v>
       </c>
@@ -20883,7 +20874,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="401" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A401" s="2">
         <v>46256</v>
       </c>
@@ -20932,7 +20923,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="402" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A402" s="2">
         <v>46256</v>
       </c>
@@ -20981,7 +20972,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="403" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A403" s="2">
         <v>46256</v>
       </c>
@@ -21030,7 +21021,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="404" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A404" s="2">
         <v>46256</v>
       </c>
@@ -21079,7 +21070,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="405" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A405" s="2">
         <v>46256</v>
       </c>
@@ -21128,7 +21119,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="406" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A406" s="2">
         <v>46256</v>
       </c>
@@ -21177,7 +21168,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="407" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A407" s="2">
         <v>46256</v>
       </c>
@@ -21226,7 +21217,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="408" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A408" s="2">
         <v>46256</v>
       </c>
@@ -21275,7 +21266,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="409" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A409" s="2">
         <v>46256</v>
       </c>
@@ -21324,7 +21315,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="410" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A410" s="2">
         <v>46256</v>
       </c>
@@ -21373,7 +21364,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="411" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A411" s="2">
         <v>46256</v>
       </c>
@@ -21422,7 +21413,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="412" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A412" s="2">
         <v>46256</v>
       </c>
@@ -21471,7 +21462,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="413" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A413" s="2">
         <v>46256</v>
       </c>
@@ -21520,7 +21511,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="414" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A414" s="2">
         <v>46256</v>
       </c>
@@ -21569,7 +21560,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="415" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A415" s="2">
         <v>46256</v>
       </c>
@@ -21618,7 +21609,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="416" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A416" s="2">
         <v>46256</v>
       </c>
@@ -21667,7 +21658,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="417" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A417" s="2">
         <v>46256</v>
       </c>
@@ -21716,7 +21707,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="418" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A418" s="2">
         <v>46256</v>
       </c>
@@ -21765,7 +21756,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="419" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A419" s="2">
         <v>46256</v>
       </c>
@@ -21814,7 +21805,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="420" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A420" s="2">
         <v>46256</v>
       </c>
@@ -21863,7 +21854,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="421" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A421" s="2">
         <v>46256</v>
       </c>
@@ -21912,7 +21903,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="422" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A422" s="2">
         <v>46256</v>
       </c>
@@ -21961,7 +21952,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="423" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A423" s="2">
         <v>46256</v>
       </c>
@@ -22010,7 +22001,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="424" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A424" s="2">
         <v>46256</v>
       </c>
@@ -22059,7 +22050,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="425" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A425" s="2">
         <v>46256</v>
       </c>
@@ -22108,7 +22099,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="426" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A426" s="2">
         <v>46256</v>
       </c>
@@ -22157,7 +22148,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="427" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A427" s="2">
         <v>46256</v>
       </c>
@@ -22206,7 +22197,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="428" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A428" s="2">
         <v>46256</v>
       </c>
@@ -22255,7 +22246,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="429" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A429" s="2">
         <v>46256</v>
       </c>
@@ -22304,7 +22295,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="430" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A430" s="2">
         <v>46256</v>
       </c>
@@ -22353,7 +22344,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="431" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A431" s="2">
         <v>46256</v>
       </c>
@@ -22402,7 +22393,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="432" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A432" s="2">
         <v>46256</v>
       </c>
@@ -22451,7 +22442,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="433" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A433" s="2">
         <v>46256</v>
       </c>
@@ -22500,7 +22491,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="434" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A434" s="2">
         <v>46256</v>
       </c>
@@ -22549,7 +22540,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="435" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A435" s="2">
         <v>46256</v>
       </c>
@@ -22598,7 +22589,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="436" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A436" s="2">
         <v>46256</v>
       </c>
@@ -22647,7 +22638,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="437" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A437" s="2">
         <v>46256</v>
       </c>
@@ -22696,7 +22687,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="438" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A438" s="2">
         <v>46256</v>
       </c>
@@ -22745,7 +22736,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="439" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A439" s="2">
         <v>46256</v>
       </c>
@@ -22794,7 +22785,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="440" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A440" s="2">
         <v>46256</v>
       </c>
@@ -22843,7 +22834,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="441" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A441" s="2">
         <v>46256</v>
       </c>
@@ -22892,7 +22883,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="442" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A442" s="2">
         <v>46256</v>
       </c>
@@ -22941,7 +22932,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="443" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A443" s="2">
         <v>46256</v>
       </c>
@@ -22990,7 +22981,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="444" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A444" s="2">
         <v>46256</v>
       </c>
@@ -23039,7 +23030,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="445" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A445" s="2">
         <v>46256</v>
       </c>
@@ -23088,7 +23079,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="446" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A446" s="2">
         <v>46256</v>
       </c>
@@ -23137,7 +23128,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="447" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A447" s="2">
         <v>46255</v>
       </c>
@@ -23186,7 +23177,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="448" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A448" s="2">
         <v>46255</v>
       </c>
@@ -23235,7 +23226,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="449" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A449" s="2">
         <v>46255</v>
       </c>
@@ -23284,7 +23275,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="450" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A450" s="2">
         <v>46255</v>
       </c>
@@ -23333,7 +23324,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="451" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A451" s="2">
         <v>46255</v>
       </c>
@@ -23382,7 +23373,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="452" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A452" s="2">
         <v>46255</v>
       </c>
@@ -23431,7 +23422,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="453" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A453" s="2">
         <v>46255</v>
       </c>
@@ -23480,7 +23471,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="454" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A454" s="2">
         <v>46255</v>
       </c>
@@ -23529,7 +23520,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="455" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A455" s="2">
         <v>46255</v>
       </c>
@@ -23578,7 +23569,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="456" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A456" s="2">
         <v>46255</v>
       </c>
@@ -23627,7 +23618,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="457" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A457" s="2">
         <v>46255</v>
       </c>
@@ -23676,7 +23667,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="458" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A458" s="2">
         <v>46255</v>
       </c>
@@ -23725,7 +23716,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="459" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A459" s="2">
         <v>46255</v>
       </c>
@@ -23774,7 +23765,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="460" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A460" s="2">
         <v>46255</v>
       </c>
@@ -23823,7 +23814,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="461" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A461" s="2">
         <v>46255</v>
       </c>
@@ -23872,7 +23863,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="462" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A462" s="2">
         <v>46255</v>
       </c>
@@ -23921,7 +23912,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="463" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A463" s="2">
         <v>46255</v>
       </c>
@@ -23970,7 +23961,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="464" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A464" s="2">
         <v>46255</v>
       </c>
@@ -24019,7 +24010,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="465" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A465" s="2">
         <v>46255</v>
       </c>
@@ -24068,7 +24059,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="466" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A466" s="2">
         <v>46255</v>
       </c>
@@ -24117,7 +24108,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="467" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A467" s="2">
         <v>46255</v>
       </c>
@@ -24166,7 +24157,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="468" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A468" s="2">
         <v>46255</v>
       </c>
@@ -24215,7 +24206,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="469" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A469" s="2">
         <v>46255</v>
       </c>
@@ -24264,7 +24255,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="470" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A470" s="2">
         <v>46255</v>
       </c>
@@ -24313,7 +24304,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="471" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A471" s="2">
         <v>46255</v>
       </c>
@@ -24362,7 +24353,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="472" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A472" s="2">
         <v>46255</v>
       </c>
@@ -24411,7 +24402,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="473" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A473" s="2">
         <v>46255</v>
       </c>
@@ -24460,7 +24451,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="474" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A474" s="2">
         <v>46255</v>
       </c>
@@ -24509,7 +24500,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="475" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A475" s="2">
         <v>46255</v>
       </c>
@@ -24558,7 +24549,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="476" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A476" s="2">
         <v>46255</v>
       </c>
@@ -24607,7 +24598,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="477" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A477" s="2">
         <v>46255</v>
       </c>
@@ -24656,7 +24647,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="478" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A478" s="2">
         <v>46255</v>
       </c>
@@ -24705,7 +24696,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="479" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A479" s="2">
         <v>46255</v>
       </c>
@@ -24754,7 +24745,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="480" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A480" s="2">
         <v>46255</v>
       </c>
@@ -24803,7 +24794,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="481" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A481" s="2">
         <v>46255</v>
       </c>
@@ -24852,7 +24843,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="482" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A482" s="2">
         <v>46255</v>
       </c>
@@ -24901,7 +24892,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="483" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A483" s="2">
         <v>46255</v>
       </c>
@@ -24950,7 +24941,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="484" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A484" s="2">
         <v>46255</v>
       </c>
@@ -24999,7 +24990,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="485" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A485" s="2">
         <v>46255</v>
       </c>
@@ -25048,7 +25039,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="486" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A486" s="2">
         <v>46255</v>
       </c>
@@ -25097,7 +25088,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="487" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A487" s="2">
         <v>46255</v>
       </c>
@@ -25146,7 +25137,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="488" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A488" s="2">
         <v>46255</v>
       </c>
@@ -25195,7 +25186,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="489" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A489" s="2">
         <v>46255</v>
       </c>
@@ -25244,7 +25235,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="490" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A490" s="2">
         <v>46255</v>
       </c>
@@ -25293,7 +25284,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="491" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A491" s="2">
         <v>46255</v>
       </c>
@@ -25342,7 +25333,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="492" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A492" s="2">
         <v>46255</v>
       </c>
@@ -25391,7 +25382,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="493" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A493" s="2">
         <v>46255</v>
       </c>
@@ -25440,7 +25431,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="494" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A494" s="2">
         <v>46255</v>
       </c>
@@ -25489,7 +25480,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="495" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A495" s="2">
         <v>46255</v>
       </c>
@@ -25538,7 +25529,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="496" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A496" s="2">
         <v>46255</v>
       </c>
@@ -25587,7 +25578,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="497" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A497" s="2">
         <v>46255</v>
       </c>
@@ -25636,7 +25627,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="498" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A498" s="2">
         <v>46255</v>
       </c>
@@ -25685,7 +25676,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="499" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A499" s="2">
         <v>46255</v>
       </c>
@@ -25734,7 +25725,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="500" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A500" s="2">
         <v>46255</v>
       </c>
@@ -25783,7 +25774,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="501" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A501" s="2">
         <v>46255</v>
       </c>
@@ -25832,7 +25823,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="502" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A502" s="2">
         <v>46255</v>
       </c>
@@ -25881,7 +25872,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="503" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A503" s="2">
         <v>46254</v>
       </c>
@@ -25930,7 +25921,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="504" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A504" s="2">
         <v>46254</v>
       </c>
@@ -25979,7 +25970,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="505" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A505" s="2">
         <v>46254</v>
       </c>
@@ -26028,7 +26019,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="506" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A506" s="2">
         <v>46254</v>
       </c>
@@ -26077,7 +26068,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="507" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A507" s="2">
         <v>46254</v>
       </c>
@@ -26126,7 +26117,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="508" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A508" s="2">
         <v>46254</v>
       </c>
@@ -26175,7 +26166,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="509" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A509" s="2">
         <v>46254</v>
       </c>
@@ -26224,7 +26215,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="510" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A510" s="2">
         <v>46254</v>
       </c>
@@ -26273,7 +26264,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="511" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A511" s="2">
         <v>46254</v>
       </c>
@@ -26322,7 +26313,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="512" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A512" s="2">
         <v>46254</v>
       </c>
@@ -26371,7 +26362,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="513" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A513" s="2">
         <v>46254</v>
       </c>
@@ -26420,7 +26411,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="514" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A514" s="2">
         <v>46254</v>
       </c>
@@ -26469,7 +26460,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="515" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A515" s="2">
         <v>46254</v>
       </c>
@@ -26518,7 +26509,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="516" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A516" s="2">
         <v>46254</v>
       </c>
@@ -26567,7 +26558,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="517" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A517" s="2">
         <v>46254</v>
       </c>
@@ -26616,7 +26607,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="518" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A518" s="2">
         <v>46254</v>
       </c>
@@ -26665,7 +26656,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="519" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A519" s="2">
         <v>46254</v>
       </c>
@@ -26714,7 +26705,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="520" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A520" s="2">
         <v>46255</v>
       </c>
@@ -26763,7 +26754,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="521" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A521" s="2">
         <v>46255</v>
       </c>
@@ -26812,7 +26803,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="522" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A522" s="2">
         <v>46255</v>
       </c>
@@ -26861,7 +26852,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="523" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A523" s="2">
         <v>46255</v>
       </c>
@@ -26910,7 +26901,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="524" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A524" s="2">
         <v>46255</v>
       </c>
@@ -26959,7 +26950,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="525" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A525" s="2">
         <v>46255</v>
       </c>
@@ -27008,7 +26999,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="526" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A526" s="2">
         <v>46255</v>
       </c>
@@ -27057,7 +27048,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="527" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A527" s="2">
         <v>46255</v>
       </c>
@@ -27106,7 +27097,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="528" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A528" s="2">
         <v>46255</v>
       </c>
@@ -27155,7 +27146,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="529" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A529" s="2">
         <v>46255</v>
       </c>
@@ -27204,7 +27195,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="530" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A530" s="2">
         <v>46255</v>
       </c>
@@ -27253,7 +27244,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="531" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A531" s="2">
         <v>46255</v>
       </c>
@@ -27302,7 +27293,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="532" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A532" s="2">
         <v>46255</v>
       </c>
@@ -27351,7 +27342,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="533" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A533" s="2">
         <v>46255</v>
       </c>
@@ -27400,7 +27391,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="534" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A534" s="2">
         <v>46255</v>
       </c>
@@ -27449,7 +27440,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="535" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A535" s="2">
         <v>46255</v>
       </c>
@@ -27498,7 +27489,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="536" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A536" s="2">
         <v>46255</v>
       </c>
@@ -27547,7 +27538,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="537" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A537" s="2">
         <v>46255</v>
       </c>
@@ -27596,7 +27587,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="538" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A538" s="2">
         <v>46255</v>
       </c>
@@ -27645,7 +27636,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="539" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A539" s="2">
         <v>46255</v>
       </c>
@@ -27694,7 +27685,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="540" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A540" s="2">
         <v>46255</v>
       </c>
@@ -27743,7 +27734,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="541" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A541" s="2">
         <v>46255</v>
       </c>
@@ -27792,7 +27783,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="542" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A542" s="2">
         <v>46255</v>
       </c>
@@ -27841,7 +27832,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="543" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A543" s="2">
         <v>46255</v>
       </c>
@@ -27890,7 +27881,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="544" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="544" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A544" s="2">
         <v>46254</v>
       </c>
@@ -27939,7 +27930,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="545" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A545" s="2">
         <v>46254</v>
       </c>
@@ -27988,7 +27979,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="546" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A546" s="2">
         <v>46254</v>
       </c>
@@ -28037,7 +28028,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="547" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A547" s="2">
         <v>46254</v>
       </c>
@@ -28086,7 +28077,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="548" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A548" s="2">
         <v>46254</v>
       </c>
@@ -28135,7 +28126,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="549" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A549" s="2">
         <v>46254</v>
       </c>
@@ -28184,7 +28175,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="550" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A550" s="2">
         <v>46254</v>
       </c>
@@ -28233,7 +28224,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="551" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A551" s="2">
         <v>46254</v>
       </c>
@@ -28282,7 +28273,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="552" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A552" s="2">
         <v>46254</v>
       </c>
@@ -28331,7 +28322,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="553" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A553" s="2">
         <v>46254</v>
       </c>
@@ -28380,7 +28371,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="554" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A554" s="2">
         <v>46254</v>
       </c>
@@ -28429,7 +28420,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="555" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="555" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A555" s="2">
         <v>46254</v>
       </c>
@@ -28478,7 +28469,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="556" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A556" s="2">
         <v>46254</v>
       </c>
@@ -28527,7 +28518,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="557" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A557" s="2">
         <v>46254</v>
       </c>
@@ -28576,7 +28567,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="558" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="558" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A558" s="2">
         <v>46254</v>
       </c>
@@ -28625,7 +28616,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="559" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A559" s="2">
         <v>46254</v>
       </c>
@@ -28674,7 +28665,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="560" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A560" s="2">
         <v>46254</v>
       </c>
@@ -28723,7 +28714,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="561" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A561" s="2">
         <v>46254</v>
       </c>
@@ -28772,7 +28763,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="562" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A562" s="2">
         <v>46254</v>
       </c>
@@ -28821,7 +28812,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="563" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A563" s="2">
         <v>46254</v>
       </c>
@@ -28870,7 +28861,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="564" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A564" s="2">
         <v>46254</v>
       </c>
@@ -28919,7 +28910,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="565" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A565" s="2">
         <v>46254</v>
       </c>
@@ -28968,7 +28959,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="566" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="566" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A566" s="2">
         <v>46254</v>
       </c>
@@ -29017,7 +29008,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="567" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A567" s="2">
         <v>46254</v>
       </c>
@@ -29066,7 +29057,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="568" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="568" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A568" s="2">
         <v>46254</v>
       </c>
@@ -29115,7 +29106,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="569" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="569" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A569" s="2">
         <v>46254</v>
       </c>
@@ -29164,7 +29155,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="570" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="570" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A570" s="2">
         <v>46254</v>
       </c>
@@ -29213,7 +29204,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="571" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A571" s="2">
         <v>46254</v>
       </c>
@@ -29262,7 +29253,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="572" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A572" s="2">
         <v>46254</v>
       </c>
@@ -29311,7 +29302,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="573" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="573" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A573" s="2">
         <v>46254</v>
       </c>
@@ -29360,7 +29351,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="574" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A574" s="2">
         <v>46254</v>
       </c>
@@ -29409,7 +29400,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="575" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A575" s="2">
         <v>46254</v>
       </c>
@@ -29458,7 +29449,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="576" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A576" s="2">
         <v>46254</v>
       </c>
@@ -29507,7 +29498,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="577" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A577" s="2">
         <v>46254</v>
       </c>
@@ -29556,7 +29547,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="578" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="578" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A578" s="2">
         <v>46254</v>
       </c>
@@ -29605,7 +29596,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="579" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="579" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A579" s="2">
         <v>46254</v>
       </c>
@@ -29654,7 +29645,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="580" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="580" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A580" s="2">
         <v>46254</v>
       </c>
@@ -29703,7 +29694,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="581" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A581" s="2">
         <v>46254</v>
       </c>
@@ -29752,7 +29743,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="582" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A582" s="2">
         <v>46254</v>
       </c>
@@ -29801,7 +29792,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="583" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="583" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A583" s="2">
         <v>46254</v>
       </c>
@@ -29850,7 +29841,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="584" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="584" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A584" s="2">
         <v>46254</v>
       </c>
@@ -29899,7 +29890,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="585" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A585" s="2">
         <v>46253</v>
       </c>
@@ -29948,7 +29939,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="586" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A586" s="2">
         <v>46253</v>
       </c>
@@ -29997,7 +29988,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="587" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A587" s="2">
         <v>46253</v>
       </c>
@@ -30046,7 +30037,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="588" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A588" s="2">
         <v>46253</v>
       </c>
@@ -30095,7 +30086,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="589" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A589" s="2">
         <v>46253</v>
       </c>
@@ -30144,7 +30135,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="590" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A590" s="2">
         <v>46253</v>
       </c>
@@ -30193,7 +30184,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="591" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="591" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A591" s="2">
         <v>46253</v>
       </c>
@@ -30242,7 +30233,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="592" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="592" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A592" s="2">
         <v>46253</v>
       </c>
@@ -30291,7 +30282,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="593" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="593" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A593" s="2">
         <v>46253</v>
       </c>
@@ -30340,7 +30331,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="594" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="594" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A594" s="2">
         <v>46253</v>
       </c>
@@ -30389,7 +30380,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="595" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="595" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A595" s="2">
         <v>46253</v>
       </c>
@@ -30438,7 +30429,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="596" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="596" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A596" s="2">
         <v>46253</v>
       </c>
@@ -30487,7 +30478,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="597" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="597" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A597" s="2">
         <v>46253</v>
       </c>
@@ -30536,7 +30527,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="598" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A598" s="2">
         <v>46253</v>
       </c>
@@ -30585,7 +30576,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="599" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A599" s="2">
         <v>46253</v>
       </c>
@@ -30634,7 +30625,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="600" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A600" s="2">
         <v>46253</v>
       </c>
@@ -30683,7 +30674,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="601" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="601" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A601" s="2">
         <v>46253</v>
       </c>
@@ -30732,7 +30723,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="602" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A602" s="2">
         <v>46253</v>
       </c>
@@ -30781,7 +30772,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="603" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A603" s="2">
         <v>46253</v>
       </c>
@@ -30830,7 +30821,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="604" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A604" s="2">
         <v>46253</v>
       </c>
@@ -30879,7 +30870,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="605" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="605" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A605" s="2">
         <v>46253</v>
       </c>
@@ -30928,7 +30919,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="606" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="606" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A606" s="2">
         <v>46253</v>
       </c>
@@ -30977,7 +30968,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="607" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A607" s="2">
         <v>46253</v>
       </c>
@@ -31026,7 +31017,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="608" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A608" s="2">
         <v>46253</v>
       </c>
@@ -31075,7 +31066,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="609" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A609" s="2">
         <v>46253</v>
       </c>
@@ -31124,7 +31115,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="610" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A610" s="2">
         <v>46253</v>
       </c>
@@ -31173,7 +31164,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="611" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A611" s="2">
         <v>46253</v>
       </c>
@@ -31222,7 +31213,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="612" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="612" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A612" s="2">
         <v>46253</v>
       </c>
@@ -31271,7 +31262,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="613" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="613" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A613" s="2">
         <v>46253</v>
       </c>
@@ -31320,7 +31311,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="614" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="614" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A614" s="2">
         <v>46253</v>
       </c>
@@ -31369,7 +31360,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="615" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="615" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A615" s="2">
         <v>46253</v>
       </c>
@@ -31418,7 +31409,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="616" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A616" s="2">
         <v>46253</v>
       </c>
@@ -31467,7 +31458,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="617" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="617" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A617" s="2">
         <v>46253</v>
       </c>
@@ -31516,7 +31507,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="618" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A618" s="2">
         <v>46253</v>
       </c>
@@ -31565,7 +31556,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="619" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="619" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A619" s="2">
         <v>46253</v>
       </c>
@@ -31614,7 +31605,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="620" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="620" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A620" s="2">
         <v>46253</v>
       </c>
@@ -31663,7 +31654,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="621" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="621" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A621" s="2">
         <v>46253</v>
       </c>
@@ -31712,7 +31703,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="622" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="622" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A622" s="2">
         <v>46253</v>
       </c>
@@ -31761,7 +31752,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="623" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="623" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A623" s="2">
         <v>46253</v>
       </c>
@@ -31810,7 +31801,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="624" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="624" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A624" s="2">
         <v>46253</v>
       </c>
@@ -31859,7 +31850,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="625" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="625" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A625" s="2">
         <v>46253</v>
       </c>
@@ -31908,7 +31899,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="626" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="626" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A626" s="2">
         <v>46253</v>
       </c>
@@ -31957,7 +31948,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="627" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A627" s="2">
         <v>46253</v>
       </c>
@@ -32006,7 +31997,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="628" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A628" s="2">
         <v>46253</v>
       </c>
@@ -32055,7 +32046,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="629" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A629" s="2">
         <v>46253</v>
       </c>
@@ -32104,7 +32095,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="630" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A630" s="2">
         <v>46253</v>
       </c>
@@ -32153,7 +32144,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="631" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A631" s="2">
         <v>46253</v>
       </c>
@@ -32202,7 +32193,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="632" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A632" s="2">
         <v>46253</v>
       </c>
@@ -32251,7 +32242,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="633" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A633" s="2">
         <v>46253</v>
       </c>
@@ -32300,7 +32291,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="634" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="634" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A634" s="2">
         <v>46253</v>
       </c>
@@ -32349,7 +32340,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="635" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="635" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A635" s="2">
         <v>46253</v>
       </c>
@@ -32398,7 +32389,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="636" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="636" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A636" s="2">
         <v>46253</v>
       </c>
@@ -32447,7 +32438,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="637" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="637" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A637" s="2">
         <v>46253</v>
       </c>
@@ -32496,7 +32487,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="638" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="638" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A638" s="2">
         <v>46253</v>
       </c>
@@ -32545,7 +32536,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="639" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="639" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A639" s="2">
         <v>46253</v>
       </c>
@@ -32594,7 +32585,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="640" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A640" s="2">
         <v>46253</v>
       </c>
@@ -32643,7 +32634,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="641" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="641" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A641" s="2">
         <v>46253</v>
       </c>
@@ -32692,7 +32683,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="642" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A642" s="2">
         <v>46253</v>
       </c>
@@ -32741,7 +32732,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="643" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="643" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A643" s="2">
         <v>46253</v>
       </c>
@@ -32790,7 +32781,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="644" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="644" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A644" s="2">
         <v>46253</v>
       </c>
@@ -32839,7 +32830,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="645" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="645" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A645" s="2">
         <v>46253</v>
       </c>
@@ -32888,7 +32879,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="646" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="646" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A646" s="2">
         <v>46253</v>
       </c>
@@ -32937,7 +32928,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="647" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="647" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A647" s="2">
         <v>46253</v>
       </c>
@@ -32986,7 +32977,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="648" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="648" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A648" s="2">
         <v>46253</v>
       </c>
@@ -33035,7 +33026,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="649" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A649" s="2">
         <v>46253</v>
       </c>
@@ -33084,7 +33075,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="650" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="650" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A650" s="2">
         <v>46253</v>
       </c>
@@ -33133,7 +33124,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="651" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A651" s="2">
         <v>46253</v>
       </c>
@@ -33182,7 +33173,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="652" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A652" s="2">
         <v>46253</v>
       </c>
@@ -33231,7 +33222,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="653" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A653" s="2">
         <v>46253</v>
       </c>
@@ -33280,7 +33271,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="654" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A654" s="2">
         <v>46253</v>
       </c>
@@ -33329,7 +33320,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="655" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A655" s="2">
         <v>46253</v>
       </c>
@@ -33378,7 +33369,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="656" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="656" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A656" s="2">
         <v>46253</v>
       </c>
@@ -33427,7 +33418,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="657" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="657" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A657" s="2">
         <v>46253</v>
       </c>
@@ -33476,7 +33467,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="658" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="658" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A658" s="2">
         <v>46253</v>
       </c>
@@ -33525,7 +33516,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="659" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="659" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A659" s="2">
         <v>46253</v>
       </c>
@@ -33574,7 +33565,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="660" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="660" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A660" s="2">
         <v>46253</v>
       </c>
@@ -33623,7 +33614,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="661" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="661" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A661" s="2">
         <v>46253</v>
       </c>
@@ -33672,7 +33663,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="662" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A662" s="2">
         <v>46252</v>
       </c>
@@ -33721,7 +33712,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="663" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="663" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A663" s="2">
         <v>46252</v>
       </c>
@@ -33770,7 +33761,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="664" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="664" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A664" s="2">
         <v>46252</v>
       </c>
@@ -33819,7 +33810,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="665" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="665" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A665" s="2">
         <v>46252</v>
       </c>
@@ -33868,7 +33859,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="666" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="666" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A666" s="2">
         <v>46252</v>
       </c>
@@ -33917,7 +33908,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="667" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="667" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A667" s="2">
         <v>46252</v>
       </c>
@@ -33966,7 +33957,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="668" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="668" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A668" s="2">
         <v>46252</v>
       </c>
@@ -34015,7 +34006,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="669" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="669" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A669" s="2">
         <v>46252</v>
       </c>
@@ -34064,7 +34055,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="670" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="670" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A670" s="2">
         <v>46252</v>
       </c>
@@ -34113,7 +34104,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="671" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="671" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A671" s="2">
         <v>46252</v>
       </c>
@@ -34162,7 +34153,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="672" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="672" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A672" s="2">
         <v>46252</v>
       </c>
@@ -34211,7 +34202,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="673" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="673" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A673" s="2">
         <v>46252</v>
       </c>
@@ -34260,7 +34251,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="674" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="674" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A674" s="2">
         <v>46252</v>
       </c>
@@ -34309,7 +34300,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="675" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="675" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A675" s="2">
         <v>46252</v>
       </c>
@@ -34358,7 +34349,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="676" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="676" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A676" s="2">
         <v>46252</v>
       </c>
@@ -34407,7 +34398,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="677" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="677" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A677" s="2">
         <v>46252</v>
       </c>
@@ -34456,7 +34447,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="678" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="678" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A678" s="2">
         <v>46252</v>
       </c>
@@ -34505,7 +34496,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="679" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="679" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A679" s="2">
         <v>46252</v>
       </c>
@@ -34554,7 +34545,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="680" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="680" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A680" s="2">
         <v>46252</v>
       </c>
@@ -34603,7 +34594,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="681" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="681" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A681" s="2">
         <v>46252</v>
       </c>
@@ -34652,7 +34643,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="682" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="682" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A682" s="2">
         <v>46252</v>
       </c>
@@ -34701,7 +34692,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="683" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="683" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A683" s="2">
         <v>46252</v>
       </c>
@@ -34750,7 +34741,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="684" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="684" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A684" s="2">
         <v>46252</v>
       </c>
@@ -34799,7 +34790,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="685" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="685" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A685" s="2">
         <v>46252</v>
       </c>
@@ -34848,7 +34839,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="686" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="686" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A686" s="2">
         <v>46252</v>
       </c>
@@ -34897,7 +34888,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="687" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="687" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A687" s="2">
         <v>46252</v>
       </c>
@@ -34946,7 +34937,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="688" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="688" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A688" s="2">
         <v>46252</v>
       </c>
@@ -34995,7 +34986,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="689" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="689" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A689" s="2">
         <v>46252</v>
       </c>
@@ -35044,7 +35035,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="690" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="690" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A690" s="2">
         <v>46252</v>
       </c>
@@ -35093,7 +35084,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="691" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="691" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A691" s="2">
         <v>46252</v>
       </c>
@@ -35142,7 +35133,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="692" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="692" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A692" s="2">
         <v>46252</v>
       </c>
@@ -35191,7 +35182,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="693" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="693" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A693" s="2">
         <v>46252</v>
       </c>
@@ -35240,7 +35231,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="694" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="694" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A694" s="2">
         <v>46252</v>
       </c>
@@ -35289,7 +35280,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="695" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="695" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A695" s="2">
         <v>46252</v>
       </c>
@@ -35338,7 +35329,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="696" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="696" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A696" s="2">
         <v>46252</v>
       </c>
@@ -35387,7 +35378,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="697" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="697" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A697" s="2">
         <v>46252</v>
       </c>
@@ -35436,7 +35427,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="698" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="698" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A698" s="2">
         <v>46252</v>
       </c>
@@ -35485,7 +35476,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="699" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="699" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A699" s="2">
         <v>46252</v>
       </c>
@@ -35534,7 +35525,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="700" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="700" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A700" s="2">
         <v>46252</v>
       </c>
@@ -35583,7 +35574,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="701" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="701" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A701" s="2">
         <v>46252</v>
       </c>
@@ -35632,7 +35623,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="702" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="702" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A702" s="2">
         <v>46252</v>
       </c>
@@ -35681,7 +35672,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="703" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="703" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A703" s="2">
         <v>46252</v>
       </c>
@@ -35730,7 +35721,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="704" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="704" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A704" s="2">
         <v>46252</v>
       </c>
@@ -35779,7 +35770,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="705" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="705" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A705" s="2">
         <v>46252</v>
       </c>
@@ -35828,7 +35819,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="706" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="706" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A706" s="2">
         <v>46252</v>
       </c>
@@ -35877,7 +35868,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="707" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="707" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A707" s="2">
         <v>46252</v>
       </c>
@@ -35926,7 +35917,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="708" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="708" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A708" s="2">
         <v>46252</v>
       </c>
@@ -35975,7 +35966,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="709" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="709" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A709" s="2">
         <v>46252</v>
       </c>
@@ -36024,7 +36015,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="710" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="710" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A710" s="2">
         <v>46252</v>
       </c>
@@ -36073,7 +36064,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="711" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="711" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A711" s="2">
         <v>46252</v>
       </c>
@@ -36122,7 +36113,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="712" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="712" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A712" s="2">
         <v>46252</v>
       </c>
@@ -36171,7 +36162,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="713" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="713" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A713" s="2">
         <v>46252</v>
       </c>
@@ -36220,7 +36211,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="714" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="714" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A714" s="2">
         <v>46252</v>
       </c>
@@ -36269,7 +36260,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="715" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="715" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A715" s="2">
         <v>46252</v>
       </c>
@@ -36318,7 +36309,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="716" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="716" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A716" s="2">
         <v>46252</v>
       </c>
@@ -36367,7 +36358,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="717" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="717" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A717" s="2">
         <v>46252</v>
       </c>
@@ -36416,7 +36407,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="718" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="718" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A718" s="2">
         <v>46252</v>
       </c>
@@ -36465,7 +36456,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="719" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="719" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A719" s="2">
         <v>46252</v>
       </c>
@@ -36514,7 +36505,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="720" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="720" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A720" s="2">
         <v>46252</v>
       </c>
@@ -36563,7 +36554,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="721" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="721" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A721" s="2">
         <v>46252</v>
       </c>
@@ -36612,7 +36603,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="722" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="722" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A722" s="2">
         <v>46252</v>
       </c>
@@ -36661,7 +36652,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="723" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="723" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A723" s="2">
         <v>46252</v>
       </c>
@@ -36710,7 +36701,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="724" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="724" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A724" s="2">
         <v>46252</v>
       </c>
@@ -36759,7 +36750,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="725" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="725" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A725" s="2">
         <v>46252</v>
       </c>
@@ -36808,7 +36799,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="726" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="726" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A726" s="2">
         <v>46252</v>
       </c>
@@ -36857,7 +36848,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="727" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="727" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A727" s="2">
         <v>46252</v>
       </c>
@@ -36906,7 +36897,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="728" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="728" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A728" s="2">
         <v>46252</v>
       </c>
@@ -36955,7 +36946,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="729" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="729" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A729" s="2">
         <v>46252</v>
       </c>
@@ -37004,7 +36995,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="730" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="730" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A730" s="2">
         <v>46252</v>
       </c>
@@ -37053,7 +37044,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="731" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="731" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A731" s="2">
         <v>46252</v>
       </c>
@@ -37102,7 +37093,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="732" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="732" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A732" s="2">
         <v>46252</v>
       </c>
@@ -37151,7 +37142,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="733" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="733" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A733" s="2">
         <v>46252</v>
       </c>
@@ -37200,7 +37191,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="734" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="734" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A734" s="2">
         <v>46252</v>
       </c>
@@ -37249,7 +37240,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="735" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="735" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A735" s="2">
         <v>46252</v>
       </c>
@@ -37298,7 +37289,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="736" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="736" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A736" s="2">
         <v>46252</v>
       </c>
@@ -37347,7 +37338,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="737" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="737" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A737" s="2">
         <v>46252</v>
       </c>
@@ -37396,7 +37387,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="738" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="738" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A738" s="2">
         <v>46252</v>
       </c>
@@ -37445,7 +37436,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="739" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="739" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A739" s="2">
         <v>46252</v>
       </c>
@@ -37494,7 +37485,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="740" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="740" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A740" s="2">
         <v>46252</v>
       </c>
@@ -37543,7 +37534,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="741" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="741" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A741" s="2">
         <v>46252</v>
       </c>
@@ -37592,7 +37583,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="742" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="742" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A742" s="2">
         <v>46252</v>
       </c>
@@ -37641,7 +37632,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="743" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="743" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A743" s="2">
         <v>46252</v>
       </c>
@@ -37690,7 +37681,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="744" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="744" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A744" s="2">
         <v>46252</v>
       </c>
@@ -37739,7 +37730,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="745" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="745" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A745" s="2">
         <v>46252</v>
       </c>
@@ -37788,7 +37779,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="746" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="746" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A746" s="2">
         <v>46252</v>
       </c>
@@ -37837,7 +37828,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="747" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="747" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A747" s="2">
         <v>46252</v>
       </c>
@@ -37886,7 +37877,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="748" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="748" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A748" s="2">
         <v>46252</v>
       </c>
@@ -37935,7 +37926,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="749" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="749" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A749" s="2">
         <v>46252</v>
       </c>
@@ -37984,7 +37975,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="750" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="750" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A750" s="2">
         <v>46252</v>
       </c>
@@ -38033,7 +38024,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="751" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="751" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A751" s="2">
         <v>46252</v>
       </c>
@@ -38082,7 +38073,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="752" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="752" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A752" s="2">
         <v>46252</v>
       </c>
@@ -38131,7 +38122,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="753" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="753" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A753" s="2">
         <v>46252</v>
       </c>
@@ -38180,7 +38171,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="754" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="754" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A754" s="2">
         <v>46252</v>
       </c>
@@ -38229,7 +38220,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="755" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="755" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A755" s="2">
         <v>46252</v>
       </c>
@@ -38278,7 +38269,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="756" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="756" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A756" s="2">
         <v>46252</v>
       </c>
@@ -38327,7 +38318,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="757" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="757" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A757" s="2">
         <v>46252</v>
       </c>
@@ -38376,7 +38367,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="758" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="758" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A758" s="2">
         <v>46251</v>
       </c>
@@ -38425,7 +38416,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="759" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="759" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A759" s="2">
         <v>46251</v>
       </c>
@@ -38474,7 +38465,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="760" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="760" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A760" s="2">
         <v>46251</v>
       </c>
@@ -38523,7 +38514,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="761" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="761" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A761" s="2">
         <v>46251</v>
       </c>
@@ -38572,7 +38563,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="762" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="762" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A762" s="2">
         <v>46251</v>
       </c>
@@ -38621,7 +38612,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="763" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="763" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A763" s="2">
         <v>46251</v>
       </c>
@@ -38670,7 +38661,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="764" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="764" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A764" s="2">
         <v>46251</v>
       </c>
@@ -38719,7 +38710,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="765" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="765" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A765" s="2">
         <v>46251</v>
       </c>
@@ -38768,7 +38759,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="766" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="766" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A766" s="2">
         <v>46251</v>
       </c>
@@ -38817,7 +38808,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="767" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="767" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A767" s="2">
         <v>46251</v>
       </c>
@@ -38866,7 +38857,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="768" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="768" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A768" s="2">
         <v>46251</v>
       </c>
@@ -38915,7 +38906,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="769" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="769" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A769" s="2">
         <v>46251</v>
       </c>
@@ -38964,7 +38955,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="770" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="770" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A770" s="2">
         <v>46251</v>
       </c>
@@ -39013,7 +39004,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="771" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="771" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A771" s="2">
         <v>46251</v>
       </c>
@@ -39062,7 +39053,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="772" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="772" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A772" s="2">
         <v>46251</v>
       </c>
@@ -39111,7 +39102,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="773" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="773" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A773" s="2">
         <v>46251</v>
       </c>
@@ -39160,7 +39151,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="774" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="774" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A774" s="2">
         <v>46251</v>
       </c>
@@ -39209,7 +39200,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="775" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="775" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A775" s="2">
         <v>46251</v>
       </c>
@@ -39258,7 +39249,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="776" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="776" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A776" s="2">
         <v>46251</v>
       </c>
@@ -39307,7 +39298,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="777" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="777" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A777" s="2">
         <v>46251</v>
       </c>
@@ -39356,7 +39347,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="778" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="778" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A778" s="2">
         <v>46251</v>
       </c>
@@ -39405,7 +39396,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="779" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="779" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A779" s="2">
         <v>46251</v>
       </c>
@@ -39454,7 +39445,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="780" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="780" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A780" s="2">
         <v>46251</v>
       </c>
@@ -39503,7 +39494,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="781" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="781" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A781" s="2">
         <v>46251</v>
       </c>
@@ -39552,7 +39543,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="782" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="782" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A782" s="2">
         <v>46251</v>
       </c>
@@ -39601,7 +39592,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="783" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="783" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A783" s="2">
         <v>46251</v>
       </c>
@@ -39650,7 +39641,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="784" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="784" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A784" s="2">
         <v>46251</v>
       </c>
@@ -39699,7 +39690,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="785" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="785" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A785" s="2">
         <v>46251</v>
       </c>
@@ -39748,7 +39739,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="786" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="786" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A786" s="2">
         <v>46251</v>
       </c>
@@ -39797,7 +39788,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="787" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="787" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A787" s="2">
         <v>46251</v>
       </c>
@@ -39846,7 +39837,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="788" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="788" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A788" s="2">
         <v>46251</v>
       </c>
@@ -39895,7 +39886,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="789" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="789" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A789" s="2">
         <v>46251</v>
       </c>
@@ -39944,7 +39935,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="790" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="790" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A790" s="2">
         <v>46251</v>
       </c>
@@ -39993,7 +39984,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="791" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="791" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A791" s="2">
         <v>46251</v>
       </c>
@@ -40042,7 +40033,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="792" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="792" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A792" s="2">
         <v>46251</v>
       </c>
@@ -40091,7 +40082,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="793" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="793" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A793" s="2">
         <v>46251</v>
       </c>
@@ -40140,7 +40131,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="794" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="794" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A794" s="2">
         <v>46251</v>
       </c>
@@ -40189,7 +40180,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="795" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="795" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A795" s="2">
         <v>46251</v>
       </c>
@@ -40238,7 +40229,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="796" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="796" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A796" s="2">
         <v>46251</v>
       </c>
@@ -40287,7 +40278,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="797" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="797" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A797" s="2">
         <v>46251</v>
       </c>
@@ -40336,7 +40327,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="798" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="798" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A798" s="2">
         <v>46251</v>
       </c>
@@ -40385,7 +40376,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="799" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="799" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A799" s="2">
         <v>46251</v>
       </c>
@@ -40434,7 +40425,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="800" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="800" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A800" s="2">
         <v>46251</v>
       </c>
@@ -40483,7 +40474,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="801" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="801" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A801" s="2">
         <v>46251</v>
       </c>
@@ -40532,7 +40523,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="802" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="802" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A802" s="2">
         <v>46251</v>
       </c>
@@ -40581,7 +40572,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="803" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="803" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A803" s="2">
         <v>46251</v>
       </c>
@@ -40630,7 +40621,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="804" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="804" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A804" s="2">
         <v>46251</v>
       </c>
@@ -40679,7 +40670,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="805" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="805" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A805" s="2">
         <v>46251</v>
       </c>
@@ -40728,7 +40719,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="806" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="806" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A806" s="2">
         <v>46251</v>
       </c>
@@ -40777,7 +40768,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="807" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="807" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A807" s="2">
         <v>46251</v>
       </c>
@@ -40826,7 +40817,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="808" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="808" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A808" s="2">
         <v>46251</v>
       </c>
@@ -40875,7 +40866,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="809" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="809" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A809" s="2">
         <v>46251</v>
       </c>
@@ -40924,7 +40915,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="810" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="810" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A810" s="2">
         <v>46251</v>
       </c>
@@ -40973,7 +40964,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="811" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="811" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A811" s="2">
         <v>46251</v>
       </c>
@@ -41022,7 +41013,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="812" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="812" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A812" s="2">
         <v>46251</v>
       </c>
@@ -41071,7 +41062,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="813" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="813" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A813" s="2">
         <v>46251</v>
       </c>
@@ -41120,7 +41111,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="814" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="814" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A814" s="2">
         <v>46251</v>
       </c>
@@ -41169,7 +41160,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="815" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="815" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A815" s="2">
         <v>46251</v>
       </c>
@@ -41218,7 +41209,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="816" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="816" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A816" s="2">
         <v>46251</v>
       </c>
@@ -41267,7 +41258,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="817" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="817" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A817" s="2">
         <v>46251</v>
       </c>
@@ -41316,7 +41307,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="818" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="818" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A818" s="2">
         <v>46251</v>
       </c>
@@ -41365,7 +41356,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="819" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="819" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A819" s="2">
         <v>46251</v>
       </c>
@@ -41414,7 +41405,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="820" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="820" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A820" s="2">
         <v>46251</v>
       </c>
@@ -41463,7 +41454,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="821" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="821" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A821" s="2">
         <v>46251</v>
       </c>
@@ -41512,7 +41503,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="822" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="822" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A822" s="2">
         <v>46251</v>
       </c>
@@ -41561,7 +41552,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="823" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="823" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A823" s="2">
         <v>46251</v>
       </c>
@@ -41610,7 +41601,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="824" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="824" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A824" s="2">
         <v>46251</v>
       </c>
@@ -41659,7 +41650,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="825" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="825" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A825" s="2">
         <v>46251</v>
       </c>
@@ -41708,7 +41699,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="826" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="826" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A826" s="2">
         <v>46251</v>
       </c>
@@ -41757,7 +41748,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="827" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="827" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A827" s="2">
         <v>46251</v>
       </c>
@@ -41806,7 +41797,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="828" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="828" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A828" s="2">
         <v>46251</v>
       </c>
@@ -41855,7 +41846,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="829" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="829" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A829" s="2">
         <v>46251</v>
       </c>
@@ -41904,7 +41895,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="830" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="830" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A830" s="2">
         <v>46251</v>
       </c>
@@ -41953,7 +41944,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="831" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="831" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A831" s="2">
         <v>46251</v>
       </c>
@@ -43036,7 +43027,7 @@
       </c>
       <c r="Q853" s="1"/>
     </row>
-    <row r="854" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="854" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A854" s="2">
         <v>46263</v>
       </c>
@@ -43083,7 +43074,7 @@
       </c>
       <c r="Q854" s="1"/>
     </row>
-    <row r="855" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="855" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A855" s="2">
         <v>46263</v>
       </c>
@@ -43130,7 +43121,7 @@
       </c>
       <c r="Q855" s="1"/>
     </row>
-    <row r="856" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="856" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A856" s="2">
         <v>46263</v>
       </c>
@@ -43177,7 +43168,7 @@
       </c>
       <c r="Q856" s="1"/>
     </row>
-    <row r="857" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="857" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A857" s="2">
         <v>46263</v>
       </c>
@@ -43224,7 +43215,7 @@
       </c>
       <c r="Q857" s="1"/>
     </row>
-    <row r="858" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="858" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A858" s="2">
         <v>46263</v>
       </c>
@@ -43271,7 +43262,7 @@
       </c>
       <c r="Q858" s="1"/>
     </row>
-    <row r="859" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="859" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A859" s="2">
         <v>46263</v>
       </c>
@@ -43318,7 +43309,7 @@
       </c>
       <c r="Q859" s="1"/>
     </row>
-    <row r="860" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="860" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A860" s="2">
         <v>46263</v>
       </c>
@@ -43365,7 +43356,7 @@
       </c>
       <c r="Q860" s="1"/>
     </row>
-    <row r="861" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="861" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A861" s="2">
         <v>46263</v>
       </c>
@@ -43412,7 +43403,7 @@
       </c>
       <c r="Q861" s="1"/>
     </row>
-    <row r="862" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="862" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A862" s="2">
         <v>46263</v>
       </c>
@@ -43459,7 +43450,7 @@
       </c>
       <c r="Q862" s="1"/>
     </row>
-    <row r="863" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="863" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A863" s="2">
         <v>46263</v>
       </c>
@@ -43506,7 +43497,7 @@
       </c>
       <c r="Q863" s="1"/>
     </row>
-    <row r="864" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="864" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A864" s="2">
         <v>46263</v>
       </c>
@@ -43553,7 +43544,7 @@
       </c>
       <c r="Q864" s="1"/>
     </row>
-    <row r="865" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="865" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A865" s="2">
         <v>46263</v>
       </c>
@@ -43600,7 +43591,7 @@
       </c>
       <c r="Q865" s="1"/>
     </row>
-    <row r="866" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="866" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A866" s="2">
         <v>46263</v>
       </c>
@@ -43647,7 +43638,7 @@
       </c>
       <c r="Q866" s="1"/>
     </row>
-    <row r="867" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="867" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A867" s="2">
         <v>46263</v>
       </c>
@@ -43694,7 +43685,7 @@
       </c>
       <c r="Q867" s="1"/>
     </row>
-    <row r="868" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="868" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A868" s="2">
         <v>46263</v>
       </c>
@@ -43741,7 +43732,7 @@
       </c>
       <c r="Q868" s="1"/>
     </row>
-    <row r="869" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="869" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A869" s="2">
         <v>46263</v>
       </c>
@@ -43788,7 +43779,7 @@
       </c>
       <c r="Q869" s="1"/>
     </row>
-    <row r="870" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="870" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A870" s="2">
         <v>46263</v>
       </c>
@@ -43835,7 +43826,7 @@
       </c>
       <c r="Q870" s="1"/>
     </row>
-    <row r="871" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="871" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A871" s="2">
         <v>46263</v>
       </c>
@@ -43882,7 +43873,7 @@
       </c>
       <c r="Q871" s="1"/>
     </row>
-    <row r="872" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="872" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A872" s="2">
         <v>46263</v>
       </c>
@@ -43929,7 +43920,7 @@
       </c>
       <c r="Q872" s="1"/>
     </row>
-    <row r="873" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="873" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A873" s="2">
         <v>46263</v>
       </c>
@@ -43976,7 +43967,7 @@
       </c>
       <c r="Q873" s="1"/>
     </row>
-    <row r="874" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="874" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A874" s="2">
         <v>46263</v>
       </c>
@@ -44023,7 +44014,7 @@
       </c>
       <c r="Q874" s="1"/>
     </row>
-    <row r="875" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="875" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A875" s="2">
         <v>46263</v>
       </c>
@@ -44070,7 +44061,7 @@
       </c>
       <c r="Q875" s="1"/>
     </row>
-    <row r="876" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="876" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A876" s="2">
         <v>46263</v>
       </c>
@@ -44117,7 +44108,7 @@
       </c>
       <c r="Q876" s="1"/>
     </row>
-    <row r="877" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="877" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A877" s="2">
         <v>46263</v>
       </c>
@@ -44164,7 +44155,7 @@
       </c>
       <c r="Q877" s="1"/>
     </row>
-    <row r="878" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="878" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A878" s="2">
         <v>46263</v>
       </c>
@@ -44211,7 +44202,7 @@
       </c>
       <c r="Q878" s="1"/>
     </row>
-    <row r="879" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="879" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A879" s="2">
         <v>46263</v>
       </c>
@@ -44258,7 +44249,7 @@
       </c>
       <c r="Q879" s="1"/>
     </row>
-    <row r="880" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="880" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A880" s="2">
         <v>46263</v>
       </c>
@@ -44305,7 +44296,7 @@
       </c>
       <c r="Q880" s="1"/>
     </row>
-    <row r="881" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="881" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A881" s="2">
         <v>46263</v>
       </c>
@@ -44352,7 +44343,7 @@
       </c>
       <c r="Q881" s="1"/>
     </row>
-    <row r="882" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="882" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A882" s="2">
         <v>46263</v>
       </c>
@@ -44399,7 +44390,7 @@
       </c>
       <c r="Q882" s="1"/>
     </row>
-    <row r="883" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="883" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A883" s="2">
         <v>46263</v>
       </c>
@@ -44446,7 +44437,7 @@
       </c>
       <c r="Q883" s="1"/>
     </row>
-    <row r="884" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="884" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A884" s="2">
         <v>46263</v>
       </c>
@@ -44493,7 +44484,7 @@
       </c>
       <c r="Q884" s="1"/>
     </row>
-    <row r="885" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="885" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A885" s="2">
         <v>46263</v>
       </c>
@@ -44540,7 +44531,7 @@
       </c>
       <c r="Q885" s="1"/>
     </row>
-    <row r="886" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="886" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A886" s="2">
         <v>46263</v>
       </c>
@@ -44587,7 +44578,7 @@
       </c>
       <c r="Q886" s="1"/>
     </row>
-    <row r="887" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="887" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A887" s="2">
         <v>46263</v>
       </c>
@@ -44634,7 +44625,7 @@
       </c>
       <c r="Q887" s="1"/>
     </row>
-    <row r="888" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="888" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A888" s="2">
         <v>46263</v>
       </c>
@@ -44681,7 +44672,7 @@
       </c>
       <c r="Q888" s="1"/>
     </row>
-    <row r="889" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="889" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A889" s="2">
         <v>46263</v>
       </c>
@@ -44728,7 +44719,7 @@
       </c>
       <c r="Q889" s="1"/>
     </row>
-    <row r="890" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="890" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A890" s="2">
         <v>46263</v>
       </c>
@@ -44775,7 +44766,7 @@
       </c>
       <c r="Q890" s="1"/>
     </row>
-    <row r="891" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="891" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A891" s="2">
         <v>46263</v>
       </c>
@@ -44822,7 +44813,7 @@
       </c>
       <c r="Q891" s="1"/>
     </row>
-    <row r="892" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="892" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A892" s="2">
         <v>46263</v>
       </c>
@@ -44869,7 +44860,7 @@
       </c>
       <c r="Q892" s="1"/>
     </row>
-    <row r="893" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="893" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A893" s="2">
         <v>46263</v>
       </c>
@@ -44916,7 +44907,7 @@
       </c>
       <c r="Q893" s="1"/>
     </row>
-    <row r="894" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="894" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A894" s="2">
         <v>46263</v>
       </c>
@@ -44963,7 +44954,7 @@
       </c>
       <c r="Q894" s="1"/>
     </row>
-    <row r="895" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="895" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A895" s="2">
         <v>46263</v>
       </c>
@@ -45010,7 +45001,7 @@
       </c>
       <c r="Q895" s="1"/>
     </row>
-    <row r="896" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="896" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A896" s="2">
         <v>46263</v>
       </c>
@@ -45057,7 +45048,7 @@
       </c>
       <c r="Q896" s="1"/>
     </row>
-    <row r="897" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="897" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A897" s="2">
         <v>46263</v>
       </c>
@@ -45104,7 +45095,7 @@
       </c>
       <c r="Q897" s="1"/>
     </row>
-    <row r="898" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="898" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A898" s="2">
         <v>46263</v>
       </c>
@@ -45151,7 +45142,7 @@
       </c>
       <c r="Q898" s="1"/>
     </row>
-    <row r="899" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="899" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A899" s="2">
         <v>46263</v>
       </c>
@@ -45198,7 +45189,7 @@
       </c>
       <c r="Q899" s="1"/>
     </row>
-    <row r="900" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="900" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A900" s="2">
         <v>46263</v>
       </c>
@@ -45668,7 +45659,7 @@
       </c>
       <c r="Q909" s="1"/>
     </row>
-    <row r="910" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="910" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A910" s="2">
         <v>46263</v>
       </c>
@@ -45715,7 +45706,7 @@
       </c>
       <c r="Q910" s="1"/>
     </row>
-    <row r="911" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="911" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A911" s="2">
         <v>46263</v>
       </c>
@@ -45762,7 +45753,7 @@
       </c>
       <c r="Q911" s="1"/>
     </row>
-    <row r="912" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="912" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A912" s="2">
         <v>46263</v>
       </c>
@@ -45809,7 +45800,7 @@
       </c>
       <c r="Q912" s="1"/>
     </row>
-    <row r="913" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="913" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A913" s="2">
         <v>46263</v>
       </c>
@@ -45856,7 +45847,7 @@
       </c>
       <c r="Q913" s="1"/>
     </row>
-    <row r="914" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="914" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A914" s="2">
         <v>46263</v>
       </c>
@@ -45903,7 +45894,7 @@
       </c>
       <c r="Q914" s="1"/>
     </row>
-    <row r="915" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="915" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A915" s="2">
         <v>46263</v>
       </c>
@@ -45950,7 +45941,7 @@
       </c>
       <c r="Q915" s="1"/>
     </row>
-    <row r="916" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="916" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A916" s="2">
         <v>46263</v>
       </c>
@@ -45997,7 +45988,7 @@
       </c>
       <c r="Q916" s="1"/>
     </row>
-    <row r="917" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="917" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A917" s="2">
         <v>46263</v>
       </c>
@@ -46044,7 +46035,7 @@
       </c>
       <c r="Q917" s="1"/>
     </row>
-    <row r="918" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="918" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A918" s="2">
         <v>46263</v>
       </c>
@@ -46091,7 +46082,7 @@
       </c>
       <c r="Q918" s="1"/>
     </row>
-    <row r="919" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="919" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A919" s="2">
         <v>46263</v>
       </c>
@@ -46138,7 +46129,7 @@
       </c>
       <c r="Q919" s="1"/>
     </row>
-    <row r="920" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="920" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A920" s="2">
         <v>46263</v>
       </c>
@@ -46185,7 +46176,7 @@
       </c>
       <c r="Q920" s="1"/>
     </row>
-    <row r="921" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="921" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A921" s="2">
         <v>46263</v>
       </c>
@@ -46232,7 +46223,7 @@
       </c>
       <c r="Q921" s="1"/>
     </row>
-    <row r="922" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="922" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A922" s="2">
         <v>46263</v>
       </c>
@@ -46279,7 +46270,7 @@
       </c>
       <c r="Q922" s="1"/>
     </row>
-    <row r="923" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="923" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A923" s="2">
         <v>46263</v>
       </c>
@@ -46326,7 +46317,7 @@
       </c>
       <c r="Q923" s="1"/>
     </row>
-    <row r="924" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="924" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A924" s="2">
         <v>46263</v>
       </c>
@@ -46373,7 +46364,7 @@
       </c>
       <c r="Q924" s="1"/>
     </row>
-    <row r="925" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="925" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A925" s="2">
         <v>46263</v>
       </c>
@@ -46420,7 +46411,7 @@
       </c>
       <c r="Q925" s="1"/>
     </row>
-    <row r="926" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="926" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A926" s="2">
         <v>46263</v>
       </c>
@@ -46467,7 +46458,7 @@
       </c>
       <c r="Q926" s="1"/>
     </row>
-    <row r="927" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="927" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A927" s="2">
         <v>46263</v>
       </c>
@@ -46514,7 +46505,7 @@
       </c>
       <c r="Q927" s="1"/>
     </row>
-    <row r="928" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="928" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A928" s="2">
         <v>46263</v>
       </c>
@@ -46561,7 +46552,7 @@
       </c>
       <c r="Q928" s="1"/>
     </row>
-    <row r="929" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="929" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A929" s="2">
         <v>46263</v>
       </c>
@@ -46608,7 +46599,7 @@
       </c>
       <c r="Q929" s="1"/>
     </row>
-    <row r="930" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="930" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A930" s="2">
         <v>46263</v>
       </c>
@@ -46655,7 +46646,7 @@
       </c>
       <c r="Q930" s="1"/>
     </row>
-    <row r="931" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="931" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A931" s="2">
         <v>46263</v>
       </c>
@@ -46702,7 +46693,7 @@
       </c>
       <c r="Q931" s="1"/>
     </row>
-    <row r="932" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="932" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A932" s="2">
         <v>46263</v>
       </c>
@@ -46749,7 +46740,7 @@
       </c>
       <c r="Q932" s="1"/>
     </row>
-    <row r="933" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="933" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A933" s="2">
         <v>46263</v>
       </c>
@@ -46796,7 +46787,7 @@
       </c>
       <c r="Q933" s="1"/>
     </row>
-    <row r="934" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="934" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A934" s="2">
         <v>46263</v>
       </c>
@@ -46843,7 +46834,7 @@
       </c>
       <c r="Q934" s="1"/>
     </row>
-    <row r="935" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="935" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A935" s="2">
         <v>46263</v>
       </c>
@@ -46890,7 +46881,7 @@
       </c>
       <c r="Q935" s="1"/>
     </row>
-    <row r="936" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="936" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A936" s="2">
         <v>46263</v>
       </c>
@@ -46937,7 +46928,7 @@
       </c>
       <c r="Q936" s="1"/>
     </row>
-    <row r="937" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="937" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A937" s="2">
         <v>46263</v>
       </c>
@@ -46984,7 +46975,7 @@
       </c>
       <c r="Q937" s="1"/>
     </row>
-    <row r="938" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="938" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A938" s="2">
         <v>46263</v>
       </c>
@@ -47031,7 +47022,7 @@
       </c>
       <c r="Q938" s="1"/>
     </row>
-    <row r="939" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="939" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A939" s="2">
         <v>46263</v>
       </c>
@@ -47078,7 +47069,7 @@
       </c>
       <c r="Q939" s="1"/>
     </row>
-    <row r="940" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="940" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A940" s="2">
         <v>46262</v>
       </c>
@@ -47125,7 +47116,7 @@
       </c>
       <c r="Q940" s="1"/>
     </row>
-    <row r="941" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="941" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A941" s="2">
         <v>46262</v>
       </c>
@@ -47172,7 +47163,7 @@
       </c>
       <c r="Q941" s="1"/>
     </row>
-    <row r="942" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="942" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A942" s="2">
         <v>46262</v>
       </c>
@@ -47219,7 +47210,7 @@
       </c>
       <c r="Q942" s="1"/>
     </row>
-    <row r="943" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="943" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A943" s="2">
         <v>46262</v>
       </c>
@@ -47266,7 +47257,7 @@
       </c>
       <c r="Q943" s="1"/>
     </row>
-    <row r="944" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="944" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A944" s="2">
         <v>46262</v>
       </c>
@@ -47313,7 +47304,7 @@
       </c>
       <c r="Q944" s="1"/>
     </row>
-    <row r="945" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="945" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A945" s="2">
         <v>46262</v>
       </c>
@@ -47360,7 +47351,7 @@
       </c>
       <c r="Q945" s="1"/>
     </row>
-    <row r="946" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="946" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A946" s="2">
         <v>46262</v>
       </c>
@@ -47407,7 +47398,7 @@
       </c>
       <c r="Q946" s="1"/>
     </row>
-    <row r="947" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="947" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A947" s="2">
         <v>46262</v>
       </c>
@@ -47454,7 +47445,7 @@
       </c>
       <c r="Q947" s="1"/>
     </row>
-    <row r="948" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="948" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A948" s="2">
         <v>46262</v>
       </c>
@@ -47501,7 +47492,7 @@
       </c>
       <c r="Q948" s="1"/>
     </row>
-    <row r="949" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="949" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A949" s="2">
         <v>46262</v>
       </c>
@@ -47548,7 +47539,7 @@
       </c>
       <c r="Q949" s="1"/>
     </row>
-    <row r="950" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="950" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A950" s="2">
         <v>46262</v>
       </c>
@@ -47595,7 +47586,7 @@
       </c>
       <c r="Q950" s="1"/>
     </row>
-    <row r="951" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="951" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A951" s="2">
         <v>46262</v>
       </c>
@@ -47642,7 +47633,7 @@
       </c>
       <c r="Q951" s="1"/>
     </row>
-    <row r="952" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="952" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A952" s="2">
         <v>46262</v>
       </c>
@@ -47689,7 +47680,7 @@
       </c>
       <c r="Q952" s="1"/>
     </row>
-    <row r="953" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="953" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A953" s="2">
         <v>46262</v>
       </c>
@@ -47736,7 +47727,7 @@
       </c>
       <c r="Q953" s="1"/>
     </row>
-    <row r="954" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="954" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A954" s="2">
         <v>46262</v>
       </c>
@@ -47783,7 +47774,7 @@
       </c>
       <c r="Q954" s="1"/>
     </row>
-    <row r="955" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="955" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A955" s="2">
         <v>46262</v>
       </c>
@@ -47830,7 +47821,7 @@
       </c>
       <c r="Q955" s="1"/>
     </row>
-    <row r="956" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="956" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A956" s="2">
         <v>46262</v>
       </c>
@@ -47877,7 +47868,7 @@
       </c>
       <c r="Q956" s="1"/>
     </row>
-    <row r="957" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="957" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A957" s="2">
         <v>46262</v>
       </c>
@@ -47924,7 +47915,7 @@
       </c>
       <c r="Q957" s="1"/>
     </row>
-    <row r="958" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="958" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A958" s="2">
         <v>46262</v>
       </c>
@@ -47971,7 +47962,7 @@
       </c>
       <c r="Q958" s="1"/>
     </row>
-    <row r="959" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="959" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A959" s="2">
         <v>46262</v>
       </c>
@@ -48018,7 +48009,7 @@
       </c>
       <c r="Q959" s="1"/>
     </row>
-    <row r="960" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="960" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A960" s="2">
         <v>46262</v>
       </c>
@@ -48065,7 +48056,7 @@
       </c>
       <c r="Q960" s="1"/>
     </row>
-    <row r="961" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="961" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A961" s="2">
         <v>46262</v>
       </c>
@@ -48112,7 +48103,7 @@
       </c>
       <c r="Q961" s="1"/>
     </row>
-    <row r="962" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="962" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A962" s="2">
         <v>46262</v>
       </c>
@@ -48159,7 +48150,7 @@
       </c>
       <c r="Q962" s="1"/>
     </row>
-    <row r="963" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="963" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A963" s="2">
         <v>46262</v>
       </c>
@@ -48206,7 +48197,7 @@
       </c>
       <c r="Q963" s="1"/>
     </row>
-    <row r="964" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="964" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A964" s="2">
         <v>46262</v>
       </c>
@@ -48253,7 +48244,7 @@
       </c>
       <c r="Q964" s="1"/>
     </row>
-    <row r="965" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="965" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A965" s="2">
         <v>46262</v>
       </c>
@@ -48300,7 +48291,7 @@
       </c>
       <c r="Q965" s="1"/>
     </row>
-    <row r="966" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="966" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A966" s="2">
         <v>46262</v>
       </c>
@@ -48347,7 +48338,7 @@
       </c>
       <c r="Q966" s="1"/>
     </row>
-    <row r="967" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="967" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A967" s="2">
         <v>46262</v>
       </c>
@@ -48394,7 +48385,7 @@
       </c>
       <c r="Q967" s="1"/>
     </row>
-    <row r="968" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="968" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A968" s="2">
         <v>46262</v>
       </c>
@@ -48441,7 +48432,7 @@
       </c>
       <c r="Q968" s="1"/>
     </row>
-    <row r="969" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="969" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A969" s="2">
         <v>46262</v>
       </c>
@@ -48488,7 +48479,7 @@
       </c>
       <c r="Q969" s="1"/>
     </row>
-    <row r="970" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="970" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A970" s="2">
         <v>46262</v>
       </c>
@@ -48535,7 +48526,7 @@
       </c>
       <c r="Q970" s="1"/>
     </row>
-    <row r="971" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="971" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A971" s="2">
         <v>46262</v>
       </c>
@@ -48582,7 +48573,7 @@
       </c>
       <c r="Q971" s="1"/>
     </row>
-    <row r="972" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="972" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A972" s="2">
         <v>46262</v>
       </c>
@@ -48629,7 +48620,7 @@
       </c>
       <c r="Q972" s="1"/>
     </row>
-    <row r="973" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="973" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A973" s="2">
         <v>46262</v>
       </c>
@@ -48676,7 +48667,7 @@
       </c>
       <c r="Q973" s="1"/>
     </row>
-    <row r="974" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="974" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A974" s="2">
         <v>46262</v>
       </c>
@@ -48723,7 +48714,7 @@
       </c>
       <c r="Q974" s="1"/>
     </row>
-    <row r="975" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="975" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A975" s="2">
         <v>46262</v>
       </c>
@@ -48770,7 +48761,7 @@
       </c>
       <c r="Q975" s="1"/>
     </row>
-    <row r="976" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="976" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A976" s="2">
         <v>46262</v>
       </c>
@@ -48817,7 +48808,7 @@
       </c>
       <c r="Q976" s="1"/>
     </row>
-    <row r="977" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="977" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A977" s="2">
         <v>46262</v>
       </c>
@@ -48864,7 +48855,7 @@
       </c>
       <c r="Q977" s="1"/>
     </row>
-    <row r="978" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="978" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A978" s="2">
         <v>46262</v>
       </c>
@@ -48911,7 +48902,7 @@
       </c>
       <c r="Q978" s="1"/>
     </row>
-    <row r="979" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="979" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A979" s="2">
         <v>46262</v>
       </c>
@@ -48958,7 +48949,7 @@
       </c>
       <c r="Q979" s="1"/>
     </row>
-    <row r="980" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="980" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A980" s="2">
         <v>46262</v>
       </c>
@@ -49005,7 +48996,7 @@
       </c>
       <c r="Q980" s="1"/>
     </row>
-    <row r="981" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="981" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A981" s="2">
         <v>46262</v>
       </c>
@@ -49052,7 +49043,7 @@
       </c>
       <c r="Q981" s="1"/>
     </row>
-    <row r="982" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="982" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A982" s="2">
         <v>46262</v>
       </c>
@@ -49099,7 +49090,7 @@
       </c>
       <c r="Q982" s="1"/>
     </row>
-    <row r="983" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="983" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A983" s="2">
         <v>46262</v>
       </c>
@@ -49146,7 +49137,7 @@
       </c>
       <c r="Q983" s="1"/>
     </row>
-    <row r="984" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="984" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A984" s="2">
         <v>46262</v>
       </c>
@@ -49193,7 +49184,7 @@
       </c>
       <c r="Q984" s="1"/>
     </row>
-    <row r="985" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="985" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A985" s="2">
         <v>46262</v>
       </c>
@@ -49240,7 +49231,7 @@
       </c>
       <c r="Q985" s="1"/>
     </row>
-    <row r="986" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="986" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A986" s="2">
         <v>46262</v>
       </c>
@@ -49287,7 +49278,7 @@
       </c>
       <c r="Q986" s="1"/>
     </row>
-    <row r="987" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="987" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A987" s="2">
         <v>46262</v>
       </c>
@@ -49334,7 +49325,7 @@
       </c>
       <c r="Q987" s="1"/>
     </row>
-    <row r="988" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="988" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A988" s="2">
         <v>46262</v>
       </c>
@@ -49381,7 +49372,7 @@
       </c>
       <c r="Q988" s="1"/>
     </row>
-    <row r="989" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="989" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A989" s="2">
         <v>46262</v>
       </c>
@@ -49428,7 +49419,7 @@
       </c>
       <c r="Q989" s="1"/>
     </row>
-    <row r="990" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="990" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A990" s="2">
         <v>46262</v>
       </c>
@@ -49475,7 +49466,7 @@
       </c>
       <c r="Q990" s="1"/>
     </row>
-    <row r="991" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="991" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A991" s="2">
         <v>46262</v>
       </c>
@@ -49522,7 +49513,7 @@
       </c>
       <c r="Q991" s="1"/>
     </row>
-    <row r="992" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="992" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A992" s="2">
         <v>46262</v>
       </c>
@@ -49569,7 +49560,7 @@
       </c>
       <c r="Q992" s="1"/>
     </row>
-    <row r="993" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="993" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A993" s="2">
         <v>46262</v>
       </c>
@@ -49757,7 +49748,7 @@
       </c>
       <c r="Q996" s="1"/>
     </row>
-    <row r="997" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="997" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A997" s="2">
         <v>46262</v>
       </c>
@@ -49804,7 +49795,7 @@
       </c>
       <c r="Q997" s="1"/>
     </row>
-    <row r="998" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="998" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A998" s="2">
         <v>46262</v>
       </c>
@@ -49851,7 +49842,7 @@
       </c>
       <c r="Q998" s="1"/>
     </row>
-    <row r="999" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="999" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A999" s="2">
         <v>46262</v>
       </c>
@@ -49898,7 +49889,7 @@
       </c>
       <c r="Q999" s="1"/>
     </row>
-    <row r="1000" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1000" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1000" s="2">
         <v>46262</v>
       </c>
@@ -49945,7 +49936,7 @@
       </c>
       <c r="Q1000" s="1"/>
     </row>
-    <row r="1001" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1001" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1001" s="2">
         <v>46262</v>
       </c>
@@ -49992,7 +49983,7 @@
       </c>
       <c r="Q1001" s="1"/>
     </row>
-    <row r="1002" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1002" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1002" s="2">
         <v>46262</v>
       </c>
@@ -50039,7 +50030,7 @@
       </c>
       <c r="Q1002" s="1"/>
     </row>
-    <row r="1003" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1003" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1003" s="2">
         <v>46262</v>
       </c>
@@ -50086,7 +50077,7 @@
       </c>
       <c r="Q1003" s="1"/>
     </row>
-    <row r="1004" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1004" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1004" s="2">
         <v>46262</v>
       </c>
@@ -50133,7 +50124,7 @@
       </c>
       <c r="Q1004" s="1"/>
     </row>
-    <row r="1005" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1005" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1005" s="2">
         <v>46262</v>
       </c>
@@ -50180,7 +50171,7 @@
       </c>
       <c r="Q1005" s="1"/>
     </row>
-    <row r="1006" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1006" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1006" s="2">
         <v>46262</v>
       </c>
@@ -50227,7 +50218,7 @@
       </c>
       <c r="Q1006" s="1"/>
     </row>
-    <row r="1007" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1007" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1007" s="2">
         <v>46262</v>
       </c>
@@ -50274,7 +50265,7 @@
       </c>
       <c r="Q1007" s="1"/>
     </row>
-    <row r="1008" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1008" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1008" s="2">
         <v>46262</v>
       </c>
@@ -50321,7 +50312,7 @@
       </c>
       <c r="Q1008" s="1"/>
     </row>
-    <row r="1009" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1009" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1009" s="2">
         <v>46262</v>
       </c>
@@ -50368,7 +50359,7 @@
       </c>
       <c r="Q1009" s="1"/>
     </row>
-    <row r="1010" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1010" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1010" s="2">
         <v>46262</v>
       </c>
@@ -50415,7 +50406,7 @@
       </c>
       <c r="Q1010" s="1"/>
     </row>
-    <row r="1011" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1011" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1011" s="2">
         <v>46262</v>
       </c>
@@ -50462,7 +50453,7 @@
       </c>
       <c r="Q1011" s="1"/>
     </row>
-    <row r="1012" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1012" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1012" s="2">
         <v>46262</v>
       </c>
@@ -50509,7 +50500,7 @@
       </c>
       <c r="Q1012" s="1"/>
     </row>
-    <row r="1013" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1013" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1013" s="2">
         <v>46262</v>
       </c>
@@ -50556,7 +50547,7 @@
       </c>
       <c r="Q1013" s="1"/>
     </row>
-    <row r="1014" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1014" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1014" s="2">
         <v>46262</v>
       </c>
@@ -50603,7 +50594,7 @@
       </c>
       <c r="Q1014" s="1"/>
     </row>
-    <row r="1015" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1015" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1015" s="2">
         <v>46262</v>
       </c>
@@ -50650,7 +50641,7 @@
       </c>
       <c r="Q1015" s="1"/>
     </row>
-    <row r="1016" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1016" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1016" s="2">
         <v>46262</v>
       </c>
@@ -50697,7 +50688,7 @@
       </c>
       <c r="Q1016" s="1"/>
     </row>
-    <row r="1017" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1017" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1017" s="2">
         <v>46262</v>
       </c>
@@ -50744,7 +50735,7 @@
       </c>
       <c r="Q1017" s="1"/>
     </row>
-    <row r="1018" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1018" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1018" s="2">
         <v>46262</v>
       </c>
@@ -50791,7 +50782,7 @@
       </c>
       <c r="Q1018" s="1"/>
     </row>
-    <row r="1019" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1019" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1019" s="2">
         <v>46262</v>
       </c>
@@ -50838,7 +50829,7 @@
       </c>
       <c r="Q1019" s="1"/>
     </row>
-    <row r="1020" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1020" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1020" s="2">
         <v>46262</v>
       </c>
@@ -50885,7 +50876,7 @@
       </c>
       <c r="Q1020" s="1"/>
     </row>
-    <row r="1021" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1021" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1021" s="2">
         <v>46262</v>
       </c>
@@ -50932,7 +50923,7 @@
       </c>
       <c r="Q1021" s="1"/>
     </row>
-    <row r="1022" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1022" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1022" s="2">
         <v>46262</v>
       </c>
@@ -50979,7 +50970,7 @@
       </c>
       <c r="Q1022" s="1"/>
     </row>
-    <row r="1023" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1023" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1023" s="2">
         <v>46262</v>
       </c>
@@ -51026,7 +51017,7 @@
       </c>
       <c r="Q1023" s="1"/>
     </row>
-    <row r="1024" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1024" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1024" s="2">
         <v>46262</v>
       </c>
@@ -51073,7 +51064,7 @@
       </c>
       <c r="Q1024" s="1"/>
     </row>
-    <row r="1025" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1025" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1025" s="2">
         <v>46262</v>
       </c>
@@ -51120,7 +51111,7 @@
       </c>
       <c r="Q1025" s="1"/>
     </row>
-    <row r="1026" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1026" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1026" s="2">
         <v>46262</v>
       </c>
@@ -51167,7 +51158,7 @@
       </c>
       <c r="Q1026" s="1"/>
     </row>
-    <row r="1027" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1027" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1027" s="2">
         <v>46262</v>
       </c>
@@ -51214,7 +51205,7 @@
       </c>
       <c r="Q1027" s="1"/>
     </row>
-    <row r="1028" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1028" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1028" s="2">
         <v>46262</v>
       </c>
@@ -51261,7 +51252,7 @@
       </c>
       <c r="Q1028" s="1"/>
     </row>
-    <row r="1029" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1029" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1029" s="2">
         <v>46262</v>
       </c>
@@ -51308,7 +51299,7 @@
       </c>
       <c r="Q1029" s="1"/>
     </row>
-    <row r="1030" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1030" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1030" s="2">
         <v>46262</v>
       </c>
@@ -51355,7 +51346,7 @@
       </c>
       <c r="Q1030" s="1"/>
     </row>
-    <row r="1031" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1031" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1031" s="2">
         <v>46262</v>
       </c>
@@ -51402,7 +51393,7 @@
       </c>
       <c r="Q1031" s="1"/>
     </row>
-    <row r="1032" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1032" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1032" s="2">
         <v>46262</v>
       </c>
@@ -51449,7 +51440,7 @@
       </c>
       <c r="Q1032" s="1"/>
     </row>
-    <row r="1033" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1033" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1033" s="2">
         <v>46262</v>
       </c>
@@ -51496,7 +51487,7 @@
       </c>
       <c r="Q1033" s="1"/>
     </row>
-    <row r="1034" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1034" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1034" s="2">
         <v>46262</v>
       </c>
@@ -51543,7 +51534,7 @@
       </c>
       <c r="Q1034" s="1"/>
     </row>
-    <row r="1035" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1035" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1035" s="2">
         <v>46262</v>
       </c>
@@ -51590,7 +51581,7 @@
       </c>
       <c r="Q1035" s="1"/>
     </row>
-    <row r="1036" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1036" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1036" s="2">
         <v>46262</v>
       </c>
@@ -51637,7 +51628,7 @@
       </c>
       <c r="Q1036" s="1"/>
     </row>
-    <row r="1037" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1037" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1037" s="2">
         <v>46261</v>
       </c>
@@ -51684,7 +51675,7 @@
       </c>
       <c r="Q1037" s="1"/>
     </row>
-    <row r="1038" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1038" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1038" s="2">
         <v>46261</v>
       </c>
@@ -51731,7 +51722,7 @@
       </c>
       <c r="Q1038" s="1"/>
     </row>
-    <row r="1039" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1039" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1039" s="2">
         <v>46261</v>
       </c>
@@ -51778,7 +51769,7 @@
       </c>
       <c r="Q1039" s="1"/>
     </row>
-    <row r="1040" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1040" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1040" s="2">
         <v>46261</v>
       </c>
@@ -51825,7 +51816,7 @@
       </c>
       <c r="Q1040" s="1"/>
     </row>
-    <row r="1041" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1041" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1041" s="2">
         <v>46261</v>
       </c>
@@ -51872,7 +51863,7 @@
       </c>
       <c r="Q1041" s="1"/>
     </row>
-    <row r="1042" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1042" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1042" s="2">
         <v>46261</v>
       </c>
@@ -51919,7 +51910,7 @@
       </c>
       <c r="Q1042" s="1"/>
     </row>
-    <row r="1043" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1043" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1043" s="2">
         <v>46261</v>
       </c>
@@ -51966,7 +51957,7 @@
       </c>
       <c r="Q1043" s="1"/>
     </row>
-    <row r="1044" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1044" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1044" s="2">
         <v>46261</v>
       </c>
@@ -52013,7 +52004,7 @@
       </c>
       <c r="Q1044" s="1"/>
     </row>
-    <row r="1045" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1045" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1045" s="2">
         <v>46261</v>
       </c>
@@ -52060,7 +52051,7 @@
       </c>
       <c r="Q1045" s="1"/>
     </row>
-    <row r="1046" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1046" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1046" s="2">
         <v>46261</v>
       </c>
@@ -52107,7 +52098,7 @@
       </c>
       <c r="Q1046" s="1"/>
     </row>
-    <row r="1047" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1047" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1047" s="2">
         <v>46261</v>
       </c>
@@ -52154,7 +52145,7 @@
       </c>
       <c r="Q1047" s="1"/>
     </row>
-    <row r="1048" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1048" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1048" s="2">
         <v>46261</v>
       </c>
@@ -52201,7 +52192,7 @@
       </c>
       <c r="Q1048" s="1"/>
     </row>
-    <row r="1049" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1049" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1049" s="2">
         <v>46261</v>
       </c>
@@ -52248,7 +52239,7 @@
       </c>
       <c r="Q1049" s="1"/>
     </row>
-    <row r="1050" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1050" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1050" s="2">
         <v>46261</v>
       </c>
@@ -52295,7 +52286,7 @@
       </c>
       <c r="Q1050" s="1"/>
     </row>
-    <row r="1051" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1051" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1051" s="2">
         <v>46261</v>
       </c>
@@ -52342,7 +52333,7 @@
       </c>
       <c r="Q1051" s="1"/>
     </row>
-    <row r="1052" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1052" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1052" s="2">
         <v>46261</v>
       </c>
@@ -52389,7 +52380,7 @@
       </c>
       <c r="Q1052" s="1"/>
     </row>
-    <row r="1053" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1053" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1053" s="2">
         <v>46261</v>
       </c>
@@ -52436,7 +52427,7 @@
       </c>
       <c r="Q1053" s="1"/>
     </row>
-    <row r="1054" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1054" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1054" s="2">
         <v>46261</v>
       </c>
@@ -52483,7 +52474,7 @@
       </c>
       <c r="Q1054" s="1"/>
     </row>
-    <row r="1055" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1055" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1055" s="2">
         <v>46261</v>
       </c>
@@ -52530,7 +52521,7 @@
       </c>
       <c r="Q1055" s="1"/>
     </row>
-    <row r="1056" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1056" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1056" s="2">
         <v>46261</v>
       </c>
@@ -52577,7 +52568,7 @@
       </c>
       <c r="Q1056" s="1"/>
     </row>
-    <row r="1057" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1057" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1057" s="2">
         <v>46261</v>
       </c>
@@ -52624,7 +52615,7 @@
       </c>
       <c r="Q1057" s="1"/>
     </row>
-    <row r="1058" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1058" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1058" s="2">
         <v>46261</v>
       </c>
@@ -52671,7 +52662,7 @@
       </c>
       <c r="Q1058" s="1"/>
     </row>
-    <row r="1059" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1059" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1059" s="2">
         <v>46261</v>
       </c>
@@ -52718,7 +52709,7 @@
       </c>
       <c r="Q1059" s="1"/>
     </row>
-    <row r="1060" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1060" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1060" s="2">
         <v>46261</v>
       </c>
@@ -52765,7 +52756,7 @@
       </c>
       <c r="Q1060" s="1"/>
     </row>
-    <row r="1061" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1061" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1061" s="2">
         <v>46261</v>
       </c>
@@ -52812,7 +52803,7 @@
       </c>
       <c r="Q1061" s="1"/>
     </row>
-    <row r="1062" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1062" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1062" s="2">
         <v>46261</v>
       </c>
@@ -52859,7 +52850,7 @@
       </c>
       <c r="Q1062" s="1"/>
     </row>
-    <row r="1063" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1063" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1063" s="2">
         <v>46261</v>
       </c>
@@ -52906,7 +52897,7 @@
       </c>
       <c r="Q1063" s="1"/>
     </row>
-    <row r="1064" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1064" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1064" s="2">
         <v>46261</v>
       </c>
@@ -52953,7 +52944,7 @@
       </c>
       <c r="Q1064" s="1"/>
     </row>
-    <row r="1065" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1065" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1065" s="2">
         <v>46261</v>
       </c>
@@ -53000,7 +52991,7 @@
       </c>
       <c r="Q1065" s="1"/>
     </row>
-    <row r="1066" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1066" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1066" s="2">
         <v>46261</v>
       </c>
@@ -53047,7 +53038,7 @@
       </c>
       <c r="Q1066" s="1"/>
     </row>
-    <row r="1067" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1067" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1067" s="2">
         <v>46261</v>
       </c>
@@ -53094,7 +53085,7 @@
       </c>
       <c r="Q1067" s="1"/>
     </row>
-    <row r="1068" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1068" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1068" s="2">
         <v>46261</v>
       </c>
@@ -53141,7 +53132,7 @@
       </c>
       <c r="Q1068" s="1"/>
     </row>
-    <row r="1069" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1069" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1069" s="2">
         <v>46261</v>
       </c>
@@ -53188,7 +53179,7 @@
       </c>
       <c r="Q1069" s="1"/>
     </row>
-    <row r="1070" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1070" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1070" s="2">
         <v>46261</v>
       </c>
@@ -53235,7 +53226,7 @@
       </c>
       <c r="Q1070" s="1"/>
     </row>
-    <row r="1071" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1071" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1071" s="2">
         <v>46261</v>
       </c>
@@ -53282,7 +53273,7 @@
       </c>
       <c r="Q1071" s="1"/>
     </row>
-    <row r="1072" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1072" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1072" s="2">
         <v>46261</v>
       </c>
@@ -53329,7 +53320,7 @@
       </c>
       <c r="Q1072" s="1"/>
     </row>
-    <row r="1073" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1073" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1073" s="2">
         <v>46261</v>
       </c>
@@ -53376,7 +53367,7 @@
       </c>
       <c r="Q1073" s="1"/>
     </row>
-    <row r="1074" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1074" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1074" s="2">
         <v>46261</v>
       </c>
@@ -53423,7 +53414,7 @@
       </c>
       <c r="Q1074" s="1"/>
     </row>
-    <row r="1075" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1075" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1075" s="2">
         <v>46261</v>
       </c>
@@ -53470,7 +53461,7 @@
       </c>
       <c r="Q1075" s="1"/>
     </row>
-    <row r="1076" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1076" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1076" s="2">
         <v>46261</v>
       </c>
@@ -53517,7 +53508,7 @@
       </c>
       <c r="Q1076" s="1"/>
     </row>
-    <row r="1077" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1077" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1077" s="2">
         <v>46261</v>
       </c>
@@ -53564,7 +53555,7 @@
       </c>
       <c r="Q1077" s="1"/>
     </row>
-    <row r="1078" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1078" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1078" s="2">
         <v>46261</v>
       </c>
@@ -53611,7 +53602,7 @@
       </c>
       <c r="Q1078" s="1"/>
     </row>
-    <row r="1079" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1079" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1079" s="2">
         <v>46261</v>
       </c>
@@ -53658,7 +53649,7 @@
       </c>
       <c r="Q1079" s="1"/>
     </row>
-    <row r="1080" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1080" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1080" s="2">
         <v>46261</v>
       </c>
@@ -53705,7 +53696,7 @@
       </c>
       <c r="Q1080" s="1"/>
     </row>
-    <row r="1081" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1081" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1081" s="2">
         <v>46261</v>
       </c>
@@ -53752,7 +53743,7 @@
       </c>
       <c r="Q1081" s="1"/>
     </row>
-    <row r="1082" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1082" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1082" s="2">
         <v>46261</v>
       </c>
@@ -53799,7 +53790,7 @@
       </c>
       <c r="Q1082" s="1"/>
     </row>
-    <row r="1083" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1083" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1083" s="2">
         <v>46261</v>
       </c>
@@ -53846,7 +53837,7 @@
       </c>
       <c r="Q1083" s="1"/>
     </row>
-    <row r="1084" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1084" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1084" s="2">
         <v>46261</v>
       </c>
@@ -53893,7 +53884,7 @@
       </c>
       <c r="Q1084" s="1"/>
     </row>
-    <row r="1085" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1085" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1085" s="2">
         <v>46261</v>
       </c>
@@ -53940,7 +53931,7 @@
       </c>
       <c r="Q1085" s="1"/>
     </row>
-    <row r="1086" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1086" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1086" s="2">
         <v>46261</v>
       </c>
@@ -53987,7 +53978,7 @@
       </c>
       <c r="Q1086" s="1"/>
     </row>
-    <row r="1087" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1087" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1087" s="2">
         <v>46261</v>
       </c>
@@ -54034,7 +54025,7 @@
       </c>
       <c r="Q1087" s="1"/>
     </row>
-    <row r="1088" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1088" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1088" s="2">
         <v>46261</v>
       </c>
@@ -54081,7 +54072,7 @@
       </c>
       <c r="Q1088" s="1"/>
     </row>
-    <row r="1089" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1089" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1089" s="2">
         <v>46261</v>
       </c>
@@ -54128,7 +54119,7 @@
       </c>
       <c r="Q1089" s="1"/>
     </row>
-    <row r="1090" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1090" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1090" s="2">
         <v>46261</v>
       </c>
@@ -54175,7 +54166,7 @@
       </c>
       <c r="Q1090" s="1"/>
     </row>
-    <row r="1091" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1091" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1091" s="2">
         <v>46261</v>
       </c>
@@ -54222,7 +54213,7 @@
       </c>
       <c r="Q1091" s="1"/>
     </row>
-    <row r="1092" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1092" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1092" s="2">
         <v>46261</v>
       </c>
@@ -54269,7 +54260,7 @@
       </c>
       <c r="Q1092" s="1"/>
     </row>
-    <row r="1093" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1093" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1093" s="2">
         <v>46261</v>
       </c>

--- a/Donnees_Mensuelle.xlsx
+++ b/Donnees_Mensuelle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AECF04C-EF20-4DFF-986A-3CFD8356CEA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00795D44-F44A-4BCD-8F21-8243EC713E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4911" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4912" uniqueCount="119">
   <si>
     <t>Date</t>
   </si>
@@ -387,6 +387,9 @@
   </si>
   <si>
     <t>YARAKH</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -783,7 +786,18 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}" name="Tableau1" displayName="Tableau1" ref="A1:Q700" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:Q700" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}"/>
+  <autoFilter ref="A1:Q700" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="TATA 2"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="6">
+      <filters>
+        <filter val="Ado DABO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{713E4B58-7C9F-4B80-8C6C-D9C3181B21C1}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{0868AEE8-A7A6-4928-8DDB-60543BB07F07}" name="Telephone_Team_Leader" dataDxfId="14"/>
@@ -1199,7 +1213,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>46270</v>
       </c>
@@ -1246,7 +1260,7 @@
       </c>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>46270</v>
       </c>
@@ -1293,7 +1307,7 @@
       </c>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>46270</v>
       </c>
@@ -1340,7 +1354,7 @@
       </c>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>46270</v>
       </c>
@@ -1387,7 +1401,7 @@
       </c>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>46270</v>
       </c>
@@ -1434,7 +1448,7 @@
       </c>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>46270</v>
       </c>
@@ -1481,7 +1495,7 @@
       </c>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>46270</v>
       </c>
@@ -1528,7 +1542,7 @@
       </c>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>46270</v>
       </c>
@@ -1575,7 +1589,7 @@
       </c>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>46270</v>
       </c>
@@ -1622,7 +1636,7 @@
       </c>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <v>46270</v>
       </c>
@@ -1669,7 +1683,7 @@
       </c>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
         <v>46270</v>
       </c>
@@ -1716,7 +1730,7 @@
       </c>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
         <v>46270</v>
       </c>
@@ -1763,7 +1777,7 @@
       </c>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
         <v>46270</v>
       </c>
@@ -1810,7 +1824,7 @@
       </c>
       <c r="Q14" s="1"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" s="2">
         <v>46270</v>
       </c>
@@ -1857,7 +1871,7 @@
       </c>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
         <v>46270</v>
       </c>
@@ -1904,7 +1918,7 @@
       </c>
       <c r="Q16" s="1"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
         <v>46270</v>
       </c>
@@ -1951,7 +1965,7 @@
       </c>
       <c r="Q17" s="1"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
         <v>46270</v>
       </c>
@@ -1998,7 +2012,7 @@
       </c>
       <c r="Q18" s="1"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
         <v>46270</v>
       </c>
@@ -2045,7 +2059,7 @@
       </c>
       <c r="Q19" s="1"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
         <v>46270</v>
       </c>
@@ -2092,7 +2106,7 @@
       </c>
       <c r="Q20" s="1"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
         <v>46270</v>
       </c>
@@ -2139,7 +2153,7 @@
       </c>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>46270</v>
       </c>
@@ -2186,7 +2200,7 @@
       </c>
       <c r="Q22" s="1"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
         <v>46270</v>
       </c>
@@ -2233,7 +2247,7 @@
       </c>
       <c r="Q23" s="1"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <v>46270</v>
       </c>
@@ -2280,7 +2294,7 @@
       </c>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <v>46270</v>
       </c>
@@ -2327,7 +2341,7 @@
       </c>
       <c r="Q25" s="1"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
         <v>46270</v>
       </c>
@@ -2374,7 +2388,7 @@
       </c>
       <c r="Q26" s="1"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
         <v>46270</v>
       </c>
@@ -2421,7 +2435,7 @@
       </c>
       <c r="Q27" s="1"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A28" s="2">
         <v>46270</v>
       </c>
@@ -2468,7 +2482,7 @@
       </c>
       <c r="Q28" s="1"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
         <v>46270</v>
       </c>
@@ -2515,7 +2529,7 @@
       </c>
       <c r="Q29" s="1"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
         <v>46270</v>
       </c>
@@ -2562,7 +2576,7 @@
       </c>
       <c r="Q30" s="1"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
         <v>46270</v>
       </c>
@@ -2609,7 +2623,7 @@
       </c>
       <c r="Q31" s="1"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
         <v>46270</v>
       </c>
@@ -2656,7 +2670,7 @@
       </c>
       <c r="Q32" s="1"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
         <v>46270</v>
       </c>
@@ -2703,7 +2717,7 @@
       </c>
       <c r="Q33" s="1"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
         <v>46270</v>
       </c>
@@ -2750,7 +2764,7 @@
       </c>
       <c r="Q34" s="1"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
         <v>46270</v>
       </c>
@@ -2797,7 +2811,7 @@
       </c>
       <c r="Q35" s="1"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
         <v>46270</v>
       </c>
@@ -2844,7 +2858,7 @@
       </c>
       <c r="Q36" s="1"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
         <v>46270</v>
       </c>
@@ -2891,7 +2905,7 @@
       </c>
       <c r="Q37" s="1"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
         <v>46270</v>
       </c>
@@ -2938,7 +2952,7 @@
       </c>
       <c r="Q38" s="1"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
         <v>46270</v>
       </c>
@@ -2985,7 +2999,7 @@
       </c>
       <c r="Q39" s="1"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
         <v>46270</v>
       </c>
@@ -3032,7 +3046,7 @@
       </c>
       <c r="Q40" s="1"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A41" s="2">
         <v>46270</v>
       </c>
@@ -3079,7 +3093,7 @@
       </c>
       <c r="Q41" s="1"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
         <v>46270</v>
       </c>
@@ -3126,7 +3140,7 @@
       </c>
       <c r="Q42" s="1"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
         <v>46270</v>
       </c>
@@ -3173,7 +3187,7 @@
       </c>
       <c r="Q43" s="1"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A44" s="2">
         <v>46270</v>
       </c>
@@ -3220,7 +3234,7 @@
       </c>
       <c r="Q44" s="1"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A45" s="2">
         <v>46270</v>
       </c>
@@ -3267,7 +3281,7 @@
       </c>
       <c r="Q45" s="1"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
         <v>46270</v>
       </c>
@@ -3314,7 +3328,7 @@
       </c>
       <c r="Q46" s="1"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A47" s="2">
         <v>46270</v>
       </c>
@@ -3361,7 +3375,7 @@
       </c>
       <c r="Q47" s="1"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A48" s="2">
         <v>46270</v>
       </c>
@@ -3408,7 +3422,7 @@
       </c>
       <c r="Q48" s="1"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A49" s="2">
         <v>46270</v>
       </c>
@@ -3455,7 +3469,7 @@
       </c>
       <c r="Q49" s="1"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
         <v>46270</v>
       </c>
@@ -3502,7 +3516,7 @@
       </c>
       <c r="Q50" s="1"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
         <v>46270</v>
       </c>
@@ -3549,7 +3563,7 @@
       </c>
       <c r="Q51" s="1"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
         <v>46270</v>
       </c>
@@ -3596,7 +3610,7 @@
       </c>
       <c r="Q52" s="1"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
         <v>46270</v>
       </c>
@@ -3643,7 +3657,7 @@
       </c>
       <c r="Q53" s="1"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
         <v>46270</v>
       </c>
@@ -3690,7 +3704,7 @@
       </c>
       <c r="Q54" s="1"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A55" s="2">
         <v>46270</v>
       </c>
@@ -3737,7 +3751,7 @@
       </c>
       <c r="Q55" s="1"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A56" s="2">
         <v>46270</v>
       </c>
@@ -3784,7 +3798,7 @@
       </c>
       <c r="Q56" s="1"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
         <v>46270</v>
       </c>
@@ -3831,7 +3845,7 @@
       </c>
       <c r="Q57" s="1"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
         <v>46270</v>
       </c>
@@ -3878,7 +3892,7 @@
       </c>
       <c r="Q58" s="1"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A59" s="2">
         <v>46270</v>
       </c>
@@ -3925,7 +3939,7 @@
       </c>
       <c r="Q59" s="1"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
         <v>46270</v>
       </c>
@@ -3972,7 +3986,7 @@
       </c>
       <c r="Q60" s="1"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
         <v>46270</v>
       </c>
@@ -4019,7 +4033,7 @@
       </c>
       <c r="Q61" s="1"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A62" s="2">
         <v>46270</v>
       </c>
@@ -4066,7 +4080,7 @@
       </c>
       <c r="Q62" s="1"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A63" s="2">
         <v>46270</v>
       </c>
@@ -4113,7 +4127,7 @@
       </c>
       <c r="Q63" s="1"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A64" s="2">
         <v>46270</v>
       </c>
@@ -4160,7 +4174,7 @@
       </c>
       <c r="Q64" s="1"/>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A65" s="2">
         <v>46270</v>
       </c>
@@ -4207,7 +4221,7 @@
       </c>
       <c r="Q65" s="1"/>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A66" s="2">
         <v>46270</v>
       </c>
@@ -4254,7 +4268,7 @@
       </c>
       <c r="Q66" s="1"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A67" s="2">
         <v>46270</v>
       </c>
@@ -4301,7 +4315,7 @@
       </c>
       <c r="Q67" s="1"/>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A68" s="2">
         <v>46270</v>
       </c>
@@ -4348,7 +4362,7 @@
       </c>
       <c r="Q68" s="1"/>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A69" s="2">
         <v>46270</v>
       </c>
@@ -4395,7 +4409,7 @@
       </c>
       <c r="Q69" s="1"/>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A70" s="2">
         <v>46270</v>
       </c>
@@ -4442,7 +4456,7 @@
       </c>
       <c r="Q70" s="1"/>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A71" s="2">
         <v>46270</v>
       </c>
@@ -4489,7 +4503,7 @@
       </c>
       <c r="Q71" s="1"/>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A72" s="2">
         <v>46270</v>
       </c>
@@ -4536,7 +4550,7 @@
       </c>
       <c r="Q72" s="1"/>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A73" s="2">
         <v>46270</v>
       </c>
@@ -4583,7 +4597,7 @@
       </c>
       <c r="Q73" s="1"/>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A74" s="2">
         <v>46270</v>
       </c>
@@ -4630,7 +4644,7 @@
       </c>
       <c r="Q74" s="1"/>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A75" s="2">
         <v>46270</v>
       </c>
@@ -4677,7 +4691,7 @@
       </c>
       <c r="Q75" s="1"/>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A76" s="2">
         <v>46270</v>
       </c>
@@ -4724,7 +4738,7 @@
       </c>
       <c r="Q76" s="1"/>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A77" s="2">
         <v>46270</v>
       </c>
@@ -4771,7 +4785,7 @@
       </c>
       <c r="Q77" s="1"/>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A78" s="2">
         <v>46270</v>
       </c>
@@ -4820,7 +4834,7 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A79" s="2">
-        <v>46270</v>
+        <v>46268</v>
       </c>
       <c r="B79" s="1">
         <v>0</v>
@@ -4865,7 +4879,7 @@
       </c>
       <c r="Q79" s="1"/>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A80" s="2">
         <v>46270</v>
       </c>
@@ -4912,7 +4926,7 @@
       </c>
       <c r="Q80" s="1"/>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A81" s="2">
         <v>46270</v>
       </c>
@@ -4959,7 +4973,7 @@
       </c>
       <c r="Q81" s="1"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A82" s="2">
         <v>46270</v>
       </c>
@@ -5006,7 +5020,7 @@
       </c>
       <c r="Q82" s="1"/>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A83" s="2">
         <v>46270</v>
       </c>
@@ -5053,7 +5067,7 @@
       </c>
       <c r="Q83" s="1"/>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A84" s="2">
         <v>46270</v>
       </c>
@@ -5100,7 +5114,7 @@
       </c>
       <c r="Q84" s="1"/>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A85" s="2">
         <v>46270</v>
       </c>
@@ -5147,7 +5161,7 @@
       </c>
       <c r="Q85" s="1"/>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A86" s="2">
         <v>46270</v>
       </c>
@@ -5194,7 +5208,7 @@
       </c>
       <c r="Q86" s="1"/>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A87" s="2">
         <v>46270</v>
       </c>
@@ -5241,7 +5255,7 @@
       </c>
       <c r="Q87" s="1"/>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A88" s="2">
         <v>46270</v>
       </c>
@@ -5288,7 +5302,7 @@
       </c>
       <c r="Q88" s="1"/>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A89" s="2">
         <v>46270</v>
       </c>
@@ -5335,7 +5349,7 @@
       </c>
       <c r="Q89" s="1"/>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A90" s="2">
         <v>46270</v>
       </c>
@@ -5382,7 +5396,7 @@
       </c>
       <c r="Q90" s="1"/>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A91" s="2">
         <v>46270</v>
       </c>
@@ -5429,7 +5443,7 @@
       </c>
       <c r="Q91" s="1"/>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A92" s="2">
         <v>46270</v>
       </c>
@@ -5476,7 +5490,7 @@
       </c>
       <c r="Q92" s="1"/>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A93" s="2">
         <v>46270</v>
       </c>
@@ -5523,7 +5537,7 @@
       </c>
       <c r="Q93" s="1"/>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A94" s="2">
         <v>46270</v>
       </c>
@@ -5570,7 +5584,7 @@
       </c>
       <c r="Q94" s="1"/>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A95" s="2">
         <v>46270</v>
       </c>
@@ -5617,7 +5631,7 @@
       </c>
       <c r="Q95" s="1"/>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A96" s="2">
         <v>46270</v>
       </c>
@@ -5664,7 +5678,7 @@
       </c>
       <c r="Q96" s="1"/>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A97" s="2">
         <v>46270</v>
       </c>
@@ -5711,7 +5725,7 @@
       </c>
       <c r="Q97" s="1"/>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A98" s="2">
         <v>46270</v>
       </c>
@@ -5758,7 +5772,7 @@
       </c>
       <c r="Q98" s="1"/>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A99" s="2">
         <v>46270</v>
       </c>
@@ -5805,7 +5819,7 @@
       </c>
       <c r="Q99" s="1"/>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A100" s="2">
         <v>46270</v>
       </c>
@@ -5852,7 +5866,7 @@
       </c>
       <c r="Q100" s="1"/>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A101" s="2">
         <v>46270</v>
       </c>
@@ -5899,7 +5913,7 @@
       </c>
       <c r="Q101" s="1"/>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A102" s="2">
         <v>46270</v>
       </c>
@@ -5946,9 +5960,9 @@
       </c>
       <c r="Q102" s="1"/>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A103" s="2">
-        <v>46270</v>
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A103" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="B103" s="1">
         <v>0</v>
@@ -5993,7 +6007,7 @@
       </c>
       <c r="Q103" s="1"/>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A104" s="2">
         <v>46270</v>
       </c>
@@ -6040,7 +6054,7 @@
       </c>
       <c r="Q104" s="1"/>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A105" s="2">
         <v>46269</v>
       </c>
@@ -6087,7 +6101,7 @@
       </c>
       <c r="Q105" s="1"/>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A106" s="2">
         <v>46269</v>
       </c>
@@ -6134,7 +6148,7 @@
       </c>
       <c r="Q106" s="1"/>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A107" s="2">
         <v>46269</v>
       </c>
@@ -6181,7 +6195,7 @@
       </c>
       <c r="Q107" s="1"/>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A108" s="2">
         <v>46269</v>
       </c>
@@ -6228,7 +6242,7 @@
       </c>
       <c r="Q108" s="1"/>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A109" s="2">
         <v>46269</v>
       </c>
@@ -6275,7 +6289,7 @@
       </c>
       <c r="Q109" s="1"/>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A110" s="2">
         <v>46269</v>
       </c>
@@ -6322,7 +6336,7 @@
       </c>
       <c r="Q110" s="1"/>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A111" s="2">
         <v>46269</v>
       </c>
@@ -6369,7 +6383,7 @@
       </c>
       <c r="Q111" s="1"/>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A112" s="2">
         <v>46269</v>
       </c>
@@ -6416,7 +6430,7 @@
       </c>
       <c r="Q112" s="1"/>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A113" s="2">
         <v>46269</v>
       </c>
@@ -6463,7 +6477,7 @@
       </c>
       <c r="Q113" s="1"/>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A114" s="2">
         <v>46269</v>
       </c>
@@ -6510,7 +6524,7 @@
       </c>
       <c r="Q114" s="1"/>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A115" s="2">
         <v>46269</v>
       </c>
@@ -6557,7 +6571,7 @@
       </c>
       <c r="Q115" s="1"/>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A116" s="2">
         <v>46269</v>
       </c>
@@ -6604,7 +6618,7 @@
       </c>
       <c r="Q116" s="1"/>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A117" s="2">
         <v>46269</v>
       </c>
@@ -6651,7 +6665,7 @@
       </c>
       <c r="Q117" s="1"/>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A118" s="2">
         <v>46269</v>
       </c>
@@ -6698,7 +6712,7 @@
       </c>
       <c r="Q118" s="1"/>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A119" s="2">
         <v>46269</v>
       </c>
@@ -6745,7 +6759,7 @@
       </c>
       <c r="Q119" s="1"/>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A120" s="2">
         <v>46269</v>
       </c>
@@ -6792,7 +6806,7 @@
       </c>
       <c r="Q120" s="1"/>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A121" s="2">
         <v>46269</v>
       </c>
@@ -6839,7 +6853,7 @@
       </c>
       <c r="Q121" s="1"/>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A122" s="2">
         <v>46269</v>
       </c>
@@ -6886,7 +6900,7 @@
       </c>
       <c r="Q122" s="1"/>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A123" s="2">
         <v>46269</v>
       </c>
@@ -6933,7 +6947,7 @@
       </c>
       <c r="Q123" s="1"/>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A124" s="2">
         <v>46269</v>
       </c>
@@ -6980,7 +6994,7 @@
       </c>
       <c r="Q124" s="1"/>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A125" s="2">
         <v>46269</v>
       </c>
@@ -7027,7 +7041,7 @@
       </c>
       <c r="Q125" s="1"/>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A126" s="2">
         <v>46269</v>
       </c>
@@ -7074,7 +7088,7 @@
       </c>
       <c r="Q126" s="1"/>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A127" s="2">
         <v>46269</v>
       </c>
@@ -7121,7 +7135,7 @@
       </c>
       <c r="Q127" s="1"/>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A128" s="2">
         <v>46269</v>
       </c>
@@ -7168,7 +7182,7 @@
       </c>
       <c r="Q128" s="1"/>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A129" s="2">
         <v>46269</v>
       </c>
@@ -7215,7 +7229,7 @@
       </c>
       <c r="Q129" s="1"/>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A130" s="2">
         <v>46269</v>
       </c>
@@ -7262,7 +7276,7 @@
       </c>
       <c r="Q130" s="1"/>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A131" s="2">
         <v>46269</v>
       </c>
@@ -7309,7 +7323,7 @@
       </c>
       <c r="Q131" s="1"/>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A132" s="2">
         <v>46269</v>
       </c>
@@ -7356,7 +7370,7 @@
       </c>
       <c r="Q132" s="1"/>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A133" s="2">
         <v>46269</v>
       </c>
@@ -7403,7 +7417,7 @@
       </c>
       <c r="Q133" s="1"/>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A134" s="2">
         <v>46269</v>
       </c>
@@ -7450,7 +7464,7 @@
       </c>
       <c r="Q134" s="1"/>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A135" s="2">
         <v>46269</v>
       </c>
@@ -7497,7 +7511,7 @@
       </c>
       <c r="Q135" s="1"/>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A136" s="2">
         <v>46269</v>
       </c>
@@ -7544,7 +7558,7 @@
       </c>
       <c r="Q136" s="1"/>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A137" s="2">
         <v>46269</v>
       </c>
@@ -7591,7 +7605,7 @@
       </c>
       <c r="Q137" s="1"/>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A138" s="2">
         <v>46269</v>
       </c>
@@ -7638,7 +7652,7 @@
       </c>
       <c r="Q138" s="1"/>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A139" s="2">
         <v>46269</v>
       </c>
@@ -7685,7 +7699,7 @@
       </c>
       <c r="Q139" s="1"/>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A140" s="2">
         <v>46269</v>
       </c>
@@ -7732,7 +7746,7 @@
       </c>
       <c r="Q140" s="1"/>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A141" s="2">
         <v>46269</v>
       </c>
@@ -7779,7 +7793,7 @@
       </c>
       <c r="Q141" s="1"/>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A142" s="2">
         <v>46269</v>
       </c>
@@ -7826,7 +7840,7 @@
       </c>
       <c r="Q142" s="1"/>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A143" s="2">
         <v>46269</v>
       </c>
@@ -7873,7 +7887,7 @@
       </c>
       <c r="Q143" s="1"/>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A144" s="2">
         <v>46269</v>
       </c>
@@ -7920,7 +7934,7 @@
       </c>
       <c r="Q144" s="1"/>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A145" s="2">
         <v>46269</v>
       </c>
@@ -7967,7 +7981,7 @@
       </c>
       <c r="Q145" s="1"/>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A146" s="2">
         <v>46269</v>
       </c>
@@ -8014,7 +8028,7 @@
       </c>
       <c r="Q146" s="1"/>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A147" s="2">
         <v>46269</v>
       </c>
@@ -8061,7 +8075,7 @@
       </c>
       <c r="Q147" s="1"/>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A148" s="2">
         <v>46269</v>
       </c>
@@ -8108,7 +8122,7 @@
       </c>
       <c r="Q148" s="1"/>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A149" s="2">
         <v>46269</v>
       </c>
@@ -8155,7 +8169,7 @@
       </c>
       <c r="Q149" s="1"/>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A150" s="2">
         <v>46269</v>
       </c>
@@ -8202,7 +8216,7 @@
       </c>
       <c r="Q150" s="1"/>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A151" s="2">
         <v>46269</v>
       </c>
@@ -8249,7 +8263,7 @@
       </c>
       <c r="Q151" s="1"/>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A152" s="2">
         <v>46269</v>
       </c>
@@ -8296,7 +8310,7 @@
       </c>
       <c r="Q152" s="1"/>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A153" s="2">
         <v>46269</v>
       </c>
@@ -8343,7 +8357,7 @@
       </c>
       <c r="Q153" s="1"/>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A154" s="2">
         <v>46269</v>
       </c>
@@ -8390,7 +8404,7 @@
       </c>
       <c r="Q154" s="1"/>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A155" s="2">
         <v>46269</v>
       </c>
@@ -8437,7 +8451,7 @@
       </c>
       <c r="Q155" s="1"/>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A156" s="2">
         <v>46269</v>
       </c>
@@ -8484,7 +8498,7 @@
       </c>
       <c r="Q156" s="1"/>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A157" s="2">
         <v>46269</v>
       </c>
@@ -8531,7 +8545,7 @@
       </c>
       <c r="Q157" s="1"/>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A158" s="2">
         <v>46269</v>
       </c>
@@ -8578,7 +8592,7 @@
       </c>
       <c r="Q158" s="1"/>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A159" s="2">
         <v>46269</v>
       </c>
@@ -8625,7 +8639,7 @@
       </c>
       <c r="Q159" s="1"/>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A160" s="2">
         <v>46269</v>
       </c>
@@ -8672,7 +8686,7 @@
       </c>
       <c r="Q160" s="1"/>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A161" s="2">
         <v>46269</v>
       </c>
@@ -8719,7 +8733,7 @@
       </c>
       <c r="Q161" s="1"/>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A162" s="2">
         <v>46269</v>
       </c>
@@ -8766,7 +8780,7 @@
       </c>
       <c r="Q162" s="1"/>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A163" s="2">
         <v>46269</v>
       </c>
@@ -8813,7 +8827,7 @@
       </c>
       <c r="Q163" s="1"/>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A164" s="2">
         <v>46269</v>
       </c>
@@ -8860,7 +8874,7 @@
       </c>
       <c r="Q164" s="1"/>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A165" s="2">
         <v>46269</v>
       </c>
@@ -8907,7 +8921,7 @@
       </c>
       <c r="Q165" s="1"/>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A166" s="2">
         <v>46269</v>
       </c>
@@ -8954,7 +8968,7 @@
       </c>
       <c r="Q166" s="1"/>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A167" s="2">
         <v>46269</v>
       </c>
@@ -9001,7 +9015,7 @@
       </c>
       <c r="Q167" s="1"/>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A168" s="2">
         <v>46269</v>
       </c>
@@ -9048,7 +9062,7 @@
       </c>
       <c r="Q168" s="1"/>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A169" s="2">
         <v>46269</v>
       </c>
@@ -9095,7 +9109,7 @@
       </c>
       <c r="Q169" s="1"/>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A170" s="2">
         <v>46269</v>
       </c>
@@ -9142,7 +9156,7 @@
       </c>
       <c r="Q170" s="1"/>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A171" s="2">
         <v>46269</v>
       </c>
@@ -9189,7 +9203,7 @@
       </c>
       <c r="Q171" s="1"/>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A172" s="2">
         <v>46269</v>
       </c>
@@ -9236,7 +9250,7 @@
       </c>
       <c r="Q172" s="1"/>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A173" s="2">
         <v>46269</v>
       </c>
@@ -9283,7 +9297,7 @@
       </c>
       <c r="Q173" s="1"/>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A174" s="2">
         <v>46269</v>
       </c>
@@ -9330,7 +9344,7 @@
       </c>
       <c r="Q174" s="1"/>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A175" s="2">
         <v>46269</v>
       </c>
@@ -9377,7 +9391,7 @@
       </c>
       <c r="Q175" s="1"/>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A176" s="2">
         <v>46269</v>
       </c>
@@ -9424,7 +9438,7 @@
       </c>
       <c r="Q176" s="1"/>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A177" s="2">
         <v>46269</v>
       </c>
@@ -9471,9 +9485,9 @@
       </c>
       <c r="Q177" s="1"/>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A178" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B178" s="1">
         <v>0</v>
@@ -9518,9 +9532,9 @@
       </c>
       <c r="Q178" s="1"/>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A179" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B179" s="1">
         <v>0</v>
@@ -9565,9 +9579,9 @@
       </c>
       <c r="Q179" s="1"/>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A180" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B180" s="1">
         <v>0</v>
@@ -9612,7 +9626,7 @@
       </c>
       <c r="Q180" s="1"/>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A181" s="2">
         <v>46269</v>
       </c>
@@ -9659,7 +9673,7 @@
       </c>
       <c r="Q181" s="1"/>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A182" s="2">
         <v>46269</v>
       </c>
@@ -9706,7 +9720,7 @@
       </c>
       <c r="Q182" s="1"/>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A183" s="2">
         <v>46269</v>
       </c>
@@ -9753,7 +9767,7 @@
       </c>
       <c r="Q183" s="1"/>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A184" s="2">
         <v>46269</v>
       </c>
@@ -9800,7 +9814,7 @@
       </c>
       <c r="Q184" s="1"/>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A185" s="2">
         <v>46269</v>
       </c>
@@ -9847,7 +9861,7 @@
       </c>
       <c r="Q185" s="1"/>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A186" s="2">
         <v>46269</v>
       </c>
@@ -9894,7 +9908,7 @@
       </c>
       <c r="Q186" s="1"/>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A187" s="2">
         <v>46269</v>
       </c>
@@ -9941,7 +9955,7 @@
       </c>
       <c r="Q187" s="1"/>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A188" s="2">
         <v>46269</v>
       </c>
@@ -9988,7 +10002,7 @@
       </c>
       <c r="Q188" s="1"/>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A189" s="2">
         <v>46269</v>
       </c>
@@ -10035,7 +10049,7 @@
       </c>
       <c r="Q189" s="1"/>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A190" s="2">
         <v>46269</v>
       </c>
@@ -10082,7 +10096,7 @@
       </c>
       <c r="Q190" s="1"/>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A191" s="2">
         <v>46269</v>
       </c>
@@ -10129,7 +10143,7 @@
       </c>
       <c r="Q191" s="1"/>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A192" s="2">
         <v>46269</v>
       </c>
@@ -10176,7 +10190,7 @@
       </c>
       <c r="Q192" s="1"/>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A193" s="2">
         <v>46269</v>
       </c>
@@ -10223,7 +10237,7 @@
       </c>
       <c r="Q193" s="1"/>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A194" s="2">
         <v>46269</v>
       </c>
@@ -10270,7 +10284,7 @@
       </c>
       <c r="Q194" s="1"/>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A195" s="2">
         <v>46269</v>
       </c>
@@ -10317,7 +10331,7 @@
       </c>
       <c r="Q195" s="1"/>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A196" s="2">
         <v>46269</v>
       </c>
@@ -10364,7 +10378,7 @@
       </c>
       <c r="Q196" s="1"/>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A197" s="2">
         <v>46269</v>
       </c>
@@ -10411,7 +10425,7 @@
       </c>
       <c r="Q197" s="1"/>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A198" s="2">
         <v>46269</v>
       </c>
@@ -10458,7 +10472,7 @@
       </c>
       <c r="Q198" s="1"/>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A199" s="2">
         <v>46269</v>
       </c>
@@ -10505,7 +10519,7 @@
       </c>
       <c r="Q199" s="1"/>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A200" s="2">
         <v>46269</v>
       </c>
@@ -10552,7 +10566,7 @@
       </c>
       <c r="Q200" s="1"/>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A201" s="2">
         <v>46269</v>
       </c>
@@ -10599,7 +10613,7 @@
       </c>
       <c r="Q201" s="1"/>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A202" s="2">
         <v>46269</v>
       </c>
@@ -10646,7 +10660,7 @@
       </c>
       <c r="Q202" s="1"/>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A203" s="2">
         <v>46269</v>
       </c>
@@ -10693,7 +10707,7 @@
       </c>
       <c r="Q203" s="1"/>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A204" s="2">
         <v>46269</v>
       </c>
@@ -10740,7 +10754,7 @@
       </c>
       <c r="Q204" s="1"/>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A205" s="2">
         <v>46269</v>
       </c>
@@ -10787,7 +10801,7 @@
       </c>
       <c r="Q205" s="1"/>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A206" s="2">
         <v>46269</v>
       </c>
@@ -10834,7 +10848,7 @@
       </c>
       <c r="Q206" s="1"/>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A207" s="2">
         <v>46269</v>
       </c>
@@ -10881,7 +10895,7 @@
       </c>
       <c r="Q207" s="1"/>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A208" s="2">
         <v>46269</v>
       </c>
@@ -10928,7 +10942,7 @@
       </c>
       <c r="Q208" s="1"/>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A209" s="2">
         <v>46269</v>
       </c>
@@ -10975,7 +10989,7 @@
       </c>
       <c r="Q209" s="1"/>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A210" s="2">
         <v>46269</v>
       </c>
@@ -11022,7 +11036,7 @@
       </c>
       <c r="Q210" s="1"/>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A211" s="2">
         <v>46269</v>
       </c>
@@ -11069,9 +11083,9 @@
       </c>
       <c r="Q211" s="1"/>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A212" s="2">
-        <v>46269</v>
+        <v>46265</v>
       </c>
       <c r="B212" s="1">
         <v>0</v>
@@ -11116,7 +11130,7 @@
       </c>
       <c r="Q212" s="1"/>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A213" s="2">
         <v>46269</v>
       </c>
@@ -11163,7 +11177,7 @@
       </c>
       <c r="Q213" s="1"/>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A214" s="2">
         <v>46269</v>
       </c>
@@ -11210,7 +11224,7 @@
       </c>
       <c r="Q214" s="1"/>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A215" s="2">
         <v>46268</v>
       </c>
@@ -11257,7 +11271,7 @@
       </c>
       <c r="Q215" s="1"/>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A216" s="2">
         <v>46268</v>
       </c>
@@ -11304,7 +11318,7 @@
       </c>
       <c r="Q216" s="1"/>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A217" s="2">
         <v>46268</v>
       </c>
@@ -11351,7 +11365,7 @@
       </c>
       <c r="Q217" s="1"/>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A218" s="2">
         <v>46268</v>
       </c>
@@ -11398,7 +11412,7 @@
       </c>
       <c r="Q218" s="1"/>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A219" s="2">
         <v>46268</v>
       </c>
@@ -11445,7 +11459,7 @@
       </c>
       <c r="Q219" s="1"/>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A220" s="2">
         <v>46268</v>
       </c>
@@ -11492,7 +11506,7 @@
       </c>
       <c r="Q220" s="1"/>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A221" s="2">
         <v>46268</v>
       </c>
@@ -11539,7 +11553,7 @@
       </c>
       <c r="Q221" s="1"/>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A222" s="2">
         <v>46268</v>
       </c>
@@ -11586,7 +11600,7 @@
       </c>
       <c r="Q222" s="1"/>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A223" s="2">
         <v>46268</v>
       </c>
@@ -11633,7 +11647,7 @@
       </c>
       <c r="Q223" s="1"/>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A224" s="2">
         <v>46268</v>
       </c>
@@ -11680,7 +11694,7 @@
       </c>
       <c r="Q224" s="1"/>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A225" s="2">
         <v>46268</v>
       </c>
@@ -11727,7 +11741,7 @@
       </c>
       <c r="Q225" s="1"/>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A226" s="2">
         <v>46268</v>
       </c>
@@ -11774,7 +11788,7 @@
       </c>
       <c r="Q226" s="1"/>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A227" s="2">
         <v>46268</v>
       </c>
@@ -11821,7 +11835,7 @@
       </c>
       <c r="Q227" s="1"/>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A228" s="2">
         <v>46268</v>
       </c>
@@ -11868,7 +11882,7 @@
       </c>
       <c r="Q228" s="1"/>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A229" s="2">
         <v>46268</v>
       </c>
@@ -11915,7 +11929,7 @@
       </c>
       <c r="Q229" s="1"/>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A230" s="2">
         <v>46268</v>
       </c>
@@ -11962,7 +11976,7 @@
       </c>
       <c r="Q230" s="1"/>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A231" s="2">
         <v>46268</v>
       </c>
@@ -12009,7 +12023,7 @@
       </c>
       <c r="Q231" s="1"/>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A232" s="2">
         <v>46268</v>
       </c>
@@ -12056,7 +12070,7 @@
       </c>
       <c r="Q232" s="1"/>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A233" s="2">
         <v>46268</v>
       </c>
@@ -12103,7 +12117,7 @@
       </c>
       <c r="Q233" s="1"/>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A234" s="2">
         <v>46268</v>
       </c>
@@ -12150,7 +12164,7 @@
       </c>
       <c r="Q234" s="1"/>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A235" s="2">
         <v>46268</v>
       </c>
@@ -12197,7 +12211,7 @@
       </c>
       <c r="Q235" s="1"/>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A236" s="2">
         <v>46268</v>
       </c>
@@ -12244,7 +12258,7 @@
       </c>
       <c r="Q236" s="1"/>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A237" s="2">
         <v>46268</v>
       </c>
@@ -12291,7 +12305,7 @@
       </c>
       <c r="Q237" s="1"/>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A238" s="2">
         <v>46268</v>
       </c>
@@ -12338,7 +12352,7 @@
       </c>
       <c r="Q238" s="1"/>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A239" s="2">
         <v>46268</v>
       </c>
@@ -12385,7 +12399,7 @@
       </c>
       <c r="Q239" s="1"/>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A240" s="2">
         <v>46268</v>
       </c>
@@ -12432,7 +12446,7 @@
       </c>
       <c r="Q240" s="1"/>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A241" s="2">
         <v>46268</v>
       </c>
@@ -12479,7 +12493,7 @@
       </c>
       <c r="Q241" s="1"/>
     </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A242" s="2">
         <v>46268</v>
       </c>
@@ -12526,7 +12540,7 @@
       </c>
       <c r="Q242" s="1"/>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A243" s="2">
         <v>46268</v>
       </c>
@@ -12573,7 +12587,7 @@
       </c>
       <c r="Q243" s="1"/>
     </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A244" s="2">
         <v>46268</v>
       </c>
@@ -12620,7 +12634,7 @@
       </c>
       <c r="Q244" s="1"/>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A245" s="2">
         <v>46268</v>
       </c>
@@ -12667,7 +12681,7 @@
       </c>
       <c r="Q245" s="1"/>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A246" s="2">
         <v>46268</v>
       </c>
@@ -12714,7 +12728,7 @@
       </c>
       <c r="Q246" s="1"/>
     </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A247" s="2">
         <v>46268</v>
       </c>
@@ -12761,7 +12775,7 @@
       </c>
       <c r="Q247" s="1"/>
     </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A248" s="2">
         <v>46268</v>
       </c>
@@ -12808,7 +12822,7 @@
       </c>
       <c r="Q248" s="1"/>
     </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A249" s="2">
         <v>46268</v>
       </c>
@@ -12855,7 +12869,7 @@
       </c>
       <c r="Q249" s="1"/>
     </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A250" s="2">
         <v>46268</v>
       </c>
@@ -12902,7 +12916,7 @@
       </c>
       <c r="Q250" s="1"/>
     </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A251" s="2">
         <v>46268</v>
       </c>
@@ -12949,7 +12963,7 @@
       </c>
       <c r="Q251" s="1"/>
     </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A252" s="2">
         <v>46268</v>
       </c>
@@ -12996,7 +13010,7 @@
       </c>
       <c r="Q252" s="1"/>
     </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A253" s="2">
         <v>46268</v>
       </c>
@@ -13043,7 +13057,7 @@
       </c>
       <c r="Q253" s="1"/>
     </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A254" s="2">
         <v>46268</v>
       </c>
@@ -13090,7 +13104,7 @@
       </c>
       <c r="Q254" s="1"/>
     </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A255" s="2">
         <v>46268</v>
       </c>
@@ -13137,7 +13151,7 @@
       </c>
       <c r="Q255" s="1"/>
     </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A256" s="2">
         <v>46268</v>
       </c>
@@ -13184,7 +13198,7 @@
       </c>
       <c r="Q256" s="1"/>
     </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A257" s="2">
         <v>46268</v>
       </c>
@@ -13231,7 +13245,7 @@
       </c>
       <c r="Q257" s="1"/>
     </row>
-    <row r="258" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A258" s="2">
         <v>46268</v>
       </c>
@@ -13278,7 +13292,7 @@
       </c>
       <c r="Q258" s="1"/>
     </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A259" s="2">
         <v>46268</v>
       </c>
@@ -13325,7 +13339,7 @@
       </c>
       <c r="Q259" s="1"/>
     </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A260" s="2">
         <v>46268</v>
       </c>
@@ -13372,7 +13386,7 @@
       </c>
       <c r="Q260" s="1"/>
     </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A261" s="2">
         <v>46268</v>
       </c>
@@ -13419,7 +13433,7 @@
       </c>
       <c r="Q261" s="1"/>
     </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A262" s="2">
         <v>46268</v>
       </c>
@@ -13466,7 +13480,7 @@
       </c>
       <c r="Q262" s="1"/>
     </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A263" s="2">
         <v>46268</v>
       </c>
@@ -13513,7 +13527,7 @@
       </c>
       <c r="Q263" s="1"/>
     </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A264" s="2">
         <v>46268</v>
       </c>
@@ -13560,7 +13574,7 @@
       </c>
       <c r="Q264" s="1"/>
     </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A265" s="2">
         <v>46268</v>
       </c>
@@ -13607,7 +13621,7 @@
       </c>
       <c r="Q265" s="1"/>
     </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A266" s="2">
         <v>46268</v>
       </c>
@@ -13654,7 +13668,7 @@
       </c>
       <c r="Q266" s="1"/>
     </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A267" s="2">
         <v>46268</v>
       </c>
@@ -13701,7 +13715,7 @@
       </c>
       <c r="Q267" s="1"/>
     </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A268" s="2">
         <v>46268</v>
       </c>
@@ -13748,7 +13762,7 @@
       </c>
       <c r="Q268" s="1"/>
     </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A269" s="2">
         <v>46268</v>
       </c>
@@ -13795,7 +13809,7 @@
       </c>
       <c r="Q269" s="1"/>
     </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A270" s="2">
         <v>46268</v>
       </c>
@@ -13842,7 +13856,7 @@
       </c>
       <c r="Q270" s="1"/>
     </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A271" s="2">
         <v>46268</v>
       </c>
@@ -13889,7 +13903,7 @@
       </c>
       <c r="Q271" s="1"/>
     </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A272" s="2">
         <v>46268</v>
       </c>
@@ -13936,7 +13950,7 @@
       </c>
       <c r="Q272" s="1"/>
     </row>
-    <row r="273" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A273" s="2">
         <v>46268</v>
       </c>
@@ -13983,7 +13997,7 @@
       </c>
       <c r="Q273" s="1"/>
     </row>
-    <row r="274" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A274" s="2">
         <v>46268</v>
       </c>
@@ -14030,7 +14044,7 @@
       </c>
       <c r="Q274" s="1"/>
     </row>
-    <row r="275" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A275" s="2">
         <v>46268</v>
       </c>
@@ -14077,7 +14091,7 @@
       </c>
       <c r="Q275" s="1"/>
     </row>
-    <row r="276" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A276" s="2">
         <v>46268</v>
       </c>
@@ -14124,7 +14138,7 @@
       </c>
       <c r="Q276" s="1"/>
     </row>
-    <row r="277" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A277" s="2">
         <v>46268</v>
       </c>
@@ -14171,7 +14185,7 @@
       </c>
       <c r="Q277" s="1"/>
     </row>
-    <row r="278" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A278" s="2">
         <v>46268</v>
       </c>
@@ -14218,7 +14232,7 @@
       </c>
       <c r="Q278" s="1"/>
     </row>
-    <row r="279" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A279" s="2">
         <v>46268</v>
       </c>
@@ -14265,7 +14279,7 @@
       </c>
       <c r="Q279" s="1"/>
     </row>
-    <row r="280" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A280" s="2">
         <v>46268</v>
       </c>
@@ -14312,7 +14326,7 @@
       </c>
       <c r="Q280" s="1"/>
     </row>
-    <row r="281" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A281" s="2">
         <v>46268</v>
       </c>
@@ -14359,7 +14373,7 @@
       </c>
       <c r="Q281" s="1"/>
     </row>
-    <row r="282" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A282" s="2">
         <v>46268</v>
       </c>
@@ -14406,7 +14420,7 @@
       </c>
       <c r="Q282" s="1"/>
     </row>
-    <row r="283" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A283" s="2">
         <v>46268</v>
       </c>
@@ -14453,7 +14467,7 @@
       </c>
       <c r="Q283" s="1"/>
     </row>
-    <row r="284" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A284" s="2">
         <v>46268</v>
       </c>
@@ -14500,7 +14514,7 @@
       </c>
       <c r="Q284" s="1"/>
     </row>
-    <row r="285" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A285" s="2">
         <v>46268</v>
       </c>
@@ -14547,7 +14561,7 @@
       </c>
       <c r="Q285" s="1"/>
     </row>
-    <row r="286" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A286" s="2">
         <v>46268</v>
       </c>
@@ -14594,7 +14608,7 @@
       </c>
       <c r="Q286" s="1"/>
     </row>
-    <row r="287" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A287" s="2">
         <v>46268</v>
       </c>
@@ -14641,7 +14655,7 @@
       </c>
       <c r="Q287" s="1"/>
     </row>
-    <row r="288" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A288" s="2">
         <v>46268</v>
       </c>
@@ -14688,7 +14702,7 @@
       </c>
       <c r="Q288" s="1"/>
     </row>
-    <row r="289" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A289" s="2">
         <v>46268</v>
       </c>
@@ -14735,7 +14749,7 @@
       </c>
       <c r="Q289" s="1"/>
     </row>
-    <row r="290" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A290" s="2">
         <v>46268</v>
       </c>
@@ -14782,7 +14796,7 @@
       </c>
       <c r="Q290" s="1"/>
     </row>
-    <row r="291" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A291" s="2">
         <v>46268</v>
       </c>
@@ -14829,7 +14843,7 @@
       </c>
       <c r="Q291" s="1"/>
     </row>
-    <row r="292" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A292" s="2">
         <v>46268</v>
       </c>
@@ -14876,7 +14890,7 @@
       </c>
       <c r="Q292" s="1"/>
     </row>
-    <row r="293" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A293" s="2">
         <v>46268</v>
       </c>
@@ -14923,7 +14937,7 @@
       </c>
       <c r="Q293" s="1"/>
     </row>
-    <row r="294" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A294" s="2">
         <v>46268</v>
       </c>
@@ -14970,7 +14984,7 @@
       </c>
       <c r="Q294" s="1"/>
     </row>
-    <row r="295" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A295" s="2">
         <v>46268</v>
       </c>
@@ -15017,7 +15031,7 @@
       </c>
       <c r="Q295" s="1"/>
     </row>
-    <row r="296" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A296" s="2">
         <v>46268</v>
       </c>
@@ -15064,7 +15078,7 @@
       </c>
       <c r="Q296" s="1"/>
     </row>
-    <row r="297" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A297" s="2">
         <v>46268</v>
       </c>
@@ -15111,7 +15125,7 @@
       </c>
       <c r="Q297" s="1"/>
     </row>
-    <row r="298" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A298" s="2">
         <v>46268</v>
       </c>
@@ -15158,7 +15172,7 @@
       </c>
       <c r="Q298" s="1"/>
     </row>
-    <row r="299" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A299" s="2">
         <v>46268</v>
       </c>
@@ -15205,7 +15219,7 @@
       </c>
       <c r="Q299" s="1"/>
     </row>
-    <row r="300" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A300" s="2">
         <v>46268</v>
       </c>
@@ -15252,7 +15266,7 @@
       </c>
       <c r="Q300" s="1"/>
     </row>
-    <row r="301" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A301" s="2">
         <v>46268</v>
       </c>
@@ -15393,7 +15407,7 @@
       </c>
       <c r="Q303" s="1"/>
     </row>
-    <row r="304" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A304" s="2">
         <v>46268</v>
       </c>
@@ -15440,7 +15454,7 @@
       </c>
       <c r="Q304" s="1"/>
     </row>
-    <row r="305" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A305" s="2">
         <v>46268</v>
       </c>
@@ -15487,7 +15501,7 @@
       </c>
       <c r="Q305" s="1"/>
     </row>
-    <row r="306" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A306" s="2">
         <v>46268</v>
       </c>
@@ -15534,7 +15548,7 @@
       </c>
       <c r="Q306" s="1"/>
     </row>
-    <row r="307" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A307" s="2">
         <v>46268</v>
       </c>
@@ -15581,7 +15595,7 @@
       </c>
       <c r="Q307" s="1"/>
     </row>
-    <row r="308" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A308" s="2">
         <v>46268</v>
       </c>
@@ -15628,7 +15642,7 @@
       </c>
       <c r="Q308" s="1"/>
     </row>
-    <row r="309" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A309" s="2">
         <v>46268</v>
       </c>
@@ -15675,7 +15689,7 @@
       </c>
       <c r="Q309" s="1"/>
     </row>
-    <row r="310" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A310" s="2">
         <v>46268</v>
       </c>
@@ -15722,7 +15736,7 @@
       </c>
       <c r="Q310" s="1"/>
     </row>
-    <row r="311" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A311" s="2">
         <v>46268</v>
       </c>
@@ -15769,7 +15783,7 @@
       </c>
       <c r="Q311" s="1"/>
     </row>
-    <row r="312" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A312" s="2">
         <v>46268</v>
       </c>
@@ -15816,7 +15830,7 @@
       </c>
       <c r="Q312" s="1"/>
     </row>
-    <row r="313" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A313" s="2">
         <v>46268</v>
       </c>
@@ -15863,7 +15877,7 @@
       </c>
       <c r="Q313" s="1"/>
     </row>
-    <row r="314" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A314" s="2">
         <v>46268</v>
       </c>
@@ -15910,7 +15924,7 @@
       </c>
       <c r="Q314" s="1"/>
     </row>
-    <row r="315" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A315" s="2">
         <v>46268</v>
       </c>
@@ -15957,7 +15971,7 @@
       </c>
       <c r="Q315" s="1"/>
     </row>
-    <row r="316" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A316" s="2">
         <v>46268</v>
       </c>
@@ -16004,7 +16018,7 @@
       </c>
       <c r="Q316" s="1"/>
     </row>
-    <row r="317" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A317" s="2">
         <v>46268</v>
       </c>
@@ -16051,7 +16065,7 @@
       </c>
       <c r="Q317" s="1"/>
     </row>
-    <row r="318" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A318" s="2">
         <v>46268</v>
       </c>
@@ -16098,7 +16112,7 @@
       </c>
       <c r="Q318" s="1"/>
     </row>
-    <row r="319" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A319" s="2">
         <v>46268</v>
       </c>
@@ -16145,7 +16159,7 @@
       </c>
       <c r="Q319" s="1"/>
     </row>
-    <row r="320" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A320" s="2">
         <v>46268</v>
       </c>
@@ -16192,7 +16206,7 @@
       </c>
       <c r="Q320" s="1"/>
     </row>
-    <row r="321" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A321" s="2">
         <v>46268</v>
       </c>
@@ -16239,7 +16253,7 @@
       </c>
       <c r="Q321" s="1"/>
     </row>
-    <row r="322" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A322" s="2">
         <v>46268</v>
       </c>
@@ -16286,7 +16300,7 @@
       </c>
       <c r="Q322" s="1"/>
     </row>
-    <row r="323" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A323" s="2">
         <v>46268</v>
       </c>
@@ -16333,7 +16347,7 @@
       </c>
       <c r="Q323" s="1"/>
     </row>
-    <row r="324" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A324" s="2">
         <v>46268</v>
       </c>
@@ -16380,7 +16394,7 @@
       </c>
       <c r="Q324" s="1"/>
     </row>
-    <row r="325" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A325" s="2">
         <v>46268</v>
       </c>
@@ -16427,7 +16441,7 @@
       </c>
       <c r="Q325" s="1"/>
     </row>
-    <row r="326" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A326" s="2">
         <v>46268</v>
       </c>
@@ -16474,7 +16488,7 @@
       </c>
       <c r="Q326" s="1"/>
     </row>
-    <row r="327" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A327" s="2">
         <v>46268</v>
       </c>
@@ -16521,7 +16535,7 @@
       </c>
       <c r="Q327" s="1"/>
     </row>
-    <row r="328" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A328" s="2">
         <v>46268</v>
       </c>
@@ -16568,7 +16582,7 @@
       </c>
       <c r="Q328" s="1"/>
     </row>
-    <row r="329" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A329" s="2">
         <v>46268</v>
       </c>
@@ -16615,7 +16629,7 @@
       </c>
       <c r="Q329" s="1"/>
     </row>
-    <row r="330" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A330" s="2">
         <v>46268</v>
       </c>
@@ -16662,7 +16676,7 @@
       </c>
       <c r="Q330" s="1"/>
     </row>
-    <row r="331" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A331" s="2">
         <v>46268</v>
       </c>
@@ -16709,7 +16723,7 @@
       </c>
       <c r="Q331" s="1"/>
     </row>
-    <row r="332" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A332" s="2">
         <v>46268</v>
       </c>
@@ -16756,7 +16770,7 @@
       </c>
       <c r="Q332" s="1"/>
     </row>
-    <row r="333" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A333" s="2">
         <v>46268</v>
       </c>
@@ -16803,7 +16817,7 @@
       </c>
       <c r="Q333" s="1"/>
     </row>
-    <row r="334" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A334" s="2">
         <v>46268</v>
       </c>
@@ -16850,7 +16864,7 @@
       </c>
       <c r="Q334" s="1"/>
     </row>
-    <row r="335" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A335" s="2">
         <v>46268</v>
       </c>
@@ -16897,7 +16911,7 @@
       </c>
       <c r="Q335" s="1"/>
     </row>
-    <row r="336" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A336" s="2">
         <v>46268</v>
       </c>
@@ -16944,7 +16958,7 @@
       </c>
       <c r="Q336" s="1"/>
     </row>
-    <row r="337" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A337" s="2">
         <v>46268</v>
       </c>
@@ -16991,7 +17005,7 @@
       </c>
       <c r="Q337" s="1"/>
     </row>
-    <row r="338" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A338" s="2">
         <v>46268</v>
       </c>
@@ -17038,7 +17052,7 @@
       </c>
       <c r="Q338" s="1"/>
     </row>
-    <row r="339" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A339" s="2">
         <v>46268</v>
       </c>
@@ -17085,7 +17099,7 @@
       </c>
       <c r="Q339" s="1"/>
     </row>
-    <row r="340" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A340" s="2">
         <v>46268</v>
       </c>
@@ -17132,7 +17146,7 @@
       </c>
       <c r="Q340" s="1"/>
     </row>
-    <row r="341" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A341" s="2">
         <v>46268</v>
       </c>
@@ -17179,7 +17193,7 @@
       </c>
       <c r="Q341" s="1"/>
     </row>
-    <row r="342" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A342" s="2">
         <v>46267</v>
       </c>
@@ -17226,7 +17240,7 @@
       </c>
       <c r="Q342" s="1"/>
     </row>
-    <row r="343" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A343" s="2">
         <v>46267</v>
       </c>
@@ -17273,7 +17287,7 @@
       </c>
       <c r="Q343" s="1"/>
     </row>
-    <row r="344" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A344" s="2">
         <v>46267</v>
       </c>
@@ -17320,7 +17334,7 @@
       </c>
       <c r="Q344" s="1"/>
     </row>
-    <row r="345" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A345" s="2">
         <v>46267</v>
       </c>
@@ -17367,7 +17381,7 @@
       </c>
       <c r="Q345" s="1"/>
     </row>
-    <row r="346" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A346" s="2">
         <v>46267</v>
       </c>
@@ -17414,7 +17428,7 @@
       </c>
       <c r="Q346" s="1"/>
     </row>
-    <row r="347" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A347" s="2">
         <v>46267</v>
       </c>
@@ -17461,7 +17475,7 @@
       </c>
       <c r="Q347" s="1"/>
     </row>
-    <row r="348" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A348" s="2">
         <v>46267</v>
       </c>
@@ -17508,7 +17522,7 @@
       </c>
       <c r="Q348" s="1"/>
     </row>
-    <row r="349" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A349" s="2">
         <v>46267</v>
       </c>
@@ -17555,7 +17569,7 @@
       </c>
       <c r="Q349" s="1"/>
     </row>
-    <row r="350" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A350" s="2">
         <v>46267</v>
       </c>
@@ -17602,7 +17616,7 @@
       </c>
       <c r="Q350" s="1"/>
     </row>
-    <row r="351" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A351" s="2">
         <v>46267</v>
       </c>
@@ -17649,7 +17663,7 @@
       </c>
       <c r="Q351" s="1"/>
     </row>
-    <row r="352" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A352" s="2">
         <v>46267</v>
       </c>
@@ -17696,7 +17710,7 @@
       </c>
       <c r="Q352" s="1"/>
     </row>
-    <row r="353" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A353" s="2">
         <v>46267</v>
       </c>
@@ -17743,7 +17757,7 @@
       </c>
       <c r="Q353" s="1"/>
     </row>
-    <row r="354" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A354" s="2">
         <v>46267</v>
       </c>
@@ -17790,7 +17804,7 @@
       </c>
       <c r="Q354" s="1"/>
     </row>
-    <row r="355" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A355" s="2">
         <v>46267</v>
       </c>
@@ -17837,7 +17851,7 @@
       </c>
       <c r="Q355" s="1"/>
     </row>
-    <row r="356" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A356" s="2">
         <v>46267</v>
       </c>
@@ -17884,7 +17898,7 @@
       </c>
       <c r="Q356" s="1"/>
     </row>
-    <row r="357" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A357" s="2">
         <v>46267</v>
       </c>
@@ -17931,7 +17945,7 @@
       </c>
       <c r="Q357" s="1"/>
     </row>
-    <row r="358" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A358" s="2">
         <v>46267</v>
       </c>
@@ -17978,7 +17992,7 @@
       </c>
       <c r="Q358" s="1"/>
     </row>
-    <row r="359" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A359" s="2">
         <v>46267</v>
       </c>
@@ -18025,7 +18039,7 @@
       </c>
       <c r="Q359" s="1"/>
     </row>
-    <row r="360" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A360" s="2">
         <v>46267</v>
       </c>
@@ -18072,7 +18086,7 @@
       </c>
       <c r="Q360" s="1"/>
     </row>
-    <row r="361" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A361" s="2">
         <v>46267</v>
       </c>
@@ -18119,7 +18133,7 @@
       </c>
       <c r="Q361" s="1"/>
     </row>
-    <row r="362" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A362" s="2">
         <v>46267</v>
       </c>
@@ -18166,7 +18180,7 @@
       </c>
       <c r="Q362" s="1"/>
     </row>
-    <row r="363" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A363" s="2">
         <v>46267</v>
       </c>
@@ -18213,7 +18227,7 @@
       </c>
       <c r="Q363" s="1"/>
     </row>
-    <row r="364" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A364" s="2">
         <v>46267</v>
       </c>
@@ -18260,7 +18274,7 @@
       </c>
       <c r="Q364" s="1"/>
     </row>
-    <row r="365" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A365" s="2">
         <v>46267</v>
       </c>
@@ -18307,7 +18321,7 @@
       </c>
       <c r="Q365" s="1"/>
     </row>
-    <row r="366" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A366" s="2">
         <v>46267</v>
       </c>
@@ -18354,7 +18368,7 @@
       </c>
       <c r="Q366" s="1"/>
     </row>
-    <row r="367" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A367" s="2">
         <v>46267</v>
       </c>
@@ -18401,7 +18415,7 @@
       </c>
       <c r="Q367" s="1"/>
     </row>
-    <row r="368" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A368" s="2">
         <v>46267</v>
       </c>
@@ -18448,7 +18462,7 @@
       </c>
       <c r="Q368" s="1"/>
     </row>
-    <row r="369" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A369" s="2">
         <v>46267</v>
       </c>
@@ -18495,7 +18509,7 @@
       </c>
       <c r="Q369" s="1"/>
     </row>
-    <row r="370" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A370" s="2">
         <v>46267</v>
       </c>
@@ -18542,7 +18556,7 @@
       </c>
       <c r="Q370" s="1"/>
     </row>
-    <row r="371" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A371" s="2">
         <v>46267</v>
       </c>
@@ -18589,7 +18603,7 @@
       </c>
       <c r="Q371" s="1"/>
     </row>
-    <row r="372" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A372" s="2">
         <v>46267</v>
       </c>
@@ -18636,7 +18650,7 @@
       </c>
       <c r="Q372" s="1"/>
     </row>
-    <row r="373" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A373" s="2">
         <v>46267</v>
       </c>
@@ -18683,7 +18697,7 @@
       </c>
       <c r="Q373" s="1"/>
     </row>
-    <row r="374" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A374" s="2">
         <v>46267</v>
       </c>
@@ -18730,7 +18744,7 @@
       </c>
       <c r="Q374" s="1"/>
     </row>
-    <row r="375" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A375" s="2">
         <v>46267</v>
       </c>
@@ -18777,7 +18791,7 @@
       </c>
       <c r="Q375" s="1"/>
     </row>
-    <row r="376" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A376" s="2">
         <v>46267</v>
       </c>
@@ -18824,7 +18838,7 @@
       </c>
       <c r="Q376" s="1"/>
     </row>
-    <row r="377" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A377" s="2">
         <v>46267</v>
       </c>
@@ -18871,7 +18885,7 @@
       </c>
       <c r="Q377" s="1"/>
     </row>
-    <row r="378" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A378" s="2">
         <v>46267</v>
       </c>
@@ -18918,7 +18932,7 @@
       </c>
       <c r="Q378" s="1"/>
     </row>
-    <row r="379" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A379" s="2">
         <v>46267</v>
       </c>
@@ -18965,7 +18979,7 @@
       </c>
       <c r="Q379" s="1"/>
     </row>
-    <row r="380" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A380" s="2">
         <v>46267</v>
       </c>
@@ -19012,7 +19026,7 @@
       </c>
       <c r="Q380" s="1"/>
     </row>
-    <row r="381" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A381" s="2">
         <v>46267</v>
       </c>
@@ -19059,7 +19073,7 @@
       </c>
       <c r="Q381" s="1"/>
     </row>
-    <row r="382" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A382" s="2">
         <v>46267</v>
       </c>
@@ -19106,7 +19120,7 @@
       </c>
       <c r="Q382" s="1"/>
     </row>
-    <row r="383" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A383" s="2">
         <v>46267</v>
       </c>
@@ -19153,7 +19167,7 @@
       </c>
       <c r="Q383" s="1"/>
     </row>
-    <row r="384" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A384" s="2">
         <v>46267</v>
       </c>
@@ -19200,7 +19214,7 @@
       </c>
       <c r="Q384" s="1"/>
     </row>
-    <row r="385" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A385" s="2">
         <v>46267</v>
       </c>
@@ -19247,7 +19261,7 @@
       </c>
       <c r="Q385" s="1"/>
     </row>
-    <row r="386" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A386" s="2">
         <v>46267</v>
       </c>
@@ -19294,7 +19308,7 @@
       </c>
       <c r="Q386" s="1"/>
     </row>
-    <row r="387" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A387" s="2">
         <v>46267</v>
       </c>
@@ -19341,7 +19355,7 @@
       </c>
       <c r="Q387" s="1"/>
     </row>
-    <row r="388" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A388" s="2">
         <v>46267</v>
       </c>
@@ -19388,7 +19402,7 @@
       </c>
       <c r="Q388" s="1"/>
     </row>
-    <row r="389" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A389" s="2">
         <v>46267</v>
       </c>
@@ -19435,7 +19449,7 @@
       </c>
       <c r="Q389" s="1"/>
     </row>
-    <row r="390" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A390" s="2">
         <v>46267</v>
       </c>
@@ -19482,7 +19496,7 @@
       </c>
       <c r="Q390" s="1"/>
     </row>
-    <row r="391" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A391" s="2">
         <v>46267</v>
       </c>
@@ -19529,7 +19543,7 @@
       </c>
       <c r="Q391" s="1"/>
     </row>
-    <row r="392" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A392" s="2">
         <v>46267</v>
       </c>
@@ -19576,7 +19590,7 @@
       </c>
       <c r="Q392" s="1"/>
     </row>
-    <row r="393" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A393" s="2">
         <v>46267</v>
       </c>
@@ -19623,7 +19637,7 @@
       </c>
       <c r="Q393" s="1"/>
     </row>
-    <row r="394" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A394" s="2">
         <v>46267</v>
       </c>
@@ -19670,7 +19684,7 @@
       </c>
       <c r="Q394" s="1"/>
     </row>
-    <row r="395" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A395" s="2">
         <v>46267</v>
       </c>
@@ -19717,7 +19731,7 @@
       </c>
       <c r="Q395" s="1"/>
     </row>
-    <row r="396" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A396" s="2">
         <v>46267</v>
       </c>
@@ -19764,7 +19778,7 @@
       </c>
       <c r="Q396" s="1"/>
     </row>
-    <row r="397" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A397" s="2">
         <v>46267</v>
       </c>
@@ -19811,7 +19825,7 @@
       </c>
       <c r="Q397" s="1"/>
     </row>
-    <row r="398" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A398" s="2">
         <v>46267</v>
       </c>
@@ -19858,7 +19872,7 @@
       </c>
       <c r="Q398" s="1"/>
     </row>
-    <row r="399" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A399" s="2">
         <v>46267</v>
       </c>
@@ -19905,7 +19919,7 @@
       </c>
       <c r="Q399" s="1"/>
     </row>
-    <row r="400" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A400" s="2">
         <v>46267</v>
       </c>
@@ -19952,7 +19966,7 @@
       </c>
       <c r="Q400" s="1"/>
     </row>
-    <row r="401" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A401" s="2">
         <v>46267</v>
       </c>
@@ -19999,7 +20013,7 @@
       </c>
       <c r="Q401" s="1"/>
     </row>
-    <row r="402" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A402" s="2">
         <v>46267</v>
       </c>
@@ -20046,7 +20060,7 @@
       </c>
       <c r="Q402" s="1"/>
     </row>
-    <row r="403" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A403" s="2">
         <v>46267</v>
       </c>
@@ -20093,7 +20107,7 @@
       </c>
       <c r="Q403" s="1"/>
     </row>
-    <row r="404" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A404" s="2">
         <v>46267</v>
       </c>
@@ -20140,7 +20154,7 @@
       </c>
       <c r="Q404" s="1"/>
     </row>
-    <row r="405" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A405" s="2">
         <v>46267</v>
       </c>
@@ -20187,7 +20201,7 @@
       </c>
       <c r="Q405" s="1"/>
     </row>
-    <row r="406" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A406" s="2">
         <v>46267</v>
       </c>
@@ -20234,7 +20248,7 @@
       </c>
       <c r="Q406" s="1"/>
     </row>
-    <row r="407" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A407" s="2">
         <v>46267</v>
       </c>
@@ -20281,7 +20295,7 @@
       </c>
       <c r="Q407" s="1"/>
     </row>
-    <row r="408" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A408" s="2">
         <v>46267</v>
       </c>
@@ -20328,7 +20342,7 @@
       </c>
       <c r="Q408" s="1"/>
     </row>
-    <row r="409" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A409" s="2">
         <v>46267</v>
       </c>
@@ -20375,7 +20389,7 @@
       </c>
       <c r="Q409" s="1"/>
     </row>
-    <row r="410" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A410" s="2">
         <v>46267</v>
       </c>
@@ -20422,7 +20436,7 @@
       </c>
       <c r="Q410" s="1"/>
     </row>
-    <row r="411" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A411" s="2">
         <v>46267</v>
       </c>
@@ -20469,7 +20483,7 @@
       </c>
       <c r="Q411" s="1"/>
     </row>
-    <row r="412" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A412" s="2">
         <v>46267</v>
       </c>
@@ -20516,7 +20530,7 @@
       </c>
       <c r="Q412" s="1"/>
     </row>
-    <row r="413" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A413" s="2">
         <v>46267</v>
       </c>
@@ -20563,7 +20577,7 @@
       </c>
       <c r="Q413" s="1"/>
     </row>
-    <row r="414" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A414" s="2">
         <v>46267</v>
       </c>
@@ -20610,7 +20624,7 @@
       </c>
       <c r="Q414" s="1"/>
     </row>
-    <row r="415" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A415" s="2">
         <v>46267</v>
       </c>
@@ -20657,7 +20671,7 @@
       </c>
       <c r="Q415" s="1"/>
     </row>
-    <row r="416" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A416" s="2">
         <v>46267</v>
       </c>
@@ -20704,7 +20718,7 @@
       </c>
       <c r="Q416" s="1"/>
     </row>
-    <row r="417" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A417" s="2">
         <v>46267</v>
       </c>
@@ -20751,7 +20765,7 @@
       </c>
       <c r="Q417" s="1"/>
     </row>
-    <row r="418" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A418" s="2">
         <v>46267</v>
       </c>
@@ -20798,7 +20812,7 @@
       </c>
       <c r="Q418" s="1"/>
     </row>
-    <row r="419" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A419" s="2">
         <v>46267</v>
       </c>
@@ -20845,7 +20859,7 @@
       </c>
       <c r="Q419" s="1"/>
     </row>
-    <row r="420" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A420" s="2">
         <v>46267</v>
       </c>
@@ -20892,7 +20906,7 @@
       </c>
       <c r="Q420" s="1"/>
     </row>
-    <row r="421" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A421" s="2">
         <v>46267</v>
       </c>
@@ -20939,7 +20953,7 @@
       </c>
       <c r="Q421" s="1"/>
     </row>
-    <row r="422" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A422" s="2">
         <v>46267</v>
       </c>
@@ -20986,7 +21000,7 @@
       </c>
       <c r="Q422" s="1"/>
     </row>
-    <row r="423" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A423" s="2">
         <v>46267</v>
       </c>
@@ -21033,7 +21047,7 @@
       </c>
       <c r="Q423" s="1"/>
     </row>
-    <row r="424" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A424" s="2">
         <v>46267</v>
       </c>
@@ -21080,7 +21094,7 @@
       </c>
       <c r="Q424" s="1"/>
     </row>
-    <row r="425" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A425" s="2">
         <v>46267</v>
       </c>
@@ -21127,7 +21141,7 @@
       </c>
       <c r="Q425" s="1"/>
     </row>
-    <row r="426" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A426" s="2">
         <v>46267</v>
       </c>
@@ -21174,7 +21188,7 @@
       </c>
       <c r="Q426" s="1"/>
     </row>
-    <row r="427" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A427" s="2">
         <v>46267</v>
       </c>
@@ -21223,7 +21237,7 @@
     </row>
     <row r="428" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A428" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B428" s="1">
         <v>0</v>
@@ -21268,7 +21282,7 @@
       </c>
       <c r="Q428" s="1"/>
     </row>
-    <row r="429" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A429" s="2">
         <v>46267</v>
       </c>
@@ -21315,7 +21329,7 @@
       </c>
       <c r="Q429" s="1"/>
     </row>
-    <row r="430" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A430" s="2">
         <v>46267</v>
       </c>
@@ -21362,7 +21376,7 @@
       </c>
       <c r="Q430" s="1"/>
     </row>
-    <row r="431" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A431" s="2">
         <v>46267</v>
       </c>
@@ -21409,7 +21423,7 @@
       </c>
       <c r="Q431" s="1"/>
     </row>
-    <row r="432" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A432" s="2">
         <v>46267</v>
       </c>
@@ -21456,7 +21470,7 @@
       </c>
       <c r="Q432" s="1"/>
     </row>
-    <row r="433" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A433" s="2">
         <v>46267</v>
       </c>
@@ -21503,7 +21517,7 @@
       </c>
       <c r="Q433" s="1"/>
     </row>
-    <row r="434" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A434" s="2">
         <v>46267</v>
       </c>
@@ -21550,7 +21564,7 @@
       </c>
       <c r="Q434" s="1"/>
     </row>
-    <row r="435" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A435" s="2">
         <v>46267</v>
       </c>
@@ -21597,7 +21611,7 @@
       </c>
       <c r="Q435" s="1"/>
     </row>
-    <row r="436" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A436" s="2">
         <v>46267</v>
       </c>
@@ -21644,7 +21658,7 @@
       </c>
       <c r="Q436" s="1"/>
     </row>
-    <row r="437" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A437" s="2">
         <v>46267</v>
       </c>
@@ -21691,7 +21705,7 @@
       </c>
       <c r="Q437" s="1"/>
     </row>
-    <row r="438" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A438" s="2">
         <v>46267</v>
       </c>
@@ -21738,7 +21752,7 @@
       </c>
       <c r="Q438" s="1"/>
     </row>
-    <row r="439" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A439" s="2">
         <v>46267</v>
       </c>
@@ -21785,7 +21799,7 @@
       </c>
       <c r="Q439" s="1"/>
     </row>
-    <row r="440" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A440" s="2">
         <v>46267</v>
       </c>
@@ -21832,7 +21846,7 @@
       </c>
       <c r="Q440" s="1"/>
     </row>
-    <row r="441" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A441" s="2">
         <v>46267</v>
       </c>
@@ -21879,7 +21893,7 @@
       </c>
       <c r="Q441" s="1"/>
     </row>
-    <row r="442" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A442" s="2">
         <v>46267</v>
       </c>
@@ -21926,7 +21940,7 @@
       </c>
       <c r="Q442" s="1"/>
     </row>
-    <row r="443" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A443" s="2">
         <v>46267</v>
       </c>
@@ -21973,7 +21987,7 @@
       </c>
       <c r="Q443" s="1"/>
     </row>
-    <row r="444" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A444" s="2">
         <v>46267</v>
       </c>
@@ -22020,9 +22034,9 @@
       </c>
       <c r="Q444" s="1"/>
     </row>
-    <row r="445" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A445" s="2">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B445" s="1">
         <v>0</v>
@@ -22067,7 +22081,7 @@
       </c>
       <c r="Q445" s="1"/>
     </row>
-    <row r="446" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A446" s="2">
         <v>46267</v>
       </c>
@@ -22114,7 +22128,7 @@
       </c>
       <c r="Q446" s="1"/>
     </row>
-    <row r="447" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A447" s="2">
         <v>46267</v>
       </c>
@@ -22161,7 +22175,7 @@
       </c>
       <c r="Q447" s="1"/>
     </row>
-    <row r="448" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A448" s="2">
         <v>46267</v>
       </c>
@@ -22208,7 +22222,7 @@
       </c>
       <c r="Q448" s="1"/>
     </row>
-    <row r="449" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A449" s="2">
         <v>46267</v>
       </c>
@@ -22255,7 +22269,7 @@
       </c>
       <c r="Q449" s="1"/>
     </row>
-    <row r="450" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A450" s="2">
         <v>46267</v>
       </c>
@@ -22302,7 +22316,7 @@
       </c>
       <c r="Q450" s="1"/>
     </row>
-    <row r="451" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A451" s="2">
         <v>46267</v>
       </c>
@@ -22349,7 +22363,7 @@
       </c>
       <c r="Q451" s="1"/>
     </row>
-    <row r="452" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A452" s="2">
         <v>46267</v>
       </c>
@@ -22396,7 +22410,7 @@
       </c>
       <c r="Q452" s="1"/>
     </row>
-    <row r="453" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A453" s="2">
         <v>46267</v>
       </c>
@@ -22443,7 +22457,7 @@
       </c>
       <c r="Q453" s="1"/>
     </row>
-    <row r="454" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A454" s="2">
         <v>46267</v>
       </c>
@@ -22490,9 +22504,9 @@
       </c>
       <c r="Q454" s="1"/>
     </row>
-    <row r="455" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A455" s="2">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="B455" s="1">
         <v>0</v>
@@ -22537,7 +22551,7 @@
       </c>
       <c r="Q455" s="1"/>
     </row>
-    <row r="456" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A456" s="2">
         <v>46267</v>
       </c>
@@ -22584,7 +22598,7 @@
       </c>
       <c r="Q456" s="1"/>
     </row>
-    <row r="457" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A457" s="2">
         <v>46267</v>
       </c>
@@ -22631,7 +22645,7 @@
       </c>
       <c r="Q457" s="1"/>
     </row>
-    <row r="458" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A458" s="2">
         <v>46267</v>
       </c>
@@ -22678,7 +22692,7 @@
       </c>
       <c r="Q458" s="1"/>
     </row>
-    <row r="459" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A459" s="2">
         <v>46266</v>
       </c>
@@ -22725,7 +22739,7 @@
       </c>
       <c r="Q459" s="1"/>
     </row>
-    <row r="460" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A460" s="2">
         <v>46266</v>
       </c>
@@ -22772,7 +22786,7 @@
       </c>
       <c r="Q460" s="1"/>
     </row>
-    <row r="461" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A461" s="2">
         <v>46266</v>
       </c>
@@ -22819,7 +22833,7 @@
       </c>
       <c r="Q461" s="1"/>
     </row>
-    <row r="462" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A462" s="2">
         <v>46266</v>
       </c>
@@ -22866,7 +22880,7 @@
       </c>
       <c r="Q462" s="1"/>
     </row>
-    <row r="463" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A463" s="2">
         <v>46266</v>
       </c>
@@ -22913,7 +22927,7 @@
       </c>
       <c r="Q463" s="1"/>
     </row>
-    <row r="464" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A464" s="2">
         <v>46266</v>
       </c>
@@ -22960,7 +22974,7 @@
       </c>
       <c r="Q464" s="1"/>
     </row>
-    <row r="465" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A465" s="2">
         <v>46266</v>
       </c>
@@ -23007,7 +23021,7 @@
       </c>
       <c r="Q465" s="1"/>
     </row>
-    <row r="466" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A466" s="2">
         <v>46266</v>
       </c>
@@ -23054,7 +23068,7 @@
       </c>
       <c r="Q466" s="1"/>
     </row>
-    <row r="467" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A467" s="2">
         <v>46266</v>
       </c>
@@ -23101,7 +23115,7 @@
       </c>
       <c r="Q467" s="1"/>
     </row>
-    <row r="468" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A468" s="2">
         <v>46266</v>
       </c>
@@ -23148,7 +23162,7 @@
       </c>
       <c r="Q468" s="1"/>
     </row>
-    <row r="469" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A469" s="2">
         <v>46266</v>
       </c>
@@ -23195,7 +23209,7 @@
       </c>
       <c r="Q469" s="1"/>
     </row>
-    <row r="470" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A470" s="2">
         <v>46266</v>
       </c>
@@ -23242,7 +23256,7 @@
       </c>
       <c r="Q470" s="1"/>
     </row>
-    <row r="471" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A471" s="2">
         <v>46266</v>
       </c>
@@ -23289,7 +23303,7 @@
       </c>
       <c r="Q471" s="1"/>
     </row>
-    <row r="472" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A472" s="2">
         <v>46266</v>
       </c>
@@ -23336,7 +23350,7 @@
       </c>
       <c r="Q472" s="1"/>
     </row>
-    <row r="473" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A473" s="2">
         <v>46266</v>
       </c>
@@ -23383,7 +23397,7 @@
       </c>
       <c r="Q473" s="1"/>
     </row>
-    <row r="474" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A474" s="2">
         <v>46266</v>
       </c>
@@ -23430,7 +23444,7 @@
       </c>
       <c r="Q474" s="1"/>
     </row>
-    <row r="475" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A475" s="2">
         <v>46266</v>
       </c>
@@ -23477,7 +23491,7 @@
       </c>
       <c r="Q475" s="1"/>
     </row>
-    <row r="476" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A476" s="2">
         <v>46266</v>
       </c>
@@ -23524,7 +23538,7 @@
       </c>
       <c r="Q476" s="1"/>
     </row>
-    <row r="477" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A477" s="2">
         <v>46266</v>
       </c>
@@ -23571,7 +23585,7 @@
       </c>
       <c r="Q477" s="1"/>
     </row>
-    <row r="478" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A478" s="2">
         <v>46266</v>
       </c>
@@ -23618,7 +23632,7 @@
       </c>
       <c r="Q478" s="1"/>
     </row>
-    <row r="479" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A479" s="2">
         <v>46266</v>
       </c>
@@ -23665,7 +23679,7 @@
       </c>
       <c r="Q479" s="1"/>
     </row>
-    <row r="480" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A480" s="2">
         <v>46266</v>
       </c>
@@ -23712,7 +23726,7 @@
       </c>
       <c r="Q480" s="1"/>
     </row>
-    <row r="481" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A481" s="2">
         <v>46266</v>
       </c>
@@ -23759,7 +23773,7 @@
       </c>
       <c r="Q481" s="1"/>
     </row>
-    <row r="482" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A482" s="2">
         <v>46266</v>
       </c>
@@ -23806,7 +23820,7 @@
       </c>
       <c r="Q482" s="1"/>
     </row>
-    <row r="483" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A483" s="2">
         <v>46266</v>
       </c>
@@ -23853,7 +23867,7 @@
       </c>
       <c r="Q483" s="1"/>
     </row>
-    <row r="484" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A484" s="2">
         <v>46266</v>
       </c>
@@ -23900,7 +23914,7 @@
       </c>
       <c r="Q484" s="1"/>
     </row>
-    <row r="485" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A485" s="2">
         <v>46266</v>
       </c>
@@ -23947,7 +23961,7 @@
       </c>
       <c r="Q485" s="1"/>
     </row>
-    <row r="486" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A486" s="2">
         <v>46266</v>
       </c>
@@ -23994,7 +24008,7 @@
       </c>
       <c r="Q486" s="1"/>
     </row>
-    <row r="487" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A487" s="2">
         <v>46266</v>
       </c>
@@ -24041,7 +24055,7 @@
       </c>
       <c r="Q487" s="1"/>
     </row>
-    <row r="488" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A488" s="2">
         <v>46266</v>
       </c>
@@ -24088,7 +24102,7 @@
       </c>
       <c r="Q488" s="1"/>
     </row>
-    <row r="489" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A489" s="2">
         <v>46266</v>
       </c>
@@ -24135,7 +24149,7 @@
       </c>
       <c r="Q489" s="1"/>
     </row>
-    <row r="490" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A490" s="2">
         <v>46266</v>
       </c>
@@ -24182,7 +24196,7 @@
       </c>
       <c r="Q490" s="1"/>
     </row>
-    <row r="491" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A491" s="2">
         <v>46266</v>
       </c>
@@ -24229,7 +24243,7 @@
       </c>
       <c r="Q491" s="1"/>
     </row>
-    <row r="492" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A492" s="2">
         <v>46266</v>
       </c>
@@ -24276,7 +24290,7 @@
       </c>
       <c r="Q492" s="1"/>
     </row>
-    <row r="493" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A493" s="2">
         <v>46266</v>
       </c>
@@ -24323,7 +24337,7 @@
       </c>
       <c r="Q493" s="1"/>
     </row>
-    <row r="494" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A494" s="2">
         <v>46266</v>
       </c>
@@ -24370,7 +24384,7 @@
       </c>
       <c r="Q494" s="1"/>
     </row>
-    <row r="495" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A495" s="2">
         <v>46266</v>
       </c>
@@ -24417,7 +24431,7 @@
       </c>
       <c r="Q495" s="1"/>
     </row>
-    <row r="496" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A496" s="2">
         <v>46266</v>
       </c>
@@ -24464,7 +24478,7 @@
       </c>
       <c r="Q496" s="1"/>
     </row>
-    <row r="497" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A497" s="2">
         <v>46266</v>
       </c>
@@ -24511,7 +24525,7 @@
       </c>
       <c r="Q497" s="1"/>
     </row>
-    <row r="498" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A498" s="2">
         <v>46266</v>
       </c>
@@ -24558,7 +24572,7 @@
       </c>
       <c r="Q498" s="1"/>
     </row>
-    <row r="499" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A499" s="2">
         <v>46266</v>
       </c>
@@ -24605,7 +24619,7 @@
       </c>
       <c r="Q499" s="1"/>
     </row>
-    <row r="500" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A500" s="2">
         <v>46266</v>
       </c>
@@ -24652,7 +24666,7 @@
       </c>
       <c r="Q500" s="1"/>
     </row>
-    <row r="501" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A501" s="2">
         <v>46266</v>
       </c>
@@ -24699,7 +24713,7 @@
       </c>
       <c r="Q501" s="1"/>
     </row>
-    <row r="502" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A502" s="2">
         <v>46266</v>
       </c>
@@ -24746,7 +24760,7 @@
       </c>
       <c r="Q502" s="1"/>
     </row>
-    <row r="503" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A503" s="2">
         <v>46266</v>
       </c>
@@ -24793,7 +24807,7 @@
       </c>
       <c r="Q503" s="1"/>
     </row>
-    <row r="504" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A504" s="2">
         <v>46266</v>
       </c>
@@ -24840,7 +24854,7 @@
       </c>
       <c r="Q504" s="1"/>
     </row>
-    <row r="505" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A505" s="2">
         <v>46266</v>
       </c>
@@ -24887,7 +24901,7 @@
       </c>
       <c r="Q505" s="1"/>
     </row>
-    <row r="506" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A506" s="2">
         <v>46266</v>
       </c>
@@ -24934,7 +24948,7 @@
       </c>
       <c r="Q506" s="1"/>
     </row>
-    <row r="507" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A507" s="2">
         <v>46266</v>
       </c>
@@ -24981,7 +24995,7 @@
       </c>
       <c r="Q507" s="1"/>
     </row>
-    <row r="508" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A508" s="2">
         <v>46266</v>
       </c>
@@ -25028,7 +25042,7 @@
       </c>
       <c r="Q508" s="1"/>
     </row>
-    <row r="509" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A509" s="2">
         <v>46266</v>
       </c>
@@ -25075,7 +25089,7 @@
       </c>
       <c r="Q509" s="1"/>
     </row>
-    <row r="510" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A510" s="2">
         <v>46266</v>
       </c>
@@ -25122,7 +25136,7 @@
       </c>
       <c r="Q510" s="1"/>
     </row>
-    <row r="511" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A511" s="2">
         <v>46266</v>
       </c>
@@ -25169,7 +25183,7 @@
       </c>
       <c r="Q511" s="1"/>
     </row>
-    <row r="512" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A512" s="2">
         <v>46266</v>
       </c>
@@ -25216,7 +25230,7 @@
       </c>
       <c r="Q512" s="1"/>
     </row>
-    <row r="513" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A513" s="2">
         <v>46266</v>
       </c>
@@ -25263,7 +25277,7 @@
       </c>
       <c r="Q513" s="1"/>
     </row>
-    <row r="514" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A514" s="2">
         <v>46266</v>
       </c>
@@ -25310,7 +25324,7 @@
       </c>
       <c r="Q514" s="1"/>
     </row>
-    <row r="515" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A515" s="2">
         <v>46266</v>
       </c>
@@ -25357,7 +25371,7 @@
       </c>
       <c r="Q515" s="1"/>
     </row>
-    <row r="516" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A516" s="2">
         <v>46266</v>
       </c>
@@ -25404,7 +25418,7 @@
       </c>
       <c r="Q516" s="1"/>
     </row>
-    <row r="517" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A517" s="2">
         <v>46266</v>
       </c>
@@ -25451,7 +25465,7 @@
       </c>
       <c r="Q517" s="1"/>
     </row>
-    <row r="518" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A518" s="2">
         <v>46266</v>
       </c>
@@ -25498,7 +25512,7 @@
       </c>
       <c r="Q518" s="1"/>
     </row>
-    <row r="519" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A519" s="2">
         <v>46266</v>
       </c>
@@ -25545,7 +25559,7 @@
       </c>
       <c r="Q519" s="1"/>
     </row>
-    <row r="520" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A520" s="2">
         <v>46266</v>
       </c>
@@ -25592,7 +25606,7 @@
       </c>
       <c r="Q520" s="1"/>
     </row>
-    <row r="521" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A521" s="2">
         <v>46266</v>
       </c>
@@ -25639,7 +25653,7 @@
       </c>
       <c r="Q521" s="1"/>
     </row>
-    <row r="522" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A522" s="2">
         <v>46266</v>
       </c>
@@ -25686,7 +25700,7 @@
       </c>
       <c r="Q522" s="1"/>
     </row>
-    <row r="523" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A523" s="2">
         <v>46266</v>
       </c>
@@ -25733,7 +25747,7 @@
       </c>
       <c r="Q523" s="1"/>
     </row>
-    <row r="524" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A524" s="2">
         <v>46266</v>
       </c>
@@ -25780,7 +25794,7 @@
       </c>
       <c r="Q524" s="1"/>
     </row>
-    <row r="525" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A525" s="2">
         <v>46266</v>
       </c>
@@ -25827,7 +25841,7 @@
       </c>
       <c r="Q525" s="1"/>
     </row>
-    <row r="526" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A526" s="2">
         <v>46266</v>
       </c>
@@ -25874,7 +25888,7 @@
       </c>
       <c r="Q526" s="1"/>
     </row>
-    <row r="527" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A527" s="2">
         <v>46266</v>
       </c>
@@ -25921,7 +25935,7 @@
       </c>
       <c r="Q527" s="1"/>
     </row>
-    <row r="528" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A528" s="2">
         <v>46266</v>
       </c>
@@ -25968,7 +25982,7 @@
       </c>
       <c r="Q528" s="1"/>
     </row>
-    <row r="529" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A529" s="2">
         <v>46266</v>
       </c>
@@ -26015,7 +26029,7 @@
       </c>
       <c r="Q529" s="1"/>
     </row>
-    <row r="530" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A530" s="2">
         <v>46266</v>
       </c>
@@ -26062,7 +26076,7 @@
       </c>
       <c r="Q530" s="1"/>
     </row>
-    <row r="531" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A531" s="2">
         <v>46266</v>
       </c>
@@ -26109,7 +26123,7 @@
       </c>
       <c r="Q531" s="1"/>
     </row>
-    <row r="532" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A532" s="2">
         <v>46266</v>
       </c>
@@ -26156,7 +26170,7 @@
       </c>
       <c r="Q532" s="1"/>
     </row>
-    <row r="533" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A533" s="2">
         <v>46266</v>
       </c>
@@ -26203,7 +26217,7 @@
       </c>
       <c r="Q533" s="1"/>
     </row>
-    <row r="534" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A534" s="2">
         <v>46266</v>
       </c>
@@ -26250,7 +26264,7 @@
       </c>
       <c r="Q534" s="1"/>
     </row>
-    <row r="535" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A535" s="2">
         <v>46266</v>
       </c>
@@ -26297,7 +26311,7 @@
       </c>
       <c r="Q535" s="1"/>
     </row>
-    <row r="536" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A536" s="2">
         <v>46266</v>
       </c>
@@ -26344,7 +26358,7 @@
       </c>
       <c r="Q536" s="1"/>
     </row>
-    <row r="537" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A537" s="2">
         <v>46266</v>
       </c>
@@ -26391,7 +26405,7 @@
       </c>
       <c r="Q537" s="1"/>
     </row>
-    <row r="538" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A538" s="2">
         <v>46266</v>
       </c>
@@ -26438,7 +26452,7 @@
       </c>
       <c r="Q538" s="1"/>
     </row>
-    <row r="539" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A539" s="2">
         <v>46266</v>
       </c>
@@ -26485,7 +26499,7 @@
       </c>
       <c r="Q539" s="1"/>
     </row>
-    <row r="540" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A540" s="2">
         <v>46266</v>
       </c>
@@ -26532,7 +26546,7 @@
       </c>
       <c r="Q540" s="1"/>
     </row>
-    <row r="541" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A541" s="2">
         <v>46266</v>
       </c>
@@ -26579,7 +26593,7 @@
       </c>
       <c r="Q541" s="1"/>
     </row>
-    <row r="542" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A542" s="2">
         <v>46266</v>
       </c>
@@ -26626,7 +26640,7 @@
       </c>
       <c r="Q542" s="1"/>
     </row>
-    <row r="543" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A543" s="2">
         <v>46266</v>
       </c>
@@ -26673,7 +26687,7 @@
       </c>
       <c r="Q543" s="1"/>
     </row>
-    <row r="544" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="544" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A544" s="2">
         <v>46266</v>
       </c>
@@ -26720,7 +26734,7 @@
       </c>
       <c r="Q544" s="1"/>
     </row>
-    <row r="545" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A545" s="2">
         <v>46266</v>
       </c>
@@ -26767,7 +26781,7 @@
       </c>
       <c r="Q545" s="1"/>
     </row>
-    <row r="546" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A546" s="2">
         <v>46266</v>
       </c>
@@ -26814,7 +26828,7 @@
       </c>
       <c r="Q546" s="1"/>
     </row>
-    <row r="547" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A547" s="2">
         <v>46266</v>
       </c>
@@ -26861,7 +26875,7 @@
       </c>
       <c r="Q547" s="1"/>
     </row>
-    <row r="548" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A548" s="2">
         <v>46266</v>
       </c>
@@ -26908,7 +26922,7 @@
       </c>
       <c r="Q548" s="1"/>
     </row>
-    <row r="549" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A549" s="2">
         <v>46266</v>
       </c>
@@ -26955,7 +26969,7 @@
       </c>
       <c r="Q549" s="1"/>
     </row>
-    <row r="550" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A550" s="2">
         <v>46266</v>
       </c>
@@ -27002,7 +27016,7 @@
       </c>
       <c r="Q550" s="1"/>
     </row>
-    <row r="551" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A551" s="2">
         <v>46266</v>
       </c>
@@ -27049,7 +27063,7 @@
       </c>
       <c r="Q551" s="1"/>
     </row>
-    <row r="552" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A552" s="2">
         <v>46266</v>
       </c>
@@ -27098,7 +27112,7 @@
     </row>
     <row r="553" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A553" s="2">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B553" s="1">
         <v>0</v>
@@ -27143,7 +27157,7 @@
       </c>
       <c r="Q553" s="1"/>
     </row>
-    <row r="554" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A554" s="2">
         <v>46266</v>
       </c>
@@ -27190,7 +27204,7 @@
       </c>
       <c r="Q554" s="1"/>
     </row>
-    <row r="555" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="555" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A555" s="2">
         <v>46266</v>
       </c>
@@ -27237,7 +27251,7 @@
       </c>
       <c r="Q555" s="1"/>
     </row>
-    <row r="556" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A556" s="2">
         <v>46266</v>
       </c>
@@ -27284,7 +27298,7 @@
       </c>
       <c r="Q556" s="1"/>
     </row>
-    <row r="557" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A557" s="2">
         <v>46266</v>
       </c>
@@ -27331,7 +27345,7 @@
       </c>
       <c r="Q557" s="1"/>
     </row>
-    <row r="558" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="558" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A558" s="2">
         <v>46266</v>
       </c>
@@ -27378,7 +27392,7 @@
       </c>
       <c r="Q558" s="1"/>
     </row>
-    <row r="559" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A559" s="2">
         <v>46266</v>
       </c>
@@ -27425,9 +27439,9 @@
       </c>
       <c r="Q559" s="1"/>
     </row>
-    <row r="560" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A560" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B560" s="1">
         <v>0</v>
@@ -27472,9 +27486,9 @@
       </c>
       <c r="Q560" s="1"/>
     </row>
-    <row r="561" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A561" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B561" s="1">
         <v>0</v>
@@ -27519,9 +27533,9 @@
       </c>
       <c r="Q561" s="1"/>
     </row>
-    <row r="562" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A562" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B562" s="1">
         <v>0</v>
@@ -27566,9 +27580,9 @@
       </c>
       <c r="Q562" s="1"/>
     </row>
-    <row r="563" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A563" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B563" s="1">
         <v>0</v>
@@ -27613,9 +27627,9 @@
       </c>
       <c r="Q563" s="1"/>
     </row>
-    <row r="564" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A564" s="2">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B564" s="1">
         <v>0</v>
@@ -27660,9 +27674,9 @@
       </c>
       <c r="Q564" s="1"/>
     </row>
-    <row r="565" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A565" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B565" s="1">
         <v>0</v>
@@ -27707,7 +27721,7 @@
       </c>
       <c r="Q565" s="1"/>
     </row>
-    <row r="566" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="566" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A566" s="2">
         <v>46266</v>
       </c>
@@ -27754,7 +27768,7 @@
       </c>
       <c r="Q566" s="1"/>
     </row>
-    <row r="567" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A567" s="2">
         <v>46266</v>
       </c>
@@ -27801,7 +27815,7 @@
       </c>
       <c r="Q567" s="1"/>
     </row>
-    <row r="568" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="568" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A568" s="2">
         <v>46266</v>
       </c>
@@ -27848,7 +27862,7 @@
       </c>
       <c r="Q568" s="1"/>
     </row>
-    <row r="569" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="569" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A569" s="2">
         <v>46266</v>
       </c>
@@ -27895,7 +27909,7 @@
       </c>
       <c r="Q569" s="1"/>
     </row>
-    <row r="570" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="570" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A570" s="2">
         <v>46266</v>
       </c>
@@ -27942,7 +27956,7 @@
       </c>
       <c r="Q570" s="1"/>
     </row>
-    <row r="571" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A571" s="2">
         <v>46266</v>
       </c>
@@ -27989,7 +28003,7 @@
       </c>
       <c r="Q571" s="1"/>
     </row>
-    <row r="572" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A572" s="2">
         <v>46266</v>
       </c>
@@ -28036,7 +28050,7 @@
       </c>
       <c r="Q572" s="1"/>
     </row>
-    <row r="573" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="573" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A573" s="2">
         <v>46266</v>
       </c>
@@ -28083,7 +28097,7 @@
       </c>
       <c r="Q573" s="1"/>
     </row>
-    <row r="574" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A574" s="2">
         <v>46266</v>
       </c>
@@ -28130,7 +28144,7 @@
       </c>
       <c r="Q574" s="1"/>
     </row>
-    <row r="575" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A575" s="2">
         <v>46266</v>
       </c>
@@ -28177,9 +28191,9 @@
       </c>
       <c r="Q575" s="1"/>
     </row>
-    <row r="576" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A576" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B576" s="1">
         <v>0</v>
@@ -28224,9 +28238,9 @@
       </c>
       <c r="Q576" s="1"/>
     </row>
-    <row r="577" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A577" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B577" s="1">
         <v>0</v>
@@ -28271,9 +28285,9 @@
       </c>
       <c r="Q577" s="1"/>
     </row>
-    <row r="578" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="578" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A578" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B578" s="1">
         <v>0</v>
@@ -28318,7 +28332,7 @@
       </c>
       <c r="Q578" s="1"/>
     </row>
-    <row r="579" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="579" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A579" s="2">
         <v>46266</v>
       </c>
@@ -28365,7 +28379,7 @@
       </c>
       <c r="Q579" s="1"/>
     </row>
-    <row r="580" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="580" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A580" s="2">
         <v>46266</v>
       </c>
@@ -28412,7 +28426,7 @@
       </c>
       <c r="Q580" s="1"/>
     </row>
-    <row r="581" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A581" s="2">
         <v>46266</v>
       </c>
@@ -28459,7 +28473,7 @@
       </c>
       <c r="Q581" s="1"/>
     </row>
-    <row r="582" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A582" s="2">
         <v>46266</v>
       </c>
@@ -28506,7 +28520,7 @@
       </c>
       <c r="Q582" s="1"/>
     </row>
-    <row r="583" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="583" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A583" s="2">
         <v>46266</v>
       </c>
@@ -28553,9 +28567,9 @@
       </c>
       <c r="Q583" s="1"/>
     </row>
-    <row r="584" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="584" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A584" s="2">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B584" s="1">
         <v>0</v>
@@ -28600,7 +28614,7 @@
       </c>
       <c r="Q584" s="1"/>
     </row>
-    <row r="585" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A585" s="2">
         <v>46266</v>
       </c>
@@ -28647,7 +28661,7 @@
       </c>
       <c r="Q585" s="1"/>
     </row>
-    <row r="586" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A586" s="2">
         <v>46265</v>
       </c>
@@ -28694,7 +28708,7 @@
       </c>
       <c r="Q586" s="1"/>
     </row>
-    <row r="587" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A587" s="2">
         <v>46265</v>
       </c>
@@ -28741,7 +28755,7 @@
       </c>
       <c r="Q587" s="1"/>
     </row>
-    <row r="588" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A588" s="2">
         <v>46265</v>
       </c>
@@ -28788,7 +28802,7 @@
       </c>
       <c r="Q588" s="1"/>
     </row>
-    <row r="589" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A589" s="2">
         <v>46265</v>
       </c>
@@ -28835,7 +28849,7 @@
       </c>
       <c r="Q589" s="1"/>
     </row>
-    <row r="590" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A590" s="2">
         <v>46265</v>
       </c>
@@ -28882,7 +28896,7 @@
       </c>
       <c r="Q590" s="1"/>
     </row>
-    <row r="591" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="591" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A591" s="2">
         <v>46265</v>
       </c>
@@ -28929,7 +28943,7 @@
       </c>
       <c r="Q591" s="1"/>
     </row>
-    <row r="592" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="592" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A592" s="2">
         <v>46265</v>
       </c>
@@ -28976,7 +28990,7 @@
       </c>
       <c r="Q592" s="1"/>
     </row>
-    <row r="593" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="593" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A593" s="2">
         <v>46265</v>
       </c>
@@ -29023,7 +29037,7 @@
       </c>
       <c r="Q593" s="1"/>
     </row>
-    <row r="594" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="594" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A594" s="2">
         <v>46265</v>
       </c>
@@ -29070,7 +29084,7 @@
       </c>
       <c r="Q594" s="1"/>
     </row>
-    <row r="595" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="595" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A595" s="2">
         <v>46265</v>
       </c>
@@ -29117,7 +29131,7 @@
       </c>
       <c r="Q595" s="1"/>
     </row>
-    <row r="596" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="596" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A596" s="2">
         <v>46265</v>
       </c>
@@ -29164,7 +29178,7 @@
       </c>
       <c r="Q596" s="1"/>
     </row>
-    <row r="597" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="597" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A597" s="2">
         <v>46265</v>
       </c>
@@ -29211,7 +29225,7 @@
       </c>
       <c r="Q597" s="1"/>
     </row>
-    <row r="598" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A598" s="2">
         <v>46265</v>
       </c>
@@ -29258,9 +29272,9 @@
       </c>
       <c r="Q598" s="1"/>
     </row>
-    <row r="599" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A599" s="2">
-        <v>46265</v>
+        <v>46235</v>
       </c>
       <c r="B599" s="1">
         <v>0</v>
@@ -29305,9 +29319,9 @@
       </c>
       <c r="Q599" s="1"/>
     </row>
-    <row r="600" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A600" s="2">
-        <v>46265</v>
+        <v>46235</v>
       </c>
       <c r="B600" s="1">
         <v>0</v>
@@ -29352,7 +29366,7 @@
       </c>
       <c r="Q600" s="1"/>
     </row>
-    <row r="601" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="601" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A601" s="2">
         <v>46265</v>
       </c>
@@ -29399,7 +29413,7 @@
       </c>
       <c r="Q601" s="1"/>
     </row>
-    <row r="602" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A602" s="2">
         <v>46265</v>
       </c>
@@ -29446,7 +29460,7 @@
       </c>
       <c r="Q602" s="1"/>
     </row>
-    <row r="603" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A603" s="2">
         <v>46265</v>
       </c>
@@ -29493,7 +29507,7 @@
       </c>
       <c r="Q603" s="1"/>
     </row>
-    <row r="604" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A604" s="2">
         <v>46265</v>
       </c>
@@ -29540,7 +29554,7 @@
       </c>
       <c r="Q604" s="1"/>
     </row>
-    <row r="605" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="605" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A605" s="2">
         <v>46265</v>
       </c>
@@ -29587,7 +29601,7 @@
       </c>
       <c r="Q605" s="1"/>
     </row>
-    <row r="606" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="606" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A606" s="2">
         <v>46265</v>
       </c>
@@ -29634,7 +29648,7 @@
       </c>
       <c r="Q606" s="1"/>
     </row>
-    <row r="607" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A607" s="2">
         <v>46265</v>
       </c>
@@ -29681,7 +29695,7 @@
       </c>
       <c r="Q607" s="1"/>
     </row>
-    <row r="608" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A608" s="2">
         <v>46265</v>
       </c>
@@ -29728,7 +29742,7 @@
       </c>
       <c r="Q608" s="1"/>
     </row>
-    <row r="609" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A609" s="2">
         <v>46265</v>
       </c>
@@ -29775,7 +29789,7 @@
       </c>
       <c r="Q609" s="1"/>
     </row>
-    <row r="610" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A610" s="2">
         <v>46265</v>
       </c>
@@ -29822,7 +29836,7 @@
       </c>
       <c r="Q610" s="1"/>
     </row>
-    <row r="611" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A611" s="2">
         <v>46265</v>
       </c>
@@ -29869,7 +29883,7 @@
       </c>
       <c r="Q611" s="1"/>
     </row>
-    <row r="612" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="612" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A612" s="2">
         <v>46265</v>
       </c>
@@ -29916,7 +29930,7 @@
       </c>
       <c r="Q612" s="1"/>
     </row>
-    <row r="613" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="613" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A613" s="2">
         <v>46265</v>
       </c>
@@ -29963,7 +29977,7 @@
       </c>
       <c r="Q613" s="1"/>
     </row>
-    <row r="614" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="614" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A614" s="2">
         <v>46265</v>
       </c>
@@ -30010,7 +30024,7 @@
       </c>
       <c r="Q614" s="1"/>
     </row>
-    <row r="615" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="615" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A615" s="2">
         <v>46265</v>
       </c>
@@ -30057,7 +30071,7 @@
       </c>
       <c r="Q615" s="1"/>
     </row>
-    <row r="616" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A616" s="2">
         <v>46265</v>
       </c>
@@ -30104,7 +30118,7 @@
       </c>
       <c r="Q616" s="1"/>
     </row>
-    <row r="617" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="617" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A617" s="2">
         <v>46265</v>
       </c>
@@ -30151,7 +30165,7 @@
       </c>
       <c r="Q617" s="1"/>
     </row>
-    <row r="618" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A618" s="2">
         <v>46265</v>
       </c>
@@ -30198,7 +30212,7 @@
       </c>
       <c r="Q618" s="1"/>
     </row>
-    <row r="619" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="619" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A619" s="2">
         <v>46265</v>
       </c>
@@ -30245,7 +30259,7 @@
       </c>
       <c r="Q619" s="1"/>
     </row>
-    <row r="620" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="620" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A620" s="2">
         <v>46265</v>
       </c>
@@ -30292,7 +30306,7 @@
       </c>
       <c r="Q620" s="1"/>
     </row>
-    <row r="621" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="621" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A621" s="2">
         <v>46265</v>
       </c>
@@ -30339,7 +30353,7 @@
       </c>
       <c r="Q621" s="1"/>
     </row>
-    <row r="622" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="622" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A622" s="2">
         <v>46265</v>
       </c>
@@ -30386,9 +30400,9 @@
       </c>
       <c r="Q622" s="1"/>
     </row>
-    <row r="623" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="623" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A623" s="2">
-        <v>46265</v>
+        <v>46235</v>
       </c>
       <c r="B623" s="1">
         <v>0</v>
@@ -30433,7 +30447,7 @@
       </c>
       <c r="Q623" s="1"/>
     </row>
-    <row r="624" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="624" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A624" s="2">
         <v>46265</v>
       </c>
@@ -30480,7 +30494,7 @@
       </c>
       <c r="Q624" s="1"/>
     </row>
-    <row r="625" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="625" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A625" s="2">
         <v>46265</v>
       </c>
@@ -30527,7 +30541,7 @@
       </c>
       <c r="Q625" s="1"/>
     </row>
-    <row r="626" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="626" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A626" s="2">
         <v>46265</v>
       </c>
@@ -30574,7 +30588,7 @@
       </c>
       <c r="Q626" s="1"/>
     </row>
-    <row r="627" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A627" s="2">
         <v>46265</v>
       </c>
@@ -30621,7 +30635,7 @@
       </c>
       <c r="Q627" s="1"/>
     </row>
-    <row r="628" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A628" s="2">
         <v>46265</v>
       </c>
@@ -30668,7 +30682,7 @@
       </c>
       <c r="Q628" s="1"/>
     </row>
-    <row r="629" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A629" s="2">
         <v>46265</v>
       </c>
@@ -30715,7 +30729,7 @@
       </c>
       <c r="Q629" s="1"/>
     </row>
-    <row r="630" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A630" s="2">
         <v>46265</v>
       </c>
@@ -30762,7 +30776,7 @@
       </c>
       <c r="Q630" s="1"/>
     </row>
-    <row r="631" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A631" s="2">
         <v>46265</v>
       </c>
@@ -30809,7 +30823,7 @@
       </c>
       <c r="Q631" s="1"/>
     </row>
-    <row r="632" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A632" s="2">
         <v>46265</v>
       </c>
@@ -30856,7 +30870,7 @@
       </c>
       <c r="Q632" s="1"/>
     </row>
-    <row r="633" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A633" s="2">
         <v>46265</v>
       </c>
@@ -30903,7 +30917,7 @@
       </c>
       <c r="Q633" s="1"/>
     </row>
-    <row r="634" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="634" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A634" s="2">
         <v>46265</v>
       </c>
@@ -30950,7 +30964,7 @@
       </c>
       <c r="Q634" s="1"/>
     </row>
-    <row r="635" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="635" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A635" s="2">
         <v>46265</v>
       </c>
@@ -30997,7 +31011,7 @@
       </c>
       <c r="Q635" s="1"/>
     </row>
-    <row r="636" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="636" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A636" s="2">
         <v>46265</v>
       </c>
@@ -31044,7 +31058,7 @@
       </c>
       <c r="Q636" s="1"/>
     </row>
-    <row r="637" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="637" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A637" s="2">
         <v>46265</v>
       </c>
@@ -31091,7 +31105,7 @@
       </c>
       <c r="Q637" s="1"/>
     </row>
-    <row r="638" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="638" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A638" s="2">
         <v>46265</v>
       </c>
@@ -31138,7 +31152,7 @@
       </c>
       <c r="Q638" s="1"/>
     </row>
-    <row r="639" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="639" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A639" s="2">
         <v>46265</v>
       </c>
@@ -31185,7 +31199,7 @@
       </c>
       <c r="Q639" s="1"/>
     </row>
-    <row r="640" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A640" s="2">
         <v>46265</v>
       </c>
@@ -31232,7 +31246,7 @@
       </c>
       <c r="Q640" s="1"/>
     </row>
-    <row r="641" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="641" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A641" s="2">
         <v>46265</v>
       </c>
@@ -31279,7 +31293,7 @@
       </c>
       <c r="Q641" s="1"/>
     </row>
-    <row r="642" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A642" s="2">
         <v>46265</v>
       </c>
@@ -31326,7 +31340,7 @@
       </c>
       <c r="Q642" s="1"/>
     </row>
-    <row r="643" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="643" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A643" s="2">
         <v>46265</v>
       </c>
@@ -31373,7 +31387,7 @@
       </c>
       <c r="Q643" s="1"/>
     </row>
-    <row r="644" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="644" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A644" s="2">
         <v>46265</v>
       </c>
@@ -31420,7 +31434,7 @@
       </c>
       <c r="Q644" s="1"/>
     </row>
-    <row r="645" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="645" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A645" s="2">
         <v>46265</v>
       </c>
@@ -31467,7 +31481,7 @@
       </c>
       <c r="Q645" s="1"/>
     </row>
-    <row r="646" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="646" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A646" s="2">
         <v>46265</v>
       </c>
@@ -31514,7 +31528,7 @@
       </c>
       <c r="Q646" s="1"/>
     </row>
-    <row r="647" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="647" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A647" s="2">
         <v>46265</v>
       </c>
@@ -31561,7 +31575,7 @@
       </c>
       <c r="Q647" s="1"/>
     </row>
-    <row r="648" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="648" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A648" s="2">
         <v>46265</v>
       </c>
@@ -31608,7 +31622,7 @@
       </c>
       <c r="Q648" s="1"/>
     </row>
-    <row r="649" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A649" s="2">
         <v>46265</v>
       </c>
@@ -31655,7 +31669,7 @@
       </c>
       <c r="Q649" s="1"/>
     </row>
-    <row r="650" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="650" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A650" s="2">
         <v>46265</v>
       </c>
@@ -31702,7 +31716,7 @@
       </c>
       <c r="Q650" s="1"/>
     </row>
-    <row r="651" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A651" s="2">
         <v>46265</v>
       </c>
@@ -31749,7 +31763,7 @@
       </c>
       <c r="Q651" s="1"/>
     </row>
-    <row r="652" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A652" s="2">
         <v>46265</v>
       </c>
@@ -31796,7 +31810,7 @@
       </c>
       <c r="Q652" s="1"/>
     </row>
-    <row r="653" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A653" s="2">
         <v>46265</v>
       </c>
@@ -31843,7 +31857,7 @@
       </c>
       <c r="Q653" s="1"/>
     </row>
-    <row r="654" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A654" s="2">
         <v>46265</v>
       </c>
@@ -31890,7 +31904,7 @@
       </c>
       <c r="Q654" s="1"/>
     </row>
-    <row r="655" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A655" s="2">
         <v>46265</v>
       </c>
@@ -31937,7 +31951,7 @@
       </c>
       <c r="Q655" s="1"/>
     </row>
-    <row r="656" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="656" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A656" s="2">
         <v>46265</v>
       </c>
@@ -31984,7 +31998,7 @@
       </c>
       <c r="Q656" s="1"/>
     </row>
-    <row r="657" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="657" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A657" s="2">
         <v>46265</v>
       </c>
@@ -32031,7 +32045,7 @@
       </c>
       <c r="Q657" s="1"/>
     </row>
-    <row r="658" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="658" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A658" s="2">
         <v>46265</v>
       </c>
@@ -32078,7 +32092,7 @@
       </c>
       <c r="Q658" s="1"/>
     </row>
-    <row r="659" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="659" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A659" s="2">
         <v>46265</v>
       </c>
@@ -32125,7 +32139,7 @@
       </c>
       <c r="Q659" s="1"/>
     </row>
-    <row r="660" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="660" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A660" s="2">
         <v>46265</v>
       </c>
@@ -32172,7 +32186,7 @@
       </c>
       <c r="Q660" s="1"/>
     </row>
-    <row r="661" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="661" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A661" s="2">
         <v>46265</v>
       </c>
@@ -32219,7 +32233,7 @@
       </c>
       <c r="Q661" s="1"/>
     </row>
-    <row r="662" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A662" s="2">
         <v>46265</v>
       </c>
@@ -32266,7 +32280,7 @@
       </c>
       <c r="Q662" s="1"/>
     </row>
-    <row r="663" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="663" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A663" s="2">
         <v>46265</v>
       </c>
@@ -32313,7 +32327,7 @@
       </c>
       <c r="Q663" s="1"/>
     </row>
-    <row r="664" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="664" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A664" s="2">
         <v>46265</v>
       </c>
@@ -32360,7 +32374,7 @@
       </c>
       <c r="Q664" s="1"/>
     </row>
-    <row r="665" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="665" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A665" s="2">
         <v>46265</v>
       </c>
@@ -32407,7 +32421,7 @@
       </c>
       <c r="Q665" s="1"/>
     </row>
-    <row r="666" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="666" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A666" s="2">
         <v>46265</v>
       </c>
@@ -32454,7 +32468,7 @@
       </c>
       <c r="Q666" s="1"/>
     </row>
-    <row r="667" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="667" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A667" s="2">
         <v>46265</v>
       </c>
@@ -32501,7 +32515,7 @@
       </c>
       <c r="Q667" s="1"/>
     </row>
-    <row r="668" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="668" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A668" s="2">
         <v>46265</v>
       </c>
@@ -32548,7 +32562,7 @@
       </c>
       <c r="Q668" s="1"/>
     </row>
-    <row r="669" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="669" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A669" s="2">
         <v>46265</v>
       </c>
@@ -32595,7 +32609,7 @@
       </c>
       <c r="Q669" s="1"/>
     </row>
-    <row r="670" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="670" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A670" s="2">
         <v>46265</v>
       </c>
@@ -32642,7 +32656,7 @@
       </c>
       <c r="Q670" s="1"/>
     </row>
-    <row r="671" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="671" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A671" s="2">
         <v>46265</v>
       </c>
@@ -32691,7 +32705,7 @@
     </row>
     <row r="672" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A672" s="2">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="B672" s="1">
         <v>0</v>
@@ -32736,7 +32750,7 @@
       </c>
       <c r="Q672" s="1"/>
     </row>
-    <row r="673" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="673" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A673" s="2">
         <v>46265</v>
       </c>
@@ -32783,7 +32797,7 @@
       </c>
       <c r="Q673" s="1"/>
     </row>
-    <row r="674" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="674" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A674" s="2">
         <v>46265</v>
       </c>
@@ -32830,7 +32844,7 @@
       </c>
       <c r="Q674" s="1"/>
     </row>
-    <row r="675" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="675" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A675" s="2">
         <v>46265</v>
       </c>
@@ -32877,7 +32891,7 @@
       </c>
       <c r="Q675" s="1"/>
     </row>
-    <row r="676" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="676" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A676" s="2">
         <v>46265</v>
       </c>
@@ -32924,7 +32938,7 @@
       </c>
       <c r="Q676" s="1"/>
     </row>
-    <row r="677" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="677" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A677" s="2">
         <v>46265</v>
       </c>
@@ -32971,7 +32985,7 @@
       </c>
       <c r="Q677" s="1"/>
     </row>
-    <row r="678" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="678" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A678" s="2">
         <v>46265</v>
       </c>
@@ -33018,7 +33032,7 @@
       </c>
       <c r="Q678" s="1"/>
     </row>
-    <row r="679" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="679" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A679" s="2">
         <v>46265</v>
       </c>
@@ -33065,7 +33079,7 @@
       </c>
       <c r="Q679" s="1"/>
     </row>
-    <row r="680" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="680" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A680" s="2">
         <v>46265</v>
       </c>
@@ -33112,7 +33126,7 @@
       </c>
       <c r="Q680" s="1"/>
     </row>
-    <row r="681" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="681" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A681" s="2">
         <v>46265</v>
       </c>
@@ -33159,7 +33173,7 @@
       </c>
       <c r="Q681" s="1"/>
     </row>
-    <row r="682" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="682" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A682" s="2">
         <v>46265</v>
       </c>
@@ -33206,7 +33220,7 @@
       </c>
       <c r="Q682" s="1"/>
     </row>
-    <row r="683" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="683" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A683" s="2">
         <v>46265</v>
       </c>
@@ -33253,7 +33267,7 @@
       </c>
       <c r="Q683" s="1"/>
     </row>
-    <row r="684" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="684" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A684" s="2">
         <v>46265</v>
       </c>
@@ -33300,7 +33314,7 @@
       </c>
       <c r="Q684" s="1"/>
     </row>
-    <row r="685" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="685" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A685" s="2">
         <v>46265</v>
       </c>
@@ -33347,7 +33361,7 @@
       </c>
       <c r="Q685" s="1"/>
     </row>
-    <row r="686" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="686" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A686" s="2">
         <v>46265</v>
       </c>
@@ -33394,7 +33408,7 @@
       </c>
       <c r="Q686" s="1"/>
     </row>
-    <row r="687" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="687" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A687" s="2">
         <v>46265</v>
       </c>
@@ -33441,7 +33455,7 @@
       </c>
       <c r="Q687" s="1"/>
     </row>
-    <row r="688" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="688" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A688" s="2">
         <v>46265</v>
       </c>
@@ -33488,7 +33502,7 @@
       </c>
       <c r="Q688" s="1"/>
     </row>
-    <row r="689" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="689" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A689" s="2">
         <v>46265</v>
       </c>
@@ -33535,7 +33549,7 @@
       </c>
       <c r="Q689" s="1"/>
     </row>
-    <row r="690" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="690" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A690" s="2">
         <v>46265</v>
       </c>
@@ -33582,7 +33596,7 @@
       </c>
       <c r="Q690" s="1"/>
     </row>
-    <row r="691" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="691" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A691" s="2">
         <v>46265</v>
       </c>
@@ -33629,7 +33643,7 @@
       </c>
       <c r="Q691" s="1"/>
     </row>
-    <row r="692" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="692" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A692" s="2">
         <v>46265</v>
       </c>
@@ -33676,7 +33690,7 @@
       </c>
       <c r="Q692" s="1"/>
     </row>
-    <row r="693" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="693" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A693" s="2">
         <v>46265</v>
       </c>
@@ -33723,7 +33737,7 @@
       </c>
       <c r="Q693" s="1"/>
     </row>
-    <row r="694" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="694" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A694" s="2">
         <v>46265</v>
       </c>
@@ -33770,7 +33784,7 @@
       </c>
       <c r="Q694" s="1"/>
     </row>
-    <row r="695" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="695" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A695" s="2">
         <v>46265</v>
       </c>
@@ -33817,7 +33831,7 @@
       </c>
       <c r="Q695" s="1"/>
     </row>
-    <row r="696" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="696" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A696" s="2">
         <v>46265</v>
       </c>
@@ -33864,7 +33878,7 @@
       </c>
       <c r="Q696" s="1"/>
     </row>
-    <row r="697" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="697" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A697" s="2">
         <v>46265</v>
       </c>
@@ -33911,7 +33925,7 @@
       </c>
       <c r="Q697" s="1"/>
     </row>
-    <row r="698" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="698" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A698" s="2">
         <v>46265</v>
       </c>
@@ -33958,7 +33972,7 @@
       </c>
       <c r="Q698" s="1"/>
     </row>
-    <row r="699" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="699" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A699" s="2">
         <v>46265</v>
       </c>
@@ -34005,7 +34019,7 @@
       </c>
       <c r="Q699" s="1"/>
     </row>
-    <row r="700" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="700" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A700" s="2">
         <v>46265</v>
       </c>

--- a/Donnees_Mensuelle.xlsx
+++ b/Donnees_Mensuelle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00795D44-F44A-4BCD-8F21-8243EC713E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5751C3E-6D27-4D73-8B87-7E95125275B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4912" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4911" uniqueCount="118">
   <si>
     <t>Date</t>
   </si>
@@ -387,9 +387,6 @@
   </si>
   <si>
     <t>YARAKH</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -794,7 +791,7 @@
     </filterColumn>
     <filterColumn colId="6">
       <filters>
-        <filter val="Ado DABO"/>
+        <filter val="Adama DIALLO"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -4832,7 +4829,7 @@
       </c>
       <c r="Q78" s="1"/>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A79" s="2">
         <v>46268</v>
       </c>
@@ -5960,9 +5957,9 @@
       </c>
       <c r="Q102" s="1"/>
     </row>
-    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A103" s="2" t="s">
-        <v>118</v>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A103" s="2">
+        <v>46265</v>
       </c>
       <c r="B103" s="1">
         <v>0</v>
@@ -11083,7 +11080,7 @@
       </c>
       <c r="Q211" s="1"/>
     </row>
-    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A212" s="2">
         <v>46265</v>
       </c>
@@ -15313,7 +15310,7 @@
       </c>
       <c r="Q301" s="1"/>
     </row>
-    <row r="302" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A302" s="2">
         <v>46268</v>
       </c>
@@ -15360,7 +15357,7 @@
       </c>
       <c r="Q302" s="1"/>
     </row>
-    <row r="303" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A303" s="2">
         <v>46268</v>
       </c>
@@ -16958,7 +16955,7 @@
       </c>
       <c r="Q336" s="1"/>
     </row>
-    <row r="337" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A337" s="2">
         <v>46268</v>
       </c>
@@ -17005,7 +17002,7 @@
       </c>
       <c r="Q337" s="1"/>
     </row>
-    <row r="338" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A338" s="2">
         <v>46268</v>
       </c>
@@ -21235,7 +21232,7 @@
       </c>
       <c r="Q427" s="1"/>
     </row>
-    <row r="428" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A428" s="2">
         <v>46268</v>
       </c>
@@ -22504,7 +22501,7 @@
       </c>
       <c r="Q454" s="1"/>
     </row>
-    <row r="455" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A455" s="2">
         <v>46265</v>
       </c>
@@ -27110,7 +27107,7 @@
       </c>
       <c r="Q552" s="1"/>
     </row>
-    <row r="553" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A553" s="2">
         <v>46268</v>
       </c>
@@ -28567,7 +28564,7 @@
       </c>
       <c r="Q583" s="1"/>
     </row>
-    <row r="584" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="584" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A584" s="2">
         <v>46265</v>
       </c>
@@ -32703,7 +32700,7 @@
       </c>
       <c r="Q671" s="1"/>
     </row>
-    <row r="672" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="672" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
       <c r="A672" s="2">
         <v>46268</v>
       </c>
@@ -33925,7 +33922,7 @@
       </c>
       <c r="Q697" s="1"/>
     </row>
-    <row r="698" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="698" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A698" s="2">
         <v>46265</v>
       </c>

--- a/Donnees_Mensuelle.xlsx
+++ b/Donnees_Mensuelle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5751C3E-6D27-4D73-8B87-7E95125275B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAACC848-F602-464A-BC88-3DBCB57EB002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -783,18 +783,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}" name="Tableau1" displayName="Tableau1" ref="A1:Q700" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:Q700" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="TATA 2"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="6">
-      <filters>
-        <filter val="Adama DIALLO"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:Q700" xr:uid="{7C06FBCE-2570-4223-B913-F3F326A2A667}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{713E4B58-7C9F-4B80-8C6C-D9C3181B21C1}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{0868AEE8-A7A6-4928-8DDB-60543BB07F07}" name="Telephone_Team_Leader" dataDxfId="14"/>
@@ -1210,7 +1199,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>46270</v>
       </c>
@@ -1257,7 +1246,7 @@
       </c>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>46270</v>
       </c>
@@ -1304,7 +1293,7 @@
       </c>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>46270</v>
       </c>
@@ -1351,7 +1340,7 @@
       </c>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>46270</v>
       </c>
@@ -1398,7 +1387,7 @@
       </c>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>46270</v>
       </c>
@@ -1445,7 +1434,7 @@
       </c>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>46270</v>
       </c>
@@ -1492,7 +1481,7 @@
       </c>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>46270</v>
       </c>
@@ -1539,7 +1528,7 @@
       </c>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>46270</v>
       </c>
@@ -1586,7 +1575,7 @@
       </c>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>46270</v>
       </c>
@@ -1633,7 +1622,7 @@
       </c>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <v>46270</v>
       </c>
@@ -1680,7 +1669,7 @@
       </c>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
         <v>46270</v>
       </c>
@@ -1727,7 +1716,7 @@
       </c>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
         <v>46270</v>
       </c>
@@ -1774,7 +1763,7 @@
       </c>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
         <v>46270</v>
       </c>
@@ -1821,7 +1810,7 @@
       </c>
       <c r="Q14" s="1"/>
     </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A15" s="2">
         <v>46270</v>
       </c>
@@ -1868,7 +1857,7 @@
       </c>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
         <v>46270</v>
       </c>
@@ -1915,7 +1904,7 @@
       </c>
       <c r="Q16" s="1"/>
     </row>
-    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
         <v>46270</v>
       </c>
@@ -1962,7 +1951,7 @@
       </c>
       <c r="Q17" s="1"/>
     </row>
-    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
         <v>46270</v>
       </c>
@@ -2009,7 +1998,7 @@
       </c>
       <c r="Q18" s="1"/>
     </row>
-    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
         <v>46270</v>
       </c>
@@ -2056,7 +2045,7 @@
       </c>
       <c r="Q19" s="1"/>
     </row>
-    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
         <v>46270</v>
       </c>
@@ -2103,7 +2092,7 @@
       </c>
       <c r="Q20" s="1"/>
     </row>
-    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
         <v>46270</v>
       </c>
@@ -2150,7 +2139,7 @@
       </c>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>46270</v>
       </c>
@@ -2197,7 +2186,7 @@
       </c>
       <c r="Q22" s="1"/>
     </row>
-    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
         <v>46270</v>
       </c>
@@ -2244,7 +2233,7 @@
       </c>
       <c r="Q23" s="1"/>
     </row>
-    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <v>46270</v>
       </c>
@@ -2291,7 +2280,7 @@
       </c>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <v>46270</v>
       </c>
@@ -2338,7 +2327,7 @@
       </c>
       <c r="Q25" s="1"/>
     </row>
-    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
         <v>46270</v>
       </c>
@@ -2385,7 +2374,7 @@
       </c>
       <c r="Q26" s="1"/>
     </row>
-    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
         <v>46270</v>
       </c>
@@ -2432,7 +2421,7 @@
       </c>
       <c r="Q27" s="1"/>
     </row>
-    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A28" s="2">
         <v>46270</v>
       </c>
@@ -2479,7 +2468,7 @@
       </c>
       <c r="Q28" s="1"/>
     </row>
-    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
         <v>46270</v>
       </c>
@@ -2526,7 +2515,7 @@
       </c>
       <c r="Q29" s="1"/>
     </row>
-    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
         <v>46270</v>
       </c>
@@ -2573,7 +2562,7 @@
       </c>
       <c r="Q30" s="1"/>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
         <v>46270</v>
       </c>
@@ -2620,7 +2609,7 @@
       </c>
       <c r="Q31" s="1"/>
     </row>
-    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
         <v>46270</v>
       </c>
@@ -2667,7 +2656,7 @@
       </c>
       <c r="Q32" s="1"/>
     </row>
-    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
         <v>46270</v>
       </c>
@@ -2714,7 +2703,7 @@
       </c>
       <c r="Q33" s="1"/>
     </row>
-    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
         <v>46270</v>
       </c>
@@ -2761,7 +2750,7 @@
       </c>
       <c r="Q34" s="1"/>
     </row>
-    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
         <v>46270</v>
       </c>
@@ -2808,7 +2797,7 @@
       </c>
       <c r="Q35" s="1"/>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
         <v>46270</v>
       </c>
@@ -2855,7 +2844,7 @@
       </c>
       <c r="Q36" s="1"/>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
         <v>46270</v>
       </c>
@@ -2902,7 +2891,7 @@
       </c>
       <c r="Q37" s="1"/>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
         <v>46270</v>
       </c>
@@ -2949,7 +2938,7 @@
       </c>
       <c r="Q38" s="1"/>
     </row>
-    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
         <v>46270</v>
       </c>
@@ -2996,7 +2985,7 @@
       </c>
       <c r="Q39" s="1"/>
     </row>
-    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
         <v>46270</v>
       </c>
@@ -3043,7 +3032,7 @@
       </c>
       <c r="Q40" s="1"/>
     </row>
-    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A41" s="2">
         <v>46270</v>
       </c>
@@ -3090,7 +3079,7 @@
       </c>
       <c r="Q41" s="1"/>
     </row>
-    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
         <v>46270</v>
       </c>
@@ -3137,7 +3126,7 @@
       </c>
       <c r="Q42" s="1"/>
     </row>
-    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
         <v>46270</v>
       </c>
@@ -3184,7 +3173,7 @@
       </c>
       <c r="Q43" s="1"/>
     </row>
-    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A44" s="2">
         <v>46270</v>
       </c>
@@ -3231,7 +3220,7 @@
       </c>
       <c r="Q44" s="1"/>
     </row>
-    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A45" s="2">
         <v>46270</v>
       </c>
@@ -3278,7 +3267,7 @@
       </c>
       <c r="Q45" s="1"/>
     </row>
-    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
         <v>46270</v>
       </c>
@@ -3325,7 +3314,7 @@
       </c>
       <c r="Q46" s="1"/>
     </row>
-    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A47" s="2">
         <v>46270</v>
       </c>
@@ -3372,7 +3361,7 @@
       </c>
       <c r="Q47" s="1"/>
     </row>
-    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A48" s="2">
         <v>46270</v>
       </c>
@@ -3419,7 +3408,7 @@
       </c>
       <c r="Q48" s="1"/>
     </row>
-    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A49" s="2">
         <v>46270</v>
       </c>
@@ -3466,7 +3455,7 @@
       </c>
       <c r="Q49" s="1"/>
     </row>
-    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
         <v>46270</v>
       </c>
@@ -3513,7 +3502,7 @@
       </c>
       <c r="Q50" s="1"/>
     </row>
-    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
         <v>46270</v>
       </c>
@@ -3560,7 +3549,7 @@
       </c>
       <c r="Q51" s="1"/>
     </row>
-    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
         <v>46270</v>
       </c>
@@ -3607,7 +3596,7 @@
       </c>
       <c r="Q52" s="1"/>
     </row>
-    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
         <v>46270</v>
       </c>
@@ -3654,7 +3643,7 @@
       </c>
       <c r="Q53" s="1"/>
     </row>
-    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
         <v>46270</v>
       </c>
@@ -3701,7 +3690,7 @@
       </c>
       <c r="Q54" s="1"/>
     </row>
-    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A55" s="2">
         <v>46270</v>
       </c>
@@ -3748,7 +3737,7 @@
       </c>
       <c r="Q55" s="1"/>
     </row>
-    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A56" s="2">
         <v>46270</v>
       </c>
@@ -3795,7 +3784,7 @@
       </c>
       <c r="Q56" s="1"/>
     </row>
-    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
         <v>46270</v>
       </c>
@@ -3842,7 +3831,7 @@
       </c>
       <c r="Q57" s="1"/>
     </row>
-    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
         <v>46270</v>
       </c>
@@ -3889,7 +3878,7 @@
       </c>
       <c r="Q58" s="1"/>
     </row>
-    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A59" s="2">
         <v>46270</v>
       </c>
@@ -3936,7 +3925,7 @@
       </c>
       <c r="Q59" s="1"/>
     </row>
-    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
         <v>46270</v>
       </c>
@@ -3983,7 +3972,7 @@
       </c>
       <c r="Q60" s="1"/>
     </row>
-    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
         <v>46270</v>
       </c>
@@ -4030,7 +4019,7 @@
       </c>
       <c r="Q61" s="1"/>
     </row>
-    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A62" s="2">
         <v>46270</v>
       </c>
@@ -4077,7 +4066,7 @@
       </c>
       <c r="Q62" s="1"/>
     </row>
-    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A63" s="2">
         <v>46270</v>
       </c>
@@ -4124,7 +4113,7 @@
       </c>
       <c r="Q63" s="1"/>
     </row>
-    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A64" s="2">
         <v>46270</v>
       </c>
@@ -4171,7 +4160,7 @@
       </c>
       <c r="Q64" s="1"/>
     </row>
-    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A65" s="2">
         <v>46270</v>
       </c>
@@ -4218,7 +4207,7 @@
       </c>
       <c r="Q65" s="1"/>
     </row>
-    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A66" s="2">
         <v>46270</v>
       </c>
@@ -4265,7 +4254,7 @@
       </c>
       <c r="Q66" s="1"/>
     </row>
-    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A67" s="2">
         <v>46270</v>
       </c>
@@ -4312,7 +4301,7 @@
       </c>
       <c r="Q67" s="1"/>
     </row>
-    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A68" s="2">
         <v>46270</v>
       </c>
@@ -4359,7 +4348,7 @@
       </c>
       <c r="Q68" s="1"/>
     </row>
-    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A69" s="2">
         <v>46270</v>
       </c>
@@ -4406,7 +4395,7 @@
       </c>
       <c r="Q69" s="1"/>
     </row>
-    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A70" s="2">
         <v>46270</v>
       </c>
@@ -4453,7 +4442,7 @@
       </c>
       <c r="Q70" s="1"/>
     </row>
-    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A71" s="2">
         <v>46270</v>
       </c>
@@ -4500,7 +4489,7 @@
       </c>
       <c r="Q71" s="1"/>
     </row>
-    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A72" s="2">
         <v>46270</v>
       </c>
@@ -4547,7 +4536,7 @@
       </c>
       <c r="Q72" s="1"/>
     </row>
-    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A73" s="2">
         <v>46270</v>
       </c>
@@ -4594,7 +4583,7 @@
       </c>
       <c r="Q73" s="1"/>
     </row>
-    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A74" s="2">
         <v>46270</v>
       </c>
@@ -4641,7 +4630,7 @@
       </c>
       <c r="Q74" s="1"/>
     </row>
-    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A75" s="2">
         <v>46270</v>
       </c>
@@ -4688,7 +4677,7 @@
       </c>
       <c r="Q75" s="1"/>
     </row>
-    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A76" s="2">
         <v>46270</v>
       </c>
@@ -4735,7 +4724,7 @@
       </c>
       <c r="Q76" s="1"/>
     </row>
-    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A77" s="2">
         <v>46270</v>
       </c>
@@ -4782,7 +4771,7 @@
       </c>
       <c r="Q77" s="1"/>
     </row>
-    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A78" s="2">
         <v>46270</v>
       </c>
@@ -4829,7 +4818,7 @@
       </c>
       <c r="Q78" s="1"/>
     </row>
-    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A79" s="2">
         <v>46268</v>
       </c>
@@ -4876,7 +4865,7 @@
       </c>
       <c r="Q79" s="1"/>
     </row>
-    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A80" s="2">
         <v>46270</v>
       </c>
@@ -4923,7 +4912,7 @@
       </c>
       <c r="Q80" s="1"/>
     </row>
-    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A81" s="2">
         <v>46270</v>
       </c>
@@ -4970,7 +4959,7 @@
       </c>
       <c r="Q81" s="1"/>
     </row>
-    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A82" s="2">
         <v>46270</v>
       </c>
@@ -5017,7 +5006,7 @@
       </c>
       <c r="Q82" s="1"/>
     </row>
-    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A83" s="2">
         <v>46270</v>
       </c>
@@ -5064,7 +5053,7 @@
       </c>
       <c r="Q83" s="1"/>
     </row>
-    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A84" s="2">
         <v>46270</v>
       </c>
@@ -5111,7 +5100,7 @@
       </c>
       <c r="Q84" s="1"/>
     </row>
-    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A85" s="2">
         <v>46270</v>
       </c>
@@ -5158,7 +5147,7 @@
       </c>
       <c r="Q85" s="1"/>
     </row>
-    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A86" s="2">
         <v>46270</v>
       </c>
@@ -5205,7 +5194,7 @@
       </c>
       <c r="Q86" s="1"/>
     </row>
-    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A87" s="2">
         <v>46270</v>
       </c>
@@ -5252,7 +5241,7 @@
       </c>
       <c r="Q87" s="1"/>
     </row>
-    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A88" s="2">
         <v>46270</v>
       </c>
@@ -5299,7 +5288,7 @@
       </c>
       <c r="Q88" s="1"/>
     </row>
-    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A89" s="2">
         <v>46270</v>
       </c>
@@ -5346,7 +5335,7 @@
       </c>
       <c r="Q89" s="1"/>
     </row>
-    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A90" s="2">
         <v>46270</v>
       </c>
@@ -5393,7 +5382,7 @@
       </c>
       <c r="Q90" s="1"/>
     </row>
-    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A91" s="2">
         <v>46270</v>
       </c>
@@ -5440,7 +5429,7 @@
       </c>
       <c r="Q91" s="1"/>
     </row>
-    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A92" s="2">
         <v>46270</v>
       </c>
@@ -5487,7 +5476,7 @@
       </c>
       <c r="Q92" s="1"/>
     </row>
-    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A93" s="2">
         <v>46270</v>
       </c>
@@ -5534,7 +5523,7 @@
       </c>
       <c r="Q93" s="1"/>
     </row>
-    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A94" s="2">
         <v>46270</v>
       </c>
@@ -5581,7 +5570,7 @@
       </c>
       <c r="Q94" s="1"/>
     </row>
-    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A95" s="2">
         <v>46270</v>
       </c>
@@ -5628,7 +5617,7 @@
       </c>
       <c r="Q95" s="1"/>
     </row>
-    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A96" s="2">
         <v>46270</v>
       </c>
@@ -5675,7 +5664,7 @@
       </c>
       <c r="Q96" s="1"/>
     </row>
-    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A97" s="2">
         <v>46270</v>
       </c>
@@ -5722,7 +5711,7 @@
       </c>
       <c r="Q97" s="1"/>
     </row>
-    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A98" s="2">
         <v>46270</v>
       </c>
@@ -5769,7 +5758,7 @@
       </c>
       <c r="Q98" s="1"/>
     </row>
-    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A99" s="2">
         <v>46270</v>
       </c>
@@ -5816,7 +5805,7 @@
       </c>
       <c r="Q99" s="1"/>
     </row>
-    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A100" s="2">
         <v>46270</v>
       </c>
@@ -5863,7 +5852,7 @@
       </c>
       <c r="Q100" s="1"/>
     </row>
-    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A101" s="2">
         <v>46270</v>
       </c>
@@ -5910,7 +5899,7 @@
       </c>
       <c r="Q101" s="1"/>
     </row>
-    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A102" s="2">
         <v>46270</v>
       </c>
@@ -6004,7 +5993,7 @@
       </c>
       <c r="Q103" s="1"/>
     </row>
-    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A104" s="2">
         <v>46270</v>
       </c>
@@ -6051,7 +6040,7 @@
       </c>
       <c r="Q104" s="1"/>
     </row>
-    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A105" s="2">
         <v>46269</v>
       </c>
@@ -6098,7 +6087,7 @@
       </c>
       <c r="Q105" s="1"/>
     </row>
-    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A106" s="2">
         <v>46269</v>
       </c>
@@ -6145,7 +6134,7 @@
       </c>
       <c r="Q106" s="1"/>
     </row>
-    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A107" s="2">
         <v>46269</v>
       </c>
@@ -6192,7 +6181,7 @@
       </c>
       <c r="Q107" s="1"/>
     </row>
-    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A108" s="2">
         <v>46269</v>
       </c>
@@ -6239,7 +6228,7 @@
       </c>
       <c r="Q108" s="1"/>
     </row>
-    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A109" s="2">
         <v>46269</v>
       </c>
@@ -6286,7 +6275,7 @@
       </c>
       <c r="Q109" s="1"/>
     </row>
-    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A110" s="2">
         <v>46269</v>
       </c>
@@ -6333,7 +6322,7 @@
       </c>
       <c r="Q110" s="1"/>
     </row>
-    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A111" s="2">
         <v>46269</v>
       </c>
@@ -6380,7 +6369,7 @@
       </c>
       <c r="Q111" s="1"/>
     </row>
-    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A112" s="2">
         <v>46269</v>
       </c>
@@ -6427,7 +6416,7 @@
       </c>
       <c r="Q112" s="1"/>
     </row>
-    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A113" s="2">
         <v>46269</v>
       </c>
@@ -6474,7 +6463,7 @@
       </c>
       <c r="Q113" s="1"/>
     </row>
-    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A114" s="2">
         <v>46269</v>
       </c>
@@ -6521,7 +6510,7 @@
       </c>
       <c r="Q114" s="1"/>
     </row>
-    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A115" s="2">
         <v>46269</v>
       </c>
@@ -6568,7 +6557,7 @@
       </c>
       <c r="Q115" s="1"/>
     </row>
-    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A116" s="2">
         <v>46269</v>
       </c>
@@ -6615,7 +6604,7 @@
       </c>
       <c r="Q116" s="1"/>
     </row>
-    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A117" s="2">
         <v>46269</v>
       </c>
@@ -6662,7 +6651,7 @@
       </c>
       <c r="Q117" s="1"/>
     </row>
-    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A118" s="2">
         <v>46269</v>
       </c>
@@ -6709,7 +6698,7 @@
       </c>
       <c r="Q118" s="1"/>
     </row>
-    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A119" s="2">
         <v>46269</v>
       </c>
@@ -6756,7 +6745,7 @@
       </c>
       <c r="Q119" s="1"/>
     </row>
-    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A120" s="2">
         <v>46269</v>
       </c>
@@ -6803,7 +6792,7 @@
       </c>
       <c r="Q120" s="1"/>
     </row>
-    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A121" s="2">
         <v>46269</v>
       </c>
@@ -6850,7 +6839,7 @@
       </c>
       <c r="Q121" s="1"/>
     </row>
-    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A122" s="2">
         <v>46269</v>
       </c>
@@ -6897,7 +6886,7 @@
       </c>
       <c r="Q122" s="1"/>
     </row>
-    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A123" s="2">
         <v>46269</v>
       </c>
@@ -6944,7 +6933,7 @@
       </c>
       <c r="Q123" s="1"/>
     </row>
-    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A124" s="2">
         <v>46269</v>
       </c>
@@ -6991,7 +6980,7 @@
       </c>
       <c r="Q124" s="1"/>
     </row>
-    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A125" s="2">
         <v>46269</v>
       </c>
@@ -7038,7 +7027,7 @@
       </c>
       <c r="Q125" s="1"/>
     </row>
-    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A126" s="2">
         <v>46269</v>
       </c>
@@ -7085,7 +7074,7 @@
       </c>
       <c r="Q126" s="1"/>
     </row>
-    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A127" s="2">
         <v>46269</v>
       </c>
@@ -7132,7 +7121,7 @@
       </c>
       <c r="Q127" s="1"/>
     </row>
-    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A128" s="2">
         <v>46269</v>
       </c>
@@ -7179,7 +7168,7 @@
       </c>
       <c r="Q128" s="1"/>
     </row>
-    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A129" s="2">
         <v>46269</v>
       </c>
@@ -7226,7 +7215,7 @@
       </c>
       <c r="Q129" s="1"/>
     </row>
-    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A130" s="2">
         <v>46269</v>
       </c>
@@ -7273,7 +7262,7 @@
       </c>
       <c r="Q130" s="1"/>
     </row>
-    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A131" s="2">
         <v>46269</v>
       </c>
@@ -7320,7 +7309,7 @@
       </c>
       <c r="Q131" s="1"/>
     </row>
-    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A132" s="2">
         <v>46269</v>
       </c>
@@ -7367,7 +7356,7 @@
       </c>
       <c r="Q132" s="1"/>
     </row>
-    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A133" s="2">
         <v>46269</v>
       </c>
@@ -7414,7 +7403,7 @@
       </c>
       <c r="Q133" s="1"/>
     </row>
-    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A134" s="2">
         <v>46269</v>
       </c>
@@ -7461,7 +7450,7 @@
       </c>
       <c r="Q134" s="1"/>
     </row>
-    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A135" s="2">
         <v>46269</v>
       </c>
@@ -7508,7 +7497,7 @@
       </c>
       <c r="Q135" s="1"/>
     </row>
-    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A136" s="2">
         <v>46269</v>
       </c>
@@ -7555,7 +7544,7 @@
       </c>
       <c r="Q136" s="1"/>
     </row>
-    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A137" s="2">
         <v>46269</v>
       </c>
@@ -7602,7 +7591,7 @@
       </c>
       <c r="Q137" s="1"/>
     </row>
-    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A138" s="2">
         <v>46269</v>
       </c>
@@ -7649,7 +7638,7 @@
       </c>
       <c r="Q138" s="1"/>
     </row>
-    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A139" s="2">
         <v>46269</v>
       </c>
@@ -7696,7 +7685,7 @@
       </c>
       <c r="Q139" s="1"/>
     </row>
-    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A140" s="2">
         <v>46269</v>
       </c>
@@ -7743,7 +7732,7 @@
       </c>
       <c r="Q140" s="1"/>
     </row>
-    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A141" s="2">
         <v>46269</v>
       </c>
@@ -7790,7 +7779,7 @@
       </c>
       <c r="Q141" s="1"/>
     </row>
-    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A142" s="2">
         <v>46269</v>
       </c>
@@ -7837,7 +7826,7 @@
       </c>
       <c r="Q142" s="1"/>
     </row>
-    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A143" s="2">
         <v>46269</v>
       </c>
@@ -7884,7 +7873,7 @@
       </c>
       <c r="Q143" s="1"/>
     </row>
-    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A144" s="2">
         <v>46269</v>
       </c>
@@ -7931,7 +7920,7 @@
       </c>
       <c r="Q144" s="1"/>
     </row>
-    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A145" s="2">
         <v>46269</v>
       </c>
@@ -7978,7 +7967,7 @@
       </c>
       <c r="Q145" s="1"/>
     </row>
-    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A146" s="2">
         <v>46269</v>
       </c>
@@ -8025,7 +8014,7 @@
       </c>
       <c r="Q146" s="1"/>
     </row>
-    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A147" s="2">
         <v>46269</v>
       </c>
@@ -8072,7 +8061,7 @@
       </c>
       <c r="Q147" s="1"/>
     </row>
-    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A148" s="2">
         <v>46269</v>
       </c>
@@ -8119,7 +8108,7 @@
       </c>
       <c r="Q148" s="1"/>
     </row>
-    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A149" s="2">
         <v>46269</v>
       </c>
@@ -8166,7 +8155,7 @@
       </c>
       <c r="Q149" s="1"/>
     </row>
-    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A150" s="2">
         <v>46269</v>
       </c>
@@ -8213,7 +8202,7 @@
       </c>
       <c r="Q150" s="1"/>
     </row>
-    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A151" s="2">
         <v>46269</v>
       </c>
@@ -8260,7 +8249,7 @@
       </c>
       <c r="Q151" s="1"/>
     </row>
-    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A152" s="2">
         <v>46269</v>
       </c>
@@ -8307,7 +8296,7 @@
       </c>
       <c r="Q152" s="1"/>
     </row>
-    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A153" s="2">
         <v>46269</v>
       </c>
@@ -8354,7 +8343,7 @@
       </c>
       <c r="Q153" s="1"/>
     </row>
-    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A154" s="2">
         <v>46269</v>
       </c>
@@ -8401,7 +8390,7 @@
       </c>
       <c r="Q154" s="1"/>
     </row>
-    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A155" s="2">
         <v>46269</v>
       </c>
@@ -8448,7 +8437,7 @@
       </c>
       <c r="Q155" s="1"/>
     </row>
-    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A156" s="2">
         <v>46269</v>
       </c>
@@ -8495,7 +8484,7 @@
       </c>
       <c r="Q156" s="1"/>
     </row>
-    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A157" s="2">
         <v>46269</v>
       </c>
@@ -8542,7 +8531,7 @@
       </c>
       <c r="Q157" s="1"/>
     </row>
-    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A158" s="2">
         <v>46269</v>
       </c>
@@ -8589,7 +8578,7 @@
       </c>
       <c r="Q158" s="1"/>
     </row>
-    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A159" s="2">
         <v>46269</v>
       </c>
@@ -8636,7 +8625,7 @@
       </c>
       <c r="Q159" s="1"/>
     </row>
-    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A160" s="2">
         <v>46269</v>
       </c>
@@ -8683,7 +8672,7 @@
       </c>
       <c r="Q160" s="1"/>
     </row>
-    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A161" s="2">
         <v>46269</v>
       </c>
@@ -8730,7 +8719,7 @@
       </c>
       <c r="Q161" s="1"/>
     </row>
-    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A162" s="2">
         <v>46269</v>
       </c>
@@ -8777,7 +8766,7 @@
       </c>
       <c r="Q162" s="1"/>
     </row>
-    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A163" s="2">
         <v>46269</v>
       </c>
@@ -8824,7 +8813,7 @@
       </c>
       <c r="Q163" s="1"/>
     </row>
-    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A164" s="2">
         <v>46269</v>
       </c>
@@ -8871,7 +8860,7 @@
       </c>
       <c r="Q164" s="1"/>
     </row>
-    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A165" s="2">
         <v>46269</v>
       </c>
@@ -8918,7 +8907,7 @@
       </c>
       <c r="Q165" s="1"/>
     </row>
-    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A166" s="2">
         <v>46269</v>
       </c>
@@ -8965,7 +8954,7 @@
       </c>
       <c r="Q166" s="1"/>
     </row>
-    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A167" s="2">
         <v>46269</v>
       </c>
@@ -9012,7 +9001,7 @@
       </c>
       <c r="Q167" s="1"/>
     </row>
-    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A168" s="2">
         <v>46269</v>
       </c>
@@ -9059,7 +9048,7 @@
       </c>
       <c r="Q168" s="1"/>
     </row>
-    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A169" s="2">
         <v>46269</v>
       </c>
@@ -9106,7 +9095,7 @@
       </c>
       <c r="Q169" s="1"/>
     </row>
-    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A170" s="2">
         <v>46269</v>
       </c>
@@ -9153,7 +9142,7 @@
       </c>
       <c r="Q170" s="1"/>
     </row>
-    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A171" s="2">
         <v>46269</v>
       </c>
@@ -9200,7 +9189,7 @@
       </c>
       <c r="Q171" s="1"/>
     </row>
-    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A172" s="2">
         <v>46269</v>
       </c>
@@ -9247,7 +9236,7 @@
       </c>
       <c r="Q172" s="1"/>
     </row>
-    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A173" s="2">
         <v>46269</v>
       </c>
@@ -9294,7 +9283,7 @@
       </c>
       <c r="Q173" s="1"/>
     </row>
-    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A174" s="2">
         <v>46269</v>
       </c>
@@ -9341,7 +9330,7 @@
       </c>
       <c r="Q174" s="1"/>
     </row>
-    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A175" s="2">
         <v>46269</v>
       </c>
@@ -9388,7 +9377,7 @@
       </c>
       <c r="Q175" s="1"/>
     </row>
-    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A176" s="2">
         <v>46269</v>
       </c>
@@ -9435,7 +9424,7 @@
       </c>
       <c r="Q176" s="1"/>
     </row>
-    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A177" s="2">
         <v>46269</v>
       </c>
@@ -9482,7 +9471,7 @@
       </c>
       <c r="Q177" s="1"/>
     </row>
-    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A178" s="2">
         <v>46270</v>
       </c>
@@ -9529,7 +9518,7 @@
       </c>
       <c r="Q178" s="1"/>
     </row>
-    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A179" s="2">
         <v>46270</v>
       </c>
@@ -9576,7 +9565,7 @@
       </c>
       <c r="Q179" s="1"/>
     </row>
-    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A180" s="2">
         <v>46270</v>
       </c>
@@ -9623,7 +9612,7 @@
       </c>
       <c r="Q180" s="1"/>
     </row>
-    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A181" s="2">
         <v>46269</v>
       </c>
@@ -9670,7 +9659,7 @@
       </c>
       <c r="Q181" s="1"/>
     </row>
-    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A182" s="2">
         <v>46269</v>
       </c>
@@ -9717,7 +9706,7 @@
       </c>
       <c r="Q182" s="1"/>
     </row>
-    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A183" s="2">
         <v>46269</v>
       </c>
@@ -9764,7 +9753,7 @@
       </c>
       <c r="Q183" s="1"/>
     </row>
-    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A184" s="2">
         <v>46269</v>
       </c>
@@ -9811,7 +9800,7 @@
       </c>
       <c r="Q184" s="1"/>
     </row>
-    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A185" s="2">
         <v>46269</v>
       </c>
@@ -9858,7 +9847,7 @@
       </c>
       <c r="Q185" s="1"/>
     </row>
-    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A186" s="2">
         <v>46269</v>
       </c>
@@ -9905,7 +9894,7 @@
       </c>
       <c r="Q186" s="1"/>
     </row>
-    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A187" s="2">
         <v>46269</v>
       </c>
@@ -9952,7 +9941,7 @@
       </c>
       <c r="Q187" s="1"/>
     </row>
-    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A188" s="2">
         <v>46269</v>
       </c>
@@ -9999,7 +9988,7 @@
       </c>
       <c r="Q188" s="1"/>
     </row>
-    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A189" s="2">
         <v>46269</v>
       </c>
@@ -10046,7 +10035,7 @@
       </c>
       <c r="Q189" s="1"/>
     </row>
-    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A190" s="2">
         <v>46269</v>
       </c>
@@ -10093,7 +10082,7 @@
       </c>
       <c r="Q190" s="1"/>
     </row>
-    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A191" s="2">
         <v>46269</v>
       </c>
@@ -10140,7 +10129,7 @@
       </c>
       <c r="Q191" s="1"/>
     </row>
-    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A192" s="2">
         <v>46269</v>
       </c>
@@ -10187,7 +10176,7 @@
       </c>
       <c r="Q192" s="1"/>
     </row>
-    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A193" s="2">
         <v>46269</v>
       </c>
@@ -10234,7 +10223,7 @@
       </c>
       <c r="Q193" s="1"/>
     </row>
-    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A194" s="2">
         <v>46269</v>
       </c>
@@ -10281,7 +10270,7 @@
       </c>
       <c r="Q194" s="1"/>
     </row>
-    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A195" s="2">
         <v>46269</v>
       </c>
@@ -10328,7 +10317,7 @@
       </c>
       <c r="Q195" s="1"/>
     </row>
-    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A196" s="2">
         <v>46269</v>
       </c>
@@ -10375,7 +10364,7 @@
       </c>
       <c r="Q196" s="1"/>
     </row>
-    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A197" s="2">
         <v>46269</v>
       </c>
@@ -10422,7 +10411,7 @@
       </c>
       <c r="Q197" s="1"/>
     </row>
-    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A198" s="2">
         <v>46269</v>
       </c>
@@ -10469,7 +10458,7 @@
       </c>
       <c r="Q198" s="1"/>
     </row>
-    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A199" s="2">
         <v>46269</v>
       </c>
@@ -10516,7 +10505,7 @@
       </c>
       <c r="Q199" s="1"/>
     </row>
-    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A200" s="2">
         <v>46269</v>
       </c>
@@ -10563,7 +10552,7 @@
       </c>
       <c r="Q200" s="1"/>
     </row>
-    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A201" s="2">
         <v>46269</v>
       </c>
@@ -10610,7 +10599,7 @@
       </c>
       <c r="Q201" s="1"/>
     </row>
-    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A202" s="2">
         <v>46269</v>
       </c>
@@ -10657,7 +10646,7 @@
       </c>
       <c r="Q202" s="1"/>
     </row>
-    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A203" s="2">
         <v>46269</v>
       </c>
@@ -10704,7 +10693,7 @@
       </c>
       <c r="Q203" s="1"/>
     </row>
-    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A204" s="2">
         <v>46269</v>
       </c>
@@ -10751,7 +10740,7 @@
       </c>
       <c r="Q204" s="1"/>
     </row>
-    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A205" s="2">
         <v>46269</v>
       </c>
@@ -10798,7 +10787,7 @@
       </c>
       <c r="Q205" s="1"/>
     </row>
-    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A206" s="2">
         <v>46269</v>
       </c>
@@ -10845,7 +10834,7 @@
       </c>
       <c r="Q206" s="1"/>
     </row>
-    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A207" s="2">
         <v>46269</v>
       </c>
@@ -10892,7 +10881,7 @@
       </c>
       <c r="Q207" s="1"/>
     </row>
-    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A208" s="2">
         <v>46269</v>
       </c>
@@ -10939,7 +10928,7 @@
       </c>
       <c r="Q208" s="1"/>
     </row>
-    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A209" s="2">
         <v>46269</v>
       </c>
@@ -10986,7 +10975,7 @@
       </c>
       <c r="Q209" s="1"/>
     </row>
-    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A210" s="2">
         <v>46269</v>
       </c>
@@ -11033,7 +11022,7 @@
       </c>
       <c r="Q210" s="1"/>
     </row>
-    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A211" s="2">
         <v>46269</v>
       </c>
@@ -11127,7 +11116,7 @@
       </c>
       <c r="Q212" s="1"/>
     </row>
-    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A213" s="2">
         <v>46269</v>
       </c>
@@ -11174,7 +11163,7 @@
       </c>
       <c r="Q213" s="1"/>
     </row>
-    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A214" s="2">
         <v>46269</v>
       </c>
@@ -11221,7 +11210,7 @@
       </c>
       <c r="Q214" s="1"/>
     </row>
-    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A215" s="2">
         <v>46268</v>
       </c>
@@ -11268,7 +11257,7 @@
       </c>
       <c r="Q215" s="1"/>
     </row>
-    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A216" s="2">
         <v>46268</v>
       </c>
@@ -11315,7 +11304,7 @@
       </c>
       <c r="Q216" s="1"/>
     </row>
-    <row r="217" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A217" s="2">
         <v>46268</v>
       </c>
@@ -11362,7 +11351,7 @@
       </c>
       <c r="Q217" s="1"/>
     </row>
-    <row r="218" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A218" s="2">
         <v>46268</v>
       </c>
@@ -11409,7 +11398,7 @@
       </c>
       <c r="Q218" s="1"/>
     </row>
-    <row r="219" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A219" s="2">
         <v>46268</v>
       </c>
@@ -11456,7 +11445,7 @@
       </c>
       <c r="Q219" s="1"/>
     </row>
-    <row r="220" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A220" s="2">
         <v>46268</v>
       </c>
@@ -11503,7 +11492,7 @@
       </c>
       <c r="Q220" s="1"/>
     </row>
-    <row r="221" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A221" s="2">
         <v>46268</v>
       </c>
@@ -11550,7 +11539,7 @@
       </c>
       <c r="Q221" s="1"/>
     </row>
-    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A222" s="2">
         <v>46268</v>
       </c>
@@ -11597,7 +11586,7 @@
       </c>
       <c r="Q222" s="1"/>
     </row>
-    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A223" s="2">
         <v>46268</v>
       </c>
@@ -11644,7 +11633,7 @@
       </c>
       <c r="Q223" s="1"/>
     </row>
-    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A224" s="2">
         <v>46268</v>
       </c>
@@ -11691,7 +11680,7 @@
       </c>
       <c r="Q224" s="1"/>
     </row>
-    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A225" s="2">
         <v>46268</v>
       </c>
@@ -11738,7 +11727,7 @@
       </c>
       <c r="Q225" s="1"/>
     </row>
-    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A226" s="2">
         <v>46268</v>
       </c>
@@ -11785,7 +11774,7 @@
       </c>
       <c r="Q226" s="1"/>
     </row>
-    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A227" s="2">
         <v>46268</v>
       </c>
@@ -11832,7 +11821,7 @@
       </c>
       <c r="Q227" s="1"/>
     </row>
-    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A228" s="2">
         <v>46268</v>
       </c>
@@ -11879,7 +11868,7 @@
       </c>
       <c r="Q228" s="1"/>
     </row>
-    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A229" s="2">
         <v>46268</v>
       </c>
@@ -11926,7 +11915,7 @@
       </c>
       <c r="Q229" s="1"/>
     </row>
-    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A230" s="2">
         <v>46268</v>
       </c>
@@ -11973,7 +11962,7 @@
       </c>
       <c r="Q230" s="1"/>
     </row>
-    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A231" s="2">
         <v>46268</v>
       </c>
@@ -12020,7 +12009,7 @@
       </c>
       <c r="Q231" s="1"/>
     </row>
-    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A232" s="2">
         <v>46268</v>
       </c>
@@ -12067,7 +12056,7 @@
       </c>
       <c r="Q232" s="1"/>
     </row>
-    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A233" s="2">
         <v>46268</v>
       </c>
@@ -12114,7 +12103,7 @@
       </c>
       <c r="Q233" s="1"/>
     </row>
-    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A234" s="2">
         <v>46268</v>
       </c>
@@ -12161,7 +12150,7 @@
       </c>
       <c r="Q234" s="1"/>
     </row>
-    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A235" s="2">
         <v>46268</v>
       </c>
@@ -12208,7 +12197,7 @@
       </c>
       <c r="Q235" s="1"/>
     </row>
-    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A236" s="2">
         <v>46268</v>
       </c>
@@ -12255,7 +12244,7 @@
       </c>
       <c r="Q236" s="1"/>
     </row>
-    <row r="237" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A237" s="2">
         <v>46268</v>
       </c>
@@ -12302,7 +12291,7 @@
       </c>
       <c r="Q237" s="1"/>
     </row>
-    <row r="238" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A238" s="2">
         <v>46268</v>
       </c>
@@ -12349,7 +12338,7 @@
       </c>
       <c r="Q238" s="1"/>
     </row>
-    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A239" s="2">
         <v>46268</v>
       </c>
@@ -12396,7 +12385,7 @@
       </c>
       <c r="Q239" s="1"/>
     </row>
-    <row r="240" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A240" s="2">
         <v>46268</v>
       </c>
@@ -12443,7 +12432,7 @@
       </c>
       <c r="Q240" s="1"/>
     </row>
-    <row r="241" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A241" s="2">
         <v>46268</v>
       </c>
@@ -12490,7 +12479,7 @@
       </c>
       <c r="Q241" s="1"/>
     </row>
-    <row r="242" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A242" s="2">
         <v>46268</v>
       </c>
@@ -12537,7 +12526,7 @@
       </c>
       <c r="Q242" s="1"/>
     </row>
-    <row r="243" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A243" s="2">
         <v>46268</v>
       </c>
@@ -12584,7 +12573,7 @@
       </c>
       <c r="Q243" s="1"/>
     </row>
-    <row r="244" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A244" s="2">
         <v>46268</v>
       </c>
@@ -12631,7 +12620,7 @@
       </c>
       <c r="Q244" s="1"/>
     </row>
-    <row r="245" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A245" s="2">
         <v>46268</v>
       </c>
@@ -12678,7 +12667,7 @@
       </c>
       <c r="Q245" s="1"/>
     </row>
-    <row r="246" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A246" s="2">
         <v>46268</v>
       </c>
@@ -12725,7 +12714,7 @@
       </c>
       <c r="Q246" s="1"/>
     </row>
-    <row r="247" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A247" s="2">
         <v>46268</v>
       </c>
@@ -12772,7 +12761,7 @@
       </c>
       <c r="Q247" s="1"/>
     </row>
-    <row r="248" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A248" s="2">
         <v>46268</v>
       </c>
@@ -12819,7 +12808,7 @@
       </c>
       <c r="Q248" s="1"/>
     </row>
-    <row r="249" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A249" s="2">
         <v>46268</v>
       </c>
@@ -12866,7 +12855,7 @@
       </c>
       <c r="Q249" s="1"/>
     </row>
-    <row r="250" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A250" s="2">
         <v>46268</v>
       </c>
@@ -12913,7 +12902,7 @@
       </c>
       <c r="Q250" s="1"/>
     </row>
-    <row r="251" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A251" s="2">
         <v>46268</v>
       </c>
@@ -12960,7 +12949,7 @@
       </c>
       <c r="Q251" s="1"/>
     </row>
-    <row r="252" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A252" s="2">
         <v>46268</v>
       </c>
@@ -13007,7 +12996,7 @@
       </c>
       <c r="Q252" s="1"/>
     </row>
-    <row r="253" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A253" s="2">
         <v>46268</v>
       </c>
@@ -13054,7 +13043,7 @@
       </c>
       <c r="Q253" s="1"/>
     </row>
-    <row r="254" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A254" s="2">
         <v>46268</v>
       </c>
@@ -13101,7 +13090,7 @@
       </c>
       <c r="Q254" s="1"/>
     </row>
-    <row r="255" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A255" s="2">
         <v>46268</v>
       </c>
@@ -13148,7 +13137,7 @@
       </c>
       <c r="Q255" s="1"/>
     </row>
-    <row r="256" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A256" s="2">
         <v>46268</v>
       </c>
@@ -13195,7 +13184,7 @@
       </c>
       <c r="Q256" s="1"/>
     </row>
-    <row r="257" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A257" s="2">
         <v>46268</v>
       </c>
@@ -13242,7 +13231,7 @@
       </c>
       <c r="Q257" s="1"/>
     </row>
-    <row r="258" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A258" s="2">
         <v>46268</v>
       </c>
@@ -13289,7 +13278,7 @@
       </c>
       <c r="Q258" s="1"/>
     </row>
-    <row r="259" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A259" s="2">
         <v>46268</v>
       </c>
@@ -13336,7 +13325,7 @@
       </c>
       <c r="Q259" s="1"/>
     </row>
-    <row r="260" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A260" s="2">
         <v>46268</v>
       </c>
@@ -13383,7 +13372,7 @@
       </c>
       <c r="Q260" s="1"/>
     </row>
-    <row r="261" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A261" s="2">
         <v>46268</v>
       </c>
@@ -13430,7 +13419,7 @@
       </c>
       <c r="Q261" s="1"/>
     </row>
-    <row r="262" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A262" s="2">
         <v>46268</v>
       </c>
@@ -13477,7 +13466,7 @@
       </c>
       <c r="Q262" s="1"/>
     </row>
-    <row r="263" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A263" s="2">
         <v>46268</v>
       </c>
@@ -13524,7 +13513,7 @@
       </c>
       <c r="Q263" s="1"/>
     </row>
-    <row r="264" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A264" s="2">
         <v>46268</v>
       </c>
@@ -13571,7 +13560,7 @@
       </c>
       <c r="Q264" s="1"/>
     </row>
-    <row r="265" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A265" s="2">
         <v>46268</v>
       </c>
@@ -13618,7 +13607,7 @@
       </c>
       <c r="Q265" s="1"/>
     </row>
-    <row r="266" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A266" s="2">
         <v>46268</v>
       </c>
@@ -13665,7 +13654,7 @@
       </c>
       <c r="Q266" s="1"/>
     </row>
-    <row r="267" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A267" s="2">
         <v>46268</v>
       </c>
@@ -13712,7 +13701,7 @@
       </c>
       <c r="Q267" s="1"/>
     </row>
-    <row r="268" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A268" s="2">
         <v>46268</v>
       </c>
@@ -13759,7 +13748,7 @@
       </c>
       <c r="Q268" s="1"/>
     </row>
-    <row r="269" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A269" s="2">
         <v>46268</v>
       </c>
@@ -13806,7 +13795,7 @@
       </c>
       <c r="Q269" s="1"/>
     </row>
-    <row r="270" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A270" s="2">
         <v>46268</v>
       </c>
@@ -13853,7 +13842,7 @@
       </c>
       <c r="Q270" s="1"/>
     </row>
-    <row r="271" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A271" s="2">
         <v>46268</v>
       </c>
@@ -13900,7 +13889,7 @@
       </c>
       <c r="Q271" s="1"/>
     </row>
-    <row r="272" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A272" s="2">
         <v>46268</v>
       </c>
@@ -13947,7 +13936,7 @@
       </c>
       <c r="Q272" s="1"/>
     </row>
-    <row r="273" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A273" s="2">
         <v>46268</v>
       </c>
@@ -13994,7 +13983,7 @@
       </c>
       <c r="Q273" s="1"/>
     </row>
-    <row r="274" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A274" s="2">
         <v>46268</v>
       </c>
@@ -14041,7 +14030,7 @@
       </c>
       <c r="Q274" s="1"/>
     </row>
-    <row r="275" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A275" s="2">
         <v>46268</v>
       </c>
@@ -14088,7 +14077,7 @@
       </c>
       <c r="Q275" s="1"/>
     </row>
-    <row r="276" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A276" s="2">
         <v>46268</v>
       </c>
@@ -14135,7 +14124,7 @@
       </c>
       <c r="Q276" s="1"/>
     </row>
-    <row r="277" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A277" s="2">
         <v>46268</v>
       </c>
@@ -14182,7 +14171,7 @@
       </c>
       <c r="Q277" s="1"/>
     </row>
-    <row r="278" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A278" s="2">
         <v>46268</v>
       </c>
@@ -14229,7 +14218,7 @@
       </c>
       <c r="Q278" s="1"/>
     </row>
-    <row r="279" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A279" s="2">
         <v>46268</v>
       </c>
@@ -14276,7 +14265,7 @@
       </c>
       <c r="Q279" s="1"/>
     </row>
-    <row r="280" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A280" s="2">
         <v>46268</v>
       </c>
@@ -14323,7 +14312,7 @@
       </c>
       <c r="Q280" s="1"/>
     </row>
-    <row r="281" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A281" s="2">
         <v>46268</v>
       </c>
@@ -14370,7 +14359,7 @@
       </c>
       <c r="Q281" s="1"/>
     </row>
-    <row r="282" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A282" s="2">
         <v>46268</v>
       </c>
@@ -14417,7 +14406,7 @@
       </c>
       <c r="Q282" s="1"/>
     </row>
-    <row r="283" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A283" s="2">
         <v>46268</v>
       </c>
@@ -14464,7 +14453,7 @@
       </c>
       <c r="Q283" s="1"/>
     </row>
-    <row r="284" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A284" s="2">
         <v>46268</v>
       </c>
@@ -14511,7 +14500,7 @@
       </c>
       <c r="Q284" s="1"/>
     </row>
-    <row r="285" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A285" s="2">
         <v>46268</v>
       </c>
@@ -14558,7 +14547,7 @@
       </c>
       <c r="Q285" s="1"/>
     </row>
-    <row r="286" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A286" s="2">
         <v>46268</v>
       </c>
@@ -14605,7 +14594,7 @@
       </c>
       <c r="Q286" s="1"/>
     </row>
-    <row r="287" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A287" s="2">
         <v>46268</v>
       </c>
@@ -14652,7 +14641,7 @@
       </c>
       <c r="Q287" s="1"/>
     </row>
-    <row r="288" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A288" s="2">
         <v>46268</v>
       </c>
@@ -14699,7 +14688,7 @@
       </c>
       <c r="Q288" s="1"/>
     </row>
-    <row r="289" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A289" s="2">
         <v>46268</v>
       </c>
@@ -14746,7 +14735,7 @@
       </c>
       <c r="Q289" s="1"/>
     </row>
-    <row r="290" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A290" s="2">
         <v>46268</v>
       </c>
@@ -14793,7 +14782,7 @@
       </c>
       <c r="Q290" s="1"/>
     </row>
-    <row r="291" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A291" s="2">
         <v>46268</v>
       </c>
@@ -14840,7 +14829,7 @@
       </c>
       <c r="Q291" s="1"/>
     </row>
-    <row r="292" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A292" s="2">
         <v>46268</v>
       </c>
@@ -14887,7 +14876,7 @@
       </c>
       <c r="Q292" s="1"/>
     </row>
-    <row r="293" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A293" s="2">
         <v>46268</v>
       </c>
@@ -14934,7 +14923,7 @@
       </c>
       <c r="Q293" s="1"/>
     </row>
-    <row r="294" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A294" s="2">
         <v>46268</v>
       </c>
@@ -14981,7 +14970,7 @@
       </c>
       <c r="Q294" s="1"/>
     </row>
-    <row r="295" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A295" s="2">
         <v>46268</v>
       </c>
@@ -15028,7 +15017,7 @@
       </c>
       <c r="Q295" s="1"/>
     </row>
-    <row r="296" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A296" s="2">
         <v>46268</v>
       </c>
@@ -15075,7 +15064,7 @@
       </c>
       <c r="Q296" s="1"/>
     </row>
-    <row r="297" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A297" s="2">
         <v>46268</v>
       </c>
@@ -15122,7 +15111,7 @@
       </c>
       <c r="Q297" s="1"/>
     </row>
-    <row r="298" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A298" s="2">
         <v>46268</v>
       </c>
@@ -15169,7 +15158,7 @@
       </c>
       <c r="Q298" s="1"/>
     </row>
-    <row r="299" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A299" s="2">
         <v>46268</v>
       </c>
@@ -15216,7 +15205,7 @@
       </c>
       <c r="Q299" s="1"/>
     </row>
-    <row r="300" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A300" s="2">
         <v>46268</v>
       </c>
@@ -15263,7 +15252,7 @@
       </c>
       <c r="Q300" s="1"/>
     </row>
-    <row r="301" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A301" s="2">
         <v>46268</v>
       </c>
@@ -15310,7 +15299,7 @@
       </c>
       <c r="Q301" s="1"/>
     </row>
-    <row r="302" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A302" s="2">
         <v>46268</v>
       </c>
@@ -15357,7 +15346,7 @@
       </c>
       <c r="Q302" s="1"/>
     </row>
-    <row r="303" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A303" s="2">
         <v>46268</v>
       </c>
@@ -15404,7 +15393,7 @@
       </c>
       <c r="Q303" s="1"/>
     </row>
-    <row r="304" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A304" s="2">
         <v>46268</v>
       </c>
@@ -15451,7 +15440,7 @@
       </c>
       <c r="Q304" s="1"/>
     </row>
-    <row r="305" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A305" s="2">
         <v>46268</v>
       </c>
@@ -15498,7 +15487,7 @@
       </c>
       <c r="Q305" s="1"/>
     </row>
-    <row r="306" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A306" s="2">
         <v>46268</v>
       </c>
@@ -15545,7 +15534,7 @@
       </c>
       <c r="Q306" s="1"/>
     </row>
-    <row r="307" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A307" s="2">
         <v>46268</v>
       </c>
@@ -15592,7 +15581,7 @@
       </c>
       <c r="Q307" s="1"/>
     </row>
-    <row r="308" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A308" s="2">
         <v>46268</v>
       </c>
@@ -15639,7 +15628,7 @@
       </c>
       <c r="Q308" s="1"/>
     </row>
-    <row r="309" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A309" s="2">
         <v>46268</v>
       </c>
@@ -15686,7 +15675,7 @@
       </c>
       <c r="Q309" s="1"/>
     </row>
-    <row r="310" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A310" s="2">
         <v>46268</v>
       </c>
@@ -15733,7 +15722,7 @@
       </c>
       <c r="Q310" s="1"/>
     </row>
-    <row r="311" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A311" s="2">
         <v>46268</v>
       </c>
@@ -15780,7 +15769,7 @@
       </c>
       <c r="Q311" s="1"/>
     </row>
-    <row r="312" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A312" s="2">
         <v>46268</v>
       </c>
@@ -15827,7 +15816,7 @@
       </c>
       <c r="Q312" s="1"/>
     </row>
-    <row r="313" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A313" s="2">
         <v>46268</v>
       </c>
@@ -15874,7 +15863,7 @@
       </c>
       <c r="Q313" s="1"/>
     </row>
-    <row r="314" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A314" s="2">
         <v>46268</v>
       </c>
@@ -15921,7 +15910,7 @@
       </c>
       <c r="Q314" s="1"/>
     </row>
-    <row r="315" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A315" s="2">
         <v>46268</v>
       </c>
@@ -15968,7 +15957,7 @@
       </c>
       <c r="Q315" s="1"/>
     </row>
-    <row r="316" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A316" s="2">
         <v>46268</v>
       </c>
@@ -16015,7 +16004,7 @@
       </c>
       <c r="Q316" s="1"/>
     </row>
-    <row r="317" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A317" s="2">
         <v>46268</v>
       </c>
@@ -16062,7 +16051,7 @@
       </c>
       <c r="Q317" s="1"/>
     </row>
-    <row r="318" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A318" s="2">
         <v>46268</v>
       </c>
@@ -16109,7 +16098,7 @@
       </c>
       <c r="Q318" s="1"/>
     </row>
-    <row r="319" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A319" s="2">
         <v>46268</v>
       </c>
@@ -16156,7 +16145,7 @@
       </c>
       <c r="Q319" s="1"/>
     </row>
-    <row r="320" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A320" s="2">
         <v>46268</v>
       </c>
@@ -16203,7 +16192,7 @@
       </c>
       <c r="Q320" s="1"/>
     </row>
-    <row r="321" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A321" s="2">
         <v>46268</v>
       </c>
@@ -16250,7 +16239,7 @@
       </c>
       <c r="Q321" s="1"/>
     </row>
-    <row r="322" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A322" s="2">
         <v>46268</v>
       </c>
@@ -16297,7 +16286,7 @@
       </c>
       <c r="Q322" s="1"/>
     </row>
-    <row r="323" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A323" s="2">
         <v>46268</v>
       </c>
@@ -16344,7 +16333,7 @@
       </c>
       <c r="Q323" s="1"/>
     </row>
-    <row r="324" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A324" s="2">
         <v>46268</v>
       </c>
@@ -16391,7 +16380,7 @@
       </c>
       <c r="Q324" s="1"/>
     </row>
-    <row r="325" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A325" s="2">
         <v>46268</v>
       </c>
@@ -16438,7 +16427,7 @@
       </c>
       <c r="Q325" s="1"/>
     </row>
-    <row r="326" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A326" s="2">
         <v>46268</v>
       </c>
@@ -16485,7 +16474,7 @@
       </c>
       <c r="Q326" s="1"/>
     </row>
-    <row r="327" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A327" s="2">
         <v>46268</v>
       </c>
@@ -16532,7 +16521,7 @@
       </c>
       <c r="Q327" s="1"/>
     </row>
-    <row r="328" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A328" s="2">
         <v>46268</v>
       </c>
@@ -16579,7 +16568,7 @@
       </c>
       <c r="Q328" s="1"/>
     </row>
-    <row r="329" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A329" s="2">
         <v>46268</v>
       </c>
@@ -16626,7 +16615,7 @@
       </c>
       <c r="Q329" s="1"/>
     </row>
-    <row r="330" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A330" s="2">
         <v>46268</v>
       </c>
@@ -16673,7 +16662,7 @@
       </c>
       <c r="Q330" s="1"/>
     </row>
-    <row r="331" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A331" s="2">
         <v>46268</v>
       </c>
@@ -16720,7 +16709,7 @@
       </c>
       <c r="Q331" s="1"/>
     </row>
-    <row r="332" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A332" s="2">
         <v>46268</v>
       </c>
@@ -16767,7 +16756,7 @@
       </c>
       <c r="Q332" s="1"/>
     </row>
-    <row r="333" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A333" s="2">
         <v>46268</v>
       </c>
@@ -16814,7 +16803,7 @@
       </c>
       <c r="Q333" s="1"/>
     </row>
-    <row r="334" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A334" s="2">
         <v>46268</v>
       </c>
@@ -16861,7 +16850,7 @@
       </c>
       <c r="Q334" s="1"/>
     </row>
-    <row r="335" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A335" s="2">
         <v>46268</v>
       </c>
@@ -16908,7 +16897,7 @@
       </c>
       <c r="Q335" s="1"/>
     </row>
-    <row r="336" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A336" s="2">
         <v>46268</v>
       </c>
@@ -17049,7 +17038,7 @@
       </c>
       <c r="Q338" s="1"/>
     </row>
-    <row r="339" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A339" s="2">
         <v>46268</v>
       </c>
@@ -17096,7 +17085,7 @@
       </c>
       <c r="Q339" s="1"/>
     </row>
-    <row r="340" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A340" s="2">
         <v>46268</v>
       </c>
@@ -17143,7 +17132,7 @@
       </c>
       <c r="Q340" s="1"/>
     </row>
-    <row r="341" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A341" s="2">
         <v>46268</v>
       </c>
@@ -17190,7 +17179,7 @@
       </c>
       <c r="Q341" s="1"/>
     </row>
-    <row r="342" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A342" s="2">
         <v>46267</v>
       </c>
@@ -17237,7 +17226,7 @@
       </c>
       <c r="Q342" s="1"/>
     </row>
-    <row r="343" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A343" s="2">
         <v>46267</v>
       </c>
@@ -17284,7 +17273,7 @@
       </c>
       <c r="Q343" s="1"/>
     </row>
-    <row r="344" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A344" s="2">
         <v>46267</v>
       </c>
@@ -17331,7 +17320,7 @@
       </c>
       <c r="Q344" s="1"/>
     </row>
-    <row r="345" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A345" s="2">
         <v>46267</v>
       </c>
@@ -17378,7 +17367,7 @@
       </c>
       <c r="Q345" s="1"/>
     </row>
-    <row r="346" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A346" s="2">
         <v>46267</v>
       </c>
@@ -17425,7 +17414,7 @@
       </c>
       <c r="Q346" s="1"/>
     </row>
-    <row r="347" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A347" s="2">
         <v>46267</v>
       </c>
@@ -17472,7 +17461,7 @@
       </c>
       <c r="Q347" s="1"/>
     </row>
-    <row r="348" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A348" s="2">
         <v>46267</v>
       </c>
@@ -17519,7 +17508,7 @@
       </c>
       <c r="Q348" s="1"/>
     </row>
-    <row r="349" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A349" s="2">
         <v>46267</v>
       </c>
@@ -17566,7 +17555,7 @@
       </c>
       <c r="Q349" s="1"/>
     </row>
-    <row r="350" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A350" s="2">
         <v>46267</v>
       </c>
@@ -17613,7 +17602,7 @@
       </c>
       <c r="Q350" s="1"/>
     </row>
-    <row r="351" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A351" s="2">
         <v>46267</v>
       </c>
@@ -17660,7 +17649,7 @@
       </c>
       <c r="Q351" s="1"/>
     </row>
-    <row r="352" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A352" s="2">
         <v>46267</v>
       </c>
@@ -17707,7 +17696,7 @@
       </c>
       <c r="Q352" s="1"/>
     </row>
-    <row r="353" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A353" s="2">
         <v>46267</v>
       </c>
@@ -17754,7 +17743,7 @@
       </c>
       <c r="Q353" s="1"/>
     </row>
-    <row r="354" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A354" s="2">
         <v>46267</v>
       </c>
@@ -17801,7 +17790,7 @@
       </c>
       <c r="Q354" s="1"/>
     </row>
-    <row r="355" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A355" s="2">
         <v>46267</v>
       </c>
@@ -17848,7 +17837,7 @@
       </c>
       <c r="Q355" s="1"/>
     </row>
-    <row r="356" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A356" s="2">
         <v>46267</v>
       </c>
@@ -17895,7 +17884,7 @@
       </c>
       <c r="Q356" s="1"/>
     </row>
-    <row r="357" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A357" s="2">
         <v>46267</v>
       </c>
@@ -17942,7 +17931,7 @@
       </c>
       <c r="Q357" s="1"/>
     </row>
-    <row r="358" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A358" s="2">
         <v>46267</v>
       </c>
@@ -17989,7 +17978,7 @@
       </c>
       <c r="Q358" s="1"/>
     </row>
-    <row r="359" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A359" s="2">
         <v>46267</v>
       </c>
@@ -18036,7 +18025,7 @@
       </c>
       <c r="Q359" s="1"/>
     </row>
-    <row r="360" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A360" s="2">
         <v>46267</v>
       </c>
@@ -18083,7 +18072,7 @@
       </c>
       <c r="Q360" s="1"/>
     </row>
-    <row r="361" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A361" s="2">
         <v>46267</v>
       </c>
@@ -18130,7 +18119,7 @@
       </c>
       <c r="Q361" s="1"/>
     </row>
-    <row r="362" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A362" s="2">
         <v>46267</v>
       </c>
@@ -18177,7 +18166,7 @@
       </c>
       <c r="Q362" s="1"/>
     </row>
-    <row r="363" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A363" s="2">
         <v>46267</v>
       </c>
@@ -18224,7 +18213,7 @@
       </c>
       <c r="Q363" s="1"/>
     </row>
-    <row r="364" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A364" s="2">
         <v>46267</v>
       </c>
@@ -18271,7 +18260,7 @@
       </c>
       <c r="Q364" s="1"/>
     </row>
-    <row r="365" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A365" s="2">
         <v>46267</v>
       </c>
@@ -18318,7 +18307,7 @@
       </c>
       <c r="Q365" s="1"/>
     </row>
-    <row r="366" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A366" s="2">
         <v>46267</v>
       </c>
@@ -18365,7 +18354,7 @@
       </c>
       <c r="Q366" s="1"/>
     </row>
-    <row r="367" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A367" s="2">
         <v>46267</v>
       </c>
@@ -18412,7 +18401,7 @@
       </c>
       <c r="Q367" s="1"/>
     </row>
-    <row r="368" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A368" s="2">
         <v>46267</v>
       </c>
@@ -18459,7 +18448,7 @@
       </c>
       <c r="Q368" s="1"/>
     </row>
-    <row r="369" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A369" s="2">
         <v>46267</v>
       </c>
@@ -18506,7 +18495,7 @@
       </c>
       <c r="Q369" s="1"/>
     </row>
-    <row r="370" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A370" s="2">
         <v>46267</v>
       </c>
@@ -18553,7 +18542,7 @@
       </c>
       <c r="Q370" s="1"/>
     </row>
-    <row r="371" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A371" s="2">
         <v>46267</v>
       </c>
@@ -18600,7 +18589,7 @@
       </c>
       <c r="Q371" s="1"/>
     </row>
-    <row r="372" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A372" s="2">
         <v>46267</v>
       </c>
@@ -18647,7 +18636,7 @@
       </c>
       <c r="Q372" s="1"/>
     </row>
-    <row r="373" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A373" s="2">
         <v>46267</v>
       </c>
@@ -18694,7 +18683,7 @@
       </c>
       <c r="Q373" s="1"/>
     </row>
-    <row r="374" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A374" s="2">
         <v>46267</v>
       </c>
@@ -18741,7 +18730,7 @@
       </c>
       <c r="Q374" s="1"/>
     </row>
-    <row r="375" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A375" s="2">
         <v>46267</v>
       </c>
@@ -18788,7 +18777,7 @@
       </c>
       <c r="Q375" s="1"/>
     </row>
-    <row r="376" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A376" s="2">
         <v>46267</v>
       </c>
@@ -18835,7 +18824,7 @@
       </c>
       <c r="Q376" s="1"/>
     </row>
-    <row r="377" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A377" s="2">
         <v>46267</v>
       </c>
@@ -18882,7 +18871,7 @@
       </c>
       <c r="Q377" s="1"/>
     </row>
-    <row r="378" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A378" s="2">
         <v>46267</v>
       </c>
@@ -18929,7 +18918,7 @@
       </c>
       <c r="Q378" s="1"/>
     </row>
-    <row r="379" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A379" s="2">
         <v>46267</v>
       </c>
@@ -18976,7 +18965,7 @@
       </c>
       <c r="Q379" s="1"/>
     </row>
-    <row r="380" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A380" s="2">
         <v>46267</v>
       </c>
@@ -19023,7 +19012,7 @@
       </c>
       <c r="Q380" s="1"/>
     </row>
-    <row r="381" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A381" s="2">
         <v>46267</v>
       </c>
@@ -19070,7 +19059,7 @@
       </c>
       <c r="Q381" s="1"/>
     </row>
-    <row r="382" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A382" s="2">
         <v>46267</v>
       </c>
@@ -19117,7 +19106,7 @@
       </c>
       <c r="Q382" s="1"/>
     </row>
-    <row r="383" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A383" s="2">
         <v>46267</v>
       </c>
@@ -19164,7 +19153,7 @@
       </c>
       <c r="Q383" s="1"/>
     </row>
-    <row r="384" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A384" s="2">
         <v>46267</v>
       </c>
@@ -19211,7 +19200,7 @@
       </c>
       <c r="Q384" s="1"/>
     </row>
-    <row r="385" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A385" s="2">
         <v>46267</v>
       </c>
@@ -19258,7 +19247,7 @@
       </c>
       <c r="Q385" s="1"/>
     </row>
-    <row r="386" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A386" s="2">
         <v>46267</v>
       </c>
@@ -19305,7 +19294,7 @@
       </c>
       <c r="Q386" s="1"/>
     </row>
-    <row r="387" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A387" s="2">
         <v>46267</v>
       </c>
@@ -19352,7 +19341,7 @@
       </c>
       <c r="Q387" s="1"/>
     </row>
-    <row r="388" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A388" s="2">
         <v>46267</v>
       </c>
@@ -19399,7 +19388,7 @@
       </c>
       <c r="Q388" s="1"/>
     </row>
-    <row r="389" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A389" s="2">
         <v>46267</v>
       </c>
@@ -19446,7 +19435,7 @@
       </c>
       <c r="Q389" s="1"/>
     </row>
-    <row r="390" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A390" s="2">
         <v>46267</v>
       </c>
@@ -19493,7 +19482,7 @@
       </c>
       <c r="Q390" s="1"/>
     </row>
-    <row r="391" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A391" s="2">
         <v>46267</v>
       </c>
@@ -19540,7 +19529,7 @@
       </c>
       <c r="Q391" s="1"/>
     </row>
-    <row r="392" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A392" s="2">
         <v>46267</v>
       </c>
@@ -19587,7 +19576,7 @@
       </c>
       <c r="Q392" s="1"/>
     </row>
-    <row r="393" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A393" s="2">
         <v>46267</v>
       </c>
@@ -19634,7 +19623,7 @@
       </c>
       <c r="Q393" s="1"/>
     </row>
-    <row r="394" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A394" s="2">
         <v>46267</v>
       </c>
@@ -19681,7 +19670,7 @@
       </c>
       <c r="Q394" s="1"/>
     </row>
-    <row r="395" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A395" s="2">
         <v>46267</v>
       </c>
@@ -19728,7 +19717,7 @@
       </c>
       <c r="Q395" s="1"/>
     </row>
-    <row r="396" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A396" s="2">
         <v>46267</v>
       </c>
@@ -19775,7 +19764,7 @@
       </c>
       <c r="Q396" s="1"/>
     </row>
-    <row r="397" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A397" s="2">
         <v>46267</v>
       </c>
@@ -19822,7 +19811,7 @@
       </c>
       <c r="Q397" s="1"/>
     </row>
-    <row r="398" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A398" s="2">
         <v>46267</v>
       </c>
@@ -19869,7 +19858,7 @@
       </c>
       <c r="Q398" s="1"/>
     </row>
-    <row r="399" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A399" s="2">
         <v>46267</v>
       </c>
@@ -19916,7 +19905,7 @@
       </c>
       <c r="Q399" s="1"/>
     </row>
-    <row r="400" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A400" s="2">
         <v>46267</v>
       </c>
@@ -19963,7 +19952,7 @@
       </c>
       <c r="Q400" s="1"/>
     </row>
-    <row r="401" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A401" s="2">
         <v>46267</v>
       </c>
@@ -20010,7 +19999,7 @@
       </c>
       <c r="Q401" s="1"/>
     </row>
-    <row r="402" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A402" s="2">
         <v>46267</v>
       </c>
@@ -20057,7 +20046,7 @@
       </c>
       <c r="Q402" s="1"/>
     </row>
-    <row r="403" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A403" s="2">
         <v>46267</v>
       </c>
@@ -20104,7 +20093,7 @@
       </c>
       <c r="Q403" s="1"/>
     </row>
-    <row r="404" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A404" s="2">
         <v>46267</v>
       </c>
@@ -20151,7 +20140,7 @@
       </c>
       <c r="Q404" s="1"/>
     </row>
-    <row r="405" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A405" s="2">
         <v>46267</v>
       </c>
@@ -20198,7 +20187,7 @@
       </c>
       <c r="Q405" s="1"/>
     </row>
-    <row r="406" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A406" s="2">
         <v>46267</v>
       </c>
@@ -20245,7 +20234,7 @@
       </c>
       <c r="Q406" s="1"/>
     </row>
-    <row r="407" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A407" s="2">
         <v>46267</v>
       </c>
@@ -20292,7 +20281,7 @@
       </c>
       <c r="Q407" s="1"/>
     </row>
-    <row r="408" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A408" s="2">
         <v>46267</v>
       </c>
@@ -20339,7 +20328,7 @@
       </c>
       <c r="Q408" s="1"/>
     </row>
-    <row r="409" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A409" s="2">
         <v>46267</v>
       </c>
@@ -20386,7 +20375,7 @@
       </c>
       <c r="Q409" s="1"/>
     </row>
-    <row r="410" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A410" s="2">
         <v>46267</v>
       </c>
@@ -20433,7 +20422,7 @@
       </c>
       <c r="Q410" s="1"/>
     </row>
-    <row r="411" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A411" s="2">
         <v>46267</v>
       </c>
@@ -20480,7 +20469,7 @@
       </c>
       <c r="Q411" s="1"/>
     </row>
-    <row r="412" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A412" s="2">
         <v>46267</v>
       </c>
@@ -20527,7 +20516,7 @@
       </c>
       <c r="Q412" s="1"/>
     </row>
-    <row r="413" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A413" s="2">
         <v>46267</v>
       </c>
@@ -20574,7 +20563,7 @@
       </c>
       <c r="Q413" s="1"/>
     </row>
-    <row r="414" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A414" s="2">
         <v>46267</v>
       </c>
@@ -20621,7 +20610,7 @@
       </c>
       <c r="Q414" s="1"/>
     </row>
-    <row r="415" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A415" s="2">
         <v>46267</v>
       </c>
@@ -20668,7 +20657,7 @@
       </c>
       <c r="Q415" s="1"/>
     </row>
-    <row r="416" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A416" s="2">
         <v>46267</v>
       </c>
@@ -20715,7 +20704,7 @@
       </c>
       <c r="Q416" s="1"/>
     </row>
-    <row r="417" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A417" s="2">
         <v>46267</v>
       </c>
@@ -20762,7 +20751,7 @@
       </c>
       <c r="Q417" s="1"/>
     </row>
-    <row r="418" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A418" s="2">
         <v>46267</v>
       </c>
@@ -20809,7 +20798,7 @@
       </c>
       <c r="Q418" s="1"/>
     </row>
-    <row r="419" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A419" s="2">
         <v>46267</v>
       </c>
@@ -20856,7 +20845,7 @@
       </c>
       <c r="Q419" s="1"/>
     </row>
-    <row r="420" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A420" s="2">
         <v>46267</v>
       </c>
@@ -20903,7 +20892,7 @@
       </c>
       <c r="Q420" s="1"/>
     </row>
-    <row r="421" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A421" s="2">
         <v>46267</v>
       </c>
@@ -20950,7 +20939,7 @@
       </c>
       <c r="Q421" s="1"/>
     </row>
-    <row r="422" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A422" s="2">
         <v>46267</v>
       </c>
@@ -20997,7 +20986,7 @@
       </c>
       <c r="Q422" s="1"/>
     </row>
-    <row r="423" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A423" s="2">
         <v>46267</v>
       </c>
@@ -21044,7 +21033,7 @@
       </c>
       <c r="Q423" s="1"/>
     </row>
-    <row r="424" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A424" s="2">
         <v>46267</v>
       </c>
@@ -21091,7 +21080,7 @@
       </c>
       <c r="Q424" s="1"/>
     </row>
-    <row r="425" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A425" s="2">
         <v>46267</v>
       </c>
@@ -21138,7 +21127,7 @@
       </c>
       <c r="Q425" s="1"/>
     </row>
-    <row r="426" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A426" s="2">
         <v>46267</v>
       </c>
@@ -21185,7 +21174,7 @@
       </c>
       <c r="Q426" s="1"/>
     </row>
-    <row r="427" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A427" s="2">
         <v>46267</v>
       </c>
@@ -21232,7 +21221,7 @@
       </c>
       <c r="Q427" s="1"/>
     </row>
-    <row r="428" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A428" s="2">
         <v>46268</v>
       </c>
@@ -21279,7 +21268,7 @@
       </c>
       <c r="Q428" s="1"/>
     </row>
-    <row r="429" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A429" s="2">
         <v>46267</v>
       </c>
@@ -21326,7 +21315,7 @@
       </c>
       <c r="Q429" s="1"/>
     </row>
-    <row r="430" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A430" s="2">
         <v>46267</v>
       </c>
@@ -21373,7 +21362,7 @@
       </c>
       <c r="Q430" s="1"/>
     </row>
-    <row r="431" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A431" s="2">
         <v>46267</v>
       </c>
@@ -21420,7 +21409,7 @@
       </c>
       <c r="Q431" s="1"/>
     </row>
-    <row r="432" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A432" s="2">
         <v>46267</v>
       </c>
@@ -21467,7 +21456,7 @@
       </c>
       <c r="Q432" s="1"/>
     </row>
-    <row r="433" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A433" s="2">
         <v>46267</v>
       </c>
@@ -21514,7 +21503,7 @@
       </c>
       <c r="Q433" s="1"/>
     </row>
-    <row r="434" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A434" s="2">
         <v>46267</v>
       </c>
@@ -21561,7 +21550,7 @@
       </c>
       <c r="Q434" s="1"/>
     </row>
-    <row r="435" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A435" s="2">
         <v>46267</v>
       </c>
@@ -21608,7 +21597,7 @@
       </c>
       <c r="Q435" s="1"/>
     </row>
-    <row r="436" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A436" s="2">
         <v>46267</v>
       </c>
@@ -21655,7 +21644,7 @@
       </c>
       <c r="Q436" s="1"/>
     </row>
-    <row r="437" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A437" s="2">
         <v>46267</v>
       </c>
@@ -21702,7 +21691,7 @@
       </c>
       <c r="Q437" s="1"/>
     </row>
-    <row r="438" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A438" s="2">
         <v>46267</v>
       </c>
@@ -21749,7 +21738,7 @@
       </c>
       <c r="Q438" s="1"/>
     </row>
-    <row r="439" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A439" s="2">
         <v>46267</v>
       </c>
@@ -21796,7 +21785,7 @@
       </c>
       <c r="Q439" s="1"/>
     </row>
-    <row r="440" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A440" s="2">
         <v>46267</v>
       </c>
@@ -21843,7 +21832,7 @@
       </c>
       <c r="Q440" s="1"/>
     </row>
-    <row r="441" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A441" s="2">
         <v>46267</v>
       </c>
@@ -21890,7 +21879,7 @@
       </c>
       <c r="Q441" s="1"/>
     </row>
-    <row r="442" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A442" s="2">
         <v>46267</v>
       </c>
@@ -21937,7 +21926,7 @@
       </c>
       <c r="Q442" s="1"/>
     </row>
-    <row r="443" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A443" s="2">
         <v>46267</v>
       </c>
@@ -21984,7 +21973,7 @@
       </c>
       <c r="Q443" s="1"/>
     </row>
-    <row r="444" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A444" s="2">
         <v>46267</v>
       </c>
@@ -22031,7 +22020,7 @@
       </c>
       <c r="Q444" s="1"/>
     </row>
-    <row r="445" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A445" s="2">
         <v>46266</v>
       </c>
@@ -22078,7 +22067,7 @@
       </c>
       <c r="Q445" s="1"/>
     </row>
-    <row r="446" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A446" s="2">
         <v>46267</v>
       </c>
@@ -22125,7 +22114,7 @@
       </c>
       <c r="Q446" s="1"/>
     </row>
-    <row r="447" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A447" s="2">
         <v>46267</v>
       </c>
@@ -22172,7 +22161,7 @@
       </c>
       <c r="Q447" s="1"/>
     </row>
-    <row r="448" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A448" s="2">
         <v>46267</v>
       </c>
@@ -22219,7 +22208,7 @@
       </c>
       <c r="Q448" s="1"/>
     </row>
-    <row r="449" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A449" s="2">
         <v>46267</v>
       </c>
@@ -22266,7 +22255,7 @@
       </c>
       <c r="Q449" s="1"/>
     </row>
-    <row r="450" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A450" s="2">
         <v>46267</v>
       </c>
@@ -22313,7 +22302,7 @@
       </c>
       <c r="Q450" s="1"/>
     </row>
-    <row r="451" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A451" s="2">
         <v>46267</v>
       </c>
@@ -22360,7 +22349,7 @@
       </c>
       <c r="Q451" s="1"/>
     </row>
-    <row r="452" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A452" s="2">
         <v>46267</v>
       </c>
@@ -22407,7 +22396,7 @@
       </c>
       <c r="Q452" s="1"/>
     </row>
-    <row r="453" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A453" s="2">
         <v>46267</v>
       </c>
@@ -22454,7 +22443,7 @@
       </c>
       <c r="Q453" s="1"/>
     </row>
-    <row r="454" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A454" s="2">
         <v>46267</v>
       </c>
@@ -22548,7 +22537,7 @@
       </c>
       <c r="Q455" s="1"/>
     </row>
-    <row r="456" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A456" s="2">
         <v>46267</v>
       </c>
@@ -22595,7 +22584,7 @@
       </c>
       <c r="Q456" s="1"/>
     </row>
-    <row r="457" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A457" s="2">
         <v>46267</v>
       </c>
@@ -22642,7 +22631,7 @@
       </c>
       <c r="Q457" s="1"/>
     </row>
-    <row r="458" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A458" s="2">
         <v>46267</v>
       </c>
@@ -22689,7 +22678,7 @@
       </c>
       <c r="Q458" s="1"/>
     </row>
-    <row r="459" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A459" s="2">
         <v>46266</v>
       </c>
@@ -22736,7 +22725,7 @@
       </c>
       <c r="Q459" s="1"/>
     </row>
-    <row r="460" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A460" s="2">
         <v>46266</v>
       </c>
@@ -22783,7 +22772,7 @@
       </c>
       <c r="Q460" s="1"/>
     </row>
-    <row r="461" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A461" s="2">
         <v>46266</v>
       </c>
@@ -22830,7 +22819,7 @@
       </c>
       <c r="Q461" s="1"/>
     </row>
-    <row r="462" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A462" s="2">
         <v>46266</v>
       </c>
@@ -22877,7 +22866,7 @@
       </c>
       <c r="Q462" s="1"/>
     </row>
-    <row r="463" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A463" s="2">
         <v>46266</v>
       </c>
@@ -22924,7 +22913,7 @@
       </c>
       <c r="Q463" s="1"/>
     </row>
-    <row r="464" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A464" s="2">
         <v>46266</v>
       </c>
@@ -22971,7 +22960,7 @@
       </c>
       <c r="Q464" s="1"/>
     </row>
-    <row r="465" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A465" s="2">
         <v>46266</v>
       </c>
@@ -23018,7 +23007,7 @@
       </c>
       <c r="Q465" s="1"/>
     </row>
-    <row r="466" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A466" s="2">
         <v>46266</v>
       </c>
@@ -23065,7 +23054,7 @@
       </c>
       <c r="Q466" s="1"/>
     </row>
-    <row r="467" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A467" s="2">
         <v>46266</v>
       </c>
@@ -23112,7 +23101,7 @@
       </c>
       <c r="Q467" s="1"/>
     </row>
-    <row r="468" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A468" s="2">
         <v>46266</v>
       </c>
@@ -23159,7 +23148,7 @@
       </c>
       <c r="Q468" s="1"/>
     </row>
-    <row r="469" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A469" s="2">
         <v>46266</v>
       </c>
@@ -23206,7 +23195,7 @@
       </c>
       <c r="Q469" s="1"/>
     </row>
-    <row r="470" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A470" s="2">
         <v>46266</v>
       </c>
@@ -23253,7 +23242,7 @@
       </c>
       <c r="Q470" s="1"/>
     </row>
-    <row r="471" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A471" s="2">
         <v>46266</v>
       </c>
@@ -23300,7 +23289,7 @@
       </c>
       <c r="Q471" s="1"/>
     </row>
-    <row r="472" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A472" s="2">
         <v>46266</v>
       </c>
@@ -23347,7 +23336,7 @@
       </c>
       <c r="Q472" s="1"/>
     </row>
-    <row r="473" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A473" s="2">
         <v>46266</v>
       </c>
@@ -23394,7 +23383,7 @@
       </c>
       <c r="Q473" s="1"/>
     </row>
-    <row r="474" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A474" s="2">
         <v>46266</v>
       </c>
@@ -23441,7 +23430,7 @@
       </c>
       <c r="Q474" s="1"/>
     </row>
-    <row r="475" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A475" s="2">
         <v>46266</v>
       </c>
@@ -23488,7 +23477,7 @@
       </c>
       <c r="Q475" s="1"/>
     </row>
-    <row r="476" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A476" s="2">
         <v>46266</v>
       </c>
@@ -23535,7 +23524,7 @@
       </c>
       <c r="Q476" s="1"/>
     </row>
-    <row r="477" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A477" s="2">
         <v>46266</v>
       </c>
@@ -23582,7 +23571,7 @@
       </c>
       <c r="Q477" s="1"/>
     </row>
-    <row r="478" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A478" s="2">
         <v>46266</v>
       </c>
@@ -23629,7 +23618,7 @@
       </c>
       <c r="Q478" s="1"/>
     </row>
-    <row r="479" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A479" s="2">
         <v>46266</v>
       </c>
@@ -23676,7 +23665,7 @@
       </c>
       <c r="Q479" s="1"/>
     </row>
-    <row r="480" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A480" s="2">
         <v>46266</v>
       </c>
@@ -23723,7 +23712,7 @@
       </c>
       <c r="Q480" s="1"/>
     </row>
-    <row r="481" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A481" s="2">
         <v>46266</v>
       </c>
@@ -23770,7 +23759,7 @@
       </c>
       <c r="Q481" s="1"/>
     </row>
-    <row r="482" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A482" s="2">
         <v>46266</v>
       </c>
@@ -23817,7 +23806,7 @@
       </c>
       <c r="Q482" s="1"/>
     </row>
-    <row r="483" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A483" s="2">
         <v>46266</v>
       </c>
@@ -23864,7 +23853,7 @@
       </c>
       <c r="Q483" s="1"/>
     </row>
-    <row r="484" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A484" s="2">
         <v>46266</v>
       </c>
@@ -23911,7 +23900,7 @@
       </c>
       <c r="Q484" s="1"/>
     </row>
-    <row r="485" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A485" s="2">
         <v>46266</v>
       </c>
@@ -23958,7 +23947,7 @@
       </c>
       <c r="Q485" s="1"/>
     </row>
-    <row r="486" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A486" s="2">
         <v>46266</v>
       </c>
@@ -24005,7 +23994,7 @@
       </c>
       <c r="Q486" s="1"/>
     </row>
-    <row r="487" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A487" s="2">
         <v>46266</v>
       </c>
@@ -24052,7 +24041,7 @@
       </c>
       <c r="Q487" s="1"/>
     </row>
-    <row r="488" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A488" s="2">
         <v>46266</v>
       </c>
@@ -24099,7 +24088,7 @@
       </c>
       <c r="Q488" s="1"/>
     </row>
-    <row r="489" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A489" s="2">
         <v>46266</v>
       </c>
@@ -24146,7 +24135,7 @@
       </c>
       <c r="Q489" s="1"/>
     </row>
-    <row r="490" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A490" s="2">
         <v>46266</v>
       </c>
@@ -24193,7 +24182,7 @@
       </c>
       <c r="Q490" s="1"/>
     </row>
-    <row r="491" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A491" s="2">
         <v>46266</v>
       </c>
@@ -24240,7 +24229,7 @@
       </c>
       <c r="Q491" s="1"/>
     </row>
-    <row r="492" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A492" s="2">
         <v>46266</v>
       </c>
@@ -24287,7 +24276,7 @@
       </c>
       <c r="Q492" s="1"/>
     </row>
-    <row r="493" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A493" s="2">
         <v>46266</v>
       </c>
@@ -24334,7 +24323,7 @@
       </c>
       <c r="Q493" s="1"/>
     </row>
-    <row r="494" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A494" s="2">
         <v>46266</v>
       </c>
@@ -24381,7 +24370,7 @@
       </c>
       <c r="Q494" s="1"/>
     </row>
-    <row r="495" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A495" s="2">
         <v>46266</v>
       </c>
@@ -24428,7 +24417,7 @@
       </c>
       <c r="Q495" s="1"/>
     </row>
-    <row r="496" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A496" s="2">
         <v>46266</v>
       </c>
@@ -24475,7 +24464,7 @@
       </c>
       <c r="Q496" s="1"/>
     </row>
-    <row r="497" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A497" s="2">
         <v>46266</v>
       </c>
@@ -24522,7 +24511,7 @@
       </c>
       <c r="Q497" s="1"/>
     </row>
-    <row r="498" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A498" s="2">
         <v>46266</v>
       </c>
@@ -24569,7 +24558,7 @@
       </c>
       <c r="Q498" s="1"/>
     </row>
-    <row r="499" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A499" s="2">
         <v>46266</v>
       </c>
@@ -24616,7 +24605,7 @@
       </c>
       <c r="Q499" s="1"/>
     </row>
-    <row r="500" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A500" s="2">
         <v>46266</v>
       </c>
@@ -24663,7 +24652,7 @@
       </c>
       <c r="Q500" s="1"/>
     </row>
-    <row r="501" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A501" s="2">
         <v>46266</v>
       </c>
@@ -24710,7 +24699,7 @@
       </c>
       <c r="Q501" s="1"/>
     </row>
-    <row r="502" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A502" s="2">
         <v>46266</v>
       </c>
@@ -24757,7 +24746,7 @@
       </c>
       <c r="Q502" s="1"/>
     </row>
-    <row r="503" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A503" s="2">
         <v>46266</v>
       </c>
@@ -24804,7 +24793,7 @@
       </c>
       <c r="Q503" s="1"/>
     </row>
-    <row r="504" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A504" s="2">
         <v>46266</v>
       </c>
@@ -24851,7 +24840,7 @@
       </c>
       <c r="Q504" s="1"/>
     </row>
-    <row r="505" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A505" s="2">
         <v>46266</v>
       </c>
@@ -24898,7 +24887,7 @@
       </c>
       <c r="Q505" s="1"/>
     </row>
-    <row r="506" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A506" s="2">
         <v>46266</v>
       </c>
@@ -24945,7 +24934,7 @@
       </c>
       <c r="Q506" s="1"/>
     </row>
-    <row r="507" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A507" s="2">
         <v>46266</v>
       </c>
@@ -24992,7 +24981,7 @@
       </c>
       <c r="Q507" s="1"/>
     </row>
-    <row r="508" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A508" s="2">
         <v>46266</v>
       </c>
@@ -25039,7 +25028,7 @@
       </c>
       <c r="Q508" s="1"/>
     </row>
-    <row r="509" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A509" s="2">
         <v>46266</v>
       </c>
@@ -25086,7 +25075,7 @@
       </c>
       <c r="Q509" s="1"/>
     </row>
-    <row r="510" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A510" s="2">
         <v>46266</v>
       </c>
@@ -25133,7 +25122,7 @@
       </c>
       <c r="Q510" s="1"/>
     </row>
-    <row r="511" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A511" s="2">
         <v>46266</v>
       </c>
@@ -25180,7 +25169,7 @@
       </c>
       <c r="Q511" s="1"/>
     </row>
-    <row r="512" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A512" s="2">
         <v>46266</v>
       </c>
@@ -25227,7 +25216,7 @@
       </c>
       <c r="Q512" s="1"/>
     </row>
-    <row r="513" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A513" s="2">
         <v>46266</v>
       </c>
@@ -25274,7 +25263,7 @@
       </c>
       <c r="Q513" s="1"/>
     </row>
-    <row r="514" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A514" s="2">
         <v>46266</v>
       </c>
@@ -25321,7 +25310,7 @@
       </c>
       <c r="Q514" s="1"/>
     </row>
-    <row r="515" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A515" s="2">
         <v>46266</v>
       </c>
@@ -25368,7 +25357,7 @@
       </c>
       <c r="Q515" s="1"/>
     </row>
-    <row r="516" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A516" s="2">
         <v>46266</v>
       </c>
@@ -25415,7 +25404,7 @@
       </c>
       <c r="Q516" s="1"/>
     </row>
-    <row r="517" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A517" s="2">
         <v>46266</v>
       </c>
@@ -25462,7 +25451,7 @@
       </c>
       <c r="Q517" s="1"/>
     </row>
-    <row r="518" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A518" s="2">
         <v>46266</v>
       </c>
@@ -25509,7 +25498,7 @@
       </c>
       <c r="Q518" s="1"/>
     </row>
-    <row r="519" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A519" s="2">
         <v>46266</v>
       </c>
@@ -25556,7 +25545,7 @@
       </c>
       <c r="Q519" s="1"/>
     </row>
-    <row r="520" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A520" s="2">
         <v>46266</v>
       </c>
@@ -25603,7 +25592,7 @@
       </c>
       <c r="Q520" s="1"/>
     </row>
-    <row r="521" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A521" s="2">
         <v>46266</v>
       </c>
@@ -25650,7 +25639,7 @@
       </c>
       <c r="Q521" s="1"/>
     </row>
-    <row r="522" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A522" s="2">
         <v>46266</v>
       </c>
@@ -25697,7 +25686,7 @@
       </c>
       <c r="Q522" s="1"/>
     </row>
-    <row r="523" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A523" s="2">
         <v>46266</v>
       </c>
@@ -25744,7 +25733,7 @@
       </c>
       <c r="Q523" s="1"/>
     </row>
-    <row r="524" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A524" s="2">
         <v>46266</v>
       </c>
@@ -25791,7 +25780,7 @@
       </c>
       <c r="Q524" s="1"/>
     </row>
-    <row r="525" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A525" s="2">
         <v>46266</v>
       </c>
@@ -25838,7 +25827,7 @@
       </c>
       <c r="Q525" s="1"/>
     </row>
-    <row r="526" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A526" s="2">
         <v>46266</v>
       </c>
@@ -25885,7 +25874,7 @@
       </c>
       <c r="Q526" s="1"/>
     </row>
-    <row r="527" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A527" s="2">
         <v>46266</v>
       </c>
@@ -25932,7 +25921,7 @@
       </c>
       <c r="Q527" s="1"/>
     </row>
-    <row r="528" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A528" s="2">
         <v>46266</v>
       </c>
@@ -25979,7 +25968,7 @@
       </c>
       <c r="Q528" s="1"/>
     </row>
-    <row r="529" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A529" s="2">
         <v>46266</v>
       </c>
@@ -26026,7 +26015,7 @@
       </c>
       <c r="Q529" s="1"/>
     </row>
-    <row r="530" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A530" s="2">
         <v>46266</v>
       </c>
@@ -26073,7 +26062,7 @@
       </c>
       <c r="Q530" s="1"/>
     </row>
-    <row r="531" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A531" s="2">
         <v>46266</v>
       </c>
@@ -26120,7 +26109,7 @@
       </c>
       <c r="Q531" s="1"/>
     </row>
-    <row r="532" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A532" s="2">
         <v>46266</v>
       </c>
@@ -26167,7 +26156,7 @@
       </c>
       <c r="Q532" s="1"/>
     </row>
-    <row r="533" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A533" s="2">
         <v>46266</v>
       </c>
@@ -26214,7 +26203,7 @@
       </c>
       <c r="Q533" s="1"/>
     </row>
-    <row r="534" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A534" s="2">
         <v>46266</v>
       </c>
@@ -26261,7 +26250,7 @@
       </c>
       <c r="Q534" s="1"/>
     </row>
-    <row r="535" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A535" s="2">
         <v>46266</v>
       </c>
@@ -26308,7 +26297,7 @@
       </c>
       <c r="Q535" s="1"/>
     </row>
-    <row r="536" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A536" s="2">
         <v>46266</v>
       </c>
@@ -26355,7 +26344,7 @@
       </c>
       <c r="Q536" s="1"/>
     </row>
-    <row r="537" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A537" s="2">
         <v>46266</v>
       </c>
@@ -26402,7 +26391,7 @@
       </c>
       <c r="Q537" s="1"/>
     </row>
-    <row r="538" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A538" s="2">
         <v>46266</v>
       </c>
@@ -26449,7 +26438,7 @@
       </c>
       <c r="Q538" s="1"/>
     </row>
-    <row r="539" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A539" s="2">
         <v>46266</v>
       </c>
@@ -26496,7 +26485,7 @@
       </c>
       <c r="Q539" s="1"/>
     </row>
-    <row r="540" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A540" s="2">
         <v>46266</v>
       </c>
@@ -26543,7 +26532,7 @@
       </c>
       <c r="Q540" s="1"/>
     </row>
-    <row r="541" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A541" s="2">
         <v>46266</v>
       </c>
@@ -26590,7 +26579,7 @@
       </c>
       <c r="Q541" s="1"/>
     </row>
-    <row r="542" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A542" s="2">
         <v>46266</v>
       </c>
@@ -26637,7 +26626,7 @@
       </c>
       <c r="Q542" s="1"/>
     </row>
-    <row r="543" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A543" s="2">
         <v>46266</v>
       </c>
@@ -26684,7 +26673,7 @@
       </c>
       <c r="Q543" s="1"/>
     </row>
-    <row r="544" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="544" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A544" s="2">
         <v>46266</v>
       </c>
@@ -26731,7 +26720,7 @@
       </c>
       <c r="Q544" s="1"/>
     </row>
-    <row r="545" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A545" s="2">
         <v>46266</v>
       </c>
@@ -26778,7 +26767,7 @@
       </c>
       <c r="Q545" s="1"/>
     </row>
-    <row r="546" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A546" s="2">
         <v>46266</v>
       </c>
@@ -26825,7 +26814,7 @@
       </c>
       <c r="Q546" s="1"/>
     </row>
-    <row r="547" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A547" s="2">
         <v>46266</v>
       </c>
@@ -26872,7 +26861,7 @@
       </c>
       <c r="Q547" s="1"/>
     </row>
-    <row r="548" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A548" s="2">
         <v>46266</v>
       </c>
@@ -26919,7 +26908,7 @@
       </c>
       <c r="Q548" s="1"/>
     </row>
-    <row r="549" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A549" s="2">
         <v>46266</v>
       </c>
@@ -26966,7 +26955,7 @@
       </c>
       <c r="Q549" s="1"/>
     </row>
-    <row r="550" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A550" s="2">
         <v>46266</v>
       </c>
@@ -27013,7 +27002,7 @@
       </c>
       <c r="Q550" s="1"/>
     </row>
-    <row r="551" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A551" s="2">
         <v>46266</v>
       </c>
@@ -27060,7 +27049,7 @@
       </c>
       <c r="Q551" s="1"/>
     </row>
-    <row r="552" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A552" s="2">
         <v>46266</v>
       </c>
@@ -27107,7 +27096,7 @@
       </c>
       <c r="Q552" s="1"/>
     </row>
-    <row r="553" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A553" s="2">
         <v>46268</v>
       </c>
@@ -27154,7 +27143,7 @@
       </c>
       <c r="Q553" s="1"/>
     </row>
-    <row r="554" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A554" s="2">
         <v>46266</v>
       </c>
@@ -27201,7 +27190,7 @@
       </c>
       <c r="Q554" s="1"/>
     </row>
-    <row r="555" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="555" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A555" s="2">
         <v>46266</v>
       </c>
@@ -27248,7 +27237,7 @@
       </c>
       <c r="Q555" s="1"/>
     </row>
-    <row r="556" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A556" s="2">
         <v>46266</v>
       </c>
@@ -27295,7 +27284,7 @@
       </c>
       <c r="Q556" s="1"/>
     </row>
-    <row r="557" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A557" s="2">
         <v>46266</v>
       </c>
@@ -27342,7 +27331,7 @@
       </c>
       <c r="Q557" s="1"/>
     </row>
-    <row r="558" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="558" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A558" s="2">
         <v>46266</v>
       </c>
@@ -27389,7 +27378,7 @@
       </c>
       <c r="Q558" s="1"/>
     </row>
-    <row r="559" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A559" s="2">
         <v>46266</v>
       </c>
@@ -27436,7 +27425,7 @@
       </c>
       <c r="Q559" s="1"/>
     </row>
-    <row r="560" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A560" s="2">
         <v>46267</v>
       </c>
@@ -27483,7 +27472,7 @@
       </c>
       <c r="Q560" s="1"/>
     </row>
-    <row r="561" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A561" s="2">
         <v>46267</v>
       </c>
@@ -27530,7 +27519,7 @@
       </c>
       <c r="Q561" s="1"/>
     </row>
-    <row r="562" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A562" s="2">
         <v>46267</v>
       </c>
@@ -27577,7 +27566,7 @@
       </c>
       <c r="Q562" s="1"/>
     </row>
-    <row r="563" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A563" s="2">
         <v>46267</v>
       </c>
@@ -27624,7 +27613,7 @@
       </c>
       <c r="Q563" s="1"/>
     </row>
-    <row r="564" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A564" s="2">
         <v>46268</v>
       </c>
@@ -27671,7 +27660,7 @@
       </c>
       <c r="Q564" s="1"/>
     </row>
-    <row r="565" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A565" s="2">
         <v>46267</v>
       </c>
@@ -27718,7 +27707,7 @@
       </c>
       <c r="Q565" s="1"/>
     </row>
-    <row r="566" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="566" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A566" s="2">
         <v>46266</v>
       </c>
@@ -27765,7 +27754,7 @@
       </c>
       <c r="Q566" s="1"/>
     </row>
-    <row r="567" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A567" s="2">
         <v>46266</v>
       </c>
@@ -27812,7 +27801,7 @@
       </c>
       <c r="Q567" s="1"/>
     </row>
-    <row r="568" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="568" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A568" s="2">
         <v>46266</v>
       </c>
@@ -27859,7 +27848,7 @@
       </c>
       <c r="Q568" s="1"/>
     </row>
-    <row r="569" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="569" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A569" s="2">
         <v>46266</v>
       </c>
@@ -27906,7 +27895,7 @@
       </c>
       <c r="Q569" s="1"/>
     </row>
-    <row r="570" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="570" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A570" s="2">
         <v>46266</v>
       </c>
@@ -27953,7 +27942,7 @@
       </c>
       <c r="Q570" s="1"/>
     </row>
-    <row r="571" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A571" s="2">
         <v>46266</v>
       </c>
@@ -28000,7 +27989,7 @@
       </c>
       <c r="Q571" s="1"/>
     </row>
-    <row r="572" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A572" s="2">
         <v>46266</v>
       </c>
@@ -28047,7 +28036,7 @@
       </c>
       <c r="Q572" s="1"/>
     </row>
-    <row r="573" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="573" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A573" s="2">
         <v>46266</v>
       </c>
@@ -28094,7 +28083,7 @@
       </c>
       <c r="Q573" s="1"/>
     </row>
-    <row r="574" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A574" s="2">
         <v>46266</v>
       </c>
@@ -28141,7 +28130,7 @@
       </c>
       <c r="Q574" s="1"/>
     </row>
-    <row r="575" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A575" s="2">
         <v>46266</v>
       </c>
@@ -28188,7 +28177,7 @@
       </c>
       <c r="Q575" s="1"/>
     </row>
-    <row r="576" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A576" s="2">
         <v>46267</v>
       </c>
@@ -28235,7 +28224,7 @@
       </c>
       <c r="Q576" s="1"/>
     </row>
-    <row r="577" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A577" s="2">
         <v>46267</v>
       </c>
@@ -28282,7 +28271,7 @@
       </c>
       <c r="Q577" s="1"/>
     </row>
-    <row r="578" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="578" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A578" s="2">
         <v>46267</v>
       </c>
@@ -28329,7 +28318,7 @@
       </c>
       <c r="Q578" s="1"/>
     </row>
-    <row r="579" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="579" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A579" s="2">
         <v>46266</v>
       </c>
@@ -28376,7 +28365,7 @@
       </c>
       <c r="Q579" s="1"/>
     </row>
-    <row r="580" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="580" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A580" s="2">
         <v>46266</v>
       </c>
@@ -28423,7 +28412,7 @@
       </c>
       <c r="Q580" s="1"/>
     </row>
-    <row r="581" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A581" s="2">
         <v>46266</v>
       </c>
@@ -28470,7 +28459,7 @@
       </c>
       <c r="Q581" s="1"/>
     </row>
-    <row r="582" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A582" s="2">
         <v>46266</v>
       </c>
@@ -28517,7 +28506,7 @@
       </c>
       <c r="Q582" s="1"/>
     </row>
-    <row r="583" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="583" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A583" s="2">
         <v>46266</v>
       </c>
@@ -28611,7 +28600,7 @@
       </c>
       <c r="Q584" s="1"/>
     </row>
-    <row r="585" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A585" s="2">
         <v>46266</v>
       </c>
@@ -28658,7 +28647,7 @@
       </c>
       <c r="Q585" s="1"/>
     </row>
-    <row r="586" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A586" s="2">
         <v>46265</v>
       </c>
@@ -28705,7 +28694,7 @@
       </c>
       <c r="Q586" s="1"/>
     </row>
-    <row r="587" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A587" s="2">
         <v>46265</v>
       </c>
@@ -28752,7 +28741,7 @@
       </c>
       <c r="Q587" s="1"/>
     </row>
-    <row r="588" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A588" s="2">
         <v>46265</v>
       </c>
@@ -28799,7 +28788,7 @@
       </c>
       <c r="Q588" s="1"/>
     </row>
-    <row r="589" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A589" s="2">
         <v>46265</v>
       </c>
@@ -28846,7 +28835,7 @@
       </c>
       <c r="Q589" s="1"/>
     </row>
-    <row r="590" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A590" s="2">
         <v>46265</v>
       </c>
@@ -28893,7 +28882,7 @@
       </c>
       <c r="Q590" s="1"/>
     </row>
-    <row r="591" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="591" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A591" s="2">
         <v>46265</v>
       </c>
@@ -28940,7 +28929,7 @@
       </c>
       <c r="Q591" s="1"/>
     </row>
-    <row r="592" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="592" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A592" s="2">
         <v>46265</v>
       </c>
@@ -28987,7 +28976,7 @@
       </c>
       <c r="Q592" s="1"/>
     </row>
-    <row r="593" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="593" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A593" s="2">
         <v>46265</v>
       </c>
@@ -29034,7 +29023,7 @@
       </c>
       <c r="Q593" s="1"/>
     </row>
-    <row r="594" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="594" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A594" s="2">
         <v>46265</v>
       </c>
@@ -29081,7 +29070,7 @@
       </c>
       <c r="Q594" s="1"/>
     </row>
-    <row r="595" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="595" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A595" s="2">
         <v>46265</v>
       </c>
@@ -29128,7 +29117,7 @@
       </c>
       <c r="Q595" s="1"/>
     </row>
-    <row r="596" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="596" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A596" s="2">
         <v>46265</v>
       </c>
@@ -29175,7 +29164,7 @@
       </c>
       <c r="Q596" s="1"/>
     </row>
-    <row r="597" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="597" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A597" s="2">
         <v>46265</v>
       </c>
@@ -29222,7 +29211,7 @@
       </c>
       <c r="Q597" s="1"/>
     </row>
-    <row r="598" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A598" s="2">
         <v>46265</v>
       </c>
@@ -29269,7 +29258,7 @@
       </c>
       <c r="Q598" s="1"/>
     </row>
-    <row r="599" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A599" s="2">
         <v>46235</v>
       </c>
@@ -29316,7 +29305,7 @@
       </c>
       <c r="Q599" s="1"/>
     </row>
-    <row r="600" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A600" s="2">
         <v>46235</v>
       </c>
@@ -29363,7 +29352,7 @@
       </c>
       <c r="Q600" s="1"/>
     </row>
-    <row r="601" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="601" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A601" s="2">
         <v>46265</v>
       </c>
@@ -29410,7 +29399,7 @@
       </c>
       <c r="Q601" s="1"/>
     </row>
-    <row r="602" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A602" s="2">
         <v>46265</v>
       </c>
@@ -29457,7 +29446,7 @@
       </c>
       <c r="Q602" s="1"/>
     </row>
-    <row r="603" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A603" s="2">
         <v>46265</v>
       </c>
@@ -29504,7 +29493,7 @@
       </c>
       <c r="Q603" s="1"/>
     </row>
-    <row r="604" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A604" s="2">
         <v>46265</v>
       </c>
@@ -29551,7 +29540,7 @@
       </c>
       <c r="Q604" s="1"/>
     </row>
-    <row r="605" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="605" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A605" s="2">
         <v>46265</v>
       </c>
@@ -29598,7 +29587,7 @@
       </c>
       <c r="Q605" s="1"/>
     </row>
-    <row r="606" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="606" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A606" s="2">
         <v>46265</v>
       </c>
@@ -29645,7 +29634,7 @@
       </c>
       <c r="Q606" s="1"/>
     </row>
-    <row r="607" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A607" s="2">
         <v>46265</v>
       </c>
@@ -29692,7 +29681,7 @@
       </c>
       <c r="Q607" s="1"/>
     </row>
-    <row r="608" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A608" s="2">
         <v>46265</v>
       </c>
@@ -29739,7 +29728,7 @@
       </c>
       <c r="Q608" s="1"/>
     </row>
-    <row r="609" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A609" s="2">
         <v>46265</v>
       </c>
@@ -29786,7 +29775,7 @@
       </c>
       <c r="Q609" s="1"/>
     </row>
-    <row r="610" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A610" s="2">
         <v>46265</v>
       </c>
@@ -29833,7 +29822,7 @@
       </c>
       <c r="Q610" s="1"/>
     </row>
-    <row r="611" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A611" s="2">
         <v>46265</v>
       </c>
@@ -29880,7 +29869,7 @@
       </c>
       <c r="Q611" s="1"/>
     </row>
-    <row r="612" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="612" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A612" s="2">
         <v>46265</v>
       </c>
@@ -29927,7 +29916,7 @@
       </c>
       <c r="Q612" s="1"/>
     </row>
-    <row r="613" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="613" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A613" s="2">
         <v>46265</v>
       </c>
@@ -29974,7 +29963,7 @@
       </c>
       <c r="Q613" s="1"/>
     </row>
-    <row r="614" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="614" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A614" s="2">
         <v>46265</v>
       </c>
@@ -30021,7 +30010,7 @@
       </c>
       <c r="Q614" s="1"/>
     </row>
-    <row r="615" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="615" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A615" s="2">
         <v>46265</v>
       </c>
@@ -30068,7 +30057,7 @@
       </c>
       <c r="Q615" s="1"/>
     </row>
-    <row r="616" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A616" s="2">
         <v>46265</v>
       </c>
@@ -30115,7 +30104,7 @@
       </c>
       <c r="Q616" s="1"/>
     </row>
-    <row r="617" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="617" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A617" s="2">
         <v>46265</v>
       </c>
@@ -30162,7 +30151,7 @@
       </c>
       <c r="Q617" s="1"/>
     </row>
-    <row r="618" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A618" s="2">
         <v>46265</v>
       </c>
@@ -30209,7 +30198,7 @@
       </c>
       <c r="Q618" s="1"/>
     </row>
-    <row r="619" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="619" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A619" s="2">
         <v>46265</v>
       </c>
@@ -30256,7 +30245,7 @@
       </c>
       <c r="Q619" s="1"/>
     </row>
-    <row r="620" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="620" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A620" s="2">
         <v>46265</v>
       </c>
@@ -30303,7 +30292,7 @@
       </c>
       <c r="Q620" s="1"/>
     </row>
-    <row r="621" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="621" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A621" s="2">
         <v>46265</v>
       </c>
@@ -30350,7 +30339,7 @@
       </c>
       <c r="Q621" s="1"/>
     </row>
-    <row r="622" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="622" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A622" s="2">
         <v>46265</v>
       </c>
@@ -30397,7 +30386,7 @@
       </c>
       <c r="Q622" s="1"/>
     </row>
-    <row r="623" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="623" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A623" s="2">
         <v>46235</v>
       </c>
@@ -30444,7 +30433,7 @@
       </c>
       <c r="Q623" s="1"/>
     </row>
-    <row r="624" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="624" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A624" s="2">
         <v>46265</v>
       </c>
@@ -30491,7 +30480,7 @@
       </c>
       <c r="Q624" s="1"/>
     </row>
-    <row r="625" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="625" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A625" s="2">
         <v>46265</v>
       </c>
@@ -30538,7 +30527,7 @@
       </c>
       <c r="Q625" s="1"/>
     </row>
-    <row r="626" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="626" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A626" s="2">
         <v>46265</v>
       </c>
@@ -30585,7 +30574,7 @@
       </c>
       <c r="Q626" s="1"/>
     </row>
-    <row r="627" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A627" s="2">
         <v>46265</v>
       </c>
@@ -30632,7 +30621,7 @@
       </c>
       <c r="Q627" s="1"/>
     </row>
-    <row r="628" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A628" s="2">
         <v>46265</v>
       </c>
@@ -30679,7 +30668,7 @@
       </c>
       <c r="Q628" s="1"/>
     </row>
-    <row r="629" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A629" s="2">
         <v>46265</v>
       </c>
@@ -30726,7 +30715,7 @@
       </c>
       <c r="Q629" s="1"/>
     </row>
-    <row r="630" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A630" s="2">
         <v>46265</v>
       </c>
@@ -30773,7 +30762,7 @@
       </c>
       <c r="Q630" s="1"/>
     </row>
-    <row r="631" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A631" s="2">
         <v>46265</v>
       </c>
@@ -30820,7 +30809,7 @@
       </c>
       <c r="Q631" s="1"/>
     </row>
-    <row r="632" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A632" s="2">
         <v>46265</v>
       </c>
@@ -30867,7 +30856,7 @@
       </c>
       <c r="Q632" s="1"/>
     </row>
-    <row r="633" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A633" s="2">
         <v>46265</v>
       </c>
@@ -30914,7 +30903,7 @@
       </c>
       <c r="Q633" s="1"/>
     </row>
-    <row r="634" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="634" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A634" s="2">
         <v>46265</v>
       </c>
@@ -30961,7 +30950,7 @@
       </c>
       <c r="Q634" s="1"/>
     </row>
-    <row r="635" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="635" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A635" s="2">
         <v>46265</v>
       </c>
@@ -31008,7 +30997,7 @@
       </c>
       <c r="Q635" s="1"/>
     </row>
-    <row r="636" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="636" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A636" s="2">
         <v>46265</v>
       </c>
@@ -31055,7 +31044,7 @@
       </c>
       <c r="Q636" s="1"/>
     </row>
-    <row r="637" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="637" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A637" s="2">
         <v>46265</v>
       </c>
@@ -31102,7 +31091,7 @@
       </c>
       <c r="Q637" s="1"/>
     </row>
-    <row r="638" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="638" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A638" s="2">
         <v>46265</v>
       </c>
@@ -31149,7 +31138,7 @@
       </c>
       <c r="Q638" s="1"/>
     </row>
-    <row r="639" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="639" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A639" s="2">
         <v>46265</v>
       </c>
@@ -31196,7 +31185,7 @@
       </c>
       <c r="Q639" s="1"/>
     </row>
-    <row r="640" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A640" s="2">
         <v>46265</v>
       </c>
@@ -31243,7 +31232,7 @@
       </c>
       <c r="Q640" s="1"/>
     </row>
-    <row r="641" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="641" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A641" s="2">
         <v>46265</v>
       </c>
@@ -31290,7 +31279,7 @@
       </c>
       <c r="Q641" s="1"/>
     </row>
-    <row r="642" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A642" s="2">
         <v>46265</v>
       </c>
@@ -31337,7 +31326,7 @@
       </c>
       <c r="Q642" s="1"/>
     </row>
-    <row r="643" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="643" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A643" s="2">
         <v>46265</v>
       </c>
@@ -31384,7 +31373,7 @@
       </c>
       <c r="Q643" s="1"/>
     </row>
-    <row r="644" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="644" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A644" s="2">
         <v>46265</v>
       </c>
@@ -31431,7 +31420,7 @@
       </c>
       <c r="Q644" s="1"/>
     </row>
-    <row r="645" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="645" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A645" s="2">
         <v>46265</v>
       </c>
@@ -31478,7 +31467,7 @@
       </c>
       <c r="Q645" s="1"/>
     </row>
-    <row r="646" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="646" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A646" s="2">
         <v>46265</v>
       </c>
@@ -31525,7 +31514,7 @@
       </c>
       <c r="Q646" s="1"/>
     </row>
-    <row r="647" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="647" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A647" s="2">
         <v>46265</v>
       </c>
@@ -31572,7 +31561,7 @@
       </c>
       <c r="Q647" s="1"/>
     </row>
-    <row r="648" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="648" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A648" s="2">
         <v>46265</v>
       </c>
@@ -31619,7 +31608,7 @@
       </c>
       <c r="Q648" s="1"/>
     </row>
-    <row r="649" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A649" s="2">
         <v>46265</v>
       </c>
@@ -31666,7 +31655,7 @@
       </c>
       <c r="Q649" s="1"/>
     </row>
-    <row r="650" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="650" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A650" s="2">
         <v>46265</v>
       </c>
@@ -31713,7 +31702,7 @@
       </c>
       <c r="Q650" s="1"/>
     </row>
-    <row r="651" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A651" s="2">
         <v>46265</v>
       </c>
@@ -31760,7 +31749,7 @@
       </c>
       <c r="Q651" s="1"/>
     </row>
-    <row r="652" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A652" s="2">
         <v>46265</v>
       </c>
@@ -31807,7 +31796,7 @@
       </c>
       <c r="Q652" s="1"/>
     </row>
-    <row r="653" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A653" s="2">
         <v>46265</v>
       </c>
@@ -31854,7 +31843,7 @@
       </c>
       <c r="Q653" s="1"/>
     </row>
-    <row r="654" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A654" s="2">
         <v>46265</v>
       </c>
@@ -31901,7 +31890,7 @@
       </c>
       <c r="Q654" s="1"/>
     </row>
-    <row r="655" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A655" s="2">
         <v>46265</v>
       </c>
@@ -31948,7 +31937,7 @@
       </c>
       <c r="Q655" s="1"/>
     </row>
-    <row r="656" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="656" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A656" s="2">
         <v>46265</v>
       </c>
@@ -31995,7 +31984,7 @@
       </c>
       <c r="Q656" s="1"/>
     </row>
-    <row r="657" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="657" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A657" s="2">
         <v>46265</v>
       </c>
@@ -32042,7 +32031,7 @@
       </c>
       <c r="Q657" s="1"/>
     </row>
-    <row r="658" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="658" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A658" s="2">
         <v>46265</v>
       </c>
@@ -32089,7 +32078,7 @@
       </c>
       <c r="Q658" s="1"/>
     </row>
-    <row r="659" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="659" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A659" s="2">
         <v>46265</v>
       </c>
@@ -32136,7 +32125,7 @@
       </c>
       <c r="Q659" s="1"/>
     </row>
-    <row r="660" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="660" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A660" s="2">
         <v>46265</v>
       </c>
@@ -32183,7 +32172,7 @@
       </c>
       <c r="Q660" s="1"/>
     </row>
-    <row r="661" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="661" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A661" s="2">
         <v>46265</v>
       </c>
@@ -32230,7 +32219,7 @@
       </c>
       <c r="Q661" s="1"/>
     </row>
-    <row r="662" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A662" s="2">
         <v>46265</v>
       </c>
@@ -32277,7 +32266,7 @@
       </c>
       <c r="Q662" s="1"/>
     </row>
-    <row r="663" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="663" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A663" s="2">
         <v>46265</v>
       </c>
@@ -32324,7 +32313,7 @@
       </c>
       <c r="Q663" s="1"/>
     </row>
-    <row r="664" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="664" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A664" s="2">
         <v>46265</v>
       </c>
@@ -32371,7 +32360,7 @@
       </c>
       <c r="Q664" s="1"/>
     </row>
-    <row r="665" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="665" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A665" s="2">
         <v>46265</v>
       </c>
@@ -32418,7 +32407,7 @@
       </c>
       <c r="Q665" s="1"/>
     </row>
-    <row r="666" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="666" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A666" s="2">
         <v>46265</v>
       </c>
@@ -32465,7 +32454,7 @@
       </c>
       <c r="Q666" s="1"/>
     </row>
-    <row r="667" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="667" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A667" s="2">
         <v>46265</v>
       </c>
@@ -32512,7 +32501,7 @@
       </c>
       <c r="Q667" s="1"/>
     </row>
-    <row r="668" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="668" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A668" s="2">
         <v>46265</v>
       </c>
@@ -32559,7 +32548,7 @@
       </c>
       <c r="Q668" s="1"/>
     </row>
-    <row r="669" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="669" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A669" s="2">
         <v>46265</v>
       </c>
@@ -32606,7 +32595,7 @@
       </c>
       <c r="Q669" s="1"/>
     </row>
-    <row r="670" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="670" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A670" s="2">
         <v>46265</v>
       </c>
@@ -32653,7 +32642,7 @@
       </c>
       <c r="Q670" s="1"/>
     </row>
-    <row r="671" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="671" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A671" s="2">
         <v>46265</v>
       </c>
@@ -32700,7 +32689,7 @@
       </c>
       <c r="Q671" s="1"/>
     </row>
-    <row r="672" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="672" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A672" s="2">
         <v>46268</v>
       </c>
@@ -32747,7 +32736,7 @@
       </c>
       <c r="Q672" s="1"/>
     </row>
-    <row r="673" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="673" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A673" s="2">
         <v>46265</v>
       </c>
@@ -32794,7 +32783,7 @@
       </c>
       <c r="Q673" s="1"/>
     </row>
-    <row r="674" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="674" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A674" s="2">
         <v>46265</v>
       </c>
@@ -32841,7 +32830,7 @@
       </c>
       <c r="Q674" s="1"/>
     </row>
-    <row r="675" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="675" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A675" s="2">
         <v>46265</v>
       </c>
@@ -32888,7 +32877,7 @@
       </c>
       <c r="Q675" s="1"/>
     </row>
-    <row r="676" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="676" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A676" s="2">
         <v>46265</v>
       </c>
@@ -32935,7 +32924,7 @@
       </c>
       <c r="Q676" s="1"/>
     </row>
-    <row r="677" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="677" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A677" s="2">
         <v>46265</v>
       </c>
@@ -32982,7 +32971,7 @@
       </c>
       <c r="Q677" s="1"/>
     </row>
-    <row r="678" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="678" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A678" s="2">
         <v>46265</v>
       </c>
@@ -33029,7 +33018,7 @@
       </c>
       <c r="Q678" s="1"/>
     </row>
-    <row r="679" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="679" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A679" s="2">
         <v>46265</v>
       </c>
@@ -33076,7 +33065,7 @@
       </c>
       <c r="Q679" s="1"/>
     </row>
-    <row r="680" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="680" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A680" s="2">
         <v>46265</v>
       </c>
@@ -33123,7 +33112,7 @@
       </c>
       <c r="Q680" s="1"/>
     </row>
-    <row r="681" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="681" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A681" s="2">
         <v>46265</v>
       </c>
@@ -33170,7 +33159,7 @@
       </c>
       <c r="Q681" s="1"/>
     </row>
-    <row r="682" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="682" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A682" s="2">
         <v>46265</v>
       </c>
@@ -33217,7 +33206,7 @@
       </c>
       <c r="Q682" s="1"/>
     </row>
-    <row r="683" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="683" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A683" s="2">
         <v>46265</v>
       </c>
@@ -33264,7 +33253,7 @@
       </c>
       <c r="Q683" s="1"/>
     </row>
-    <row r="684" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="684" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A684" s="2">
         <v>46265</v>
       </c>
@@ -33311,7 +33300,7 @@
       </c>
       <c r="Q684" s="1"/>
     </row>
-    <row r="685" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="685" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A685" s="2">
         <v>46265</v>
       </c>
@@ -33358,7 +33347,7 @@
       </c>
       <c r="Q685" s="1"/>
     </row>
-    <row r="686" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="686" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A686" s="2">
         <v>46265</v>
       </c>
@@ -33405,7 +33394,7 @@
       </c>
       <c r="Q686" s="1"/>
     </row>
-    <row r="687" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="687" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A687" s="2">
         <v>46265</v>
       </c>
@@ -33452,7 +33441,7 @@
       </c>
       <c r="Q687" s="1"/>
     </row>
-    <row r="688" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="688" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A688" s="2">
         <v>46265</v>
       </c>
@@ -33499,7 +33488,7 @@
       </c>
       <c r="Q688" s="1"/>
     </row>
-    <row r="689" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="689" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A689" s="2">
         <v>46265</v>
       </c>
@@ -33546,7 +33535,7 @@
       </c>
       <c r="Q689" s="1"/>
     </row>
-    <row r="690" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="690" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A690" s="2">
         <v>46265</v>
       </c>
@@ -33593,7 +33582,7 @@
       </c>
       <c r="Q690" s="1"/>
     </row>
-    <row r="691" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="691" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A691" s="2">
         <v>46265</v>
       </c>
@@ -33640,7 +33629,7 @@
       </c>
       <c r="Q691" s="1"/>
     </row>
-    <row r="692" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="692" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A692" s="2">
         <v>46265</v>
       </c>
@@ -33687,7 +33676,7 @@
       </c>
       <c r="Q692" s="1"/>
     </row>
-    <row r="693" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="693" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A693" s="2">
         <v>46265</v>
       </c>
@@ -33734,7 +33723,7 @@
       </c>
       <c r="Q693" s="1"/>
     </row>
-    <row r="694" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="694" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A694" s="2">
         <v>46265</v>
       </c>
@@ -33781,7 +33770,7 @@
       </c>
       <c r="Q694" s="1"/>
     </row>
-    <row r="695" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="695" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A695" s="2">
         <v>46265</v>
       </c>
@@ -33828,7 +33817,7 @@
       </c>
       <c r="Q695" s="1"/>
     </row>
-    <row r="696" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="696" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A696" s="2">
         <v>46265</v>
       </c>
@@ -33875,7 +33864,7 @@
       </c>
       <c r="Q696" s="1"/>
     </row>
-    <row r="697" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="697" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A697" s="2">
         <v>46265</v>
       </c>
@@ -33969,7 +33958,7 @@
       </c>
       <c r="Q698" s="1"/>
     </row>
-    <row r="699" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="699" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A699" s="2">
         <v>46265</v>
       </c>
@@ -34016,7 +34005,7 @@
       </c>
       <c r="Q699" s="1"/>
     </row>
-    <row r="700" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="700" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A700" s="2">
         <v>46265</v>
       </c>

--- a/Donnees_Mensuelle.xlsx
+++ b/Donnees_Mensuelle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3FC7253-F186-408C-84C8-232E2101A4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D88D5A-8C4C-4971-97E3-A118B7BFFD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
